--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66925795-9227-CF46-89C9-CE763E0B4A2F}"/>
+  <xr:revisionPtr revIDLastSave="532" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F401DFC-54D7-6345-9741-7BC40F98E887}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
   <si>
     <t>Project start:</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>Define assumptions for baseline interventions in the abscence of data</t>
+  </si>
+  <si>
+    <t>Need a check for if I'm missing things</t>
   </si>
 </sst>
 </file>
@@ -843,7 +846,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1142,6 +1145,29 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1163,28 +1189,8 @@
     <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2048,7 +2054,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$Q$2" horiz="1" max="100" page="0" val="6"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$Q$2" horiz="1" max="100" page="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2381,8 +2387,8 @@
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" style="106" customWidth="1"/>
     <col min="6" max="6" width="6.6640625" style="107" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" customWidth="1"/>
-    <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="0.6640625" customWidth="1"/>
     <col min="9" max="92" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2396,29 +2402,28 @@
       <c r="E1" s="82"/>
       <c r="F1" s="83"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="114">
-        <f ca="1">TODAY()</f>
+      <c r="Q1" s="123">
         <v>46064</v>
       </c>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="115"/>
-      <c r="W1" s="115"/>
-      <c r="X1" s="115"/>
-      <c r="Y1" s="115"/>
-      <c r="Z1" s="115"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="124"/>
+      <c r="U1" s="124"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="124"/>
     </row>
     <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="71"/>
@@ -2428,28 +2433,28 @@
       <c r="D2" s="17"/>
       <c r="E2" s="84"/>
       <c r="F2" s="85"/>
-      <c r="I2" s="116" t="s">
+      <c r="I2" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="126"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="112">
-        <v>6</v>
-      </c>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
+      <c r="Q2" s="121">
+        <v>1</v>
+      </c>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="122"/>
       <c r="AP2" t="s">
         <v>63</v>
       </c>
@@ -2463,827 +2468,827 @@
     </row>
     <row r="4" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="81"/>
-      <c r="B4" s="127" t="s">
+      <c r="B4" s="110" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="88"/>
       <c r="F4" s="87"/>
-      <c r="I4" s="118">
-        <f ca="1">I5</f>
+      <c r="I4" s="127">
+        <f>I5</f>
+        <v>46062</v>
+      </c>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="119">
+        <f>P5</f>
+        <v>46069</v>
+      </c>
+      <c r="Q4" s="119"/>
+      <c r="R4" s="119"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="119"/>
+      <c r="W4" s="119">
+        <f>W5</f>
+        <v>46076</v>
+      </c>
+      <c r="X4" s="119"/>
+      <c r="Y4" s="119"/>
+      <c r="Z4" s="119"/>
+      <c r="AA4" s="119"/>
+      <c r="AB4" s="119"/>
+      <c r="AC4" s="119"/>
+      <c r="AD4" s="119">
+        <f>AD5</f>
+        <v>46083</v>
+      </c>
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119">
+        <f>AK5</f>
+        <v>46090</v>
+      </c>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
+      <c r="AQ4" s="119"/>
+      <c r="AR4" s="119">
+        <f>AR5</f>
         <v>46097</v>
       </c>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110">
-        <f ca="1">P5</f>
+      <c r="AS4" s="119"/>
+      <c r="AT4" s="119"/>
+      <c r="AU4" s="119"/>
+      <c r="AV4" s="119"/>
+      <c r="AW4" s="119"/>
+      <c r="AX4" s="119"/>
+      <c r="AY4" s="119">
+        <f>AY5</f>
         <v>46104</v>
       </c>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110"/>
-      <c r="V4" s="110"/>
-      <c r="W4" s="110">
-        <f ca="1">W5</f>
+      <c r="AZ4" s="119"/>
+      <c r="BA4" s="119"/>
+      <c r="BB4" s="119"/>
+      <c r="BC4" s="119"/>
+      <c r="BD4" s="119"/>
+      <c r="BE4" s="119"/>
+      <c r="BF4" s="119">
+        <f>BF5</f>
         <v>46111</v>
       </c>
-      <c r="X4" s="110"/>
-      <c r="Y4" s="110"/>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="110">
-        <f ca="1">AD5</f>
+      <c r="BG4" s="119"/>
+      <c r="BH4" s="119"/>
+      <c r="BI4" s="119"/>
+      <c r="BJ4" s="119"/>
+      <c r="BK4" s="119"/>
+      <c r="BL4" s="120"/>
+      <c r="BM4" s="119">
+        <f>BM5</f>
         <v>46118</v>
       </c>
-      <c r="AE4" s="110"/>
-      <c r="AF4" s="110"/>
-      <c r="AG4" s="110"/>
-      <c r="AH4" s="110"/>
-      <c r="AI4" s="110"/>
-      <c r="AJ4" s="110"/>
-      <c r="AK4" s="110">
-        <f ca="1">AK5</f>
+      <c r="BN4" s="119"/>
+      <c r="BO4" s="119"/>
+      <c r="BP4" s="119"/>
+      <c r="BQ4" s="119"/>
+      <c r="BR4" s="119"/>
+      <c r="BS4" s="120"/>
+      <c r="BT4" s="119">
+        <f>BT5</f>
         <v>46125</v>
       </c>
-      <c r="AL4" s="110"/>
-      <c r="AM4" s="110"/>
-      <c r="AN4" s="110"/>
-      <c r="AO4" s="110"/>
-      <c r="AP4" s="110"/>
-      <c r="AQ4" s="110"/>
-      <c r="AR4" s="110">
-        <f ca="1">AR5</f>
+      <c r="BU4" s="119"/>
+      <c r="BV4" s="119"/>
+      <c r="BW4" s="119"/>
+      <c r="BX4" s="119"/>
+      <c r="BY4" s="119"/>
+      <c r="BZ4" s="120"/>
+      <c r="CA4" s="119">
+        <f>CA5</f>
         <v>46132</v>
       </c>
-      <c r="AS4" s="110"/>
-      <c r="AT4" s="110"/>
-      <c r="AU4" s="110"/>
-      <c r="AV4" s="110"/>
-      <c r="AW4" s="110"/>
-      <c r="AX4" s="110"/>
-      <c r="AY4" s="110">
-        <f ca="1">AY5</f>
+      <c r="CB4" s="119"/>
+      <c r="CC4" s="119"/>
+      <c r="CD4" s="119"/>
+      <c r="CE4" s="119"/>
+      <c r="CF4" s="119"/>
+      <c r="CG4" s="120"/>
+      <c r="CH4" s="119">
+        <f>CH5</f>
         <v>46139</v>
       </c>
-      <c r="AZ4" s="110"/>
-      <c r="BA4" s="110"/>
-      <c r="BB4" s="110"/>
-      <c r="BC4" s="110"/>
-      <c r="BD4" s="110"/>
-      <c r="BE4" s="110"/>
-      <c r="BF4" s="110">
-        <f ca="1">BF5</f>
-        <v>46146</v>
-      </c>
-      <c r="BG4" s="110"/>
-      <c r="BH4" s="110"/>
-      <c r="BI4" s="110"/>
-      <c r="BJ4" s="110"/>
-      <c r="BK4" s="110"/>
-      <c r="BL4" s="111"/>
-      <c r="BM4" s="110">
-        <f ca="1">BM5</f>
-        <v>46153</v>
-      </c>
-      <c r="BN4" s="110"/>
-      <c r="BO4" s="110"/>
-      <c r="BP4" s="110"/>
-      <c r="BQ4" s="110"/>
-      <c r="BR4" s="110"/>
-      <c r="BS4" s="111"/>
-      <c r="BT4" s="110">
-        <f ca="1">BT5</f>
-        <v>46160</v>
-      </c>
-      <c r="BU4" s="110"/>
-      <c r="BV4" s="110"/>
-      <c r="BW4" s="110"/>
-      <c r="BX4" s="110"/>
-      <c r="BY4" s="110"/>
-      <c r="BZ4" s="111"/>
-      <c r="CA4" s="110">
-        <f ca="1">CA5</f>
-        <v>46167</v>
-      </c>
-      <c r="CB4" s="110"/>
-      <c r="CC4" s="110"/>
-      <c r="CD4" s="110"/>
-      <c r="CE4" s="110"/>
-      <c r="CF4" s="110"/>
-      <c r="CG4" s="111"/>
-      <c r="CH4" s="110">
-        <f ca="1">CH5</f>
-        <v>46174</v>
-      </c>
-      <c r="CI4" s="110"/>
-      <c r="CJ4" s="110"/>
-      <c r="CK4" s="110"/>
-      <c r="CL4" s="110"/>
-      <c r="CM4" s="110"/>
-      <c r="CN4" s="111"/>
+      <c r="CI4" s="119"/>
+      <c r="CJ4" s="119"/>
+      <c r="CK4" s="119"/>
+      <c r="CL4" s="119"/>
+      <c r="CM4" s="119"/>
+      <c r="CN4" s="120"/>
     </row>
     <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="119"/>
-      <c r="B5" s="120" t="s">
+      <c r="A5" s="113"/>
+      <c r="B5" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="122" t="s">
+      <c r="C5" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="124" t="s">
+      <c r="D5" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="125" t="s">
+      <c r="E5" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="125" t="s">
+      <c r="F5" s="111" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="22">
-        <f ca="1">Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
+        <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
+        <v>46062</v>
+      </c>
+      <c r="J5" s="22">
+        <f>I5+1</f>
+        <v>46063</v>
+      </c>
+      <c r="K5" s="22">
+        <f t="shared" ref="K5:AX5" si="0">J5+1</f>
+        <v>46064</v>
+      </c>
+      <c r="L5" s="22">
+        <f t="shared" si="0"/>
+        <v>46065</v>
+      </c>
+      <c r="M5" s="22">
+        <f t="shared" si="0"/>
+        <v>46066</v>
+      </c>
+      <c r="N5" s="22">
+        <f t="shared" si="0"/>
+        <v>46067</v>
+      </c>
+      <c r="O5" s="23">
+        <f t="shared" si="0"/>
+        <v>46068</v>
+      </c>
+      <c r="P5" s="24">
+        <f>O5+1</f>
+        <v>46069</v>
+      </c>
+      <c r="Q5" s="22">
+        <f>P5+1</f>
+        <v>46070</v>
+      </c>
+      <c r="R5" s="22">
+        <f t="shared" si="0"/>
+        <v>46071</v>
+      </c>
+      <c r="S5" s="22">
+        <f t="shared" si="0"/>
+        <v>46072</v>
+      </c>
+      <c r="T5" s="22">
+        <f t="shared" si="0"/>
+        <v>46073</v>
+      </c>
+      <c r="U5" s="22">
+        <f t="shared" si="0"/>
+        <v>46074</v>
+      </c>
+      <c r="V5" s="23">
+        <f t="shared" si="0"/>
+        <v>46075</v>
+      </c>
+      <c r="W5" s="24">
+        <f>V5+1</f>
+        <v>46076</v>
+      </c>
+      <c r="X5" s="22">
+        <f>W5+1</f>
+        <v>46077</v>
+      </c>
+      <c r="Y5" s="22">
+        <f t="shared" si="0"/>
+        <v>46078</v>
+      </c>
+      <c r="Z5" s="22">
+        <f t="shared" si="0"/>
+        <v>46079</v>
+      </c>
+      <c r="AA5" s="22">
+        <f t="shared" si="0"/>
+        <v>46080</v>
+      </c>
+      <c r="AB5" s="22">
+        <f t="shared" si="0"/>
+        <v>46081</v>
+      </c>
+      <c r="AC5" s="23">
+        <f t="shared" si="0"/>
+        <v>46082</v>
+      </c>
+      <c r="AD5" s="24">
+        <f>AC5+1</f>
+        <v>46083</v>
+      </c>
+      <c r="AE5" s="22">
+        <f>AD5+1</f>
+        <v>46084</v>
+      </c>
+      <c r="AF5" s="22">
+        <f t="shared" si="0"/>
+        <v>46085</v>
+      </c>
+      <c r="AG5" s="22">
+        <f t="shared" si="0"/>
+        <v>46086</v>
+      </c>
+      <c r="AH5" s="22">
+        <f t="shared" si="0"/>
+        <v>46087</v>
+      </c>
+      <c r="AI5" s="22">
+        <f t="shared" si="0"/>
+        <v>46088</v>
+      </c>
+      <c r="AJ5" s="23">
+        <f t="shared" si="0"/>
+        <v>46089</v>
+      </c>
+      <c r="AK5" s="24">
+        <f>AJ5+1</f>
+        <v>46090</v>
+      </c>
+      <c r="AL5" s="22">
+        <f>AK5+1</f>
+        <v>46091</v>
+      </c>
+      <c r="AM5" s="22">
+        <f t="shared" si="0"/>
+        <v>46092</v>
+      </c>
+      <c r="AN5" s="22">
+        <f t="shared" si="0"/>
+        <v>46093</v>
+      </c>
+      <c r="AO5" s="22">
+        <f t="shared" si="0"/>
+        <v>46094</v>
+      </c>
+      <c r="AP5" s="22">
+        <f t="shared" si="0"/>
+        <v>46095</v>
+      </c>
+      <c r="AQ5" s="23">
+        <f t="shared" si="0"/>
+        <v>46096</v>
+      </c>
+      <c r="AR5" s="24">
+        <f>AQ5+1</f>
         <v>46097</v>
       </c>
-      <c r="J5" s="22">
-        <f ca="1">I5+1</f>
+      <c r="AS5" s="22">
+        <f>AR5+1</f>
         <v>46098</v>
       </c>
-      <c r="K5" s="22">
-        <f t="shared" ref="K5:AX5" ca="1" si="0">J5+1</f>
+      <c r="AT5" s="22">
+        <f t="shared" si="0"/>
         <v>46099</v>
       </c>
-      <c r="L5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AU5" s="22">
+        <f t="shared" si="0"/>
         <v>46100</v>
       </c>
-      <c r="M5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AV5" s="22">
+        <f t="shared" si="0"/>
         <v>46101</v>
       </c>
-      <c r="N5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AW5" s="22">
+        <f t="shared" si="0"/>
         <v>46102</v>
       </c>
-      <c r="O5" s="23">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AX5" s="23">
+        <f t="shared" si="0"/>
         <v>46103</v>
       </c>
-      <c r="P5" s="24">
-        <f ca="1">O5+1</f>
+      <c r="AY5" s="24">
+        <f>AX5+1</f>
         <v>46104</v>
       </c>
-      <c r="Q5" s="22">
-        <f ca="1">P5+1</f>
+      <c r="AZ5" s="22">
+        <f>AY5+1</f>
         <v>46105</v>
       </c>
-      <c r="R5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BA5" s="22">
+        <f t="shared" ref="BA5:BE5" si="1">AZ5+1</f>
         <v>46106</v>
       </c>
-      <c r="S5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BB5" s="22">
+        <f t="shared" si="1"/>
         <v>46107</v>
       </c>
-      <c r="T5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BC5" s="22">
+        <f t="shared" si="1"/>
         <v>46108</v>
       </c>
-      <c r="U5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BD5" s="22">
+        <f t="shared" si="1"/>
         <v>46109</v>
       </c>
-      <c r="V5" s="23">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BE5" s="23">
+        <f t="shared" si="1"/>
         <v>46110</v>
       </c>
-      <c r="W5" s="24">
-        <f ca="1">V5+1</f>
+      <c r="BF5" s="24">
+        <f>BE5+1</f>
         <v>46111</v>
       </c>
-      <c r="X5" s="22">
-        <f ca="1">W5+1</f>
+      <c r="BG5" s="22">
+        <f>BF5+1</f>
         <v>46112</v>
       </c>
-      <c r="Y5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BH5" s="22">
+        <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
         <v>46113</v>
       </c>
-      <c r="Z5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BI5" s="22">
+        <f t="shared" si="2"/>
         <v>46114</v>
       </c>
-      <c r="AA5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BJ5" s="22">
+        <f t="shared" si="2"/>
         <v>46115</v>
       </c>
-      <c r="AB5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BK5" s="22">
+        <f t="shared" si="2"/>
         <v>46116</v>
       </c>
-      <c r="AC5" s="23">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BL5" s="22">
+        <f t="shared" si="2"/>
         <v>46117</v>
       </c>
-      <c r="AD5" s="24">
-        <f ca="1">AC5+1</f>
+      <c r="BM5" s="24">
+        <f>BL5+1</f>
         <v>46118</v>
       </c>
-      <c r="AE5" s="22">
-        <f ca="1">AD5+1</f>
+      <c r="BN5" s="22">
+        <f>BM5+1</f>
         <v>46119</v>
       </c>
-      <c r="AF5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BO5" s="22">
+        <f t="shared" ref="BO5" si="3">BN5+1</f>
         <v>46120</v>
       </c>
-      <c r="AG5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BP5" s="22">
+        <f t="shared" ref="BP5" si="4">BO5+1</f>
         <v>46121</v>
       </c>
-      <c r="AH5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BQ5" s="22">
+        <f t="shared" ref="BQ5" si="5">BP5+1</f>
         <v>46122</v>
       </c>
-      <c r="AI5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BR5" s="22">
+        <f t="shared" ref="BR5" si="6">BQ5+1</f>
         <v>46123</v>
       </c>
-      <c r="AJ5" s="23">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BS5" s="22">
+        <f t="shared" ref="BS5" si="7">BR5+1</f>
         <v>46124</v>
       </c>
-      <c r="AK5" s="24">
-        <f ca="1">AJ5+1</f>
+      <c r="BT5" s="24">
+        <f>BS5+1</f>
         <v>46125</v>
       </c>
-      <c r="AL5" s="22">
-        <f ca="1">AK5+1</f>
+      <c r="BU5" s="22">
+        <f>BT5+1</f>
         <v>46126</v>
       </c>
-      <c r="AM5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BV5" s="22">
+        <f t="shared" ref="BV5" si="8">BU5+1</f>
         <v>46127</v>
       </c>
-      <c r="AN5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BW5" s="22">
+        <f t="shared" ref="BW5" si="9">BV5+1</f>
         <v>46128</v>
       </c>
-      <c r="AO5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BX5" s="22">
+        <f t="shared" ref="BX5" si="10">BW5+1</f>
         <v>46129</v>
       </c>
-      <c r="AP5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BY5" s="22">
+        <f t="shared" ref="BY5" si="11">BX5+1</f>
         <v>46130</v>
       </c>
-      <c r="AQ5" s="23">
-        <f t="shared" ca="1" si="0"/>
+      <c r="BZ5" s="22">
+        <f t="shared" ref="BZ5" si="12">BY5+1</f>
         <v>46131</v>
       </c>
-      <c r="AR5" s="24">
-        <f ca="1">AQ5+1</f>
+      <c r="CA5" s="24">
+        <f>BZ5+1</f>
         <v>46132</v>
       </c>
-      <c r="AS5" s="22">
-        <f ca="1">AR5+1</f>
+      <c r="CB5" s="22">
+        <f>CA5+1</f>
         <v>46133</v>
       </c>
-      <c r="AT5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="CC5" s="22">
+        <f t="shared" ref="CC5" si="13">CB5+1</f>
         <v>46134</v>
       </c>
-      <c r="AU5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="CD5" s="22">
+        <f t="shared" ref="CD5" si="14">CC5+1</f>
         <v>46135</v>
       </c>
-      <c r="AV5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="CE5" s="22">
+        <f t="shared" ref="CE5" si="15">CD5+1</f>
         <v>46136</v>
       </c>
-      <c r="AW5" s="22">
-        <f t="shared" ca="1" si="0"/>
+      <c r="CF5" s="22">
+        <f t="shared" ref="CF5" si="16">CE5+1</f>
         <v>46137</v>
       </c>
-      <c r="AX5" s="23">
-        <f t="shared" ca="1" si="0"/>
+      <c r="CG5" s="22">
+        <f t="shared" ref="CG5" si="17">CF5+1</f>
         <v>46138</v>
       </c>
-      <c r="AY5" s="24">
-        <f ca="1">AX5+1</f>
+      <c r="CH5" s="24">
+        <f>CG5+1</f>
         <v>46139</v>
       </c>
-      <c r="AZ5" s="22">
-        <f ca="1">AY5+1</f>
+      <c r="CI5" s="22">
+        <f>CH5+1</f>
         <v>46140</v>
       </c>
-      <c r="BA5" s="22">
-        <f t="shared" ref="BA5:BE5" ca="1" si="1">AZ5+1</f>
+      <c r="CJ5" s="22">
+        <f t="shared" ref="CJ5" si="18">CI5+1</f>
         <v>46141</v>
       </c>
-      <c r="BB5" s="22">
-        <f t="shared" ca="1" si="1"/>
+      <c r="CK5" s="22">
+        <f t="shared" ref="CK5" si="19">CJ5+1</f>
         <v>46142</v>
       </c>
-      <c r="BC5" s="22">
-        <f t="shared" ca="1" si="1"/>
+      <c r="CL5" s="22">
+        <f t="shared" ref="CL5" si="20">CK5+1</f>
         <v>46143</v>
       </c>
-      <c r="BD5" s="22">
-        <f t="shared" ca="1" si="1"/>
+      <c r="CM5" s="22">
+        <f t="shared" ref="CM5" si="21">CL5+1</f>
         <v>46144</v>
       </c>
-      <c r="BE5" s="23">
-        <f t="shared" ca="1" si="1"/>
+      <c r="CN5" s="22">
+        <f t="shared" ref="CN5" si="22">CM5+1</f>
         <v>46145</v>
-      </c>
-      <c r="BF5" s="24">
-        <f ca="1">BE5+1</f>
-        <v>46146</v>
-      </c>
-      <c r="BG5" s="22">
-        <f ca="1">BF5+1</f>
-        <v>46147</v>
-      </c>
-      <c r="BH5" s="22">
-        <f t="shared" ref="BH5:BL5" ca="1" si="2">BG5+1</f>
-        <v>46148</v>
-      </c>
-      <c r="BI5" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>46149</v>
-      </c>
-      <c r="BJ5" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>46150</v>
-      </c>
-      <c r="BK5" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>46151</v>
-      </c>
-      <c r="BL5" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>46152</v>
-      </c>
-      <c r="BM5" s="24">
-        <f ca="1">BL5+1</f>
-        <v>46153</v>
-      </c>
-      <c r="BN5" s="22">
-        <f ca="1">BM5+1</f>
-        <v>46154</v>
-      </c>
-      <c r="BO5" s="22">
-        <f t="shared" ref="BO5" ca="1" si="3">BN5+1</f>
-        <v>46155</v>
-      </c>
-      <c r="BP5" s="22">
-        <f t="shared" ref="BP5" ca="1" si="4">BO5+1</f>
-        <v>46156</v>
-      </c>
-      <c r="BQ5" s="22">
-        <f t="shared" ref="BQ5" ca="1" si="5">BP5+1</f>
-        <v>46157</v>
-      </c>
-      <c r="BR5" s="22">
-        <f t="shared" ref="BR5" ca="1" si="6">BQ5+1</f>
-        <v>46158</v>
-      </c>
-      <c r="BS5" s="22">
-        <f t="shared" ref="BS5" ca="1" si="7">BR5+1</f>
-        <v>46159</v>
-      </c>
-      <c r="BT5" s="24">
-        <f ca="1">BS5+1</f>
-        <v>46160</v>
-      </c>
-      <c r="BU5" s="22">
-        <f ca="1">BT5+1</f>
-        <v>46161</v>
-      </c>
-      <c r="BV5" s="22">
-        <f t="shared" ref="BV5" ca="1" si="8">BU5+1</f>
-        <v>46162</v>
-      </c>
-      <c r="BW5" s="22">
-        <f t="shared" ref="BW5" ca="1" si="9">BV5+1</f>
-        <v>46163</v>
-      </c>
-      <c r="BX5" s="22">
-        <f t="shared" ref="BX5" ca="1" si="10">BW5+1</f>
-        <v>46164</v>
-      </c>
-      <c r="BY5" s="22">
-        <f t="shared" ref="BY5" ca="1" si="11">BX5+1</f>
-        <v>46165</v>
-      </c>
-      <c r="BZ5" s="22">
-        <f t="shared" ref="BZ5" ca="1" si="12">BY5+1</f>
-        <v>46166</v>
-      </c>
-      <c r="CA5" s="24">
-        <f ca="1">BZ5+1</f>
-        <v>46167</v>
-      </c>
-      <c r="CB5" s="22">
-        <f ca="1">CA5+1</f>
-        <v>46168</v>
-      </c>
-      <c r="CC5" s="22">
-        <f t="shared" ref="CC5" ca="1" si="13">CB5+1</f>
-        <v>46169</v>
-      </c>
-      <c r="CD5" s="22">
-        <f t="shared" ref="CD5" ca="1" si="14">CC5+1</f>
-        <v>46170</v>
-      </c>
-      <c r="CE5" s="22">
-        <f t="shared" ref="CE5" ca="1" si="15">CD5+1</f>
-        <v>46171</v>
-      </c>
-      <c r="CF5" s="22">
-        <f t="shared" ref="CF5" ca="1" si="16">CE5+1</f>
-        <v>46172</v>
-      </c>
-      <c r="CG5" s="22">
-        <f t="shared" ref="CG5" ca="1" si="17">CF5+1</f>
-        <v>46173</v>
-      </c>
-      <c r="CH5" s="24">
-        <f ca="1">CG5+1</f>
-        <v>46174</v>
-      </c>
-      <c r="CI5" s="22">
-        <f ca="1">CH5+1</f>
-        <v>46175</v>
-      </c>
-      <c r="CJ5" s="22">
-        <f t="shared" ref="CJ5" ca="1" si="18">CI5+1</f>
-        <v>46176</v>
-      </c>
-      <c r="CK5" s="22">
-        <f t="shared" ref="CK5" ca="1" si="19">CJ5+1</f>
-        <v>46177</v>
-      </c>
-      <c r="CL5" s="22">
-        <f t="shared" ref="CL5" ca="1" si="20">CK5+1</f>
-        <v>46178</v>
-      </c>
-      <c r="CM5" s="22">
-        <f t="shared" ref="CM5" ca="1" si="21">CL5+1</f>
-        <v>46179</v>
-      </c>
-      <c r="CN5" s="22">
-        <f t="shared" ref="CN5" ca="1" si="22">CM5+1</f>
-        <v>46180</v>
       </c>
     </row>
     <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="119"/>
-      <c r="B6" s="121"/>
-      <c r="C6" s="123"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="126"/>
-      <c r="F6" s="126"/>
+      <c r="A6" s="113"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
       <c r="I6" s="25" t="str">
-        <f t="shared" ref="I6:AN6" ca="1" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
+        <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
       </c>
       <c r="J6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="K6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>W</v>
       </c>
       <c r="L6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="M6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>F</v>
       </c>
       <c r="N6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="O6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="P6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>M</v>
       </c>
       <c r="Q6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="R6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>W</v>
       </c>
       <c r="S6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="T6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>F</v>
       </c>
       <c r="U6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="V6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="W6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>M</v>
       </c>
       <c r="X6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="Y6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>W</v>
       </c>
       <c r="Z6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="AA6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>F</v>
       </c>
       <c r="AB6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="AC6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="AD6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>M</v>
       </c>
       <c r="AE6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="AF6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>W</v>
       </c>
       <c r="AG6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="AH6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>F</v>
       </c>
       <c r="AI6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="AJ6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>S</v>
       </c>
       <c r="AK6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>M</v>
       </c>
       <c r="AL6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="AM6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>W</v>
       </c>
       <c r="AN6" s="26" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" si="23"/>
         <v>T</v>
       </c>
       <c r="AO6" s="26" t="str">
-        <f t="shared" ref="AO6:BL6" ca="1" si="24">LEFT(TEXT(AO5,"ddd"),1)</f>
+        <f t="shared" ref="AO6:BL6" si="24">LEFT(TEXT(AO5,"ddd"),1)</f>
         <v>F</v>
       </c>
       <c r="AP6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="AQ6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="AR6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>M</v>
       </c>
       <c r="AS6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>T</v>
       </c>
       <c r="AT6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>W</v>
       </c>
       <c r="AU6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>T</v>
       </c>
       <c r="AV6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>F</v>
       </c>
       <c r="AW6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="AX6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="AY6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>M</v>
       </c>
       <c r="AZ6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>T</v>
       </c>
       <c r="BA6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>W</v>
       </c>
       <c r="BB6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>T</v>
       </c>
       <c r="BC6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>F</v>
       </c>
       <c r="BD6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="BE6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="BF6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>M</v>
       </c>
       <c r="BG6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>T</v>
       </c>
       <c r="BH6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>W</v>
       </c>
       <c r="BI6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>T</v>
       </c>
       <c r="BJ6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>F</v>
       </c>
       <c r="BK6" s="26" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="BL6" s="27" t="str">
-        <f t="shared" ca="1" si="24"/>
+        <f t="shared" si="24"/>
         <v>S</v>
       </c>
       <c r="BM6" s="26" t="str">
-        <f t="shared" ref="BM6:BS6" ca="1" si="25">LEFT(TEXT(BM5,"ddd"),1)</f>
+        <f t="shared" ref="BM6:BS6" si="25">LEFT(TEXT(BM5,"ddd"),1)</f>
         <v>M</v>
       </c>
       <c r="BN6" s="26" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>T</v>
       </c>
       <c r="BO6" s="26" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>W</v>
       </c>
       <c r="BP6" s="26" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>T</v>
       </c>
       <c r="BQ6" s="26" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>F</v>
       </c>
       <c r="BR6" s="26" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>S</v>
       </c>
       <c r="BS6" s="27" t="str">
-        <f t="shared" ca="1" si="25"/>
+        <f t="shared" si="25"/>
         <v>S</v>
       </c>
       <c r="BT6" s="26" t="str">
-        <f t="shared" ref="BT6:BZ6" ca="1" si="26">LEFT(TEXT(BT5,"ddd"),1)</f>
+        <f t="shared" ref="BT6:BZ6" si="26">LEFT(TEXT(BT5,"ddd"),1)</f>
         <v>M</v>
       </c>
       <c r="BU6" s="26" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" si="26"/>
         <v>T</v>
       </c>
       <c r="BV6" s="26" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" si="26"/>
         <v>W</v>
       </c>
       <c r="BW6" s="26" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" si="26"/>
         <v>T</v>
       </c>
       <c r="BX6" s="26" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" si="26"/>
         <v>F</v>
       </c>
       <c r="BY6" s="26" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" si="26"/>
         <v>S</v>
       </c>
       <c r="BZ6" s="27" t="str">
-        <f t="shared" ca="1" si="26"/>
+        <f t="shared" si="26"/>
         <v>S</v>
       </c>
       <c r="CA6" s="26" t="str">
-        <f t="shared" ref="CA6:CG6" ca="1" si="27">LEFT(TEXT(CA5,"ddd"),1)</f>
+        <f t="shared" ref="CA6:CG6" si="27">LEFT(TEXT(CA5,"ddd"),1)</f>
         <v>M</v>
       </c>
       <c r="CB6" s="26" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" si="27"/>
         <v>T</v>
       </c>
       <c r="CC6" s="26" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" si="27"/>
         <v>W</v>
       </c>
       <c r="CD6" s="26" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" si="27"/>
         <v>T</v>
       </c>
       <c r="CE6" s="26" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" si="27"/>
         <v>F</v>
       </c>
       <c r="CF6" s="26" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" si="27"/>
         <v>S</v>
       </c>
       <c r="CG6" s="27" t="str">
-        <f t="shared" ca="1" si="27"/>
+        <f t="shared" si="27"/>
         <v>S</v>
       </c>
       <c r="CH6" s="26" t="str">
-        <f t="shared" ref="CH6:CN6" ca="1" si="28">LEFT(TEXT(CH5,"ddd"),1)</f>
+        <f t="shared" ref="CH6:CN6" si="28">LEFT(TEXT(CH5,"ddd"),1)</f>
         <v>M</v>
       </c>
       <c r="CI6" s="26" t="str">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="28"/>
         <v>T</v>
       </c>
       <c r="CJ6" s="26" t="str">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="28"/>
         <v>W</v>
       </c>
       <c r="CK6" s="26" t="str">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="28"/>
         <v>T</v>
       </c>
       <c r="CL6" s="26" t="str">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="28"/>
         <v>F</v>
       </c>
       <c r="CM6" s="26" t="str">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="28"/>
         <v>S</v>
       </c>
       <c r="CN6" s="27" t="str">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="28"/>
         <v>S</v>
       </c>
     </row>
@@ -3494,16 +3499,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F9" s="92">
-        <f ca="1">E9+58</f>
+        <f>E9+58</f>
         <v>46122</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I9" s="39"/>
@@ -3601,16 +3606,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F10" s="92">
-        <f ca="1">E10+58</f>
+        <f>E10+58</f>
         <v>46122</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I10" s="39"/>
@@ -3708,16 +3713,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F11" s="92">
-        <f ca="1">E11+58</f>
+        <f>E11+58</f>
         <v>46122</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I11" s="39"/>
@@ -3815,16 +3820,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F12" s="92">
-        <f ca="1">E12+58</f>
+        <f>E12+58</f>
         <v>46122</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I12" s="39"/>
@@ -3922,16 +3927,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F13" s="92">
-        <f ca="1">E13+58</f>
+        <f>E13+58</f>
         <v>46122</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I13" s="39"/>
@@ -4029,16 +4034,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="92">
-        <f ca="1">F13+1</f>
+        <f>F13+1</f>
         <v>46123</v>
       </c>
       <c r="F14" s="92">
-        <f ca="1">E14+7</f>
+        <f>E14+7</f>
         <v>46130</v>
       </c>
       <c r="G14" s="14"/>
       <c r="H14" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>8</v>
       </c>
       <c r="I14" s="39"/>
@@ -4235,16 +4240,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F16" s="92">
-        <f ca="1">E16+58</f>
+        <f>E16+58</f>
         <v>46122</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I16" s="39"/>
@@ -4342,16 +4347,16 @@
         <v>0</v>
       </c>
       <c r="E17" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F17" s="92">
-        <f ca="1">E17+58</f>
+        <f>E17+58</f>
         <v>46122</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I17" s="39"/>
@@ -4449,16 +4454,16 @@
         <v>0</v>
       </c>
       <c r="E18" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F18" s="93">
-        <f ca="1">F17</f>
+        <f>F17</f>
         <v>46122</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I18" s="39"/>
@@ -4655,16 +4660,16 @@
         <v>0.15</v>
       </c>
       <c r="E20" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F20" s="92">
-        <f ca="1">E20+58</f>
+        <f>E20+58</f>
         <v>46122</v>
       </c>
       <c r="G20" s="14"/>
       <c r="H20" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>59</v>
       </c>
       <c r="I20" s="39"/>
@@ -4760,11 +4765,11 @@
       <c r="C21" s="37"/>
       <c r="D21" s="38"/>
       <c r="E21" s="92">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F21" s="92">
-        <f ca="1">E21+58</f>
+        <f>E21+58</f>
         <v>46122</v>
       </c>
       <c r="G21" s="14"/>
@@ -4864,16 +4869,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="92">
-        <f ca="1">F21+1</f>
+        <f>F21+1</f>
         <v>46123</v>
       </c>
       <c r="F22" s="93">
-        <f ca="1">E22+7</f>
+        <f>E22+7</f>
         <v>46130</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I22" s="39"/>
@@ -4986,16 +4991,16 @@
         <v>0.5</v>
       </c>
       <c r="E24" s="96">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F24" s="96">
-        <f ca="1">E24+20</f>
+        <f>E24+20</f>
         <v>46084</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>21</v>
       </c>
       <c r="I24" s="39"/>
@@ -5093,16 +5098,16 @@
         <v>0.85</v>
       </c>
       <c r="E25" s="96">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F25" s="96">
-        <f ca="1">E25+9</f>
+        <f>E25+9</f>
         <v>46073</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>10</v>
       </c>
       <c r="I25" s="39"/>
@@ -6151,16 +6156,16 @@
         <v>0.1</v>
       </c>
       <c r="E35" s="99">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F35" s="99">
-        <f ca="1">E35+14</f>
+        <f>E35+14</f>
         <v>46078</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="I35" s="39"/>
@@ -6258,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="99">
-        <f ca="1">F35+1</f>
+        <f>F35+1</f>
         <v>46079</v>
       </c>
       <c r="F36" s="99">
@@ -6267,7 +6272,7 @@
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>52</v>
       </c>
       <c r="I36" s="39"/>
@@ -6461,19 +6466,21 @@
       </c>
       <c r="C38" s="55"/>
       <c r="D38" s="56">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E38" s="99">
-        <f ca="1">Project_Start</f>
+        <f>Project_Start</f>
         <v>46064</v>
       </c>
       <c r="F38" s="99">
-        <f ca="1">E38+21</f>
+        <f>E38+21</f>
         <v>46085</v>
       </c>
-      <c r="G38" s="14"/>
+      <c r="G38" s="128" t="s">
+        <v>65</v>
+      </c>
       <c r="H38" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>22</v>
       </c>
       <c r="I38" s="39"/>
@@ -6571,7 +6578,7 @@
         <v>0.3</v>
       </c>
       <c r="E39" s="99">
-        <f ca="1">F38</f>
+        <f>F38</f>
         <v>46085</v>
       </c>
       <c r="F39" s="99">
@@ -6580,7 +6587,7 @@
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>46</v>
       </c>
       <c r="I39" s="39"/>
@@ -6675,10 +6682,10 @@
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="56">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E40" s="99">
-        <f ca="1">F38</f>
+        <f>F38</f>
         <v>46085</v>
       </c>
       <c r="F40" s="99">
@@ -6982,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="102">
-        <f ca="1">E35</f>
+        <f>E35</f>
         <v>46064</v>
       </c>
       <c r="F43" s="102">
@@ -6991,7 +6998,7 @@
       </c>
       <c r="G43" s="14"/>
       <c r="H43" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>94</v>
       </c>
       <c r="I43" s="39"/>
@@ -7822,12 +7829,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -7844,6 +7845,12 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D50">
     <cfRule type="dataBar" priority="102">
@@ -7864,7 +7871,7 @@
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33:BK44 I4:BK8 I9:BZ10 BL14 I14:BK16 I19:BK21 I23:BK31 I32:BM32 BL33:BM33 BL36 BL40:BZ40 BL43:CA43 I47:BK48 BL44:BM44 I45:BM45">
+  <conditionalFormatting sqref="I33:BK44 I4:BK8 I9:BZ10 BL14 I14:BK16 I19:BK21 I23:BK31 I32:BM32 BL33:BM33 BL36 BL40:BZ40 BL43:CA43 BL44:BM44 I45:BM45 I47:BK48">
     <cfRule type="expression" dxfId="43" priority="80">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
@@ -7914,7 +7921,7 @@
       <formula>AND(task_end&gt;=BL$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL43:CA43 I43:BK44 I47:BK48 BL44:BM44 I45:BM45">
+  <conditionalFormatting sqref="BL43:CA43 I43:BK44 BL44:BM44 I45:BM45 I47:BK48">
     <cfRule type="expression" dxfId="33" priority="115">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
@@ -7942,7 +7949,7 @@
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I46:BT46 BN44:BT45">
+  <conditionalFormatting sqref="BN44:BT45 I46:BT46">
     <cfRule type="expression" dxfId="27" priority="48">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
@@ -7955,7 +7962,7 @@
       <formula>AND(TODAY()&gt;=BL$5, TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BS14:BT14 BM34:BR38 BM4:BR8 BM14:BR15 BM19:BR19 BM23:BR31 BN32:BS33 BM41:BR42 I46:BT46 BN44:BT45">
+  <conditionalFormatting sqref="BS14:BT14 BM34:BR38 BM4:BR8 BM14:BR15 BM19:BR19 BM23:BR31 BN32:BS33 BM41:BR42 BN44:BT45 I46:BT46">
     <cfRule type="expression" dxfId="24" priority="41">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
@@ -7970,9 +7977,9 @@
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT37:BY38 BT4:BY8 BZ14 BT14:BY15 BT19:BY19 BT23:BY35 BT41:BY42 BU44:CA44 BM47:CA47">
+  <conditionalFormatting sqref="BT37:BY38 BT4:BY8 BZ14 BT14:BY15 BT19:BY19 BT23:BY35 BT41:BY42 BU44:CA44">
     <cfRule type="expression" dxfId="21" priority="32">
-      <formula>AND(TODAY()&gt;=BM$5, TODAY()&lt;BN$5)</formula>
+      <formula>AND(TODAY()&gt;=BT$5, TODAY()&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT38:BY38">
@@ -7985,12 +7992,12 @@
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU44:CA44 BM47:CA47">
+  <conditionalFormatting sqref="BU44:CA44">
     <cfRule type="expression" dxfId="18" priority="39">
-      <formula>AND(task_start&lt;=BM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BM$5)</formula>
+      <formula>AND(task_start&lt;=BU$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BU$5)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="40" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
+      <formula>AND(task_end&gt;=BU$5,task_start&lt;BV$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CA9:CF10 I11:CF13 CA14:CF14 BM16:CF16 I17:CF18 CD20:CF21 I22:CF22">
@@ -8008,7 +8015,7 @@
       <formula>AND(task_end&gt;=BL$5,task_start&lt;BM$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA37:CF38 CA4:CF10 I11:CF13 CA14:CF15 BL16:CF16 I17:CF18 CA19:CF19 BL20:CF21 I22:CF22 CA23:CF32 BZ33:CF33 CA34:CF35 BS36:CF36 BL39:CF39 CA40:CF42 CB43:CF44 BU45:CF46 CB47:CF47">
+  <conditionalFormatting sqref="CA37:CF38 CA4:CF10 I11:CF13 CA14:CF15 BL16:CF16 I17:CF18 CA19:CF19 BL20:CF21 I22:CF22 CA23:CF32 BZ33:CF33 CA34:CF35 BS36:CF36 BL39:CF39 CA40:CF42 CB43:CF44 BU45:CF46 BM47:CF47">
     <cfRule type="expression" dxfId="13" priority="23">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
@@ -8018,12 +8025,12 @@
       <formula>AND(task_end&gt;=CA$5,task_start&lt;CB$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB43:CF44 BU45:CF46 CB47:CF47">
+  <conditionalFormatting sqref="CB43:CF44 BU45:CF46 BM47:CF47">
     <cfRule type="expression" dxfId="11" priority="30">
-      <formula>AND(task_start&lt;=BU$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BU$5)</formula>
+      <formula>AND(task_start&lt;=BM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BM$5)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="31" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BU$5,task_start&lt;BV$5)</formula>
+      <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CG9:CG14 CN9:CN14 BS14 CG16:CG18 CN16:CN18 CG20:CG22 CN20:CN22">
@@ -8274,6 +8281,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8585,36 +8621,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8635,26 +8662,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="532" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F401DFC-54D7-6345-9741-7BC40F98E887}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4904F6EB-065E-D149-ABC2-3F1339DDC63B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,9 +221,6 @@
     <t>Implement: Input limits (where relevant)</t>
   </si>
   <si>
-    <t>Implement: Limits on combinations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Implement: </t>
   </si>
   <si>
@@ -249,6 +246,9 @@
   </si>
   <si>
     <t>Need a check for if I'm missing things</t>
+  </si>
+  <si>
+    <t>Implement: Limits on combinations (prep+mmd)</t>
   </si>
 </sst>
 </file>
@@ -2456,7 +2456,7 @@
       <c r="Y2" s="122"/>
       <c r="Z2" s="122"/>
       <c r="AP2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
@@ -4760,7 +4760,7 @@
     <row r="21" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="81"/>
       <c r="B21" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38"/>
@@ -5518,7 +5518,7 @@
     <row r="29" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>
       <c r="B29" s="47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="48"/>
       <c r="D29" s="49">
@@ -5943,7 +5943,7 @@
     <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
       <c r="B33" s="47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="48"/>
       <c r="D33" s="49">
@@ -6050,7 +6050,7 @@
     <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12"/>
       <c r="B34" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="51"/>
       <c r="D34" s="52"/>
@@ -6477,7 +6477,7 @@
         <v>46085</v>
       </c>
       <c r="G38" s="128" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="30"/>
@@ -6678,11 +6678,11 @@
     <row r="40" spans="1:92" s="35" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
       <c r="B40" s="54" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E40" s="99">
         <f>F38</f>
@@ -6782,7 +6782,7 @@
     <row r="41" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
       <c r="B41" s="54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41" s="55"/>
       <c r="D41" s="56">
@@ -6982,7 +6982,7 @@
     <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>
       <c r="B43" s="61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43" s="62"/>
       <c r="D43" s="63">
@@ -7622,7 +7622,7 @@
     <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>
       <c r="B49" s="64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" s="65"/>
       <c r="D49" s="66"/>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4904F6EB-065E-D149-ABC2-3F1339DDC63B}"/>
+  <xr:revisionPtr revIDLastSave="538" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8E3A57-2325-104B-BBE7-A1E78C60678F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>Project start:</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>Implement: Limits on combinations (prep+mmd)</t>
+  </si>
+  <si>
+    <t>Check testing donwards especially, relative to current diagnoses</t>
   </si>
 </sst>
 </file>
@@ -4024,7 +4027,7 @@
       <c r="CM13" s="39"/>
       <c r="CN13" s="39"/>
     </row>
-    <row r="14" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:92" s="35" customFormat="1" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="40" t="s">
         <v>41</v>
@@ -4038,13 +4041,15 @@
         <v>46123</v>
       </c>
       <c r="F14" s="92">
-        <f>E14+7</f>
-        <v>46130</v>
-      </c>
-      <c r="G14" s="14"/>
+        <f>E14+14</f>
+        <v>46137</v>
+      </c>
+      <c r="G14" s="128" t="s">
+        <v>66</v>
+      </c>
       <c r="H14" s="4">
         <f t="shared" si="29"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I14" s="39"/>
       <c r="J14" s="39"/>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="538" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC8E3A57-2325-104B-BBE7-A1E78C60678F}"/>
+  <xr:revisionPtr revIDLastSave="539" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F97C446-34F2-1F42-AA24-11415B47F62C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="49">
-        <v>0.85</v>
+        <v>100</v>
       </c>
       <c r="E25" s="96">
         <f>Project_Start</f>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="539" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F97C446-34F2-1F42-AA24-11415B47F62C}"/>
+  <xr:revisionPtr revIDLastSave="542" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0237177B-5612-694A-8D8E-175AB405FB92}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="49">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E25" s="96">
         <f>Project_Start</f>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C35" s="55"/>
       <c r="D35" s="56">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E35" s="99">
         <f>Project_Start</f>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="C36" s="55"/>
       <c r="D36" s="56">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E36" s="99">
         <f>F35+1</f>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="542" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0237177B-5612-694A-8D8E-175AB405FB92}"/>
+  <xr:revisionPtr revIDLastSave="543" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B23D52C1-BEFC-B047-B8D4-AB36A5F59D3C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C30" s="48"/>
       <c r="D30" s="49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30" s="96">
         <f>F28+1</f>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="543" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B23D52C1-BEFC-B047-B8D4-AB36A5F59D3C}"/>
+  <xr:revisionPtr revIDLastSave="545" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47D673B2-FBE9-D541-A071-5DC00FFD6873}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="-19920" windowWidth="37380" windowHeight="19600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="C43" s="62"/>
       <c r="D43" s="63">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E43" s="102">
         <f>E35</f>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C44" s="62"/>
       <c r="D44" s="63">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E44" s="102">
         <v>46146</v>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="545" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47D673B2-FBE9-D541-A071-5DC00FFD6873}"/>
+  <xr:revisionPtr revIDLastSave="548" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB8E3818-4DB6-5647-B5BE-BCF7241B6657}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="-19920" windowWidth="37380" windowHeight="19600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="1680" windowWidth="37380" windowHeight="19600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -1151,6 +1151,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1170,30 +1194,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1317,7 +1317,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1328,7 +1328,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -1356,7 +1356,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1367,7 +1367,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -1584,7 +1584,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1595,7 +1595,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -1674,7 +1674,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1685,7 +1685,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -2171,10 +2171,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2405,28 +2401,28 @@
       <c r="E1" s="82"/>
       <c r="F1" s="83"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="125" t="s">
+      <c r="I1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="123">
+      <c r="Q1" s="116">
         <v>46064</v>
       </c>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
     </row>
     <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="71"/>
@@ -2436,28 +2432,28 @@
       <c r="D2" s="17"/>
       <c r="E2" s="84"/>
       <c r="F2" s="85"/>
-      <c r="I2" s="125" t="s">
+      <c r="I2" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="126"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
-      <c r="N2" s="126"/>
-      <c r="O2" s="126"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="121">
+      <c r="Q2" s="114">
         <v>1</v>
       </c>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="122"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="115"/>
+      <c r="U2" s="115"/>
+      <c r="V2" s="115"/>
+      <c r="W2" s="115"/>
+      <c r="X2" s="115"/>
+      <c r="Y2" s="115"/>
+      <c r="Z2" s="115"/>
       <c r="AP2" t="s">
         <v>62</v>
       </c>
@@ -2476,142 +2472,142 @@
       </c>
       <c r="E4" s="88"/>
       <c r="F4" s="87"/>
-      <c r="I4" s="127">
+      <c r="I4" s="120">
         <f>I5</f>
         <v>46062</v>
       </c>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="119">
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112">
         <f>P5</f>
         <v>46069</v>
       </c>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119">
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112">
         <f>W5</f>
         <v>46076</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="119"/>
-      <c r="Z4" s="119"/>
-      <c r="AA4" s="119"/>
-      <c r="AB4" s="119"/>
-      <c r="AC4" s="119"/>
-      <c r="AD4" s="119">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112">
         <f>AD5</f>
         <v>46083</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112">
         <f>AK5</f>
         <v>46090</v>
       </c>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="119"/>
-      <c r="AQ4" s="119"/>
-      <c r="AR4" s="119">
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="112"/>
+      <c r="AQ4" s="112"/>
+      <c r="AR4" s="112">
         <f>AR5</f>
         <v>46097</v>
       </c>
-      <c r="AS4" s="119"/>
-      <c r="AT4" s="119"/>
-      <c r="AU4" s="119"/>
-      <c r="AV4" s="119"/>
-      <c r="AW4" s="119"/>
-      <c r="AX4" s="119"/>
-      <c r="AY4" s="119">
+      <c r="AS4" s="112"/>
+      <c r="AT4" s="112"/>
+      <c r="AU4" s="112"/>
+      <c r="AV4" s="112"/>
+      <c r="AW4" s="112"/>
+      <c r="AX4" s="112"/>
+      <c r="AY4" s="112">
         <f>AY5</f>
         <v>46104</v>
       </c>
-      <c r="AZ4" s="119"/>
-      <c r="BA4" s="119"/>
-      <c r="BB4" s="119"/>
-      <c r="BC4" s="119"/>
-      <c r="BD4" s="119"/>
-      <c r="BE4" s="119"/>
-      <c r="BF4" s="119">
+      <c r="AZ4" s="112"/>
+      <c r="BA4" s="112"/>
+      <c r="BB4" s="112"/>
+      <c r="BC4" s="112"/>
+      <c r="BD4" s="112"/>
+      <c r="BE4" s="112"/>
+      <c r="BF4" s="112">
         <f>BF5</f>
         <v>46111</v>
       </c>
-      <c r="BG4" s="119"/>
-      <c r="BH4" s="119"/>
-      <c r="BI4" s="119"/>
-      <c r="BJ4" s="119"/>
-      <c r="BK4" s="119"/>
-      <c r="BL4" s="120"/>
-      <c r="BM4" s="119">
+      <c r="BG4" s="112"/>
+      <c r="BH4" s="112"/>
+      <c r="BI4" s="112"/>
+      <c r="BJ4" s="112"/>
+      <c r="BK4" s="112"/>
+      <c r="BL4" s="113"/>
+      <c r="BM4" s="112">
         <f>BM5</f>
         <v>46118</v>
       </c>
-      <c r="BN4" s="119"/>
-      <c r="BO4" s="119"/>
-      <c r="BP4" s="119"/>
-      <c r="BQ4" s="119"/>
-      <c r="BR4" s="119"/>
-      <c r="BS4" s="120"/>
-      <c r="BT4" s="119">
+      <c r="BN4" s="112"/>
+      <c r="BO4" s="112"/>
+      <c r="BP4" s="112"/>
+      <c r="BQ4" s="112"/>
+      <c r="BR4" s="112"/>
+      <c r="BS4" s="113"/>
+      <c r="BT4" s="112">
         <f>BT5</f>
         <v>46125</v>
       </c>
-      <c r="BU4" s="119"/>
-      <c r="BV4" s="119"/>
-      <c r="BW4" s="119"/>
-      <c r="BX4" s="119"/>
-      <c r="BY4" s="119"/>
-      <c r="BZ4" s="120"/>
-      <c r="CA4" s="119">
+      <c r="BU4" s="112"/>
+      <c r="BV4" s="112"/>
+      <c r="BW4" s="112"/>
+      <c r="BX4" s="112"/>
+      <c r="BY4" s="112"/>
+      <c r="BZ4" s="113"/>
+      <c r="CA4" s="112">
         <f>CA5</f>
         <v>46132</v>
       </c>
-      <c r="CB4" s="119"/>
-      <c r="CC4" s="119"/>
-      <c r="CD4" s="119"/>
-      <c r="CE4" s="119"/>
-      <c r="CF4" s="119"/>
-      <c r="CG4" s="120"/>
-      <c r="CH4" s="119">
+      <c r="CB4" s="112"/>
+      <c r="CC4" s="112"/>
+      <c r="CD4" s="112"/>
+      <c r="CE4" s="112"/>
+      <c r="CF4" s="112"/>
+      <c r="CG4" s="113"/>
+      <c r="CH4" s="112">
         <f>CH5</f>
         <v>46139</v>
       </c>
-      <c r="CI4" s="119"/>
-      <c r="CJ4" s="119"/>
-      <c r="CK4" s="119"/>
-      <c r="CL4" s="119"/>
-      <c r="CM4" s="119"/>
-      <c r="CN4" s="120"/>
+      <c r="CI4" s="112"/>
+      <c r="CJ4" s="112"/>
+      <c r="CK4" s="112"/>
+      <c r="CL4" s="112"/>
+      <c r="CM4" s="112"/>
+      <c r="CN4" s="113"/>
     </row>
     <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="113"/>
-      <c r="B5" s="114" t="s">
+      <c r="A5" s="123"/>
+      <c r="B5" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="111" t="s">
+      <c r="E5" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="111" t="s">
+      <c r="F5" s="121" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="22">
@@ -2952,12 +2948,12 @@
       </c>
     </row>
     <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="113"/>
-      <c r="B6" s="115"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="112"/>
-      <c r="F6" s="112"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
       <c r="I6" s="25" t="str">
         <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -4044,7 +4040,7 @@
         <f>E14+14</f>
         <v>46137</v>
       </c>
-      <c r="G14" s="128" t="s">
+      <c r="G14" s="111" t="s">
         <v>66</v>
       </c>
       <c r="H14" s="4">
@@ -5313,7 +5309,7 @@
       </c>
       <c r="C27" s="48"/>
       <c r="D27" s="49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="96">
         <f>F26+1</f>
@@ -5527,7 +5523,7 @@
       </c>
       <c r="C29" s="48"/>
       <c r="D29" s="49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="96">
         <f>F27+1</f>
@@ -6481,7 +6477,7 @@
         <f>E38+21</f>
         <v>46085</v>
       </c>
-      <c r="G38" s="128" t="s">
+      <c r="G38" s="111" t="s">
         <v>64</v>
       </c>
       <c r="H38" s="4">
@@ -7834,6 +7830,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -7850,12 +7852,6 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D50">
     <cfRule type="dataBar" priority="102">
@@ -7927,11 +7923,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL43:CA43 I43:BK44 BL44:BM44 I45:BM45 I47:BK48">
-    <cfRule type="expression" dxfId="33" priority="115">
+    <cfRule type="expression" dxfId="33" priority="116" stopIfTrue="1">
+      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="115">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="116" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM24:BR31 BN32:BS33">
@@ -7955,11 +7951,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BN44:BT45 I46:BT46">
-    <cfRule type="expression" dxfId="27" priority="48">
+    <cfRule type="expression" dxfId="27" priority="49" stopIfTrue="1">
+      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="48">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="49" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS14:BS15 BS33:BS35 BL4:BL8 BS4:BS8 BZ4:BZ8 CG4:CG42 CN4:CN48 BL15 BZ15 BL19 BS19 BZ19 BL23:BL31 BS23:BS31 BZ23:BZ32 BL34:BL35 BZ34:BZ35 BL37:BL38 BS37:BS38 BZ37:BZ38 BL41:BL42 BS41:BS42 BZ41:BZ42 CG44:CG47 BL47">
@@ -8031,11 +8027,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CB43:CF44 BU45:CF46 BM47:CF47">
-    <cfRule type="expression" dxfId="11" priority="30">
+    <cfRule type="expression" dxfId="11" priority="31" stopIfTrue="1">
+      <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="30">
       <formula>AND(task_start&lt;=BM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BM$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="31" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CG9:CG14 CN9:CN14 BS14 CG16:CG18 CN16:CN18 CG20:CG22 CN20:CN22">
@@ -8044,11 +8040,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CG43:CM43 CH44:CM47 BL48:CM48">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="8" priority="7" stopIfTrue="1">
+      <formula>AND(task_end&gt;=BL$5,task_start&lt;BM$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="6">
       <formula>AND(task_start&lt;=BL$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BL$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="7" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BL$5,task_start&lt;BM$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CH4:CM42 CG43:CM43 CH44:CM47 BL48:CM48">
@@ -8306,15 +8302,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8626,6 +8613,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
   <ds:schemaRefs>
@@ -8639,14 +8635,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8667,6 +8655,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="548" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB8E3818-4DB6-5647-B5BE-BCF7241B6657}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22297D18-E066-694C-9FCB-D869A0E090A9}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1680" windowWidth="37380" windowHeight="19600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -2057,7 +2057,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$Q$2" horiz="1" max="100" page="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$Q$2" horiz="1" max="100" page="0" val="5"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2443,7 +2443,7 @@
       <c r="O2" s="119"/>
       <c r="P2" s="18"/>
       <c r="Q2" s="114">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R2" s="115"/>
       <c r="S2" s="115"/>
@@ -2474,7 +2474,7 @@
       <c r="F4" s="87"/>
       <c r="I4" s="120">
         <f>I5</f>
-        <v>46062</v>
+        <v>46090</v>
       </c>
       <c r="J4" s="112"/>
       <c r="K4" s="112"/>
@@ -2484,7 +2484,7 @@
       <c r="O4" s="112"/>
       <c r="P4" s="112">
         <f>P5</f>
-        <v>46069</v>
+        <v>46097</v>
       </c>
       <c r="Q4" s="112"/>
       <c r="R4" s="112"/>
@@ -2494,7 +2494,7 @@
       <c r="V4" s="112"/>
       <c r="W4" s="112">
         <f>W5</f>
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="X4" s="112"/>
       <c r="Y4" s="112"/>
@@ -2504,7 +2504,7 @@
       <c r="AC4" s="112"/>
       <c r="AD4" s="112">
         <f>AD5</f>
-        <v>46083</v>
+        <v>46111</v>
       </c>
       <c r="AE4" s="112"/>
       <c r="AF4" s="112"/>
@@ -2514,7 +2514,7 @@
       <c r="AJ4" s="112"/>
       <c r="AK4" s="112">
         <f>AK5</f>
-        <v>46090</v>
+        <v>46118</v>
       </c>
       <c r="AL4" s="112"/>
       <c r="AM4" s="112"/>
@@ -2524,7 +2524,7 @@
       <c r="AQ4" s="112"/>
       <c r="AR4" s="112">
         <f>AR5</f>
-        <v>46097</v>
+        <v>46125</v>
       </c>
       <c r="AS4" s="112"/>
       <c r="AT4" s="112"/>
@@ -2534,7 +2534,7 @@
       <c r="AX4" s="112"/>
       <c r="AY4" s="112">
         <f>AY5</f>
-        <v>46104</v>
+        <v>46132</v>
       </c>
       <c r="AZ4" s="112"/>
       <c r="BA4" s="112"/>
@@ -2544,7 +2544,7 @@
       <c r="BE4" s="112"/>
       <c r="BF4" s="112">
         <f>BF5</f>
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="BG4" s="112"/>
       <c r="BH4" s="112"/>
@@ -2554,7 +2554,7 @@
       <c r="BL4" s="113"/>
       <c r="BM4" s="112">
         <f>BM5</f>
-        <v>46118</v>
+        <v>46146</v>
       </c>
       <c r="BN4" s="112"/>
       <c r="BO4" s="112"/>
@@ -2564,7 +2564,7 @@
       <c r="BS4" s="113"/>
       <c r="BT4" s="112">
         <f>BT5</f>
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="BU4" s="112"/>
       <c r="BV4" s="112"/>
@@ -2574,7 +2574,7 @@
       <c r="BZ4" s="113"/>
       <c r="CA4" s="112">
         <f>CA5</f>
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="CB4" s="112"/>
       <c r="CC4" s="112"/>
@@ -2584,7 +2584,7 @@
       <c r="CG4" s="113"/>
       <c r="CH4" s="112">
         <f>CH5</f>
-        <v>46139</v>
+        <v>46167</v>
       </c>
       <c r="CI4" s="112"/>
       <c r="CJ4" s="112"/>
@@ -2612,339 +2612,339 @@
       </c>
       <c r="I5" s="22">
         <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
-        <v>46062</v>
+        <v>46090</v>
       </c>
       <c r="J5" s="22">
         <f>I5+1</f>
-        <v>46063</v>
+        <v>46091</v>
       </c>
       <c r="K5" s="22">
         <f t="shared" ref="K5:AX5" si="0">J5+1</f>
-        <v>46064</v>
+        <v>46092</v>
       </c>
       <c r="L5" s="22">
         <f t="shared" si="0"/>
-        <v>46065</v>
+        <v>46093</v>
       </c>
       <c r="M5" s="22">
         <f t="shared" si="0"/>
-        <v>46066</v>
+        <v>46094</v>
       </c>
       <c r="N5" s="22">
         <f t="shared" si="0"/>
-        <v>46067</v>
+        <v>46095</v>
       </c>
       <c r="O5" s="23">
         <f t="shared" si="0"/>
-        <v>46068</v>
+        <v>46096</v>
       </c>
       <c r="P5" s="24">
         <f>O5+1</f>
-        <v>46069</v>
+        <v>46097</v>
       </c>
       <c r="Q5" s="22">
         <f>P5+1</f>
-        <v>46070</v>
+        <v>46098</v>
       </c>
       <c r="R5" s="22">
         <f t="shared" si="0"/>
-        <v>46071</v>
+        <v>46099</v>
       </c>
       <c r="S5" s="22">
         <f t="shared" si="0"/>
-        <v>46072</v>
+        <v>46100</v>
       </c>
       <c r="T5" s="22">
         <f t="shared" si="0"/>
-        <v>46073</v>
+        <v>46101</v>
       </c>
       <c r="U5" s="22">
         <f t="shared" si="0"/>
-        <v>46074</v>
+        <v>46102</v>
       </c>
       <c r="V5" s="23">
         <f t="shared" si="0"/>
-        <v>46075</v>
+        <v>46103</v>
       </c>
       <c r="W5" s="24">
         <f>V5+1</f>
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="X5" s="22">
         <f>W5+1</f>
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="Y5" s="22">
         <f t="shared" si="0"/>
-        <v>46078</v>
+        <v>46106</v>
       </c>
       <c r="Z5" s="22">
         <f t="shared" si="0"/>
-        <v>46079</v>
+        <v>46107</v>
       </c>
       <c r="AA5" s="22">
         <f t="shared" si="0"/>
-        <v>46080</v>
+        <v>46108</v>
       </c>
       <c r="AB5" s="22">
         <f t="shared" si="0"/>
-        <v>46081</v>
+        <v>46109</v>
       </c>
       <c r="AC5" s="23">
         <f t="shared" si="0"/>
-        <v>46082</v>
+        <v>46110</v>
       </c>
       <c r="AD5" s="24">
         <f>AC5+1</f>
-        <v>46083</v>
+        <v>46111</v>
       </c>
       <c r="AE5" s="22">
         <f>AD5+1</f>
-        <v>46084</v>
+        <v>46112</v>
       </c>
       <c r="AF5" s="22">
         <f t="shared" si="0"/>
-        <v>46085</v>
+        <v>46113</v>
       </c>
       <c r="AG5" s="22">
         <f t="shared" si="0"/>
-        <v>46086</v>
+        <v>46114</v>
       </c>
       <c r="AH5" s="22">
         <f t="shared" si="0"/>
-        <v>46087</v>
+        <v>46115</v>
       </c>
       <c r="AI5" s="22">
         <f t="shared" si="0"/>
-        <v>46088</v>
+        <v>46116</v>
       </c>
       <c r="AJ5" s="23">
         <f t="shared" si="0"/>
-        <v>46089</v>
+        <v>46117</v>
       </c>
       <c r="AK5" s="24">
         <f>AJ5+1</f>
-        <v>46090</v>
+        <v>46118</v>
       </c>
       <c r="AL5" s="22">
         <f>AK5+1</f>
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="AM5" s="22">
         <f t="shared" si="0"/>
-        <v>46092</v>
+        <v>46120</v>
       </c>
       <c r="AN5" s="22">
         <f t="shared" si="0"/>
-        <v>46093</v>
+        <v>46121</v>
       </c>
       <c r="AO5" s="22">
         <f t="shared" si="0"/>
-        <v>46094</v>
+        <v>46122</v>
       </c>
       <c r="AP5" s="22">
         <f t="shared" si="0"/>
-        <v>46095</v>
+        <v>46123</v>
       </c>
       <c r="AQ5" s="23">
         <f t="shared" si="0"/>
-        <v>46096</v>
+        <v>46124</v>
       </c>
       <c r="AR5" s="24">
         <f>AQ5+1</f>
-        <v>46097</v>
+        <v>46125</v>
       </c>
       <c r="AS5" s="22">
         <f>AR5+1</f>
-        <v>46098</v>
+        <v>46126</v>
       </c>
       <c r="AT5" s="22">
         <f t="shared" si="0"/>
-        <v>46099</v>
+        <v>46127</v>
       </c>
       <c r="AU5" s="22">
         <f t="shared" si="0"/>
-        <v>46100</v>
+        <v>46128</v>
       </c>
       <c r="AV5" s="22">
         <f t="shared" si="0"/>
-        <v>46101</v>
+        <v>46129</v>
       </c>
       <c r="AW5" s="22">
         <f t="shared" si="0"/>
-        <v>46102</v>
+        <v>46130</v>
       </c>
       <c r="AX5" s="23">
         <f t="shared" si="0"/>
-        <v>46103</v>
+        <v>46131</v>
       </c>
       <c r="AY5" s="24">
         <f>AX5+1</f>
-        <v>46104</v>
+        <v>46132</v>
       </c>
       <c r="AZ5" s="22">
         <f>AY5+1</f>
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="BA5" s="22">
         <f t="shared" ref="BA5:BE5" si="1">AZ5+1</f>
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="BB5" s="22">
         <f t="shared" si="1"/>
-        <v>46107</v>
+        <v>46135</v>
       </c>
       <c r="BC5" s="22">
         <f t="shared" si="1"/>
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="BD5" s="22">
         <f t="shared" si="1"/>
-        <v>46109</v>
+        <v>46137</v>
       </c>
       <c r="BE5" s="23">
         <f t="shared" si="1"/>
-        <v>46110</v>
+        <v>46138</v>
       </c>
       <c r="BF5" s="24">
         <f>BE5+1</f>
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="BG5" s="22">
         <f>BF5+1</f>
-        <v>46112</v>
+        <v>46140</v>
       </c>
       <c r="BH5" s="22">
         <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="BI5" s="22">
         <f t="shared" si="2"/>
-        <v>46114</v>
+        <v>46142</v>
       </c>
       <c r="BJ5" s="22">
         <f t="shared" si="2"/>
-        <v>46115</v>
+        <v>46143</v>
       </c>
       <c r="BK5" s="22">
         <f t="shared" si="2"/>
-        <v>46116</v>
+        <v>46144</v>
       </c>
       <c r="BL5" s="22">
         <f t="shared" si="2"/>
-        <v>46117</v>
+        <v>46145</v>
       </c>
       <c r="BM5" s="24">
         <f>BL5+1</f>
-        <v>46118</v>
+        <v>46146</v>
       </c>
       <c r="BN5" s="22">
         <f>BM5+1</f>
-        <v>46119</v>
+        <v>46147</v>
       </c>
       <c r="BO5" s="22">
         <f t="shared" ref="BO5" si="3">BN5+1</f>
-        <v>46120</v>
+        <v>46148</v>
       </c>
       <c r="BP5" s="22">
         <f t="shared" ref="BP5" si="4">BO5+1</f>
-        <v>46121</v>
+        <v>46149</v>
       </c>
       <c r="BQ5" s="22">
         <f t="shared" ref="BQ5" si="5">BP5+1</f>
-        <v>46122</v>
+        <v>46150</v>
       </c>
       <c r="BR5" s="22">
         <f t="shared" ref="BR5" si="6">BQ5+1</f>
-        <v>46123</v>
+        <v>46151</v>
       </c>
       <c r="BS5" s="22">
         <f t="shared" ref="BS5" si="7">BR5+1</f>
-        <v>46124</v>
+        <v>46152</v>
       </c>
       <c r="BT5" s="24">
         <f>BS5+1</f>
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="BU5" s="22">
         <f>BT5+1</f>
-        <v>46126</v>
+        <v>46154</v>
       </c>
       <c r="BV5" s="22">
         <f t="shared" ref="BV5" si="8">BU5+1</f>
-        <v>46127</v>
+        <v>46155</v>
       </c>
       <c r="BW5" s="22">
         <f t="shared" ref="BW5" si="9">BV5+1</f>
-        <v>46128</v>
+        <v>46156</v>
       </c>
       <c r="BX5" s="22">
         <f t="shared" ref="BX5" si="10">BW5+1</f>
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="BY5" s="22">
         <f t="shared" ref="BY5" si="11">BX5+1</f>
-        <v>46130</v>
+        <v>46158</v>
       </c>
       <c r="BZ5" s="22">
         <f t="shared" ref="BZ5" si="12">BY5+1</f>
-        <v>46131</v>
+        <v>46159</v>
       </c>
       <c r="CA5" s="24">
         <f>BZ5+1</f>
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="CB5" s="22">
         <f>CA5+1</f>
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="CC5" s="22">
         <f t="shared" ref="CC5" si="13">CB5+1</f>
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="CD5" s="22">
         <f t="shared" ref="CD5" si="14">CC5+1</f>
-        <v>46135</v>
+        <v>46163</v>
       </c>
       <c r="CE5" s="22">
         <f t="shared" ref="CE5" si="15">CD5+1</f>
-        <v>46136</v>
+        <v>46164</v>
       </c>
       <c r="CF5" s="22">
         <f t="shared" ref="CF5" si="16">CE5+1</f>
-        <v>46137</v>
+        <v>46165</v>
       </c>
       <c r="CG5" s="22">
         <f t="shared" ref="CG5" si="17">CF5+1</f>
-        <v>46138</v>
+        <v>46166</v>
       </c>
       <c r="CH5" s="24">
         <f>CG5+1</f>
-        <v>46139</v>
+        <v>46167</v>
       </c>
       <c r="CI5" s="22">
         <f>CH5+1</f>
-        <v>46140</v>
+        <v>46168</v>
       </c>
       <c r="CJ5" s="22">
         <f t="shared" ref="CJ5" si="18">CI5+1</f>
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="CK5" s="22">
         <f t="shared" ref="CK5" si="19">CJ5+1</f>
-        <v>46142</v>
+        <v>46170</v>
       </c>
       <c r="CL5" s="22">
         <f t="shared" ref="CL5" si="20">CK5+1</f>
-        <v>46143</v>
+        <v>46171</v>
       </c>
       <c r="CM5" s="22">
         <f t="shared" ref="CM5" si="21">CL5+1</f>
-        <v>46144</v>
+        <v>46172</v>
       </c>
       <c r="CN5" s="22">
         <f t="shared" ref="CN5" si="22">CM5+1</f>
-        <v>46145</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22297D18-E066-694C-9FCB-D869A0E090A9}"/>
+  <xr:revisionPtr revIDLastSave="553" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2625F50C-71FF-4242-B3A9-5974B899753B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -1154,6 +1154,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1174,26 +1194,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2401,28 +2401,28 @@
       <c r="E1" s="82"/>
       <c r="F1" s="83"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="116">
+      <c r="Q1" s="124">
         <v>46064</v>
       </c>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
     </row>
     <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="71"/>
@@ -2432,28 +2432,28 @@
       <c r="D2" s="17"/>
       <c r="E2" s="84"/>
       <c r="F2" s="85"/>
-      <c r="I2" s="118" t="s">
+      <c r="I2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="114">
+      <c r="Q2" s="122">
         <v>5</v>
       </c>
-      <c r="R2" s="115"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="115"/>
-      <c r="U2" s="115"/>
-      <c r="V2" s="115"/>
-      <c r="W2" s="115"/>
-      <c r="X2" s="115"/>
-      <c r="Y2" s="115"/>
-      <c r="Z2" s="115"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="123"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="123"/>
+      <c r="X2" s="123"/>
+      <c r="Y2" s="123"/>
+      <c r="Z2" s="123"/>
       <c r="AP2" t="s">
         <v>62</v>
       </c>
@@ -2472,142 +2472,142 @@
       </c>
       <c r="E4" s="88"/>
       <c r="F4" s="87"/>
-      <c r="I4" s="120">
+      <c r="I4" s="128">
         <f>I5</f>
         <v>46090</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112">
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="120">
         <f>P5</f>
         <v>46097</v>
       </c>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112">
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120"/>
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120"/>
+      <c r="V4" s="120"/>
+      <c r="W4" s="120">
         <f>W5</f>
         <v>46104</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112">
+      <c r="X4" s="120"/>
+      <c r="Y4" s="120"/>
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="120">
         <f>AD5</f>
         <v>46111</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112">
+      <c r="AE4" s="120"/>
+      <c r="AF4" s="120"/>
+      <c r="AG4" s="120"/>
+      <c r="AH4" s="120"/>
+      <c r="AI4" s="120"/>
+      <c r="AJ4" s="120"/>
+      <c r="AK4" s="120">
         <f>AK5</f>
         <v>46118</v>
       </c>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="112"/>
-      <c r="AQ4" s="112"/>
-      <c r="AR4" s="112">
+      <c r="AL4" s="120"/>
+      <c r="AM4" s="120"/>
+      <c r="AN4" s="120"/>
+      <c r="AO4" s="120"/>
+      <c r="AP4" s="120"/>
+      <c r="AQ4" s="120"/>
+      <c r="AR4" s="120">
         <f>AR5</f>
         <v>46125</v>
       </c>
-      <c r="AS4" s="112"/>
-      <c r="AT4" s="112"/>
-      <c r="AU4" s="112"/>
-      <c r="AV4" s="112"/>
-      <c r="AW4" s="112"/>
-      <c r="AX4" s="112"/>
-      <c r="AY4" s="112">
+      <c r="AS4" s="120"/>
+      <c r="AT4" s="120"/>
+      <c r="AU4" s="120"/>
+      <c r="AV4" s="120"/>
+      <c r="AW4" s="120"/>
+      <c r="AX4" s="120"/>
+      <c r="AY4" s="120">
         <f>AY5</f>
         <v>46132</v>
       </c>
-      <c r="AZ4" s="112"/>
-      <c r="BA4" s="112"/>
-      <c r="BB4" s="112"/>
-      <c r="BC4" s="112"/>
-      <c r="BD4" s="112"/>
-      <c r="BE4" s="112"/>
-      <c r="BF4" s="112">
+      <c r="AZ4" s="120"/>
+      <c r="BA4" s="120"/>
+      <c r="BB4" s="120"/>
+      <c r="BC4" s="120"/>
+      <c r="BD4" s="120"/>
+      <c r="BE4" s="120"/>
+      <c r="BF4" s="120">
         <f>BF5</f>
         <v>46139</v>
       </c>
-      <c r="BG4" s="112"/>
-      <c r="BH4" s="112"/>
-      <c r="BI4" s="112"/>
-      <c r="BJ4" s="112"/>
-      <c r="BK4" s="112"/>
-      <c r="BL4" s="113"/>
-      <c r="BM4" s="112">
+      <c r="BG4" s="120"/>
+      <c r="BH4" s="120"/>
+      <c r="BI4" s="120"/>
+      <c r="BJ4" s="120"/>
+      <c r="BK4" s="120"/>
+      <c r="BL4" s="121"/>
+      <c r="BM4" s="120">
         <f>BM5</f>
         <v>46146</v>
       </c>
-      <c r="BN4" s="112"/>
-      <c r="BO4" s="112"/>
-      <c r="BP4" s="112"/>
-      <c r="BQ4" s="112"/>
-      <c r="BR4" s="112"/>
-      <c r="BS4" s="113"/>
-      <c r="BT4" s="112">
+      <c r="BN4" s="120"/>
+      <c r="BO4" s="120"/>
+      <c r="BP4" s="120"/>
+      <c r="BQ4" s="120"/>
+      <c r="BR4" s="120"/>
+      <c r="BS4" s="121"/>
+      <c r="BT4" s="120">
         <f>BT5</f>
         <v>46153</v>
       </c>
-      <c r="BU4" s="112"/>
-      <c r="BV4" s="112"/>
-      <c r="BW4" s="112"/>
-      <c r="BX4" s="112"/>
-      <c r="BY4" s="112"/>
-      <c r="BZ4" s="113"/>
-      <c r="CA4" s="112">
+      <c r="BU4" s="120"/>
+      <c r="BV4" s="120"/>
+      <c r="BW4" s="120"/>
+      <c r="BX4" s="120"/>
+      <c r="BY4" s="120"/>
+      <c r="BZ4" s="121"/>
+      <c r="CA4" s="120">
         <f>CA5</f>
         <v>46160</v>
       </c>
-      <c r="CB4" s="112"/>
-      <c r="CC4" s="112"/>
-      <c r="CD4" s="112"/>
-      <c r="CE4" s="112"/>
-      <c r="CF4" s="112"/>
-      <c r="CG4" s="113"/>
-      <c r="CH4" s="112">
+      <c r="CB4" s="120"/>
+      <c r="CC4" s="120"/>
+      <c r="CD4" s="120"/>
+      <c r="CE4" s="120"/>
+      <c r="CF4" s="120"/>
+      <c r="CG4" s="121"/>
+      <c r="CH4" s="120">
         <f>CH5</f>
         <v>46167</v>
       </c>
-      <c r="CI4" s="112"/>
-      <c r="CJ4" s="112"/>
-      <c r="CK4" s="112"/>
-      <c r="CL4" s="112"/>
-      <c r="CM4" s="112"/>
-      <c r="CN4" s="113"/>
+      <c r="CI4" s="120"/>
+      <c r="CJ4" s="120"/>
+      <c r="CK4" s="120"/>
+      <c r="CL4" s="120"/>
+      <c r="CM4" s="120"/>
+      <c r="CN4" s="121"/>
     </row>
     <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="123"/>
-      <c r="B5" s="124" t="s">
+      <c r="A5" s="114"/>
+      <c r="B5" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="128" t="s">
+      <c r="D5" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="121" t="s">
+      <c r="E5" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="121" t="s">
+      <c r="F5" s="112" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="22">
@@ -2948,12 +2948,12 @@
       </c>
     </row>
     <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="123"/>
-      <c r="B6" s="125"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
+      <c r="A6" s="114"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
       <c r="I6" s="25" t="str">
         <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C26" s="48"/>
       <c r="D26" s="49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="96">
         <v>46083</v>
@@ -7830,12 +7830,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -7852,6 +7846,12 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D50">
     <cfRule type="dataBar" priority="102">
@@ -8282,23 +8282,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8614,22 +8603,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8656,9 +8652,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="553" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2625F50C-71FF-4242-B3A9-5974B899753B}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D048EA3-94F8-8D48-8A05-7DA927F7587D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
   <si>
     <t>Project start:</t>
   </si>
@@ -249,9 +249,6 @@
   </si>
   <si>
     <t>Implement: Limits on combinations (prep+mmd)</t>
-  </si>
-  <si>
-    <t>Check testing donwards especially, relative to current diagnoses</t>
   </si>
 </sst>
 </file>
@@ -1154,6 +1151,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1173,27 +1191,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2171,6 +2168,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2401,28 +2402,28 @@
       <c r="E1" s="82"/>
       <c r="F1" s="83"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="126" t="s">
+      <c r="I1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="124">
+      <c r="Q1" s="116">
         <v>46064</v>
       </c>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
     </row>
     <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="71"/>
@@ -2432,28 +2433,28 @@
       <c r="D2" s="17"/>
       <c r="E2" s="84"/>
       <c r="F2" s="85"/>
-      <c r="I2" s="126" t="s">
+      <c r="I2" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="122">
+      <c r="Q2" s="114">
         <v>5</v>
       </c>
-      <c r="R2" s="123"/>
-      <c r="S2" s="123"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="123"/>
-      <c r="V2" s="123"/>
-      <c r="W2" s="123"/>
-      <c r="X2" s="123"/>
-      <c r="Y2" s="123"/>
-      <c r="Z2" s="123"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="115"/>
+      <c r="U2" s="115"/>
+      <c r="V2" s="115"/>
+      <c r="W2" s="115"/>
+      <c r="X2" s="115"/>
+      <c r="Y2" s="115"/>
+      <c r="Z2" s="115"/>
       <c r="AP2" t="s">
         <v>62</v>
       </c>
@@ -2472,142 +2473,142 @@
       </c>
       <c r="E4" s="88"/>
       <c r="F4" s="87"/>
-      <c r="I4" s="128">
+      <c r="I4" s="120">
         <f>I5</f>
         <v>46090</v>
       </c>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120"/>
-      <c r="P4" s="120">
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112">
         <f>P5</f>
         <v>46097</v>
       </c>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120"/>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120"/>
-      <c r="V4" s="120"/>
-      <c r="W4" s="120">
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112">
         <f>W5</f>
         <v>46104</v>
       </c>
-      <c r="X4" s="120"/>
-      <c r="Y4" s="120"/>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="120">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112">
         <f>AD5</f>
         <v>46111</v>
       </c>
-      <c r="AE4" s="120"/>
-      <c r="AF4" s="120"/>
-      <c r="AG4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112">
         <f>AK5</f>
         <v>46118</v>
       </c>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
-      <c r="AO4" s="120"/>
-      <c r="AP4" s="120"/>
-      <c r="AQ4" s="120"/>
-      <c r="AR4" s="120">
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="112"/>
+      <c r="AQ4" s="112"/>
+      <c r="AR4" s="112">
         <f>AR5</f>
         <v>46125</v>
       </c>
-      <c r="AS4" s="120"/>
-      <c r="AT4" s="120"/>
-      <c r="AU4" s="120"/>
-      <c r="AV4" s="120"/>
-      <c r="AW4" s="120"/>
-      <c r="AX4" s="120"/>
-      <c r="AY4" s="120">
+      <c r="AS4" s="112"/>
+      <c r="AT4" s="112"/>
+      <c r="AU4" s="112"/>
+      <c r="AV4" s="112"/>
+      <c r="AW4" s="112"/>
+      <c r="AX4" s="112"/>
+      <c r="AY4" s="112">
         <f>AY5</f>
         <v>46132</v>
       </c>
-      <c r="AZ4" s="120"/>
-      <c r="BA4" s="120"/>
-      <c r="BB4" s="120"/>
-      <c r="BC4" s="120"/>
-      <c r="BD4" s="120"/>
-      <c r="BE4" s="120"/>
-      <c r="BF4" s="120">
+      <c r="AZ4" s="112"/>
+      <c r="BA4" s="112"/>
+      <c r="BB4" s="112"/>
+      <c r="BC4" s="112"/>
+      <c r="BD4" s="112"/>
+      <c r="BE4" s="112"/>
+      <c r="BF4" s="112">
         <f>BF5</f>
         <v>46139</v>
       </c>
-      <c r="BG4" s="120"/>
-      <c r="BH4" s="120"/>
-      <c r="BI4" s="120"/>
-      <c r="BJ4" s="120"/>
-      <c r="BK4" s="120"/>
-      <c r="BL4" s="121"/>
-      <c r="BM4" s="120">
+      <c r="BG4" s="112"/>
+      <c r="BH4" s="112"/>
+      <c r="BI4" s="112"/>
+      <c r="BJ4" s="112"/>
+      <c r="BK4" s="112"/>
+      <c r="BL4" s="113"/>
+      <c r="BM4" s="112">
         <f>BM5</f>
         <v>46146</v>
       </c>
-      <c r="BN4" s="120"/>
-      <c r="BO4" s="120"/>
-      <c r="BP4" s="120"/>
-      <c r="BQ4" s="120"/>
-      <c r="BR4" s="120"/>
-      <c r="BS4" s="121"/>
-      <c r="BT4" s="120">
+      <c r="BN4" s="112"/>
+      <c r="BO4" s="112"/>
+      <c r="BP4" s="112"/>
+      <c r="BQ4" s="112"/>
+      <c r="BR4" s="112"/>
+      <c r="BS4" s="113"/>
+      <c r="BT4" s="112">
         <f>BT5</f>
         <v>46153</v>
       </c>
-      <c r="BU4" s="120"/>
-      <c r="BV4" s="120"/>
-      <c r="BW4" s="120"/>
-      <c r="BX4" s="120"/>
-      <c r="BY4" s="120"/>
-      <c r="BZ4" s="121"/>
-      <c r="CA4" s="120">
+      <c r="BU4" s="112"/>
+      <c r="BV4" s="112"/>
+      <c r="BW4" s="112"/>
+      <c r="BX4" s="112"/>
+      <c r="BY4" s="112"/>
+      <c r="BZ4" s="113"/>
+      <c r="CA4" s="112">
         <f>CA5</f>
         <v>46160</v>
       </c>
-      <c r="CB4" s="120"/>
-      <c r="CC4" s="120"/>
-      <c r="CD4" s="120"/>
-      <c r="CE4" s="120"/>
-      <c r="CF4" s="120"/>
-      <c r="CG4" s="121"/>
-      <c r="CH4" s="120">
+      <c r="CB4" s="112"/>
+      <c r="CC4" s="112"/>
+      <c r="CD4" s="112"/>
+      <c r="CE4" s="112"/>
+      <c r="CF4" s="112"/>
+      <c r="CG4" s="113"/>
+      <c r="CH4" s="112">
         <f>CH5</f>
         <v>46167</v>
       </c>
-      <c r="CI4" s="120"/>
-      <c r="CJ4" s="120"/>
-      <c r="CK4" s="120"/>
-      <c r="CL4" s="120"/>
-      <c r="CM4" s="120"/>
-      <c r="CN4" s="121"/>
+      <c r="CI4" s="112"/>
+      <c r="CJ4" s="112"/>
+      <c r="CK4" s="112"/>
+      <c r="CL4" s="112"/>
+      <c r="CM4" s="112"/>
+      <c r="CN4" s="113"/>
     </row>
     <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="114"/>
-      <c r="B5" s="115" t="s">
+      <c r="A5" s="123"/>
+      <c r="B5" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="112" t="s">
+      <c r="E5" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="112" t="s">
+      <c r="F5" s="121" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="22">
@@ -2948,12 +2949,12 @@
       </c>
     </row>
     <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="114"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
       <c r="I6" s="25" t="str">
         <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -4040,9 +4041,7 @@
         <f>E14+14</f>
         <v>46137</v>
       </c>
-      <c r="G14" s="111" t="s">
-        <v>66</v>
-      </c>
+      <c r="G14" s="111"/>
       <c r="H14" s="4">
         <f t="shared" si="29"/>
         <v>15</v>
@@ -4989,7 +4988,7 @@
       </c>
       <c r="C24" s="48"/>
       <c r="D24" s="49">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E24" s="96">
         <f>Project_Start</f>
@@ -5096,7 +5095,7 @@
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="49">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="96">
         <f>Project_Start</f>
@@ -5627,7 +5626,7 @@
       </c>
       <c r="C30" s="48"/>
       <c r="D30" s="49">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E30" s="96">
         <f>F28+1</f>
@@ -6987,7 +6986,7 @@
       </c>
       <c r="C43" s="62"/>
       <c r="D43" s="63">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="E43" s="102">
         <f>E35</f>
@@ -7830,6 +7829,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -7846,12 +7851,6 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D50">
     <cfRule type="dataBar" priority="102">
@@ -8282,12 +8281,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8603,29 +8613,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8652,13 +8655,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D048EA3-94F8-8D48-8A05-7DA927F7587D}"/>
+  <xr:revisionPtr revIDLastSave="561" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEBFA8E-BC5A-9546-AE4F-9B12AC029CA2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>Project start:</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>Implement: Limits on combinations (prep+mmd)</t>
+  </si>
+  <si>
+    <t>Relative scenario and baseline counts</t>
   </si>
 </sst>
 </file>
@@ -1151,6 +1154,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1171,26 +1194,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1314,7 +1317,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -1325,7 +1328,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1353,7 +1356,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -1364,7 +1367,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1581,7 +1584,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -1592,7 +1595,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1671,7 +1674,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="8"/>
         </patternFill>
       </fill>
       <border>
@@ -1682,7 +1685,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -2168,10 +2171,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2378,7 +2377,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CN53"/>
+  <dimension ref="A1:CN54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="12" customWidth="1"/>
@@ -2402,28 +2401,28 @@
       <c r="E1" s="82"/>
       <c r="F1" s="83"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="116">
+      <c r="Q1" s="124">
         <v>46064</v>
       </c>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
+      <c r="R1" s="125"/>
+      <c r="S1" s="125"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
     </row>
     <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="71"/>
@@ -2433,28 +2432,28 @@
       <c r="D2" s="17"/>
       <c r="E2" s="84"/>
       <c r="F2" s="85"/>
-      <c r="I2" s="118" t="s">
+      <c r="I2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="114">
+      <c r="Q2" s="122">
         <v>5</v>
       </c>
-      <c r="R2" s="115"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="115"/>
-      <c r="U2" s="115"/>
-      <c r="V2" s="115"/>
-      <c r="W2" s="115"/>
-      <c r="X2" s="115"/>
-      <c r="Y2" s="115"/>
-      <c r="Z2" s="115"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="123"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="123"/>
+      <c r="X2" s="123"/>
+      <c r="Y2" s="123"/>
+      <c r="Z2" s="123"/>
       <c r="AP2" t="s">
         <v>62</v>
       </c>
@@ -2473,142 +2472,142 @@
       </c>
       <c r="E4" s="88"/>
       <c r="F4" s="87"/>
-      <c r="I4" s="120">
+      <c r="I4" s="128">
         <f>I5</f>
         <v>46090</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112">
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="120">
         <f>P5</f>
         <v>46097</v>
       </c>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112">
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120"/>
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120"/>
+      <c r="V4" s="120"/>
+      <c r="W4" s="120">
         <f>W5</f>
         <v>46104</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112">
+      <c r="X4" s="120"/>
+      <c r="Y4" s="120"/>
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="120">
         <f>AD5</f>
         <v>46111</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112">
+      <c r="AE4" s="120"/>
+      <c r="AF4" s="120"/>
+      <c r="AG4" s="120"/>
+      <c r="AH4" s="120"/>
+      <c r="AI4" s="120"/>
+      <c r="AJ4" s="120"/>
+      <c r="AK4" s="120">
         <f>AK5</f>
         <v>46118</v>
       </c>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="112"/>
-      <c r="AQ4" s="112"/>
-      <c r="AR4" s="112">
+      <c r="AL4" s="120"/>
+      <c r="AM4" s="120"/>
+      <c r="AN4" s="120"/>
+      <c r="AO4" s="120"/>
+      <c r="AP4" s="120"/>
+      <c r="AQ4" s="120"/>
+      <c r="AR4" s="120">
         <f>AR5</f>
         <v>46125</v>
       </c>
-      <c r="AS4" s="112"/>
-      <c r="AT4" s="112"/>
-      <c r="AU4" s="112"/>
-      <c r="AV4" s="112"/>
-      <c r="AW4" s="112"/>
-      <c r="AX4" s="112"/>
-      <c r="AY4" s="112">
+      <c r="AS4" s="120"/>
+      <c r="AT4" s="120"/>
+      <c r="AU4" s="120"/>
+      <c r="AV4" s="120"/>
+      <c r="AW4" s="120"/>
+      <c r="AX4" s="120"/>
+      <c r="AY4" s="120">
         <f>AY5</f>
         <v>46132</v>
       </c>
-      <c r="AZ4" s="112"/>
-      <c r="BA4" s="112"/>
-      <c r="BB4" s="112"/>
-      <c r="BC4" s="112"/>
-      <c r="BD4" s="112"/>
-      <c r="BE4" s="112"/>
-      <c r="BF4" s="112">
+      <c r="AZ4" s="120"/>
+      <c r="BA4" s="120"/>
+      <c r="BB4" s="120"/>
+      <c r="BC4" s="120"/>
+      <c r="BD4" s="120"/>
+      <c r="BE4" s="120"/>
+      <c r="BF4" s="120">
         <f>BF5</f>
         <v>46139</v>
       </c>
-      <c r="BG4" s="112"/>
-      <c r="BH4" s="112"/>
-      <c r="BI4" s="112"/>
-      <c r="BJ4" s="112"/>
-      <c r="BK4" s="112"/>
-      <c r="BL4" s="113"/>
-      <c r="BM4" s="112">
+      <c r="BG4" s="120"/>
+      <c r="BH4" s="120"/>
+      <c r="BI4" s="120"/>
+      <c r="BJ4" s="120"/>
+      <c r="BK4" s="120"/>
+      <c r="BL4" s="121"/>
+      <c r="BM4" s="120">
         <f>BM5</f>
         <v>46146</v>
       </c>
-      <c r="BN4" s="112"/>
-      <c r="BO4" s="112"/>
-      <c r="BP4" s="112"/>
-      <c r="BQ4" s="112"/>
-      <c r="BR4" s="112"/>
-      <c r="BS4" s="113"/>
-      <c r="BT4" s="112">
+      <c r="BN4" s="120"/>
+      <c r="BO4" s="120"/>
+      <c r="BP4" s="120"/>
+      <c r="BQ4" s="120"/>
+      <c r="BR4" s="120"/>
+      <c r="BS4" s="121"/>
+      <c r="BT4" s="120">
         <f>BT5</f>
         <v>46153</v>
       </c>
-      <c r="BU4" s="112"/>
-      <c r="BV4" s="112"/>
-      <c r="BW4" s="112"/>
-      <c r="BX4" s="112"/>
-      <c r="BY4" s="112"/>
-      <c r="BZ4" s="113"/>
-      <c r="CA4" s="112">
+      <c r="BU4" s="120"/>
+      <c r="BV4" s="120"/>
+      <c r="BW4" s="120"/>
+      <c r="BX4" s="120"/>
+      <c r="BY4" s="120"/>
+      <c r="BZ4" s="121"/>
+      <c r="CA4" s="120">
         <f>CA5</f>
         <v>46160</v>
       </c>
-      <c r="CB4" s="112"/>
-      <c r="CC4" s="112"/>
-      <c r="CD4" s="112"/>
-      <c r="CE4" s="112"/>
-      <c r="CF4" s="112"/>
-      <c r="CG4" s="113"/>
-      <c r="CH4" s="112">
+      <c r="CB4" s="120"/>
+      <c r="CC4" s="120"/>
+      <c r="CD4" s="120"/>
+      <c r="CE4" s="120"/>
+      <c r="CF4" s="120"/>
+      <c r="CG4" s="121"/>
+      <c r="CH4" s="120">
         <f>CH5</f>
         <v>46167</v>
       </c>
-      <c r="CI4" s="112"/>
-      <c r="CJ4" s="112"/>
-      <c r="CK4" s="112"/>
-      <c r="CL4" s="112"/>
-      <c r="CM4" s="112"/>
-      <c r="CN4" s="113"/>
+      <c r="CI4" s="120"/>
+      <c r="CJ4" s="120"/>
+      <c r="CK4" s="120"/>
+      <c r="CL4" s="120"/>
+      <c r="CM4" s="120"/>
+      <c r="CN4" s="121"/>
     </row>
     <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="123"/>
-      <c r="B5" s="124" t="s">
+      <c r="A5" s="114"/>
+      <c r="B5" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="128" t="s">
+      <c r="D5" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="121" t="s">
+      <c r="E5" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="121" t="s">
+      <c r="F5" s="112" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="22">
@@ -2949,12 +2948,12 @@
       </c>
     </row>
     <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="123"/>
-      <c r="B6" s="125"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
+      <c r="A6" s="114"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
       <c r="I6" s="25" t="str">
         <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -4562,7 +4561,7 @@
       <c r="F19" s="91"/>
       <c r="G19" s="14"/>
       <c r="H19" s="4" t="str">
-        <f t="shared" ref="H19:H50" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H19:H51" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I19" s="34"/>
@@ -5943,19 +5942,19 @@
     <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
       <c r="B33" s="47" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C33" s="48"/>
       <c r="D33" s="49">
         <v>0</v>
       </c>
       <c r="E33" s="96">
-        <f>F32+1</f>
-        <v>46123</v>
+        <f>F31+1</f>
+        <v>46114</v>
       </c>
       <c r="F33" s="96">
         <f>E33+7</f>
-        <v>46130</v>
+        <v>46121</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="4">
@@ -6049,231 +6048,231 @@
     </row>
     <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12"/>
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="48"/>
+      <c r="D34" s="49">
+        <v>0</v>
+      </c>
+      <c r="E34" s="96">
+        <f>F32+1</f>
+        <v>46123</v>
+      </c>
+      <c r="F34" s="96">
+        <f>E34+7</f>
+        <v>46130</v>
+      </c>
+      <c r="G34" s="14"/>
+      <c r="H34" s="4">
+        <f t="shared" si="30"/>
+        <v>8</v>
+      </c>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="39"/>
+      <c r="R34" s="39"/>
+      <c r="S34" s="39"/>
+      <c r="T34" s="39"/>
+      <c r="U34" s="39"/>
+      <c r="V34" s="39"/>
+      <c r="W34" s="39"/>
+      <c r="X34" s="39"/>
+      <c r="Y34" s="39"/>
+      <c r="Z34" s="39"/>
+      <c r="AA34" s="39"/>
+      <c r="AB34" s="39"/>
+      <c r="AC34" s="39"/>
+      <c r="AD34" s="39"/>
+      <c r="AE34" s="39"/>
+      <c r="AF34" s="39"/>
+      <c r="AG34" s="39"/>
+      <c r="AH34" s="39"/>
+      <c r="AI34" s="39"/>
+      <c r="AJ34" s="39"/>
+      <c r="AK34" s="39"/>
+      <c r="AL34" s="39"/>
+      <c r="AM34" s="39"/>
+      <c r="AN34" s="39"/>
+      <c r="AO34" s="39"/>
+      <c r="AP34" s="39"/>
+      <c r="AQ34" s="39"/>
+      <c r="AR34" s="39"/>
+      <c r="AS34" s="39"/>
+      <c r="AT34" s="39"/>
+      <c r="AU34" s="39"/>
+      <c r="AV34" s="39"/>
+      <c r="AW34" s="39"/>
+      <c r="AX34" s="39"/>
+      <c r="AY34" s="39"/>
+      <c r="AZ34" s="39"/>
+      <c r="BA34" s="39"/>
+      <c r="BB34" s="39"/>
+      <c r="BC34" s="39"/>
+      <c r="BD34" s="39"/>
+      <c r="BE34" s="39"/>
+      <c r="BF34" s="39"/>
+      <c r="BG34" s="39"/>
+      <c r="BH34" s="39"/>
+      <c r="BI34" s="39"/>
+      <c r="BJ34" s="39"/>
+      <c r="BK34" s="39"/>
+      <c r="BL34" s="39"/>
+      <c r="BM34" s="39"/>
+      <c r="BN34" s="39"/>
+      <c r="BO34" s="39"/>
+      <c r="BP34" s="39"/>
+      <c r="BQ34" s="39"/>
+      <c r="BR34" s="39"/>
+      <c r="BS34" s="39"/>
+      <c r="BT34" s="39"/>
+      <c r="BU34" s="39"/>
+      <c r="BV34" s="39"/>
+      <c r="BW34" s="39"/>
+      <c r="BX34" s="39"/>
+      <c r="BY34" s="39"/>
+      <c r="BZ34" s="39"/>
+      <c r="CA34" s="39"/>
+      <c r="CB34" s="39"/>
+      <c r="CC34" s="39"/>
+      <c r="CD34" s="39"/>
+      <c r="CE34" s="39"/>
+      <c r="CF34" s="39"/>
+      <c r="CG34" s="39"/>
+      <c r="CH34" s="39"/>
+      <c r="CI34" s="39"/>
+      <c r="CJ34" s="39"/>
+      <c r="CK34" s="39"/>
+      <c r="CL34" s="39"/>
+      <c r="CM34" s="39"/>
+      <c r="CN34" s="39"/>
+    </row>
+    <row r="35" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12"/>
+      <c r="B35" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="51"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="4" t="str">
+      <c r="C35" s="51"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="4" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="53"/>
-      <c r="Q34" s="53"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="53"/>
-      <c r="T34" s="53"/>
-      <c r="U34" s="53"/>
-      <c r="V34" s="53"/>
-      <c r="W34" s="53"/>
-      <c r="X34" s="53"/>
-      <c r="Y34" s="53"/>
-      <c r="Z34" s="53"/>
-      <c r="AA34" s="53"/>
-      <c r="AB34" s="53"/>
-      <c r="AC34" s="53"/>
-      <c r="AD34" s="53"/>
-      <c r="AE34" s="53"/>
-      <c r="AF34" s="53"/>
-      <c r="AG34" s="53"/>
-      <c r="AH34" s="53"/>
-      <c r="AI34" s="53"/>
-      <c r="AJ34" s="53"/>
-      <c r="AK34" s="53"/>
-      <c r="AL34" s="53"/>
-      <c r="AM34" s="53"/>
-      <c r="AN34" s="53"/>
-      <c r="AO34" s="53"/>
-      <c r="AP34" s="53"/>
-      <c r="AQ34" s="53"/>
-      <c r="AR34" s="53"/>
-      <c r="AS34" s="53"/>
-      <c r="AT34" s="53"/>
-      <c r="AU34" s="53"/>
-      <c r="AV34" s="53"/>
-      <c r="AW34" s="53"/>
-      <c r="AX34" s="53"/>
-      <c r="AY34" s="53"/>
-      <c r="AZ34" s="53"/>
-      <c r="BA34" s="53"/>
-      <c r="BB34" s="53"/>
-      <c r="BC34" s="53"/>
-      <c r="BD34" s="53"/>
-      <c r="BE34" s="53"/>
-      <c r="BF34" s="53"/>
-      <c r="BG34" s="53"/>
-      <c r="BH34" s="53"/>
-      <c r="BI34" s="53"/>
-      <c r="BJ34" s="53"/>
-      <c r="BK34" s="53"/>
-      <c r="BL34" s="53"/>
-      <c r="BM34" s="53"/>
-      <c r="BN34" s="53"/>
-      <c r="BO34" s="53"/>
-      <c r="BP34" s="53"/>
-      <c r="BQ34" s="53"/>
-      <c r="BR34" s="53"/>
-      <c r="BS34" s="53"/>
-      <c r="BT34" s="53"/>
-      <c r="BU34" s="53"/>
-      <c r="BV34" s="53"/>
-      <c r="BW34" s="53"/>
-      <c r="BX34" s="53"/>
-      <c r="BY34" s="53"/>
-      <c r="BZ34" s="53"/>
-      <c r="CA34" s="53"/>
-      <c r="CB34" s="53"/>
-      <c r="CC34" s="53"/>
-      <c r="CD34" s="53"/>
-      <c r="CE34" s="53"/>
-      <c r="CF34" s="53"/>
-      <c r="CG34" s="53"/>
-      <c r="CH34" s="53"/>
-      <c r="CI34" s="53"/>
-      <c r="CJ34" s="53"/>
-      <c r="CK34" s="53"/>
-      <c r="CL34" s="53"/>
-      <c r="CM34" s="53"/>
-      <c r="CN34" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="53"/>
+      <c r="Q35" s="53"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="53"/>
+      <c r="T35" s="53"/>
+      <c r="U35" s="53"/>
+      <c r="V35" s="53"/>
+      <c r="W35" s="53"/>
+      <c r="X35" s="53"/>
+      <c r="Y35" s="53"/>
+      <c r="Z35" s="53"/>
+      <c r="AA35" s="53"/>
+      <c r="AB35" s="53"/>
+      <c r="AC35" s="53"/>
+      <c r="AD35" s="53"/>
+      <c r="AE35" s="53"/>
+      <c r="AF35" s="53"/>
+      <c r="AG35" s="53"/>
+      <c r="AH35" s="53"/>
+      <c r="AI35" s="53"/>
+      <c r="AJ35" s="53"/>
+      <c r="AK35" s="53"/>
+      <c r="AL35" s="53"/>
+      <c r="AM35" s="53"/>
+      <c r="AN35" s="53"/>
+      <c r="AO35" s="53"/>
+      <c r="AP35" s="53"/>
+      <c r="AQ35" s="53"/>
+      <c r="AR35" s="53"/>
+      <c r="AS35" s="53"/>
+      <c r="AT35" s="53"/>
+      <c r="AU35" s="53"/>
+      <c r="AV35" s="53"/>
+      <c r="AW35" s="53"/>
+      <c r="AX35" s="53"/>
+      <c r="AY35" s="53"/>
+      <c r="AZ35" s="53"/>
+      <c r="BA35" s="53"/>
+      <c r="BB35" s="53"/>
+      <c r="BC35" s="53"/>
+      <c r="BD35" s="53"/>
+      <c r="BE35" s="53"/>
+      <c r="BF35" s="53"/>
+      <c r="BG35" s="53"/>
+      <c r="BH35" s="53"/>
+      <c r="BI35" s="53"/>
+      <c r="BJ35" s="53"/>
+      <c r="BK35" s="53"/>
+      <c r="BL35" s="53"/>
+      <c r="BM35" s="53"/>
+      <c r="BN35" s="53"/>
+      <c r="BO35" s="53"/>
+      <c r="BP35" s="53"/>
+      <c r="BQ35" s="53"/>
+      <c r="BR35" s="53"/>
+      <c r="BS35" s="53"/>
+      <c r="BT35" s="53"/>
+      <c r="BU35" s="53"/>
+      <c r="BV35" s="53"/>
+      <c r="BW35" s="53"/>
+      <c r="BX35" s="53"/>
+      <c r="BY35" s="53"/>
+      <c r="BZ35" s="53"/>
+      <c r="CA35" s="53"/>
+      <c r="CB35" s="53"/>
+      <c r="CC35" s="53"/>
+      <c r="CD35" s="53"/>
+      <c r="CE35" s="53"/>
+      <c r="CF35" s="53"/>
+      <c r="CG35" s="53"/>
+      <c r="CH35" s="53"/>
+      <c r="CI35" s="53"/>
+      <c r="CJ35" s="53"/>
+      <c r="CK35" s="53"/>
+      <c r="CL35" s="53"/>
+      <c r="CM35" s="53"/>
+      <c r="CN35" s="53"/>
     </row>
-    <row r="35" spans="1:92" s="35" customFormat="1" ht="68" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12"/>
-      <c r="B35" s="109" t="s">
+    <row r="36" spans="1:92" s="35" customFormat="1" ht="68" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12"/>
+      <c r="B36" s="109" t="s">
         <v>43</v>
-      </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="56">
-        <v>0.2</v>
-      </c>
-      <c r="E35" s="99">
-        <f>Project_Start</f>
-        <v>46064</v>
-      </c>
-      <c r="F35" s="99">
-        <f>E35+14</f>
-        <v>46078</v>
-      </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="4">
-        <f t="shared" si="30"/>
-        <v>15</v>
-      </c>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="39"/>
-      <c r="S35" s="39"/>
-      <c r="T35" s="39"/>
-      <c r="U35" s="39"/>
-      <c r="V35" s="39"/>
-      <c r="W35" s="39"/>
-      <c r="X35" s="39"/>
-      <c r="Y35" s="39"/>
-      <c r="Z35" s="39"/>
-      <c r="AA35" s="39"/>
-      <c r="AB35" s="39"/>
-      <c r="AC35" s="39"/>
-      <c r="AD35" s="39"/>
-      <c r="AE35" s="39"/>
-      <c r="AF35" s="39"/>
-      <c r="AG35" s="39"/>
-      <c r="AH35" s="39"/>
-      <c r="AI35" s="39"/>
-      <c r="AJ35" s="39"/>
-      <c r="AK35" s="39"/>
-      <c r="AL35" s="39"/>
-      <c r="AM35" s="39"/>
-      <c r="AN35" s="39"/>
-      <c r="AO35" s="39"/>
-      <c r="AP35" s="39"/>
-      <c r="AQ35" s="39"/>
-      <c r="AR35" s="39"/>
-      <c r="AS35" s="39"/>
-      <c r="AT35" s="39"/>
-      <c r="AU35" s="39"/>
-      <c r="AV35" s="39"/>
-      <c r="AW35" s="39"/>
-      <c r="AX35" s="39"/>
-      <c r="AY35" s="39"/>
-      <c r="AZ35" s="39"/>
-      <c r="BA35" s="39"/>
-      <c r="BB35" s="39"/>
-      <c r="BC35" s="39"/>
-      <c r="BD35" s="39"/>
-      <c r="BE35" s="39"/>
-      <c r="BF35" s="39"/>
-      <c r="BG35" s="39"/>
-      <c r="BH35" s="39"/>
-      <c r="BI35" s="39"/>
-      <c r="BJ35" s="39"/>
-      <c r="BK35" s="39"/>
-      <c r="BL35" s="39"/>
-      <c r="BM35" s="39"/>
-      <c r="BN35" s="39"/>
-      <c r="BO35" s="39"/>
-      <c r="BP35" s="39"/>
-      <c r="BQ35" s="39"/>
-      <c r="BR35" s="39"/>
-      <c r="BS35" s="39"/>
-      <c r="BT35" s="39"/>
-      <c r="BU35" s="39"/>
-      <c r="BV35" s="39"/>
-      <c r="BW35" s="39"/>
-      <c r="BX35" s="39"/>
-      <c r="BY35" s="39"/>
-      <c r="BZ35" s="39"/>
-      <c r="CA35" s="39"/>
-      <c r="CB35" s="39"/>
-      <c r="CC35" s="39"/>
-      <c r="CD35" s="39"/>
-      <c r="CE35" s="39"/>
-      <c r="CF35" s="39"/>
-      <c r="CG35" s="39"/>
-      <c r="CH35" s="39"/>
-      <c r="CI35" s="39"/>
-      <c r="CJ35" s="39"/>
-      <c r="CK35" s="39"/>
-      <c r="CL35" s="39"/>
-      <c r="CM35" s="39"/>
-      <c r="CN35" s="39"/>
-    </row>
-    <row r="36" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12"/>
-      <c r="B36" s="54" t="s">
-        <v>42</v>
       </c>
       <c r="C36" s="55"/>
       <c r="D36" s="56">
         <v>0.2</v>
       </c>
       <c r="E36" s="99">
-        <f>F35+1</f>
-        <v>46079</v>
+        <f>Project_Start</f>
+        <v>46064</v>
       </c>
       <c r="F36" s="99">
-        <f>F33</f>
-        <v>46130</v>
+        <f>E36+14</f>
+        <v>46078</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="4">
         <f t="shared" si="30"/>
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="I36" s="39"/>
       <c r="J36" s="39"/>
@@ -6362,233 +6361,233 @@
     </row>
     <row r="37" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="55"/>
+      <c r="D37" s="56">
+        <v>0.2</v>
+      </c>
+      <c r="E37" s="99">
+        <f>F36+1</f>
+        <v>46079</v>
+      </c>
+      <c r="F37" s="99">
+        <f>F34</f>
+        <v>46130</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="4">
+        <f t="shared" si="30"/>
+        <v>52</v>
+      </c>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="39"/>
+      <c r="R37" s="39"/>
+      <c r="S37" s="39"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="39"/>
+      <c r="V37" s="39"/>
+      <c r="W37" s="39"/>
+      <c r="X37" s="39"/>
+      <c r="Y37" s="39"/>
+      <c r="Z37" s="39"/>
+      <c r="AA37" s="39"/>
+      <c r="AB37" s="39"/>
+      <c r="AC37" s="39"/>
+      <c r="AD37" s="39"/>
+      <c r="AE37" s="39"/>
+      <c r="AF37" s="39"/>
+      <c r="AG37" s="39"/>
+      <c r="AH37" s="39"/>
+      <c r="AI37" s="39"/>
+      <c r="AJ37" s="39"/>
+      <c r="AK37" s="39"/>
+      <c r="AL37" s="39"/>
+      <c r="AM37" s="39"/>
+      <c r="AN37" s="39"/>
+      <c r="AO37" s="39"/>
+      <c r="AP37" s="39"/>
+      <c r="AQ37" s="39"/>
+      <c r="AR37" s="39"/>
+      <c r="AS37" s="39"/>
+      <c r="AT37" s="39"/>
+      <c r="AU37" s="39"/>
+      <c r="AV37" s="39"/>
+      <c r="AW37" s="39"/>
+      <c r="AX37" s="39"/>
+      <c r="AY37" s="39"/>
+      <c r="AZ37" s="39"/>
+      <c r="BA37" s="39"/>
+      <c r="BB37" s="39"/>
+      <c r="BC37" s="39"/>
+      <c r="BD37" s="39"/>
+      <c r="BE37" s="39"/>
+      <c r="BF37" s="39"/>
+      <c r="BG37" s="39"/>
+      <c r="BH37" s="39"/>
+      <c r="BI37" s="39"/>
+      <c r="BJ37" s="39"/>
+      <c r="BK37" s="39"/>
+      <c r="BL37" s="39"/>
+      <c r="BM37" s="39"/>
+      <c r="BN37" s="39"/>
+      <c r="BO37" s="39"/>
+      <c r="BP37" s="39"/>
+      <c r="BQ37" s="39"/>
+      <c r="BR37" s="39"/>
+      <c r="BS37" s="39"/>
+      <c r="BT37" s="39"/>
+      <c r="BU37" s="39"/>
+      <c r="BV37" s="39"/>
+      <c r="BW37" s="39"/>
+      <c r="BX37" s="39"/>
+      <c r="BY37" s="39"/>
+      <c r="BZ37" s="39"/>
+      <c r="CA37" s="39"/>
+      <c r="CB37" s="39"/>
+      <c r="CC37" s="39"/>
+      <c r="CD37" s="39"/>
+      <c r="CE37" s="39"/>
+      <c r="CF37" s="39"/>
+      <c r="CG37" s="39"/>
+      <c r="CH37" s="39"/>
+      <c r="CI37" s="39"/>
+      <c r="CJ37" s="39"/>
+      <c r="CK37" s="39"/>
+      <c r="CL37" s="39"/>
+      <c r="CM37" s="39"/>
+      <c r="CN37" s="39"/>
+    </row>
+    <row r="38" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="12"/>
+      <c r="B38" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="4" t="str">
+      <c r="C38" s="51"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="98"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="4" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="53"/>
-      <c r="U37" s="53"/>
-      <c r="V37" s="53"/>
-      <c r="W37" s="53"/>
-      <c r="X37" s="53"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="53"/>
-      <c r="AA37" s="53"/>
-      <c r="AB37" s="53"/>
-      <c r="AC37" s="53"/>
-      <c r="AD37" s="53"/>
-      <c r="AE37" s="53"/>
-      <c r="AF37" s="53"/>
-      <c r="AG37" s="53"/>
-      <c r="AH37" s="53"/>
-      <c r="AI37" s="53"/>
-      <c r="AJ37" s="53"/>
-      <c r="AK37" s="53"/>
-      <c r="AL37" s="53"/>
-      <c r="AM37" s="53"/>
-      <c r="AN37" s="53"/>
-      <c r="AO37" s="53"/>
-      <c r="AP37" s="53"/>
-      <c r="AQ37" s="53"/>
-      <c r="AR37" s="53"/>
-      <c r="AS37" s="53"/>
-      <c r="AT37" s="53"/>
-      <c r="AU37" s="53"/>
-      <c r="AV37" s="53"/>
-      <c r="AW37" s="53"/>
-      <c r="AX37" s="53"/>
-      <c r="AY37" s="53"/>
-      <c r="AZ37" s="53"/>
-      <c r="BA37" s="53"/>
-      <c r="BB37" s="53"/>
-      <c r="BC37" s="53"/>
-      <c r="BD37" s="53"/>
-      <c r="BE37" s="53"/>
-      <c r="BF37" s="53"/>
-      <c r="BG37" s="53"/>
-      <c r="BH37" s="53"/>
-      <c r="BI37" s="53"/>
-      <c r="BJ37" s="53"/>
-      <c r="BK37" s="53"/>
-      <c r="BL37" s="53"/>
-      <c r="BM37" s="53"/>
-      <c r="BN37" s="53"/>
-      <c r="BO37" s="53"/>
-      <c r="BP37" s="53"/>
-      <c r="BQ37" s="53"/>
-      <c r="BR37" s="53"/>
-      <c r="BS37" s="53"/>
-      <c r="BT37" s="53"/>
-      <c r="BU37" s="53"/>
-      <c r="BV37" s="53"/>
-      <c r="BW37" s="53"/>
-      <c r="BX37" s="53"/>
-      <c r="BY37" s="53"/>
-      <c r="BZ37" s="53"/>
-      <c r="CA37" s="53"/>
-      <c r="CB37" s="53"/>
-      <c r="CC37" s="53"/>
-      <c r="CD37" s="53"/>
-      <c r="CE37" s="53"/>
-      <c r="CF37" s="53"/>
-      <c r="CG37" s="53"/>
-      <c r="CH37" s="53"/>
-      <c r="CI37" s="53"/>
-      <c r="CJ37" s="53"/>
-      <c r="CK37" s="53"/>
-      <c r="CL37" s="53"/>
-      <c r="CM37" s="53"/>
-      <c r="CN37" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="53"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="53"/>
+      <c r="Q38" s="53"/>
+      <c r="R38" s="53"/>
+      <c r="S38" s="53"/>
+      <c r="T38" s="53"/>
+      <c r="U38" s="53"/>
+      <c r="V38" s="53"/>
+      <c r="W38" s="53"/>
+      <c r="X38" s="53"/>
+      <c r="Y38" s="53"/>
+      <c r="Z38" s="53"/>
+      <c r="AA38" s="53"/>
+      <c r="AB38" s="53"/>
+      <c r="AC38" s="53"/>
+      <c r="AD38" s="53"/>
+      <c r="AE38" s="53"/>
+      <c r="AF38" s="53"/>
+      <c r="AG38" s="53"/>
+      <c r="AH38" s="53"/>
+      <c r="AI38" s="53"/>
+      <c r="AJ38" s="53"/>
+      <c r="AK38" s="53"/>
+      <c r="AL38" s="53"/>
+      <c r="AM38" s="53"/>
+      <c r="AN38" s="53"/>
+      <c r="AO38" s="53"/>
+      <c r="AP38" s="53"/>
+      <c r="AQ38" s="53"/>
+      <c r="AR38" s="53"/>
+      <c r="AS38" s="53"/>
+      <c r="AT38" s="53"/>
+      <c r="AU38" s="53"/>
+      <c r="AV38" s="53"/>
+      <c r="AW38" s="53"/>
+      <c r="AX38" s="53"/>
+      <c r="AY38" s="53"/>
+      <c r="AZ38" s="53"/>
+      <c r="BA38" s="53"/>
+      <c r="BB38" s="53"/>
+      <c r="BC38" s="53"/>
+      <c r="BD38" s="53"/>
+      <c r="BE38" s="53"/>
+      <c r="BF38" s="53"/>
+      <c r="BG38" s="53"/>
+      <c r="BH38" s="53"/>
+      <c r="BI38" s="53"/>
+      <c r="BJ38" s="53"/>
+      <c r="BK38" s="53"/>
+      <c r="BL38" s="53"/>
+      <c r="BM38" s="53"/>
+      <c r="BN38" s="53"/>
+      <c r="BO38" s="53"/>
+      <c r="BP38" s="53"/>
+      <c r="BQ38" s="53"/>
+      <c r="BR38" s="53"/>
+      <c r="BS38" s="53"/>
+      <c r="BT38" s="53"/>
+      <c r="BU38" s="53"/>
+      <c r="BV38" s="53"/>
+      <c r="BW38" s="53"/>
+      <c r="BX38" s="53"/>
+      <c r="BY38" s="53"/>
+      <c r="BZ38" s="53"/>
+      <c r="CA38" s="53"/>
+      <c r="CB38" s="53"/>
+      <c r="CC38" s="53"/>
+      <c r="CD38" s="53"/>
+      <c r="CE38" s="53"/>
+      <c r="CF38" s="53"/>
+      <c r="CG38" s="53"/>
+      <c r="CH38" s="53"/>
+      <c r="CI38" s="53"/>
+      <c r="CJ38" s="53"/>
+      <c r="CK38" s="53"/>
+      <c r="CL38" s="53"/>
+      <c r="CM38" s="53"/>
+      <c r="CN38" s="53"/>
     </row>
-    <row r="38" spans="1:92" s="35" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12"/>
-      <c r="B38" s="109" t="s">
+    <row r="39" spans="1:92" s="35" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="12"/>
+      <c r="B39" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="55"/>
-      <c r="D38" s="56">
+      <c r="C39" s="55"/>
+      <c r="D39" s="56">
         <v>0.9</v>
       </c>
-      <c r="E38" s="99">
+      <c r="E39" s="99">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F38" s="99">
-        <f>E38+21</f>
+      <c r="F39" s="99">
+        <f>E39+21</f>
         <v>46085</v>
       </c>
-      <c r="G38" s="111" t="s">
+      <c r="G39" s="111" t="s">
         <v>64</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H39" s="4">
         <f t="shared" si="30"/>
         <v>22</v>
-      </c>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="39"/>
-      <c r="Q38" s="39"/>
-      <c r="R38" s="39"/>
-      <c r="S38" s="39"/>
-      <c r="T38" s="39"/>
-      <c r="U38" s="39"/>
-      <c r="V38" s="39"/>
-      <c r="W38" s="39"/>
-      <c r="X38" s="39"/>
-      <c r="Y38" s="39"/>
-      <c r="Z38" s="39"/>
-      <c r="AA38" s="39"/>
-      <c r="AB38" s="39"/>
-      <c r="AC38" s="39"/>
-      <c r="AD38" s="39"/>
-      <c r="AE38" s="39"/>
-      <c r="AF38" s="39"/>
-      <c r="AG38" s="39"/>
-      <c r="AH38" s="39"/>
-      <c r="AI38" s="39"/>
-      <c r="AJ38" s="39"/>
-      <c r="AK38" s="39"/>
-      <c r="AL38" s="39"/>
-      <c r="AM38" s="39"/>
-      <c r="AN38" s="39"/>
-      <c r="AO38" s="39"/>
-      <c r="AP38" s="39"/>
-      <c r="AQ38" s="39"/>
-      <c r="AR38" s="39"/>
-      <c r="AS38" s="39"/>
-      <c r="AT38" s="39"/>
-      <c r="AU38" s="39"/>
-      <c r="AV38" s="39"/>
-      <c r="AW38" s="39"/>
-      <c r="AX38" s="39"/>
-      <c r="AY38" s="39"/>
-      <c r="AZ38" s="39"/>
-      <c r="BA38" s="39"/>
-      <c r="BB38" s="39"/>
-      <c r="BC38" s="39"/>
-      <c r="BD38" s="39"/>
-      <c r="BE38" s="39"/>
-      <c r="BF38" s="39"/>
-      <c r="BG38" s="39"/>
-      <c r="BH38" s="39"/>
-      <c r="BI38" s="39"/>
-      <c r="BJ38" s="39"/>
-      <c r="BK38" s="39"/>
-      <c r="BL38" s="39"/>
-      <c r="BM38" s="39"/>
-      <c r="BN38" s="39"/>
-      <c r="BO38" s="39"/>
-      <c r="BP38" s="39"/>
-      <c r="BQ38" s="39"/>
-      <c r="BR38" s="39"/>
-      <c r="BS38" s="39"/>
-      <c r="BT38" s="39"/>
-      <c r="BU38" s="39"/>
-      <c r="BV38" s="39"/>
-      <c r="BW38" s="39"/>
-      <c r="BX38" s="39"/>
-      <c r="BY38" s="39"/>
-      <c r="BZ38" s="39"/>
-      <c r="CA38" s="39"/>
-      <c r="CB38" s="39"/>
-      <c r="CC38" s="39"/>
-      <c r="CD38" s="39"/>
-      <c r="CE38" s="39"/>
-      <c r="CF38" s="39"/>
-      <c r="CG38" s="39"/>
-      <c r="CH38" s="39"/>
-      <c r="CI38" s="39"/>
-      <c r="CJ38" s="39"/>
-      <c r="CK38" s="39"/>
-      <c r="CL38" s="39"/>
-      <c r="CM38" s="39"/>
-      <c r="CN38" s="39"/>
-    </row>
-    <row r="39" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
-      <c r="B39" s="109" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="55"/>
-      <c r="D39" s="56">
-        <v>0.3</v>
-      </c>
-      <c r="E39" s="99">
-        <f>F38</f>
-        <v>46085</v>
-      </c>
-      <c r="F39" s="99">
-        <f>F33</f>
-        <v>46130</v>
-      </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="4">
-        <f t="shared" si="30"/>
-        <v>46</v>
       </c>
       <c r="I39" s="39"/>
       <c r="J39" s="39"/>
@@ -6675,25 +6674,28 @@
       <c r="CM39" s="39"/>
       <c r="CN39" s="39"/>
     </row>
-    <row r="40" spans="1:92" s="35" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="54" t="s">
-        <v>65</v>
+      <c r="B40" s="109" t="s">
+        <v>55</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="56">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E40" s="99">
-        <f>F38</f>
+        <f>F39</f>
         <v>46085</v>
       </c>
       <c r="F40" s="99">
-        <f>F33</f>
+        <f>F34</f>
         <v>46130</v>
       </c>
       <c r="G40" s="14"/>
-      <c r="H40" s="4"/>
+      <c r="H40" s="4">
+        <f t="shared" si="30"/>
+        <v>46</v>
+      </c>
       <c r="I40" s="39"/>
       <c r="J40" s="39"/>
       <c r="K40" s="39"/>
@@ -6779,22 +6781,25 @@
       <c r="CM40" s="39"/>
       <c r="CN40" s="39"/>
     </row>
-    <row r="41" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:92" s="35" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
       <c r="B41" s="54" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C41" s="55"/>
       <c r="D41" s="56">
-        <v>0</v>
-      </c>
-      <c r="E41" s="99"/>
-      <c r="F41" s="99"/>
+        <v>1</v>
+      </c>
+      <c r="E41" s="99">
+        <f>F39</f>
+        <v>46085</v>
+      </c>
+      <c r="F41" s="99">
+        <f>F34</f>
+        <v>46130</v>
+      </c>
       <c r="G41" s="14"/>
-      <c r="H41" s="4" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
+      <c r="H41" s="4"/>
       <c r="I41" s="39"/>
       <c r="J41" s="39"/>
       <c r="K41" s="39"/>
@@ -6882,230 +6887,225 @@
     </row>
     <row r="42" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
-      <c r="B42" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="58"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="100"/>
-      <c r="F42" s="101"/>
+      <c r="B42" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="55"/>
+      <c r="D42" s="56">
+        <v>0</v>
+      </c>
+      <c r="E42" s="99"/>
+      <c r="F42" s="99"/>
       <c r="G42" s="14"/>
       <c r="H42" s="4" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I42" s="60"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="60"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="60"/>
-      <c r="P42" s="60"/>
-      <c r="Q42" s="60"/>
-      <c r="R42" s="60"/>
-      <c r="S42" s="60"/>
-      <c r="T42" s="60"/>
-      <c r="U42" s="60"/>
-      <c r="V42" s="60"/>
-      <c r="W42" s="60"/>
-      <c r="X42" s="60"/>
-      <c r="Y42" s="60"/>
-      <c r="Z42" s="60"/>
-      <c r="AA42" s="60"/>
-      <c r="AB42" s="60"/>
-      <c r="AC42" s="60"/>
-      <c r="AD42" s="60"/>
-      <c r="AE42" s="60"/>
-      <c r="AF42" s="60"/>
-      <c r="AG42" s="60"/>
-      <c r="AH42" s="60"/>
-      <c r="AI42" s="60"/>
-      <c r="AJ42" s="60"/>
-      <c r="AK42" s="60"/>
-      <c r="AL42" s="60"/>
-      <c r="AM42" s="60"/>
-      <c r="AN42" s="60"/>
-      <c r="AO42" s="60"/>
-      <c r="AP42" s="60"/>
-      <c r="AQ42" s="60"/>
-      <c r="AR42" s="60"/>
-      <c r="AS42" s="60"/>
-      <c r="AT42" s="60"/>
-      <c r="AU42" s="60"/>
-      <c r="AV42" s="60"/>
-      <c r="AW42" s="60"/>
-      <c r="AX42" s="60"/>
-      <c r="AY42" s="60"/>
-      <c r="AZ42" s="60"/>
-      <c r="BA42" s="60"/>
-      <c r="BB42" s="60"/>
-      <c r="BC42" s="60"/>
-      <c r="BD42" s="60"/>
-      <c r="BE42" s="60"/>
-      <c r="BF42" s="60"/>
-      <c r="BG42" s="60"/>
-      <c r="BH42" s="60"/>
-      <c r="BI42" s="60"/>
-      <c r="BJ42" s="60"/>
-      <c r="BK42" s="60"/>
-      <c r="BL42" s="60"/>
-      <c r="BM42" s="60"/>
-      <c r="BN42" s="60"/>
-      <c r="BO42" s="60"/>
-      <c r="BP42" s="60"/>
-      <c r="BQ42" s="60"/>
-      <c r="BR42" s="60"/>
-      <c r="BS42" s="60"/>
-      <c r="BT42" s="60"/>
-      <c r="BU42" s="60"/>
-      <c r="BV42" s="60"/>
-      <c r="BW42" s="60"/>
-      <c r="BX42" s="60"/>
-      <c r="BY42" s="60"/>
-      <c r="BZ42" s="60"/>
-      <c r="CA42" s="60"/>
-      <c r="CB42" s="60"/>
-      <c r="CC42" s="60"/>
-      <c r="CD42" s="60"/>
-      <c r="CE42" s="60"/>
-      <c r="CF42" s="60"/>
-      <c r="CG42" s="60"/>
-      <c r="CH42" s="60"/>
-      <c r="CI42" s="60"/>
-      <c r="CJ42" s="60"/>
-      <c r="CK42" s="60"/>
-      <c r="CL42" s="60"/>
-      <c r="CM42" s="60"/>
-      <c r="CN42" s="60"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
+      <c r="R42" s="39"/>
+      <c r="S42" s="39"/>
+      <c r="T42" s="39"/>
+      <c r="U42" s="39"/>
+      <c r="V42" s="39"/>
+      <c r="W42" s="39"/>
+      <c r="X42" s="39"/>
+      <c r="Y42" s="39"/>
+      <c r="Z42" s="39"/>
+      <c r="AA42" s="39"/>
+      <c r="AB42" s="39"/>
+      <c r="AC42" s="39"/>
+      <c r="AD42" s="39"/>
+      <c r="AE42" s="39"/>
+      <c r="AF42" s="39"/>
+      <c r="AG42" s="39"/>
+      <c r="AH42" s="39"/>
+      <c r="AI42" s="39"/>
+      <c r="AJ42" s="39"/>
+      <c r="AK42" s="39"/>
+      <c r="AL42" s="39"/>
+      <c r="AM42" s="39"/>
+      <c r="AN42" s="39"/>
+      <c r="AO42" s="39"/>
+      <c r="AP42" s="39"/>
+      <c r="AQ42" s="39"/>
+      <c r="AR42" s="39"/>
+      <c r="AS42" s="39"/>
+      <c r="AT42" s="39"/>
+      <c r="AU42" s="39"/>
+      <c r="AV42" s="39"/>
+      <c r="AW42" s="39"/>
+      <c r="AX42" s="39"/>
+      <c r="AY42" s="39"/>
+      <c r="AZ42" s="39"/>
+      <c r="BA42" s="39"/>
+      <c r="BB42" s="39"/>
+      <c r="BC42" s="39"/>
+      <c r="BD42" s="39"/>
+      <c r="BE42" s="39"/>
+      <c r="BF42" s="39"/>
+      <c r="BG42" s="39"/>
+      <c r="BH42" s="39"/>
+      <c r="BI42" s="39"/>
+      <c r="BJ42" s="39"/>
+      <c r="BK42" s="39"/>
+      <c r="BL42" s="39"/>
+      <c r="BM42" s="39"/>
+      <c r="BN42" s="39"/>
+      <c r="BO42" s="39"/>
+      <c r="BP42" s="39"/>
+      <c r="BQ42" s="39"/>
+      <c r="BR42" s="39"/>
+      <c r="BS42" s="39"/>
+      <c r="BT42" s="39"/>
+      <c r="BU42" s="39"/>
+      <c r="BV42" s="39"/>
+      <c r="BW42" s="39"/>
+      <c r="BX42" s="39"/>
+      <c r="BY42" s="39"/>
+      <c r="BZ42" s="39"/>
+      <c r="CA42" s="39"/>
+      <c r="CB42" s="39"/>
+      <c r="CC42" s="39"/>
+      <c r="CD42" s="39"/>
+      <c r="CE42" s="39"/>
+      <c r="CF42" s="39"/>
+      <c r="CG42" s="39"/>
+      <c r="CH42" s="39"/>
+      <c r="CI42" s="39"/>
+      <c r="CJ42" s="39"/>
+      <c r="CK42" s="39"/>
+      <c r="CL42" s="39"/>
+      <c r="CM42" s="39"/>
+      <c r="CN42" s="39"/>
     </row>
     <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>
-      <c r="B43" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="63">
-        <v>1</v>
-      </c>
-      <c r="E43" s="102">
-        <f>E35</f>
-        <v>46064</v>
-      </c>
-      <c r="F43" s="102">
-        <f>E47-3</f>
-        <v>46157</v>
-      </c>
+      <c r="B43" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="58"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="100"/>
+      <c r="F43" s="101"/>
       <c r="G43" s="14"/>
-      <c r="H43" s="4">
+      <c r="H43" s="4" t="str">
         <f t="shared" si="30"/>
-        <v>94</v>
-      </c>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="39"/>
-      <c r="Q43" s="39"/>
-      <c r="R43" s="39"/>
-      <c r="S43" s="39"/>
-      <c r="T43" s="39"/>
-      <c r="U43" s="39"/>
-      <c r="V43" s="39"/>
-      <c r="W43" s="39"/>
-      <c r="X43" s="39"/>
-      <c r="Y43" s="39"/>
-      <c r="Z43" s="39"/>
-      <c r="AA43" s="39"/>
-      <c r="AB43" s="39"/>
-      <c r="AC43" s="39"/>
-      <c r="AD43" s="39"/>
-      <c r="AE43" s="39"/>
-      <c r="AF43" s="39"/>
-      <c r="AG43" s="39"/>
-      <c r="AH43" s="39"/>
-      <c r="AI43" s="39"/>
-      <c r="AJ43" s="39"/>
-      <c r="AK43" s="39"/>
-      <c r="AL43" s="39"/>
-      <c r="AM43" s="39"/>
-      <c r="AN43" s="39"/>
-      <c r="AO43" s="39"/>
-      <c r="AP43" s="39"/>
-      <c r="AQ43" s="39"/>
-      <c r="AR43" s="39"/>
-      <c r="AS43" s="39"/>
-      <c r="AT43" s="39"/>
-      <c r="AU43" s="39"/>
-      <c r="AV43" s="39"/>
-      <c r="AW43" s="39"/>
-      <c r="AX43" s="39"/>
-      <c r="AY43" s="39"/>
-      <c r="AZ43" s="39"/>
-      <c r="BA43" s="39"/>
-      <c r="BB43" s="39"/>
-      <c r="BC43" s="39"/>
-      <c r="BD43" s="39"/>
-      <c r="BE43" s="39"/>
-      <c r="BF43" s="39"/>
-      <c r="BG43" s="39"/>
-      <c r="BH43" s="39"/>
-      <c r="BI43" s="39"/>
-      <c r="BJ43" s="39"/>
-      <c r="BK43" s="39"/>
-      <c r="BL43" s="39"/>
-      <c r="BM43" s="39"/>
-      <c r="BN43" s="39"/>
-      <c r="BO43" s="39"/>
-      <c r="BP43" s="39"/>
-      <c r="BQ43" s="39"/>
-      <c r="BR43" s="39"/>
-      <c r="BS43" s="39"/>
-      <c r="BT43" s="39"/>
-      <c r="BU43" s="39"/>
-      <c r="BV43" s="39"/>
-      <c r="BW43" s="39"/>
-      <c r="BX43" s="39"/>
-      <c r="BY43" s="39"/>
-      <c r="BZ43" s="39"/>
-      <c r="CA43" s="39"/>
-      <c r="CB43" s="39"/>
-      <c r="CC43" s="39"/>
-      <c r="CD43" s="39"/>
-      <c r="CE43" s="39"/>
-      <c r="CF43" s="39"/>
-      <c r="CG43" s="39"/>
-      <c r="CH43" s="39"/>
-      <c r="CI43" s="39"/>
-      <c r="CJ43" s="39"/>
-      <c r="CK43" s="39"/>
-      <c r="CL43" s="39"/>
-      <c r="CM43" s="39"/>
-      <c r="CN43" s="39"/>
+        <v/>
+      </c>
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
+      <c r="L43" s="60"/>
+      <c r="M43" s="60"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="60"/>
+      <c r="P43" s="60"/>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="60"/>
+      <c r="S43" s="60"/>
+      <c r="T43" s="60"/>
+      <c r="U43" s="60"/>
+      <c r="V43" s="60"/>
+      <c r="W43" s="60"/>
+      <c r="X43" s="60"/>
+      <c r="Y43" s="60"/>
+      <c r="Z43" s="60"/>
+      <c r="AA43" s="60"/>
+      <c r="AB43" s="60"/>
+      <c r="AC43" s="60"/>
+      <c r="AD43" s="60"/>
+      <c r="AE43" s="60"/>
+      <c r="AF43" s="60"/>
+      <c r="AG43" s="60"/>
+      <c r="AH43" s="60"/>
+      <c r="AI43" s="60"/>
+      <c r="AJ43" s="60"/>
+      <c r="AK43" s="60"/>
+      <c r="AL43" s="60"/>
+      <c r="AM43" s="60"/>
+      <c r="AN43" s="60"/>
+      <c r="AO43" s="60"/>
+      <c r="AP43" s="60"/>
+      <c r="AQ43" s="60"/>
+      <c r="AR43" s="60"/>
+      <c r="AS43" s="60"/>
+      <c r="AT43" s="60"/>
+      <c r="AU43" s="60"/>
+      <c r="AV43" s="60"/>
+      <c r="AW43" s="60"/>
+      <c r="AX43" s="60"/>
+      <c r="AY43" s="60"/>
+      <c r="AZ43" s="60"/>
+      <c r="BA43" s="60"/>
+      <c r="BB43" s="60"/>
+      <c r="BC43" s="60"/>
+      <c r="BD43" s="60"/>
+      <c r="BE43" s="60"/>
+      <c r="BF43" s="60"/>
+      <c r="BG43" s="60"/>
+      <c r="BH43" s="60"/>
+      <c r="BI43" s="60"/>
+      <c r="BJ43" s="60"/>
+      <c r="BK43" s="60"/>
+      <c r="BL43" s="60"/>
+      <c r="BM43" s="60"/>
+      <c r="BN43" s="60"/>
+      <c r="BO43" s="60"/>
+      <c r="BP43" s="60"/>
+      <c r="BQ43" s="60"/>
+      <c r="BR43" s="60"/>
+      <c r="BS43" s="60"/>
+      <c r="BT43" s="60"/>
+      <c r="BU43" s="60"/>
+      <c r="BV43" s="60"/>
+      <c r="BW43" s="60"/>
+      <c r="BX43" s="60"/>
+      <c r="BY43" s="60"/>
+      <c r="BZ43" s="60"/>
+      <c r="CA43" s="60"/>
+      <c r="CB43" s="60"/>
+      <c r="CC43" s="60"/>
+      <c r="CD43" s="60"/>
+      <c r="CE43" s="60"/>
+      <c r="CF43" s="60"/>
+      <c r="CG43" s="60"/>
+      <c r="CH43" s="60"/>
+      <c r="CI43" s="60"/>
+      <c r="CJ43" s="60"/>
+      <c r="CK43" s="60"/>
+      <c r="CL43" s="60"/>
+      <c r="CM43" s="60"/>
+      <c r="CN43" s="60"/>
     </row>
     <row r="44" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="61" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C44" s="62"/>
       <c r="D44" s="63">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E44" s="102">
-        <v>46146</v>
+        <f>E36</f>
+        <v>46064</v>
       </c>
       <c r="F44" s="102">
-        <f>E44+7</f>
-        <v>46153</v>
+        <f>E48-3</f>
+        <v>46157</v>
       </c>
       <c r="G44" s="14"/>
       <c r="H44" s="4">
         <f t="shared" si="30"/>
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="I44" s="39"/>
       <c r="J44" s="39"/>
@@ -7195,11 +7195,11 @@
     <row r="45" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
       <c r="B45" s="61" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C45" s="62"/>
       <c r="D45" s="63">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E45" s="102">
         <v>46146</v>
@@ -7301,19 +7301,18 @@
     <row r="46" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
       <c r="B46" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="63">
         <v>0</v>
       </c>
       <c r="E46" s="102">
-        <f>F45</f>
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="F46" s="102">
         <f>E46+7</f>
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="G46" s="14"/>
       <c r="H46" s="4">
@@ -7408,7 +7407,7 @@
     <row r="47" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
       <c r="B47" s="61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="62"/>
       <c r="D47" s="63">
@@ -7416,11 +7415,11 @@
       </c>
       <c r="E47" s="102">
         <f>F46</f>
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="F47" s="102">
         <f>E47+7</f>
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="4">
@@ -7515,7 +7514,7 @@
     <row r="48" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
       <c r="B48" s="61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="62"/>
       <c r="D48" s="63">
@@ -7523,16 +7522,16 @@
       </c>
       <c r="E48" s="102">
         <f>F47</f>
+        <v>46160</v>
+      </c>
+      <c r="F48" s="102">
+        <f>E48+7</f>
         <v>46167</v>
-      </c>
-      <c r="F48" s="102">
-        <f>E48+14</f>
-        <v>46181</v>
       </c>
       <c r="G48" s="14"/>
       <c r="H48" s="4">
         <f t="shared" si="30"/>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I48" s="39"/>
       <c r="J48" s="39"/>
@@ -7621,220 +7620,321 @@
     </row>
     <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>
-      <c r="B49" s="64" t="s">
+      <c r="B49" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="62"/>
+      <c r="D49" s="63">
+        <v>0</v>
+      </c>
+      <c r="E49" s="102">
+        <f>F48</f>
+        <v>46167</v>
+      </c>
+      <c r="F49" s="102">
+        <f>E49+14</f>
+        <v>46181</v>
+      </c>
+      <c r="G49" s="14"/>
+      <c r="H49" s="4">
+        <f t="shared" si="30"/>
+        <v>15</v>
+      </c>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="39"/>
+      <c r="L49" s="39"/>
+      <c r="M49" s="39"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+      <c r="Q49" s="39"/>
+      <c r="R49" s="39"/>
+      <c r="S49" s="39"/>
+      <c r="T49" s="39"/>
+      <c r="U49" s="39"/>
+      <c r="V49" s="39"/>
+      <c r="W49" s="39"/>
+      <c r="X49" s="39"/>
+      <c r="Y49" s="39"/>
+      <c r="Z49" s="39"/>
+      <c r="AA49" s="39"/>
+      <c r="AB49" s="39"/>
+      <c r="AC49" s="39"/>
+      <c r="AD49" s="39"/>
+      <c r="AE49" s="39"/>
+      <c r="AF49" s="39"/>
+      <c r="AG49" s="39"/>
+      <c r="AH49" s="39"/>
+      <c r="AI49" s="39"/>
+      <c r="AJ49" s="39"/>
+      <c r="AK49" s="39"/>
+      <c r="AL49" s="39"/>
+      <c r="AM49" s="39"/>
+      <c r="AN49" s="39"/>
+      <c r="AO49" s="39"/>
+      <c r="AP49" s="39"/>
+      <c r="AQ49" s="39"/>
+      <c r="AR49" s="39"/>
+      <c r="AS49" s="39"/>
+      <c r="AT49" s="39"/>
+      <c r="AU49" s="39"/>
+      <c r="AV49" s="39"/>
+      <c r="AW49" s="39"/>
+      <c r="AX49" s="39"/>
+      <c r="AY49" s="39"/>
+      <c r="AZ49" s="39"/>
+      <c r="BA49" s="39"/>
+      <c r="BB49" s="39"/>
+      <c r="BC49" s="39"/>
+      <c r="BD49" s="39"/>
+      <c r="BE49" s="39"/>
+      <c r="BF49" s="39"/>
+      <c r="BG49" s="39"/>
+      <c r="BH49" s="39"/>
+      <c r="BI49" s="39"/>
+      <c r="BJ49" s="39"/>
+      <c r="BK49" s="39"/>
+      <c r="BL49" s="39"/>
+      <c r="BM49" s="39"/>
+      <c r="BN49" s="39"/>
+      <c r="BO49" s="39"/>
+      <c r="BP49" s="39"/>
+      <c r="BQ49" s="39"/>
+      <c r="BR49" s="39"/>
+      <c r="BS49" s="39"/>
+      <c r="BT49" s="39"/>
+      <c r="BU49" s="39"/>
+      <c r="BV49" s="39"/>
+      <c r="BW49" s="39"/>
+      <c r="BX49" s="39"/>
+      <c r="BY49" s="39"/>
+      <c r="BZ49" s="39"/>
+      <c r="CA49" s="39"/>
+      <c r="CB49" s="39"/>
+      <c r="CC49" s="39"/>
+      <c r="CD49" s="39"/>
+      <c r="CE49" s="39"/>
+      <c r="CF49" s="39"/>
+      <c r="CG49" s="39"/>
+      <c r="CH49" s="39"/>
+      <c r="CI49" s="39"/>
+      <c r="CJ49" s="39"/>
+      <c r="CK49" s="39"/>
+      <c r="CL49" s="39"/>
+      <c r="CM49" s="39"/>
+      <c r="CN49" s="39"/>
+    </row>
+    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="12"/>
+      <c r="B50" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="65"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="4" t="str">
+      <c r="C50" s="65"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="4" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="34"/>
-      <c r="N49" s="34"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
-      <c r="Q49" s="34"/>
-      <c r="R49" s="34"/>
-      <c r="S49" s="34"/>
-      <c r="T49" s="34"/>
-      <c r="U49" s="34"/>
-      <c r="V49" s="34"/>
-      <c r="W49" s="34"/>
-      <c r="X49" s="34"/>
-      <c r="Y49" s="34"/>
-      <c r="Z49" s="34"/>
-      <c r="AA49" s="34"/>
-      <c r="AB49" s="34"/>
-      <c r="AC49" s="34"/>
-      <c r="AD49" s="34"/>
-      <c r="AE49" s="34"/>
-      <c r="AF49" s="34"/>
-      <c r="AG49" s="34"/>
-      <c r="AH49" s="34"/>
-      <c r="AI49" s="34"/>
-      <c r="AJ49" s="34"/>
-      <c r="AK49" s="34"/>
-      <c r="AL49" s="34"/>
-      <c r="AM49" s="34"/>
-      <c r="AN49" s="34"/>
-      <c r="AO49" s="34"/>
-      <c r="AP49" s="34"/>
-      <c r="AQ49" s="34"/>
-      <c r="AR49" s="34"/>
-      <c r="AS49" s="34"/>
-      <c r="AT49" s="34"/>
-      <c r="AU49" s="34"/>
-      <c r="AV49" s="34"/>
-      <c r="AW49" s="34"/>
-      <c r="AX49" s="34"/>
-      <c r="AY49" s="34"/>
-      <c r="AZ49" s="34"/>
-      <c r="BA49" s="34"/>
-      <c r="BB49" s="34"/>
-      <c r="BC49" s="34"/>
-      <c r="BD49" s="34"/>
-      <c r="BE49" s="34"/>
-      <c r="BF49" s="34"/>
-      <c r="BG49" s="34"/>
-      <c r="BH49" s="34"/>
-      <c r="BI49" s="34"/>
-      <c r="BJ49" s="34"/>
-      <c r="BK49" s="34"/>
-      <c r="BL49" s="34"/>
-      <c r="BM49" s="34"/>
-      <c r="BN49" s="34"/>
-      <c r="BO49" s="34"/>
-      <c r="BP49" s="34"/>
-      <c r="BQ49" s="34"/>
-      <c r="BR49" s="34"/>
-      <c r="BS49" s="34"/>
-      <c r="BT49" s="34"/>
-      <c r="BU49" s="34"/>
-      <c r="BV49" s="34"/>
-      <c r="BW49" s="34"/>
-      <c r="BX49" s="34"/>
-      <c r="BY49" s="34"/>
-      <c r="BZ49" s="34"/>
-      <c r="CA49" s="34"/>
-      <c r="CB49" s="34"/>
-      <c r="CC49" s="34"/>
-      <c r="CD49" s="34"/>
-      <c r="CE49" s="34"/>
-      <c r="CF49" s="34"/>
-      <c r="CG49" s="34"/>
-      <c r="CH49" s="34"/>
-      <c r="CI49" s="34"/>
-      <c r="CJ49" s="34"/>
-      <c r="CK49" s="34"/>
-      <c r="CL49" s="34"/>
-      <c r="CM49" s="34"/>
-      <c r="CN49" s="34"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="34"/>
+      <c r="M50" s="34"/>
+      <c r="N50" s="34"/>
+      <c r="O50" s="34"/>
+      <c r="P50" s="34"/>
+      <c r="Q50" s="34"/>
+      <c r="R50" s="34"/>
+      <c r="S50" s="34"/>
+      <c r="T50" s="34"/>
+      <c r="U50" s="34"/>
+      <c r="V50" s="34"/>
+      <c r="W50" s="34"/>
+      <c r="X50" s="34"/>
+      <c r="Y50" s="34"/>
+      <c r="Z50" s="34"/>
+      <c r="AA50" s="34"/>
+      <c r="AB50" s="34"/>
+      <c r="AC50" s="34"/>
+      <c r="AD50" s="34"/>
+      <c r="AE50" s="34"/>
+      <c r="AF50" s="34"/>
+      <c r="AG50" s="34"/>
+      <c r="AH50" s="34"/>
+      <c r="AI50" s="34"/>
+      <c r="AJ50" s="34"/>
+      <c r="AK50" s="34"/>
+      <c r="AL50" s="34"/>
+      <c r="AM50" s="34"/>
+      <c r="AN50" s="34"/>
+      <c r="AO50" s="34"/>
+      <c r="AP50" s="34"/>
+      <c r="AQ50" s="34"/>
+      <c r="AR50" s="34"/>
+      <c r="AS50" s="34"/>
+      <c r="AT50" s="34"/>
+      <c r="AU50" s="34"/>
+      <c r="AV50" s="34"/>
+      <c r="AW50" s="34"/>
+      <c r="AX50" s="34"/>
+      <c r="AY50" s="34"/>
+      <c r="AZ50" s="34"/>
+      <c r="BA50" s="34"/>
+      <c r="BB50" s="34"/>
+      <c r="BC50" s="34"/>
+      <c r="BD50" s="34"/>
+      <c r="BE50" s="34"/>
+      <c r="BF50" s="34"/>
+      <c r="BG50" s="34"/>
+      <c r="BH50" s="34"/>
+      <c r="BI50" s="34"/>
+      <c r="BJ50" s="34"/>
+      <c r="BK50" s="34"/>
+      <c r="BL50" s="34"/>
+      <c r="BM50" s="34"/>
+      <c r="BN50" s="34"/>
+      <c r="BO50" s="34"/>
+      <c r="BP50" s="34"/>
+      <c r="BQ50" s="34"/>
+      <c r="BR50" s="34"/>
+      <c r="BS50" s="34"/>
+      <c r="BT50" s="34"/>
+      <c r="BU50" s="34"/>
+      <c r="BV50" s="34"/>
+      <c r="BW50" s="34"/>
+      <c r="BX50" s="34"/>
+      <c r="BY50" s="34"/>
+      <c r="BZ50" s="34"/>
+      <c r="CA50" s="34"/>
+      <c r="CB50" s="34"/>
+      <c r="CC50" s="34"/>
+      <c r="CD50" s="34"/>
+      <c r="CE50" s="34"/>
+      <c r="CF50" s="34"/>
+      <c r="CG50" s="34"/>
+      <c r="CH50" s="34"/>
+      <c r="CI50" s="34"/>
+      <c r="CJ50" s="34"/>
+      <c r="CK50" s="34"/>
+      <c r="CL50" s="34"/>
+      <c r="CM50" s="34"/>
+      <c r="CN50" s="34"/>
     </row>
-    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="81"/>
-      <c r="B50" s="67" t="s">
+    <row r="51" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="81"/>
+      <c r="B51" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="68"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="5" t="str">
+      <c r="C51" s="68"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="105"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="5" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I50" s="70"/>
-      <c r="J50" s="70"/>
-      <c r="K50" s="70"/>
-      <c r="L50" s="70"/>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
-      <c r="O50" s="70"/>
-      <c r="P50" s="70"/>
-      <c r="Q50" s="70"/>
-      <c r="R50" s="70"/>
-      <c r="S50" s="70"/>
-      <c r="T50" s="70"/>
-      <c r="U50" s="70"/>
-      <c r="V50" s="70"/>
-      <c r="W50" s="70"/>
-      <c r="X50" s="70"/>
-      <c r="Y50" s="70"/>
-      <c r="Z50" s="70"/>
-      <c r="AA50" s="70"/>
-      <c r="AB50" s="70"/>
-      <c r="AC50" s="70"/>
-      <c r="AD50" s="70"/>
-      <c r="AE50" s="70"/>
-      <c r="AF50" s="70"/>
-      <c r="AG50" s="70"/>
-      <c r="AH50" s="70"/>
-      <c r="AI50" s="70"/>
-      <c r="AJ50" s="70"/>
-      <c r="AK50" s="70"/>
-      <c r="AL50" s="70"/>
-      <c r="AM50" s="70"/>
-      <c r="AN50" s="70"/>
-      <c r="AO50" s="70"/>
-      <c r="AP50" s="70"/>
-      <c r="AQ50" s="70"/>
-      <c r="AR50" s="70"/>
-      <c r="AS50" s="70"/>
-      <c r="AT50" s="70"/>
-      <c r="AU50" s="70"/>
-      <c r="AV50" s="70"/>
-      <c r="AW50" s="70"/>
-      <c r="AX50" s="70"/>
-      <c r="AY50" s="70"/>
-      <c r="AZ50" s="70"/>
-      <c r="BA50" s="70"/>
-      <c r="BB50" s="70"/>
-      <c r="BC50" s="70"/>
-      <c r="BD50" s="70"/>
-      <c r="BE50" s="70"/>
-      <c r="BF50" s="70"/>
-      <c r="BG50" s="70"/>
-      <c r="BH50" s="70"/>
-      <c r="BI50" s="70"/>
-      <c r="BJ50" s="70"/>
-      <c r="BK50" s="70"/>
-      <c r="BL50" s="70"/>
-      <c r="BM50" s="70"/>
-      <c r="BN50" s="70"/>
-      <c r="BO50" s="70"/>
-      <c r="BP50" s="70"/>
-      <c r="BQ50" s="70"/>
-      <c r="BR50" s="70"/>
-      <c r="BS50" s="70"/>
-      <c r="BT50" s="70"/>
-      <c r="BU50" s="70"/>
-      <c r="BV50" s="70"/>
-      <c r="BW50" s="70"/>
-      <c r="BX50" s="70"/>
-      <c r="BY50" s="70"/>
-      <c r="BZ50" s="70"/>
-      <c r="CA50" s="70"/>
-      <c r="CB50" s="70"/>
-      <c r="CC50" s="70"/>
-      <c r="CD50" s="70"/>
-      <c r="CE50" s="70"/>
-      <c r="CF50" s="70"/>
-      <c r="CG50" s="70"/>
-      <c r="CH50" s="70"/>
-      <c r="CI50" s="70"/>
-      <c r="CJ50" s="70"/>
-      <c r="CK50" s="70"/>
-      <c r="CL50" s="70"/>
-      <c r="CM50" s="70"/>
-      <c r="CN50" s="70"/>
-    </row>
-    <row r="51" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G51" s="2"/>
+      <c r="I51" s="70"/>
+      <c r="J51" s="70"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="70"/>
+      <c r="M51" s="70"/>
+      <c r="N51" s="70"/>
+      <c r="O51" s="70"/>
+      <c r="P51" s="70"/>
+      <c r="Q51" s="70"/>
+      <c r="R51" s="70"/>
+      <c r="S51" s="70"/>
+      <c r="T51" s="70"/>
+      <c r="U51" s="70"/>
+      <c r="V51" s="70"/>
+      <c r="W51" s="70"/>
+      <c r="X51" s="70"/>
+      <c r="Y51" s="70"/>
+      <c r="Z51" s="70"/>
+      <c r="AA51" s="70"/>
+      <c r="AB51" s="70"/>
+      <c r="AC51" s="70"/>
+      <c r="AD51" s="70"/>
+      <c r="AE51" s="70"/>
+      <c r="AF51" s="70"/>
+      <c r="AG51" s="70"/>
+      <c r="AH51" s="70"/>
+      <c r="AI51" s="70"/>
+      <c r="AJ51" s="70"/>
+      <c r="AK51" s="70"/>
+      <c r="AL51" s="70"/>
+      <c r="AM51" s="70"/>
+      <c r="AN51" s="70"/>
+      <c r="AO51" s="70"/>
+      <c r="AP51" s="70"/>
+      <c r="AQ51" s="70"/>
+      <c r="AR51" s="70"/>
+      <c r="AS51" s="70"/>
+      <c r="AT51" s="70"/>
+      <c r="AU51" s="70"/>
+      <c r="AV51" s="70"/>
+      <c r="AW51" s="70"/>
+      <c r="AX51" s="70"/>
+      <c r="AY51" s="70"/>
+      <c r="AZ51" s="70"/>
+      <c r="BA51" s="70"/>
+      <c r="BB51" s="70"/>
+      <c r="BC51" s="70"/>
+      <c r="BD51" s="70"/>
+      <c r="BE51" s="70"/>
+      <c r="BF51" s="70"/>
+      <c r="BG51" s="70"/>
+      <c r="BH51" s="70"/>
+      <c r="BI51" s="70"/>
+      <c r="BJ51" s="70"/>
+      <c r="BK51" s="70"/>
+      <c r="BL51" s="70"/>
+      <c r="BM51" s="70"/>
+      <c r="BN51" s="70"/>
+      <c r="BO51" s="70"/>
+      <c r="BP51" s="70"/>
+      <c r="BQ51" s="70"/>
+      <c r="BR51" s="70"/>
+      <c r="BS51" s="70"/>
+      <c r="BT51" s="70"/>
+      <c r="BU51" s="70"/>
+      <c r="BV51" s="70"/>
+      <c r="BW51" s="70"/>
+      <c r="BX51" s="70"/>
+      <c r="BY51" s="70"/>
+      <c r="BZ51" s="70"/>
+      <c r="CA51" s="70"/>
+      <c r="CB51" s="70"/>
+      <c r="CC51" s="70"/>
+      <c r="CD51" s="70"/>
+      <c r="CE51" s="70"/>
+      <c r="CF51" s="70"/>
+      <c r="CG51" s="70"/>
+      <c r="CH51" s="70"/>
+      <c r="CI51" s="70"/>
+      <c r="CJ51" s="70"/>
+      <c r="CK51" s="70"/>
+      <c r="CL51" s="70"/>
+      <c r="CM51" s="70"/>
+      <c r="CN51" s="70"/>
     </row>
     <row r="52" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C52" s="13"/>
-      <c r="F52" s="108"/>
+      <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C53" s="3"/>
+      <c r="C53" s="13"/>
+      <c r="F53" s="108"/>
+    </row>
+    <row r="54" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C54" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -7851,8 +7951,14 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:D50">
+  <conditionalFormatting sqref="D7:D51">
     <cfRule type="dataBar" priority="102">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -7866,22 +7972,22 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:BK31 I32:BM33">
+  <conditionalFormatting sqref="I24:BK31 I32:BM34">
     <cfRule type="expression" dxfId="44" priority="84" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33:BK44 I4:BK8 I9:BZ10 BL14 I14:BK16 I19:BK21 I23:BK31 I32:BM32 BL33:BM33 BL36 BL40:BZ40 BL43:CA43 BL44:BM44 I45:BM45 I47:BK48">
+  <conditionalFormatting sqref="I34:BK45 I4:BK8 I9:BZ10 BL14 I14:BK16 I19:BK21 I23:BK31 BL34:BM34 BL37 BL41:BZ41 BL44:CA44 BL45:BM45 I46:BM46 I48:BK49 I32:BM33">
     <cfRule type="expression" dxfId="43" priority="80">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I35:BK36 BL36 I39:BK41 BL40:BZ40">
+  <conditionalFormatting sqref="I36:BK37 BL37 I40:BK42 BL41:BZ41">
     <cfRule type="expression" dxfId="42" priority="82" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I38:BK38">
+  <conditionalFormatting sqref="I39:BK39">
     <cfRule type="expression" dxfId="41" priority="22" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
@@ -7896,50 +8002,50 @@
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:CN33">
+  <conditionalFormatting sqref="I24:CN34">
     <cfRule type="expression" dxfId="38" priority="26">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I35:CN36">
+  <conditionalFormatting sqref="I36:CN37">
     <cfRule type="expression" dxfId="37" priority="24">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I38:CN41">
+  <conditionalFormatting sqref="I39:CN42">
     <cfRule type="expression" dxfId="36" priority="15">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL24:BL31 BS24:BS31 BZ24:BZ32 CG24:CG33 CN24:CN33 BS33">
+  <conditionalFormatting sqref="BL24:BL31 BS24:BS31 BZ24:BZ32 CG24:CG34 CN24:CN34 BS33:BS34">
     <cfRule type="expression" dxfId="35" priority="121" stopIfTrue="1">
       <formula>AND(task_end&gt;=BL$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL35 BS35 BZ35 CG35:CG36 CN35:CN36 BL38 BS38 BZ38 CG38:CG41 CN38:CN41 BL41 BS41 BZ41">
+  <conditionalFormatting sqref="BL36 BS36 BZ36 CG36:CG37 CN36:CN37 BL39 BS39 BZ39 CG39:CG42 CN39:CN42 BL42 BS42 BZ42">
     <cfRule type="expression" dxfId="34" priority="123" stopIfTrue="1">
       <formula>AND(task_end&gt;=BL$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL43:CA43 I43:BK44 BL44:BM44 I45:BM45 I47:BK48">
-    <cfRule type="expression" dxfId="33" priority="116" stopIfTrue="1">
+  <conditionalFormatting sqref="BL44:CA44 I44:BK45 BL45:BM45 I46:BM46 I48:BK49">
+    <cfRule type="expression" dxfId="33" priority="115">
+      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="116" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="115">
-      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM24:BR31 BN32:BS33">
+  <conditionalFormatting sqref="BM24:BR31 BN32:BS34">
     <cfRule type="expression" dxfId="31" priority="45" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM35:BR36 BM41:BR41">
+  <conditionalFormatting sqref="BM36:BR37 BM42:BR42">
     <cfRule type="expression" dxfId="30" priority="43" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM38:BR38">
+  <conditionalFormatting sqref="BM39:BR39">
     <cfRule type="expression" dxfId="29" priority="20" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
@@ -7949,40 +8055,40 @@
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN44:BT45 I46:BT46">
-    <cfRule type="expression" dxfId="27" priority="49" stopIfTrue="1">
+  <conditionalFormatting sqref="BN45:BT46 I47:BT47">
+    <cfRule type="expression" dxfId="27" priority="48">
+      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="49" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="48">
-      <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BS14:BS15 BS33:BS35 BL4:BL8 BS4:BS8 BZ4:BZ8 CG4:CG42 CN4:CN48 BL15 BZ15 BL19 BS19 BZ19 BL23:BL31 BS23:BS31 BZ23:BZ32 BL34:BL35 BZ34:BZ35 BL37:BL38 BS37:BS38 BZ37:BZ38 BL41:BL42 BS41:BS42 BZ41:BZ42 CG44:CG47 BL47">
+  <conditionalFormatting sqref="BS14:BS15 BL4:BL8 BS4:BS8 BZ4:BZ8 BL15 BZ15 BL19 BS19 BZ19 BL23:BL31 BS23:BS31 BZ23:BZ32 BL35:BL36 BZ35:BZ36 BL38:BL39 BS38:BS39 BZ38:BZ39 BL42:BL43 BS42:BS43 BZ42:BZ43 CG45:CG48 BL48 BS33:BS36 CG4:CG43 CN4:CN49">
     <cfRule type="expression" dxfId="25" priority="117">
       <formula>AND(TODAY()&gt;=BL$5, TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BS14:BT14 BM34:BR38 BM4:BR8 BM14:BR15 BM19:BR19 BM23:BR31 BN32:BS33 BM41:BR42 BN44:BT45 I46:BT46">
+  <conditionalFormatting sqref="BS14:BT14 BM35:BR39 BM4:BR8 BM14:BR15 BM19:BR19 BM23:BR31 BM42:BR43 BN45:BT46 I47:BT47 BN32:BS34">
     <cfRule type="expression" dxfId="24" priority="41">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT24:BY33">
+  <conditionalFormatting sqref="BT24:BY34">
     <cfRule type="expression" dxfId="23" priority="36" stopIfTrue="1">
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT35:BY35 BT41:BY41">
+  <conditionalFormatting sqref="BT36:BY36 BT42:BY42">
     <cfRule type="expression" dxfId="22" priority="34" stopIfTrue="1">
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT37:BY38 BT4:BY8 BZ14 BT14:BY15 BT19:BY19 BT23:BY35 BT41:BY42 BU44:CA44">
+  <conditionalFormatting sqref="BT38:BY39 BT4:BY8 BZ14 BT14:BY15 BT19:BY19 BT42:BY43 BU45:CA45 BT23:BY36">
     <cfRule type="expression" dxfId="21" priority="32">
       <formula>AND(TODAY()&gt;=BT$5, TODAY()&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT38:BY38">
+  <conditionalFormatting sqref="BT39:BY39">
     <cfRule type="expression" dxfId="20" priority="18" stopIfTrue="1">
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
@@ -7992,7 +8098,7 @@
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU44:CA44">
+  <conditionalFormatting sqref="BU45:CA45">
     <cfRule type="expression" dxfId="18" priority="39">
       <formula>AND(task_start&lt;=BU$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BU$5)</formula>
     </cfRule>
@@ -8005,32 +8111,32 @@
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA24:CF32 BZ33:CF33">
+  <conditionalFormatting sqref="CA24:CF32 BZ33:CF34">
     <cfRule type="expression" dxfId="15" priority="27" stopIfTrue="1">
       <formula>AND(task_end&gt;=BZ$5,task_start&lt;CA$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA35:CF35 BS36:CF36 BL39:CF39 CA40:CF41">
+  <conditionalFormatting sqref="CA36:CF36 BS37:CF37 BL40:CF40 CA41:CF42">
     <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
       <formula>AND(task_end&gt;=BL$5,task_start&lt;BM$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA37:CF38 CA4:CF10 I11:CF13 CA14:CF15 BL16:CF16 I17:CF18 CA19:CF19 BL20:CF21 I22:CF22 CA23:CF32 BZ33:CF33 CA34:CF35 BS36:CF36 BL39:CF39 CA40:CF42 CB43:CF44 BU45:CF46 BM47:CF47">
+  <conditionalFormatting sqref="CA38:CF39 CA4:CF10 I11:CF13 CA14:CF15 BL16:CF16 I17:CF18 CA19:CF19 BL20:CF21 I22:CF22 CA23:CF32 CA35:CF36 BS37:CF37 BL40:CF40 CA41:CF43 CB44:CF45 BU46:CF47 BM48:CF48 BZ33:CF34">
     <cfRule type="expression" dxfId="13" priority="23">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA38:CF38">
+  <conditionalFormatting sqref="CA39:CF39">
     <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>AND(task_end&gt;=CA$5,task_start&lt;CB$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB43:CF44 BU45:CF46 BM47:CF47">
-    <cfRule type="expression" dxfId="11" priority="31" stopIfTrue="1">
+  <conditionalFormatting sqref="CB44:CF45 BU46:CF47 BM48:CF48">
+    <cfRule type="expression" dxfId="11" priority="30">
+      <formula>AND(task_start&lt;=BM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BM$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="31" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="30">
-      <formula>AND(task_start&lt;=BM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BM$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CG9:CG14 CN9:CN14 BS14 CG16:CG18 CN16:CN18 CG20:CG22 CN20:CN22">
@@ -8038,15 +8144,15 @@
       <formula>AND(task_end&gt;=BS$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CG43:CM43 CH44:CM47 BL48:CM48">
-    <cfRule type="expression" dxfId="8" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="CG44:CM44 CH45:CM48 BL49:CM49">
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>AND(task_start&lt;=BL$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BL$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="7" stopIfTrue="1">
       <formula>AND(task_end&gt;=BL$5,task_start&lt;BM$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="6">
-      <formula>AND(task_start&lt;=BL$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BL$5)</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH4:CM42 CG43:CM43 CH44:CM47 BL48:CM48">
+  <conditionalFormatting sqref="CG44:CM44 CH45:CM48 BL49:CM49 CH4:CM43">
     <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(TODAY()&gt;=BL$5, TODAY()&lt;BM$5)</formula>
     </cfRule>
@@ -8056,22 +8162,22 @@
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH24:CM33">
+  <conditionalFormatting sqref="CH24:CM34">
     <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH35:CM36 CH39:CM41">
+  <conditionalFormatting sqref="CH36:CM37 CH40:CM42">
     <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH38:CM38">
+  <conditionalFormatting sqref="CH39:CM39">
     <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CN43:CN48 CG44:CG47 BL47">
+  <conditionalFormatting sqref="CN44:CN49 CG45:CG48 BL48">
     <cfRule type="expression" dxfId="1" priority="124">
       <formula>AND(task_start&lt;=BL$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BL$5)</formula>
     </cfRule>
@@ -8092,9 +8198,9 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="B9 contains the task name.  C9 is the assignee.  D9 is a progress bar that shades based on the number entered into the cell.  _x000a__x000a_E9 contains the start date and F9 contains the end date._x000a__x000a_The Gantt chart will fill in starting in cell I9 based on task dates." sqref="A20:A21 A9 A16" xr:uid="{D870A2F6-6B07-4F5A-A81D-4BCCFADF8796}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Rows 10 through 13 repeat the pattern from row 9. _x000a__x000a_Repeat the instructions from cell A9 for all task rows in this worksheet. _x000a__x000a_Continue entering tasks in cells A10 through A13 or go to cell A14 to learn more." sqref="A22 A10 A17" xr:uid="{872449A7-C3CC-45B6-BA90-B1AAD66BA0E5}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B14 contains the Phase 2 sample title. Enter a new title in cell B14._x000a_To delete the phase and work only from tasks, simply delete this row. To remove the phase, simply delete the row. Add tasks to previous phase by entering a new row above this one._x000a_" sqref="A23" xr:uid="{4F48FC41-E335-47F1-87AA-3333A52AD81C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 3's sample block starts in cell B20." sqref="A34 A37" xr:uid="{956902D1-D3B5-416D-BB69-9362D193BC0A}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 4's sample block starts in cell B26." sqref="A42" xr:uid="{DE54E5DE-526D-4D71-8D03-E99B4AB2FEE5}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. _x000a_Insert new rows ABOVE this one to continue building out your Project Schedule." sqref="A50" xr:uid="{79B9237E-4DD3-4E0F-8ED6-E0B695A99D96}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 3's sample block starts in cell B20." sqref="A35 A38" xr:uid="{956902D1-D3B5-416D-BB69-9362D193BC0A}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 4's sample block starts in cell B26." sqref="A43" xr:uid="{DE54E5DE-526D-4D71-8D03-E99B4AB2FEE5}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. _x000a_Insert new rows ABOVE this one to continue building out your Project Schedule." sqref="A51" xr:uid="{79B9237E-4DD3-4E0F-8ED6-E0B695A99D96}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -8151,7 +8257,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D50</xm:sqref>
+          <xm:sqref>D7:D51</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -8281,23 +8387,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8613,22 +8708,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8655,9 +8757,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="561" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEBFA8E-BC5A-9546-AE4F-9B12AC029CA2}"/>
+  <xr:revisionPtr revIDLastSave="572" documentId="8_{E97B7BBA-A1CF-CA4D-89B6-D5BE4B7D4A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A9A9B95-2D7B-ED44-A844-247A6F97DF58}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+  <si>
+    <t>Tier Plus</t>
+  </si>
   <si>
     <t>Project start:</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Display week:</t>
   </si>
   <si>
-    <t>SIMPLE GANTT CHART by Vertex42.com</t>
+    <t>scroll to see more dates</t>
   </si>
   <si>
     <t>https://www.vertex42.com/ExcelTemplates/simple-gantt-chart.html</t>
@@ -81,7 +84,130 @@
     <t xml:space="preserve">Do not delete this row. This row is hidden to preserve a formula that is used to highlight the current day within the project schedule. </t>
   </si>
   <si>
+    <t>Data Collection - Efficacy and Cost params</t>
+  </si>
+  <si>
+    <t>Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing </t>
+  </si>
+  <si>
+    <t>Monitoring and retention</t>
+  </si>
+  <si>
+    <t>AHD and prophylaxis</t>
+  </si>
+  <si>
+    <t>ANC and PNC</t>
+  </si>
+  <si>
+    <t>Costing</t>
+  </si>
+  <si>
+    <t>Test app integration</t>
+  </si>
+  <si>
+    <t>Data Collection - Additional assumption and rates (e.g mortality rates per group)</t>
+  </si>
+  <si>
+    <t>Create parameter list with dummy values</t>
+  </si>
+  <si>
+    <t>Collect data</t>
+  </si>
+  <si>
+    <t>Integrate into app</t>
+  </si>
+  <si>
+    <t>Data Collection - Baseline intervention values (where available)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collect any available data </t>
+  </si>
+  <si>
+    <t>Define assumptions for baseline interventions in the abscence of data</t>
+  </si>
+  <si>
+    <t>Integrate both into app</t>
+  </si>
+  <si>
+    <t>Core Logic Testing - test code and documentation - usually results in app fixes as well</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Mortality</t>
+  </si>
+  <si>
+    <t>General viral suppression and infections</t>
+  </si>
+  <si>
+    <t>Populations and 95's (potentially incoporated in during above sections)</t>
+  </si>
+  <si>
+    <t>Relative scenario and baseline counts</t>
+  </si>
+  <si>
+    <t>Re-test with all new data</t>
+  </si>
+  <si>
+    <t>Validation - Logic (some incoporated during core logic testing)</t>
+  </si>
+  <si>
+    <t>Define validation cases, logic and assumptions (including eligble populations, minimum or maximum groups, overlapping interventions, impact on 90's etc)</t>
+  </si>
+  <si>
+    <t>Implement and Test</t>
+  </si>
+  <si>
+    <t>Input Validation - App - Implement and test</t>
+  </si>
+  <si>
+    <t>Define validation cases, logic and assumption (e.g prep_len + prep_oral cannot exceed eligible pop)</t>
+  </si>
+  <si>
+    <t>Need a check for if I'm missing things</t>
+  </si>
+  <si>
+    <t>Implement: Input limits (where relevant)</t>
+  </si>
+  <si>
+    <t>Implement: Limits on combinations (prep+mmd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement: </t>
+  </si>
+  <si>
+    <t>Integrated Testing and User feedback</t>
+  </si>
+  <si>
+    <t>Figure out app publishing</t>
+  </si>
+  <si>
+    <t>Test reasonable scenarios</t>
+  </si>
+  <si>
+    <t>Test unreasonable scenarios</t>
+  </si>
+  <si>
+    <t>Fix problems</t>
+  </si>
+  <si>
+    <t>Gather user feedback</t>
+  </si>
+  <si>
+    <t>Integrate feedback</t>
+  </si>
+  <si>
+    <t>END PLANNING: JUNE 15th Max</t>
+  </si>
+  <si>
     <t>Insert new rows ABOVE this one</t>
+  </si>
+  <si>
+    <t>SIMPLE GANTT CHART by Vertex42.com</t>
   </si>
   <si>
     <t>About This Template</t>
@@ -127,132 +253,6 @@
   <si>
     <t>Businesses will find invoices, time sheets, inventory trackers, financial statements, and project planning templates. Teachers and students will find resources such as class schedules, grade books, and attendance sheets. Organize your family life with meal planners, checklists, and exercise logs. Each template is thoroughly researched, refined, and improved over time through feedback from thousands of users.</t>
   </si>
-  <si>
-    <t>Tier Plus</t>
-  </si>
-  <si>
-    <t>Data Collection - Efficacy and Cost params</t>
-  </si>
-  <si>
-    <t>Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing </t>
-  </si>
-  <si>
-    <t>Monitoring and retention</t>
-  </si>
-  <si>
-    <t>AHD and prophylaxis</t>
-  </si>
-  <si>
-    <t>ANC and PNC</t>
-  </si>
-  <si>
-    <t>Data Collection - Additional assumption and rates (e.g mortality rates per group)</t>
-  </si>
-  <si>
-    <t>Collect data</t>
-  </si>
-  <si>
-    <t>Integrate into app</t>
-  </si>
-  <si>
-    <t>Create parameter list with dummy values</t>
-  </si>
-  <si>
-    <t>Data Collection - Baseline intervention values (where available)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collect any available data </t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>General viral suppression and infections</t>
-  </si>
-  <si>
-    <t>Costing</t>
-  </si>
-  <si>
-    <t>Test app integration</t>
-  </si>
-  <si>
-    <t>Implement and Test</t>
-  </si>
-  <si>
-    <t>Define validation cases, logic and assumptions (including eligble populations, minimum or maximum groups, overlapping interventions, impact on 90's etc)</t>
-  </si>
-  <si>
-    <t>Input Validation - App - Implement and test</t>
-  </si>
-  <si>
-    <t>Define validation cases, logic and assumption (e.g prep_len + prep_oral cannot exceed eligible pop)</t>
-  </si>
-  <si>
-    <t>Integrated Testing and User feedback</t>
-  </si>
-  <si>
-    <t>Test unreasonable scenarios</t>
-  </si>
-  <si>
-    <t>Fix problems</t>
-  </si>
-  <si>
-    <t>Gather user feedback</t>
-  </si>
-  <si>
-    <t>Integrate feedback</t>
-  </si>
-  <si>
-    <t>Test reasonable scenarios</t>
-  </si>
-  <si>
-    <t>Integrate both into app</t>
-  </si>
-  <si>
-    <t>Core Logic Testing - test code and documentation - usually results in app fixes as well</t>
-  </si>
-  <si>
-    <t>Populations and 95's (potentially incoporated in during above sections)</t>
-  </si>
-  <si>
-    <t>Implement: Input limits (where relevant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement: </t>
-  </si>
-  <si>
-    <t>END PLANNING: JUNE 15th Max</t>
-  </si>
-  <si>
-    <t>Figure out app publishing</t>
-  </si>
-  <si>
-    <t>Validation - Logic (some incoporated during core logic testing)</t>
-  </si>
-  <si>
-    <t>Re-test with all new data</t>
-  </si>
-  <si>
-    <t>Mortality</t>
-  </si>
-  <si>
-    <t>scroll to see more dates</t>
-  </si>
-  <si>
-    <t>Define assumptions for baseline interventions in the abscence of data</t>
-  </si>
-  <si>
-    <t>Need a check for if I'm missing things</t>
-  </si>
-  <si>
-    <t>Implement: Limits on combinations (prep+mmd)</t>
-  </si>
-  <si>
-    <t>Relative scenario and baseline counts</t>
-  </si>
 </sst>
 </file>
 
@@ -267,7 +267,7 @@
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="169" formatCode="[$-409]d\-mmm;@"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -849,7 +849,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1069,9 +1069,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1154,10 +1151,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1170,7 +1170,6 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1183,18 +1182,20 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -1205,7 +1206,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Name" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="Project Start" xfId="9" xr:uid="{8EB8A09A-C31C-40A3-B2C1-9449520178B8}"/>
     <cellStyle name="Task" xfId="12" xr:uid="{6391D789-272B-4DD2-9BF3-2CDCF610FA41}"/>
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
@@ -2377,239 +2378,332 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CN54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:CN55"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" style="106" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" style="107" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
-    <col min="8" max="8" width="0.6640625" customWidth="1"/>
-    <col min="9" max="92" width="2.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="37.375" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="105" customWidth="1"/>
+    <col min="6" max="6" width="6.625" style="106" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.875" customWidth="1"/>
+    <col min="8" max="8" width="0.625" customWidth="1"/>
+    <col min="9" max="92" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" ht="90" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A1" s="81"/>
+    <row r="1" spans="1:92" ht="90" customHeight="1">
+      <c r="A1" s="112"/>
       <c r="B1" s="73" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="16"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="83"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="82"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="126" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="I1" s="123" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="124">
+      <c r="Q1" s="122">
         <v>46064</v>
       </c>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
+      <c r="R1" s="126"/>
+      <c r="S1" s="126"/>
+      <c r="T1" s="126"/>
+      <c r="U1" s="126"/>
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
     </row>
-    <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:92" ht="30" customHeight="1">
       <c r="B2" s="71"/>
       <c r="C2" s="72" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="17"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="85"/>
-      <c r="I2" s="126" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="84"/>
+      <c r="I2" s="123" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="122">
+      <c r="Q2" s="121">
         <v>5</v>
       </c>
-      <c r="R2" s="123"/>
-      <c r="S2" s="123"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="123"/>
-      <c r="V2" s="123"/>
-      <c r="W2" s="123"/>
-      <c r="X2" s="123"/>
-      <c r="Y2" s="123"/>
-      <c r="Z2" s="123"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
       <c r="AP2" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="12"/>
       <c r="B3" s="19"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="21"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="87"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="111"/>
+      <c r="Y3" s="111"/>
+      <c r="Z3" s="111"/>
+      <c r="AA3" s="111"/>
+      <c r="AB3" s="111"/>
+      <c r="AC3" s="111"/>
+      <c r="AD3" s="111"/>
+      <c r="AE3" s="111"/>
+      <c r="AF3" s="111"/>
+      <c r="AG3" s="111"/>
+      <c r="AH3" s="111"/>
+      <c r="AI3" s="111"/>
+      <c r="AJ3" s="111"/>
+      <c r="AK3" s="111"/>
+      <c r="AL3" s="111"/>
+      <c r="AM3" s="111"/>
+      <c r="AN3" s="111"/>
+      <c r="AO3" s="111"/>
+      <c r="AP3" s="111"/>
+      <c r="AQ3" s="111"/>
+      <c r="AR3" s="111"/>
+      <c r="AS3" s="111"/>
+      <c r="AT3" s="111"/>
+      <c r="AU3" s="111"/>
+      <c r="AV3" s="111"/>
+      <c r="AW3" s="111"/>
+      <c r="AX3" s="111"/>
+      <c r="AY3" s="111"/>
+      <c r="AZ3" s="111"/>
+      <c r="BA3" s="111"/>
+      <c r="BB3" s="111"/>
+      <c r="BC3" s="111"/>
+      <c r="BD3" s="111"/>
+      <c r="BE3" s="111"/>
+      <c r="BF3" s="111"/>
+      <c r="BG3" s="111"/>
+      <c r="BH3" s="111"/>
+      <c r="BI3" s="111"/>
+      <c r="BJ3" s="111"/>
+      <c r="BK3" s="111"/>
+      <c r="BL3" s="111"/>
+      <c r="BM3" s="111"/>
+      <c r="BN3" s="111"/>
+      <c r="BO3" s="111"/>
+      <c r="BP3" s="111"/>
+      <c r="BQ3" s="111"/>
+      <c r="BR3" s="111"/>
+      <c r="BS3" s="111"/>
+      <c r="BT3" s="111"/>
+      <c r="BU3" s="111"/>
+      <c r="BV3" s="111"/>
+      <c r="BW3" s="111"/>
+      <c r="BX3" s="111"/>
+      <c r="BY3" s="111"/>
+      <c r="BZ3" s="111"/>
+      <c r="CA3" s="111"/>
+      <c r="CB3" s="111"/>
+      <c r="CC3" s="111"/>
+      <c r="CD3" s="111"/>
+      <c r="CE3" s="111"/>
+      <c r="CF3" s="111"/>
+      <c r="CG3" s="111"/>
+      <c r="CH3" s="111"/>
+      <c r="CI3" s="111"/>
+      <c r="CJ3" s="111"/>
+      <c r="CK3" s="111"/>
+      <c r="CL3" s="111"/>
+      <c r="CM3" s="111"/>
+      <c r="CN3" s="111"/>
     </row>
-    <row r="4" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="81"/>
-      <c r="B4" s="110" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="87"/>
-      <c r="I4" s="128">
+    <row r="4" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1">
+      <c r="A4" s="112"/>
+      <c r="B4" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="124">
         <f>I5</f>
         <v>46090</v>
       </c>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120"/>
-      <c r="P4" s="120">
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="119">
         <f>P5</f>
         <v>46097</v>
       </c>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120"/>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120"/>
-      <c r="V4" s="120"/>
-      <c r="W4" s="120">
+      <c r="Q4" s="119"/>
+      <c r="R4" s="119"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="119"/>
+      <c r="W4" s="119">
         <f>W5</f>
         <v>46104</v>
       </c>
-      <c r="X4" s="120"/>
-      <c r="Y4" s="120"/>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="120">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="119"/>
+      <c r="Z4" s="119"/>
+      <c r="AA4" s="119"/>
+      <c r="AB4" s="119"/>
+      <c r="AC4" s="119"/>
+      <c r="AD4" s="119">
         <f>AD5</f>
         <v>46111</v>
       </c>
-      <c r="AE4" s="120"/>
-      <c r="AF4" s="120"/>
-      <c r="AG4" s="120"/>
-      <c r="AH4" s="120"/>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="120"/>
-      <c r="AK4" s="120">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119">
         <f>AK5</f>
         <v>46118</v>
       </c>
-      <c r="AL4" s="120"/>
-      <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
-      <c r="AO4" s="120"/>
-      <c r="AP4" s="120"/>
-      <c r="AQ4" s="120"/>
-      <c r="AR4" s="120">
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
+      <c r="AQ4" s="119"/>
+      <c r="AR4" s="119">
         <f>AR5</f>
         <v>46125</v>
       </c>
-      <c r="AS4" s="120"/>
-      <c r="AT4" s="120"/>
-      <c r="AU4" s="120"/>
-      <c r="AV4" s="120"/>
-      <c r="AW4" s="120"/>
-      <c r="AX4" s="120"/>
-      <c r="AY4" s="120">
+      <c r="AS4" s="119"/>
+      <c r="AT4" s="119"/>
+      <c r="AU4" s="119"/>
+      <c r="AV4" s="119"/>
+      <c r="AW4" s="119"/>
+      <c r="AX4" s="119"/>
+      <c r="AY4" s="119">
         <f>AY5</f>
         <v>46132</v>
       </c>
-      <c r="AZ4" s="120"/>
-      <c r="BA4" s="120"/>
-      <c r="BB4" s="120"/>
-      <c r="BC4" s="120"/>
-      <c r="BD4" s="120"/>
-      <c r="BE4" s="120"/>
-      <c r="BF4" s="120">
+      <c r="AZ4" s="119"/>
+      <c r="BA4" s="119"/>
+      <c r="BB4" s="119"/>
+      <c r="BC4" s="119"/>
+      <c r="BD4" s="119"/>
+      <c r="BE4" s="119"/>
+      <c r="BF4" s="119">
         <f>BF5</f>
         <v>46139</v>
       </c>
-      <c r="BG4" s="120"/>
-      <c r="BH4" s="120"/>
-      <c r="BI4" s="120"/>
-      <c r="BJ4" s="120"/>
-      <c r="BK4" s="120"/>
-      <c r="BL4" s="121"/>
-      <c r="BM4" s="120">
+      <c r="BG4" s="119"/>
+      <c r="BH4" s="119"/>
+      <c r="BI4" s="119"/>
+      <c r="BJ4" s="119"/>
+      <c r="BK4" s="119"/>
+      <c r="BL4" s="120"/>
+      <c r="BM4" s="119">
         <f>BM5</f>
         <v>46146</v>
       </c>
-      <c r="BN4" s="120"/>
-      <c r="BO4" s="120"/>
-      <c r="BP4" s="120"/>
-      <c r="BQ4" s="120"/>
-      <c r="BR4" s="120"/>
-      <c r="BS4" s="121"/>
-      <c r="BT4" s="120">
+      <c r="BN4" s="119"/>
+      <c r="BO4" s="119"/>
+      <c r="BP4" s="119"/>
+      <c r="BQ4" s="119"/>
+      <c r="BR4" s="119"/>
+      <c r="BS4" s="120"/>
+      <c r="BT4" s="119">
         <f>BT5</f>
         <v>46153</v>
       </c>
-      <c r="BU4" s="120"/>
-      <c r="BV4" s="120"/>
-      <c r="BW4" s="120"/>
-      <c r="BX4" s="120"/>
-      <c r="BY4" s="120"/>
-      <c r="BZ4" s="121"/>
-      <c r="CA4" s="120">
+      <c r="BU4" s="119"/>
+      <c r="BV4" s="119"/>
+      <c r="BW4" s="119"/>
+      <c r="BX4" s="119"/>
+      <c r="BY4" s="119"/>
+      <c r="BZ4" s="120"/>
+      <c r="CA4" s="119">
         <f>CA5</f>
         <v>46160</v>
       </c>
-      <c r="CB4" s="120"/>
-      <c r="CC4" s="120"/>
-      <c r="CD4" s="120"/>
-      <c r="CE4" s="120"/>
-      <c r="CF4" s="120"/>
-      <c r="CG4" s="121"/>
-      <c r="CH4" s="120">
+      <c r="CB4" s="119"/>
+      <c r="CC4" s="119"/>
+      <c r="CD4" s="119"/>
+      <c r="CE4" s="119"/>
+      <c r="CF4" s="119"/>
+      <c r="CG4" s="120"/>
+      <c r="CH4" s="119">
         <f>CH5</f>
         <v>46167</v>
       </c>
-      <c r="CI4" s="120"/>
-      <c r="CJ4" s="120"/>
-      <c r="CK4" s="120"/>
-      <c r="CL4" s="120"/>
-      <c r="CM4" s="120"/>
-      <c r="CN4" s="121"/>
+      <c r="CI4" s="119"/>
+      <c r="CJ4" s="119"/>
+      <c r="CK4" s="119"/>
+      <c r="CL4" s="119"/>
+      <c r="CM4" s="119"/>
+      <c r="CN4" s="120"/>
     </row>
-    <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="114"/>
       <c r="B5" s="115" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="112" t="s">
+      <c r="D5" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="112" t="s">
+      <c r="E5" s="113" t="s">
         <v>9</v>
       </c>
+      <c r="F5" s="113" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
       <c r="I5" s="22">
         <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
         <v>46090</v>
@@ -2947,13 +3041,15 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="114"/>
       <c r="B6" s="116"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
       <c r="I6" s="25" t="str">
         <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -3291,17 +3387,18 @@
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:92" s="20" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:92" s="20" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1">
       <c r="A7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="28"/>
       <c r="C7" s="29"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="H7" s="20" t="str">
-        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111" t="str">
+        <f ca="1">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I7" s="30"/>
@@ -3389,18 +3486,18 @@
       <c r="CM7" s="30"/>
       <c r="CN7" s="30"/>
     </row>
-    <row r="8" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="81"/>
+    <row r="8" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A8" s="112"/>
       <c r="B8" s="31" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C8" s="32"/>
       <c r="D8" s="33"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="91"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="90"/>
       <c r="G8" s="14"/>
       <c r="H8" s="4" t="str">
-        <f t="shared" ref="H8:H18" si="29">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H8:H19" ca="1" si="29">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I8" s="34"/>
@@ -3488,26 +3585,26 @@
       <c r="CM8" s="34"/>
       <c r="CN8" s="34"/>
     </row>
-    <row r="9" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="81"/>
+    <row r="9" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A9" s="112"/>
       <c r="B9" s="36" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="38">
         <v>0</v>
       </c>
-      <c r="E9" s="92">
+      <c r="E9" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F9" s="92">
+      <c r="F9" s="91">
         <f>E9+58</f>
         <v>46122</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I9" s="39"/>
@@ -3595,26 +3692,26 @@
       <c r="CM9" s="39"/>
       <c r="CN9" s="39"/>
     </row>
-    <row r="10" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="81"/>
+    <row r="10" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A10" s="112"/>
       <c r="B10" s="40" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="42">
-        <v>0</v>
-      </c>
-      <c r="E10" s="92">
+        <v>0.8</v>
+      </c>
+      <c r="E10" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F10" s="92">
+      <c r="F10" s="91">
         <f>E10+58</f>
         <v>46122</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I10" s="39"/>
@@ -3702,26 +3799,26 @@
       <c r="CM10" s="39"/>
       <c r="CN10" s="39"/>
     </row>
-    <row r="11" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A11" s="12"/>
       <c r="B11" s="40" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="42">
         <v>0</v>
       </c>
-      <c r="E11" s="92">
+      <c r="E11" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F11" s="92">
+      <c r="F11" s="91">
         <f>E11+58</f>
         <v>46122</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I11" s="39"/>
@@ -3809,26 +3906,26 @@
       <c r="CM11" s="39"/>
       <c r="CN11" s="39"/>
     </row>
-    <row r="12" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A12" s="12"/>
       <c r="B12" s="40" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C12" s="41"/>
       <c r="D12" s="42">
         <v>0</v>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="91">
         <f>E12+58</f>
         <v>46122</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I12" s="39"/>
@@ -3916,26 +4013,26 @@
       <c r="CM12" s="39"/>
       <c r="CN12" s="39"/>
     </row>
-    <row r="13" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A13" s="12"/>
       <c r="B13" s="40" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="42">
         <v>0</v>
       </c>
-      <c r="E13" s="92">
+      <c r="E13" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F13" s="92">
+      <c r="F13" s="91">
         <f>E13+58</f>
         <v>46122</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I13" s="39"/>
@@ -4023,28 +4120,25 @@
       <c r="CM13" s="39"/>
       <c r="CN13" s="39"/>
     </row>
-    <row r="14" spans="1:92" s="35" customFormat="1" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A14" s="12"/>
       <c r="B14" s="40" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C14" s="41"/>
       <c r="D14" s="42">
-        <v>0</v>
-      </c>
-      <c r="E14" s="92">
-        <f>F13+1</f>
-        <v>46123</v>
-      </c>
-      <c r="F14" s="92">
-        <f>E14+14</f>
-        <v>46137</v>
-      </c>
-      <c r="G14" s="111"/>
-      <c r="H14" s="4">
-        <f t="shared" si="29"/>
-        <v>15</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="E14" s="91">
+        <f>Project_Start</f>
+        <v>46064</v>
+      </c>
+      <c r="F14" s="91">
+        <f>E14+58</f>
+        <v>46122</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="4"/>
       <c r="I14" s="39"/>
       <c r="J14" s="39"/>
       <c r="K14" s="39"/>
@@ -4130,232 +4224,232 @@
       <c r="CM14" s="39"/>
       <c r="CN14" s="39"/>
     </row>
-    <row r="15" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="81"/>
-      <c r="B15" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="4" t="str">
-        <f t="shared" si="29"/>
+    <row r="15" spans="1:92" s="35" customFormat="1" ht="53.1" customHeight="1" thickBot="1">
+      <c r="A15" s="12"/>
+      <c r="B15" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="42">
+        <v>0</v>
+      </c>
+      <c r="E15" s="91">
+        <f>F13+1</f>
+        <v>46123</v>
+      </c>
+      <c r="F15" s="91">
+        <f>E15+14</f>
+        <v>46137</v>
+      </c>
+      <c r="G15" s="110"/>
+      <c r="H15" s="4">
+        <f t="shared" ca="1" si="29"/>
+        <v>15</v>
+      </c>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="39"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
+      <c r="AJ15" s="39"/>
+      <c r="AK15" s="39"/>
+      <c r="AL15" s="39"/>
+      <c r="AM15" s="39"/>
+      <c r="AN15" s="39"/>
+      <c r="AO15" s="39"/>
+      <c r="AP15" s="39"/>
+      <c r="AQ15" s="39"/>
+      <c r="AR15" s="39"/>
+      <c r="AS15" s="39"/>
+      <c r="AT15" s="39"/>
+      <c r="AU15" s="39"/>
+      <c r="AV15" s="39"/>
+      <c r="AW15" s="39"/>
+      <c r="AX15" s="39"/>
+      <c r="AY15" s="39"/>
+      <c r="AZ15" s="39"/>
+      <c r="BA15" s="39"/>
+      <c r="BB15" s="39"/>
+      <c r="BC15" s="39"/>
+      <c r="BD15" s="39"/>
+      <c r="BE15" s="39"/>
+      <c r="BF15" s="39"/>
+      <c r="BG15" s="39"/>
+      <c r="BH15" s="39"/>
+      <c r="BI15" s="39"/>
+      <c r="BJ15" s="39"/>
+      <c r="BK15" s="39"/>
+      <c r="BL15" s="39"/>
+      <c r="BM15" s="39"/>
+      <c r="BN15" s="39"/>
+      <c r="BO15" s="39"/>
+      <c r="BP15" s="39"/>
+      <c r="BQ15" s="39"/>
+      <c r="BR15" s="39"/>
+      <c r="BS15" s="39"/>
+      <c r="BT15" s="39"/>
+      <c r="BU15" s="39"/>
+      <c r="BV15" s="39"/>
+      <c r="BW15" s="39"/>
+      <c r="BX15" s="39"/>
+      <c r="BY15" s="39"/>
+      <c r="BZ15" s="39"/>
+      <c r="CA15" s="39"/>
+      <c r="CB15" s="39"/>
+      <c r="CC15" s="39"/>
+      <c r="CD15" s="39"/>
+      <c r="CE15" s="39"/>
+      <c r="CF15" s="39"/>
+      <c r="CG15" s="39"/>
+      <c r="CH15" s="39"/>
+      <c r="CI15" s="39"/>
+      <c r="CJ15" s="39"/>
+      <c r="CK15" s="39"/>
+      <c r="CL15" s="39"/>
+      <c r="CM15" s="39"/>
+      <c r="CN15" s="39"/>
+    </row>
+    <row r="16" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A16" s="112"/>
+      <c r="B16" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="32"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="4" t="str">
+        <f t="shared" ca="1" si="29"/>
         <v/>
       </c>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34"/>
-      <c r="W15" s="34"/>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="34"/>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="34"/>
-      <c r="AC15" s="34"/>
-      <c r="AD15" s="34"/>
-      <c r="AE15" s="34"/>
-      <c r="AF15" s="34"/>
-      <c r="AG15" s="34"/>
-      <c r="AH15" s="34"/>
-      <c r="AI15" s="34"/>
-      <c r="AJ15" s="34"/>
-      <c r="AK15" s="34"/>
-      <c r="AL15" s="34"/>
-      <c r="AM15" s="34"/>
-      <c r="AN15" s="34"/>
-      <c r="AO15" s="34"/>
-      <c r="AP15" s="34"/>
-      <c r="AQ15" s="34"/>
-      <c r="AR15" s="34"/>
-      <c r="AS15" s="34"/>
-      <c r="AT15" s="34"/>
-      <c r="AU15" s="34"/>
-      <c r="AV15" s="34"/>
-      <c r="AW15" s="34"/>
-      <c r="AX15" s="34"/>
-      <c r="AY15" s="34"/>
-      <c r="AZ15" s="34"/>
-      <c r="BA15" s="34"/>
-      <c r="BB15" s="34"/>
-      <c r="BC15" s="34"/>
-      <c r="BD15" s="34"/>
-      <c r="BE15" s="34"/>
-      <c r="BF15" s="34"/>
-      <c r="BG15" s="34"/>
-      <c r="BH15" s="34"/>
-      <c r="BI15" s="34"/>
-      <c r="BJ15" s="34"/>
-      <c r="BK15" s="34"/>
-      <c r="BL15" s="34"/>
-      <c r="BM15" s="34"/>
-      <c r="BN15" s="34"/>
-      <c r="BO15" s="34"/>
-      <c r="BP15" s="34"/>
-      <c r="BQ15" s="34"/>
-      <c r="BR15" s="34"/>
-      <c r="BS15" s="34"/>
-      <c r="BT15" s="34"/>
-      <c r="BU15" s="34"/>
-      <c r="BV15" s="34"/>
-      <c r="BW15" s="34"/>
-      <c r="BX15" s="34"/>
-      <c r="BY15" s="34"/>
-      <c r="BZ15" s="34"/>
-      <c r="CA15" s="34"/>
-      <c r="CB15" s="34"/>
-      <c r="CC15" s="34"/>
-      <c r="CD15" s="34"/>
-      <c r="CE15" s="34"/>
-      <c r="CF15" s="34"/>
-      <c r="CG15" s="34"/>
-      <c r="CH15" s="34"/>
-      <c r="CI15" s="34"/>
-      <c r="CJ15" s="34"/>
-      <c r="CK15" s="34"/>
-      <c r="CL15" s="34"/>
-      <c r="CM15" s="34"/>
-      <c r="CN15" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="34"/>
+      <c r="Y16" s="34"/>
+      <c r="Z16" s="34"/>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="34"/>
+      <c r="AC16" s="34"/>
+      <c r="AD16" s="34"/>
+      <c r="AE16" s="34"/>
+      <c r="AF16" s="34"/>
+      <c r="AG16" s="34"/>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="34"/>
+      <c r="AJ16" s="34"/>
+      <c r="AK16" s="34"/>
+      <c r="AL16" s="34"/>
+      <c r="AM16" s="34"/>
+      <c r="AN16" s="34"/>
+      <c r="AO16" s="34"/>
+      <c r="AP16" s="34"/>
+      <c r="AQ16" s="34"/>
+      <c r="AR16" s="34"/>
+      <c r="AS16" s="34"/>
+      <c r="AT16" s="34"/>
+      <c r="AU16" s="34"/>
+      <c r="AV16" s="34"/>
+      <c r="AW16" s="34"/>
+      <c r="AX16" s="34"/>
+      <c r="AY16" s="34"/>
+      <c r="AZ16" s="34"/>
+      <c r="BA16" s="34"/>
+      <c r="BB16" s="34"/>
+      <c r="BC16" s="34"/>
+      <c r="BD16" s="34"/>
+      <c r="BE16" s="34"/>
+      <c r="BF16" s="34"/>
+      <c r="BG16" s="34"/>
+      <c r="BH16" s="34"/>
+      <c r="BI16" s="34"/>
+      <c r="BJ16" s="34"/>
+      <c r="BK16" s="34"/>
+      <c r="BL16" s="34"/>
+      <c r="BM16" s="34"/>
+      <c r="BN16" s="34"/>
+      <c r="BO16" s="34"/>
+      <c r="BP16" s="34"/>
+      <c r="BQ16" s="34"/>
+      <c r="BR16" s="34"/>
+      <c r="BS16" s="34"/>
+      <c r="BT16" s="34"/>
+      <c r="BU16" s="34"/>
+      <c r="BV16" s="34"/>
+      <c r="BW16" s="34"/>
+      <c r="BX16" s="34"/>
+      <c r="BY16" s="34"/>
+      <c r="BZ16" s="34"/>
+      <c r="CA16" s="34"/>
+      <c r="CB16" s="34"/>
+      <c r="CC16" s="34"/>
+      <c r="CD16" s="34"/>
+      <c r="CE16" s="34"/>
+      <c r="CF16" s="34"/>
+      <c r="CG16" s="34"/>
+      <c r="CH16" s="34"/>
+      <c r="CI16" s="34"/>
+      <c r="CJ16" s="34"/>
+      <c r="CK16" s="34"/>
+      <c r="CL16" s="34"/>
+      <c r="CM16" s="34"/>
+      <c r="CN16" s="34"/>
     </row>
-    <row r="16" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="81"/>
-      <c r="B16" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38">
+    <row r="17" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A17" s="112"/>
+      <c r="B17" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38">
         <v>1</v>
       </c>
-      <c r="E16" s="92">
+      <c r="E17" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F16" s="92">
-        <f>E16+58</f>
-        <v>46122</v>
-      </c>
-      <c r="G16" s="14"/>
-      <c r="H16" s="4">
-        <f t="shared" si="29"/>
-        <v>59</v>
-      </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="39"/>
-      <c r="S16" s="39"/>
-      <c r="T16" s="39"/>
-      <c r="U16" s="39"/>
-      <c r="V16" s="39"/>
-      <c r="W16" s="39"/>
-      <c r="X16" s="39"/>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="39"/>
-      <c r="AA16" s="39"/>
-      <c r="AB16" s="39"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="39"/>
-      <c r="AE16" s="39"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="39"/>
-      <c r="AH16" s="39"/>
-      <c r="AI16" s="39"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="39"/>
-      <c r="AL16" s="39"/>
-      <c r="AM16" s="39"/>
-      <c r="AN16" s="39"/>
-      <c r="AO16" s="39"/>
-      <c r="AP16" s="39"/>
-      <c r="AQ16" s="39"/>
-      <c r="AR16" s="39"/>
-      <c r="AS16" s="39"/>
-      <c r="AT16" s="39"/>
-      <c r="AU16" s="39"/>
-      <c r="AV16" s="39"/>
-      <c r="AW16" s="39"/>
-      <c r="AX16" s="39"/>
-      <c r="AY16" s="39"/>
-      <c r="AZ16" s="39"/>
-      <c r="BA16" s="39"/>
-      <c r="BB16" s="39"/>
-      <c r="BC16" s="39"/>
-      <c r="BD16" s="39"/>
-      <c r="BE16" s="39"/>
-      <c r="BF16" s="39"/>
-      <c r="BG16" s="39"/>
-      <c r="BH16" s="39"/>
-      <c r="BI16" s="39"/>
-      <c r="BJ16" s="39"/>
-      <c r="BK16" s="39"/>
-      <c r="BL16" s="39"/>
-      <c r="BM16" s="39"/>
-      <c r="BN16" s="39"/>
-      <c r="BO16" s="39"/>
-      <c r="BP16" s="39"/>
-      <c r="BQ16" s="39"/>
-      <c r="BR16" s="39"/>
-      <c r="BS16" s="39"/>
-      <c r="BT16" s="39"/>
-      <c r="BU16" s="39"/>
-      <c r="BV16" s="39"/>
-      <c r="BW16" s="39"/>
-      <c r="BX16" s="39"/>
-      <c r="BY16" s="39"/>
-      <c r="BZ16" s="39"/>
-      <c r="CA16" s="39"/>
-      <c r="CB16" s="39"/>
-      <c r="CC16" s="39"/>
-      <c r="CD16" s="39"/>
-      <c r="CE16" s="39"/>
-      <c r="CF16" s="39"/>
-      <c r="CG16" s="39"/>
-      <c r="CH16" s="39"/>
-      <c r="CI16" s="39"/>
-      <c r="CJ16" s="39"/>
-      <c r="CK16" s="39"/>
-      <c r="CL16" s="39"/>
-      <c r="CM16" s="39"/>
-      <c r="CN16" s="39"/>
-    </row>
-    <row r="17" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81"/>
-      <c r="B17" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42">
-        <v>0</v>
-      </c>
-      <c r="E17" s="92">
-        <f>Project_Start</f>
-        <v>46064</v>
-      </c>
-      <c r="F17" s="92">
+      <c r="F17" s="91">
         <f>E17+58</f>
         <v>46122</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I17" s="39"/>
@@ -4370,8 +4464,8 @@
       <c r="R17" s="39"/>
       <c r="S17" s="39"/>
       <c r="T17" s="39"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="39"/>
       <c r="W17" s="39"/>
       <c r="X17" s="39"/>
       <c r="Y17" s="39"/>
@@ -4443,26 +4537,26 @@
       <c r="CM17" s="39"/>
       <c r="CN17" s="39"/>
     </row>
-    <row r="18" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+    <row r="18" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A18" s="112"/>
       <c r="B18" s="40" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="42">
         <v>0</v>
       </c>
-      <c r="E18" s="92">
+      <c r="E18" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F18" s="93">
-        <f>F17</f>
+      <c r="F18" s="91">
+        <f>E18+58</f>
         <v>46122</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I18" s="39"/>
@@ -4477,8 +4571,8 @@
       <c r="R18" s="39"/>
       <c r="S18" s="39"/>
       <c r="T18" s="39"/>
-      <c r="U18" s="39"/>
-      <c r="V18" s="39"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
       <c r="W18" s="39"/>
       <c r="X18" s="39"/>
       <c r="Y18" s="39"/>
@@ -4550,229 +4644,234 @@
       <c r="CM18" s="39"/>
       <c r="CN18" s="39"/>
     </row>
-    <row r="19" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="81"/>
-      <c r="B19" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="4" t="str">
-        <f t="shared" ref="H19:H51" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
-        <v/>
-      </c>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="34"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="34"/>
-      <c r="AC19" s="34"/>
-      <c r="AD19" s="34"/>
-      <c r="AE19" s="34"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="34"/>
-      <c r="AH19" s="34"/>
-      <c r="AI19" s="34"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="34"/>
-      <c r="AL19" s="34"/>
-      <c r="AM19" s="34"/>
-      <c r="AN19" s="34"/>
-      <c r="AO19" s="34"/>
-      <c r="AP19" s="34"/>
-      <c r="AQ19" s="34"/>
-      <c r="AR19" s="34"/>
-      <c r="AS19" s="34"/>
-      <c r="AT19" s="34"/>
-      <c r="AU19" s="34"/>
-      <c r="AV19" s="34"/>
-      <c r="AW19" s="34"/>
-      <c r="AX19" s="34"/>
-      <c r="AY19" s="34"/>
-      <c r="AZ19" s="34"/>
-      <c r="BA19" s="34"/>
-      <c r="BB19" s="34"/>
-      <c r="BC19" s="34"/>
-      <c r="BD19" s="34"/>
-      <c r="BE19" s="34"/>
-      <c r="BF19" s="34"/>
-      <c r="BG19" s="34"/>
-      <c r="BH19" s="34"/>
-      <c r="BI19" s="34"/>
-      <c r="BJ19" s="34"/>
-      <c r="BK19" s="34"/>
-      <c r="BL19" s="34"/>
-      <c r="BM19" s="34"/>
-      <c r="BN19" s="34"/>
-      <c r="BO19" s="34"/>
-      <c r="BP19" s="34"/>
-      <c r="BQ19" s="34"/>
-      <c r="BR19" s="34"/>
-      <c r="BS19" s="34"/>
-      <c r="BT19" s="34"/>
-      <c r="BU19" s="34"/>
-      <c r="BV19" s="34"/>
-      <c r="BW19" s="34"/>
-      <c r="BX19" s="34"/>
-      <c r="BY19" s="34"/>
-      <c r="BZ19" s="34"/>
-      <c r="CA19" s="34"/>
-      <c r="CB19" s="34"/>
-      <c r="CC19" s="34"/>
-      <c r="CD19" s="34"/>
-      <c r="CE19" s="34"/>
-      <c r="CF19" s="34"/>
-      <c r="CG19" s="34"/>
-      <c r="CH19" s="34"/>
-      <c r="CI19" s="34"/>
-      <c r="CJ19" s="34"/>
-      <c r="CK19" s="34"/>
-      <c r="CL19" s="34"/>
-      <c r="CM19" s="34"/>
-      <c r="CN19" s="34"/>
-    </row>
-    <row r="20" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81"/>
-      <c r="B20" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="92">
+    <row r="19" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A19" s="12"/>
+      <c r="B19" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42">
+        <v>0</v>
+      </c>
+      <c r="E19" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F20" s="92">
-        <f>E20+58</f>
+      <c r="F19" s="92">
+        <f>F18</f>
         <v>46122</v>
       </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="4">
+        <f t="shared" ca="1" si="29"/>
+        <v>59</v>
+      </c>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="39"/>
+      <c r="U19" s="39"/>
+      <c r="V19" s="39"/>
+      <c r="W19" s="39"/>
+      <c r="X19" s="39"/>
+      <c r="Y19" s="39"/>
+      <c r="Z19" s="39"/>
+      <c r="AA19" s="39"/>
+      <c r="AB19" s="39"/>
+      <c r="AC19" s="39"/>
+      <c r="AD19" s="39"/>
+      <c r="AE19" s="39"/>
+      <c r="AF19" s="39"/>
+      <c r="AG19" s="39"/>
+      <c r="AH19" s="39"/>
+      <c r="AI19" s="39"/>
+      <c r="AJ19" s="39"/>
+      <c r="AK19" s="39"/>
+      <c r="AL19" s="39"/>
+      <c r="AM19" s="39"/>
+      <c r="AN19" s="39"/>
+      <c r="AO19" s="39"/>
+      <c r="AP19" s="39"/>
+      <c r="AQ19" s="39"/>
+      <c r="AR19" s="39"/>
+      <c r="AS19" s="39"/>
+      <c r="AT19" s="39"/>
+      <c r="AU19" s="39"/>
+      <c r="AV19" s="39"/>
+      <c r="AW19" s="39"/>
+      <c r="AX19" s="39"/>
+      <c r="AY19" s="39"/>
+      <c r="AZ19" s="39"/>
+      <c r="BA19" s="39"/>
+      <c r="BB19" s="39"/>
+      <c r="BC19" s="39"/>
+      <c r="BD19" s="39"/>
+      <c r="BE19" s="39"/>
+      <c r="BF19" s="39"/>
+      <c r="BG19" s="39"/>
+      <c r="BH19" s="39"/>
+      <c r="BI19" s="39"/>
+      <c r="BJ19" s="39"/>
+      <c r="BK19" s="39"/>
+      <c r="BL19" s="39"/>
+      <c r="BM19" s="39"/>
+      <c r="BN19" s="39"/>
+      <c r="BO19" s="39"/>
+      <c r="BP19" s="39"/>
+      <c r="BQ19" s="39"/>
+      <c r="BR19" s="39"/>
+      <c r="BS19" s="39"/>
+      <c r="BT19" s="39"/>
+      <c r="BU19" s="39"/>
+      <c r="BV19" s="39"/>
+      <c r="BW19" s="39"/>
+      <c r="BX19" s="39"/>
+      <c r="BY19" s="39"/>
+      <c r="BZ19" s="39"/>
+      <c r="CA19" s="39"/>
+      <c r="CB19" s="39"/>
+      <c r="CC19" s="39"/>
+      <c r="CD19" s="39"/>
+      <c r="CE19" s="39"/>
+      <c r="CF19" s="39"/>
+      <c r="CG19" s="39"/>
+      <c r="CH19" s="39"/>
+      <c r="CI19" s="39"/>
+      <c r="CJ19" s="39"/>
+      <c r="CK19" s="39"/>
+      <c r="CL19" s="39"/>
+      <c r="CM19" s="39"/>
+      <c r="CN19" s="39"/>
+    </row>
+    <row r="20" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A20" s="112"/>
+      <c r="B20" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="32"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="90"/>
       <c r="G20" s="14"/>
-      <c r="H20" s="4">
-        <f t="shared" si="30"/>
-        <v>59</v>
-      </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="39"/>
-      <c r="T20" s="39"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="39"/>
-      <c r="W20" s="39"/>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="39"/>
-      <c r="AA20" s="39"/>
-      <c r="AB20" s="39"/>
-      <c r="AC20" s="39"/>
-      <c r="AD20" s="39"/>
-      <c r="AE20" s="39"/>
-      <c r="AF20" s="39"/>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="39"/>
-      <c r="AI20" s="39"/>
-      <c r="AJ20" s="39"/>
-      <c r="AK20" s="39"/>
-      <c r="AL20" s="39"/>
-      <c r="AM20" s="39"/>
-      <c r="AN20" s="39"/>
-      <c r="AO20" s="39"/>
-      <c r="AP20" s="39"/>
-      <c r="AQ20" s="39"/>
-      <c r="AR20" s="39"/>
-      <c r="AS20" s="39"/>
-      <c r="AT20" s="39"/>
-      <c r="AU20" s="39"/>
-      <c r="AV20" s="39"/>
-      <c r="AW20" s="39"/>
-      <c r="AX20" s="39"/>
-      <c r="AY20" s="39"/>
-      <c r="AZ20" s="39"/>
-      <c r="BA20" s="39"/>
-      <c r="BB20" s="39"/>
-      <c r="BC20" s="39"/>
-      <c r="BD20" s="39"/>
-      <c r="BE20" s="39"/>
-      <c r="BF20" s="39"/>
-      <c r="BG20" s="39"/>
-      <c r="BH20" s="39"/>
-      <c r="BI20" s="39"/>
-      <c r="BJ20" s="39"/>
-      <c r="BK20" s="39"/>
-      <c r="BL20" s="39"/>
-      <c r="BM20" s="39"/>
-      <c r="BN20" s="39"/>
-      <c r="BO20" s="39"/>
-      <c r="BP20" s="39"/>
-      <c r="BQ20" s="39"/>
-      <c r="BR20" s="39"/>
-      <c r="BS20" s="39"/>
-      <c r="BT20" s="39"/>
-      <c r="BU20" s="39"/>
-      <c r="BV20" s="39"/>
-      <c r="BW20" s="39"/>
-      <c r="BX20" s="39"/>
-      <c r="BY20" s="39"/>
-      <c r="BZ20" s="39"/>
-      <c r="CA20" s="39"/>
-      <c r="CB20" s="39"/>
-      <c r="CC20" s="39"/>
-      <c r="CD20" s="39"/>
-      <c r="CE20" s="39"/>
-      <c r="CF20" s="39"/>
-      <c r="CG20" s="39"/>
-      <c r="CH20" s="39"/>
-      <c r="CI20" s="39"/>
-      <c r="CJ20" s="39"/>
-      <c r="CK20" s="39"/>
-      <c r="CL20" s="39"/>
-      <c r="CM20" s="39"/>
-      <c r="CN20" s="39"/>
+      <c r="H20" s="4" t="str">
+        <f t="shared" ref="H20:H52" ca="1" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v/>
+      </c>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="34"/>
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="34"/>
+      <c r="AE20" s="34"/>
+      <c r="AF20" s="34"/>
+      <c r="AG20" s="34"/>
+      <c r="AH20" s="34"/>
+      <c r="AI20" s="34"/>
+      <c r="AJ20" s="34"/>
+      <c r="AK20" s="34"/>
+      <c r="AL20" s="34"/>
+      <c r="AM20" s="34"/>
+      <c r="AN20" s="34"/>
+      <c r="AO20" s="34"/>
+      <c r="AP20" s="34"/>
+      <c r="AQ20" s="34"/>
+      <c r="AR20" s="34"/>
+      <c r="AS20" s="34"/>
+      <c r="AT20" s="34"/>
+      <c r="AU20" s="34"/>
+      <c r="AV20" s="34"/>
+      <c r="AW20" s="34"/>
+      <c r="AX20" s="34"/>
+      <c r="AY20" s="34"/>
+      <c r="AZ20" s="34"/>
+      <c r="BA20" s="34"/>
+      <c r="BB20" s="34"/>
+      <c r="BC20" s="34"/>
+      <c r="BD20" s="34"/>
+      <c r="BE20" s="34"/>
+      <c r="BF20" s="34"/>
+      <c r="BG20" s="34"/>
+      <c r="BH20" s="34"/>
+      <c r="BI20" s="34"/>
+      <c r="BJ20" s="34"/>
+      <c r="BK20" s="34"/>
+      <c r="BL20" s="34"/>
+      <c r="BM20" s="34"/>
+      <c r="BN20" s="34"/>
+      <c r="BO20" s="34"/>
+      <c r="BP20" s="34"/>
+      <c r="BQ20" s="34"/>
+      <c r="BR20" s="34"/>
+      <c r="BS20" s="34"/>
+      <c r="BT20" s="34"/>
+      <c r="BU20" s="34"/>
+      <c r="BV20" s="34"/>
+      <c r="BW20" s="34"/>
+      <c r="BX20" s="34"/>
+      <c r="BY20" s="34"/>
+      <c r="BZ20" s="34"/>
+      <c r="CA20" s="34"/>
+      <c r="CB20" s="34"/>
+      <c r="CC20" s="34"/>
+      <c r="CD20" s="34"/>
+      <c r="CE20" s="34"/>
+      <c r="CF20" s="34"/>
+      <c r="CG20" s="34"/>
+      <c r="CH20" s="34"/>
+      <c r="CI20" s="34"/>
+      <c r="CJ20" s="34"/>
+      <c r="CK20" s="34"/>
+      <c r="CL20" s="34"/>
+      <c r="CM20" s="34"/>
+      <c r="CN20" s="34"/>
     </row>
-    <row r="21" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81"/>
+    <row r="21" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A21" s="112"/>
       <c r="B21" s="36" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="92">
+      <c r="D21" s="38">
+        <v>0.33</v>
+      </c>
+      <c r="E21" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F21" s="92">
+      <c r="F21" s="91">
         <f>E21+58</f>
         <v>46122</v>
       </c>
       <c r="G21" s="14"/>
-      <c r="H21" s="4"/>
+      <c r="H21" s="4">
+        <f t="shared" ca="1" si="30"/>
+        <v>59</v>
+      </c>
       <c r="I21" s="39"/>
       <c r="J21" s="39"/>
       <c r="K21" s="39"/>
@@ -4858,28 +4957,23 @@
       <c r="CM21" s="39"/>
       <c r="CN21" s="39"/>
     </row>
-    <row r="22" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81"/>
-      <c r="B22" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42">
-        <v>0</v>
-      </c>
-      <c r="E22" s="92">
-        <f>F21+1</f>
-        <v>46123</v>
-      </c>
-      <c r="F22" s="93">
-        <f>E22+7</f>
-        <v>46130</v>
+    <row r="22" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A22" s="112"/>
+      <c r="B22" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="91">
+        <f>Project_Start</f>
+        <v>46064</v>
+      </c>
+      <c r="F22" s="91">
+        <f>E22+58</f>
+        <v>46122</v>
       </c>
       <c r="G22" s="14"/>
-      <c r="H22" s="4">
-        <f t="shared" si="30"/>
-        <v>8</v>
-      </c>
+      <c r="H22" s="4"/>
       <c r="I22" s="39"/>
       <c r="J22" s="39"/>
       <c r="K22" s="39"/>
@@ -4892,8 +4986,8 @@
       <c r="R22" s="39"/>
       <c r="S22" s="39"/>
       <c r="T22" s="39"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
+      <c r="U22" s="39"/>
+      <c r="V22" s="39"/>
       <c r="W22" s="39"/>
       <c r="X22" s="39"/>
       <c r="Y22" s="39"/>
@@ -4965,149 +5059,149 @@
       <c r="CM22" s="39"/>
       <c r="CN22" s="39"/>
     </row>
-    <row r="23" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="81"/>
-      <c r="B23" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="95"/>
+    <row r="23" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A23" s="112"/>
+      <c r="B23" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="41"/>
+      <c r="D23" s="42">
+        <v>0.33</v>
+      </c>
+      <c r="E23" s="91">
+        <f>F22+1</f>
+        <v>46123</v>
+      </c>
+      <c r="F23" s="92">
+        <f>E23+7</f>
+        <v>46130</v>
+      </c>
       <c r="G23" s="14"/>
-      <c r="H23" s="4" t="str">
-        <f t="shared" si="30"/>
+      <c r="H23" s="4">
+        <f t="shared" ca="1" si="30"/>
+        <v>8</v>
+      </c>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="43"/>
+      <c r="V23" s="43"/>
+      <c r="W23" s="39"/>
+      <c r="X23" s="39"/>
+      <c r="Y23" s="39"/>
+      <c r="Z23" s="39"/>
+      <c r="AA23" s="39"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="39"/>
+      <c r="AF23" s="39"/>
+      <c r="AG23" s="39"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="39"/>
+      <c r="AJ23" s="39"/>
+      <c r="AK23" s="39"/>
+      <c r="AL23" s="39"/>
+      <c r="AM23" s="39"/>
+      <c r="AN23" s="39"/>
+      <c r="AO23" s="39"/>
+      <c r="AP23" s="39"/>
+      <c r="AQ23" s="39"/>
+      <c r="AR23" s="39"/>
+      <c r="AS23" s="39"/>
+      <c r="AT23" s="39"/>
+      <c r="AU23" s="39"/>
+      <c r="AV23" s="39"/>
+      <c r="AW23" s="39"/>
+      <c r="AX23" s="39"/>
+      <c r="AY23" s="39"/>
+      <c r="AZ23" s="39"/>
+      <c r="BA23" s="39"/>
+      <c r="BB23" s="39"/>
+      <c r="BC23" s="39"/>
+      <c r="BD23" s="39"/>
+      <c r="BE23" s="39"/>
+      <c r="BF23" s="39"/>
+      <c r="BG23" s="39"/>
+      <c r="BH23" s="39"/>
+      <c r="BI23" s="39"/>
+      <c r="BJ23" s="39"/>
+      <c r="BK23" s="39"/>
+      <c r="BL23" s="39"/>
+      <c r="BM23" s="39"/>
+      <c r="BN23" s="39"/>
+      <c r="BO23" s="39"/>
+      <c r="BP23" s="39"/>
+      <c r="BQ23" s="39"/>
+      <c r="BR23" s="39"/>
+      <c r="BS23" s="39"/>
+      <c r="BT23" s="39"/>
+      <c r="BU23" s="39"/>
+      <c r="BV23" s="39"/>
+      <c r="BW23" s="39"/>
+      <c r="BX23" s="39"/>
+      <c r="BY23" s="39"/>
+      <c r="BZ23" s="39"/>
+      <c r="CA23" s="39"/>
+      <c r="CB23" s="39"/>
+      <c r="CC23" s="39"/>
+      <c r="CD23" s="39"/>
+      <c r="CE23" s="39"/>
+      <c r="CF23" s="39"/>
+      <c r="CG23" s="39"/>
+      <c r="CH23" s="39"/>
+      <c r="CI23" s="39"/>
+      <c r="CJ23" s="39"/>
+      <c r="CK23" s="39"/>
+      <c r="CL23" s="39"/>
+      <c r="CM23" s="39"/>
+      <c r="CN23" s="39"/>
+    </row>
+    <row r="24" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A24" s="112"/>
+      <c r="B24" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="45"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="4" t="str">
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="81"/>
-      <c r="B24" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="49">
+    <row r="25" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A25" s="112"/>
+      <c r="B25" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="48"/>
+      <c r="D25" s="49">
         <v>1</v>
       </c>
-      <c r="E24" s="96">
+      <c r="E25" s="95">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F24" s="96">
-        <f>E24+20</f>
+      <c r="F25" s="95">
+        <f>E25+20</f>
         <v>46084</v>
-      </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="4">
-        <f t="shared" si="30"/>
-        <v>21</v>
-      </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="39"/>
-      <c r="W24" s="39"/>
-      <c r="X24" s="39"/>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="39"/>
-      <c r="AB24" s="39"/>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="39"/>
-      <c r="AE24" s="39"/>
-      <c r="AF24" s="39"/>
-      <c r="AG24" s="39"/>
-      <c r="AH24" s="39"/>
-      <c r="AI24" s="39"/>
-      <c r="AJ24" s="39"/>
-      <c r="AK24" s="39"/>
-      <c r="AL24" s="39"/>
-      <c r="AM24" s="39"/>
-      <c r="AN24" s="39"/>
-      <c r="AO24" s="39"/>
-      <c r="AP24" s="39"/>
-      <c r="AQ24" s="39"/>
-      <c r="AR24" s="39"/>
-      <c r="AS24" s="39"/>
-      <c r="AT24" s="39"/>
-      <c r="AU24" s="39"/>
-      <c r="AV24" s="39"/>
-      <c r="AW24" s="39"/>
-      <c r="AX24" s="39"/>
-      <c r="AY24" s="39"/>
-      <c r="AZ24" s="39"/>
-      <c r="BA24" s="39"/>
-      <c r="BB24" s="39"/>
-      <c r="BC24" s="39"/>
-      <c r="BD24" s="39"/>
-      <c r="BE24" s="39"/>
-      <c r="BF24" s="39"/>
-      <c r="BG24" s="39"/>
-      <c r="BH24" s="39"/>
-      <c r="BI24" s="39"/>
-      <c r="BJ24" s="39"/>
-      <c r="BK24" s="39"/>
-      <c r="BL24" s="39"/>
-      <c r="BM24" s="39"/>
-      <c r="BN24" s="39"/>
-      <c r="BO24" s="39"/>
-      <c r="BP24" s="39"/>
-      <c r="BQ24" s="39"/>
-      <c r="BR24" s="39"/>
-      <c r="BS24" s="39"/>
-      <c r="BT24" s="39"/>
-      <c r="BU24" s="39"/>
-      <c r="BV24" s="39"/>
-      <c r="BW24" s="39"/>
-      <c r="BX24" s="39"/>
-      <c r="BY24" s="39"/>
-      <c r="BZ24" s="39"/>
-      <c r="CA24" s="39"/>
-      <c r="CB24" s="39"/>
-      <c r="CC24" s="39"/>
-      <c r="CD24" s="39"/>
-      <c r="CE24" s="39"/>
-      <c r="CF24" s="39"/>
-      <c r="CG24" s="39"/>
-      <c r="CH24" s="39"/>
-      <c r="CI24" s="39"/>
-      <c r="CJ24" s="39"/>
-      <c r="CK24" s="39"/>
-      <c r="CL24" s="39"/>
-      <c r="CM24" s="39"/>
-      <c r="CN24" s="39"/>
-    </row>
-    <row r="25" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="49">
-        <v>0.8</v>
-      </c>
-      <c r="E25" s="96">
-        <f>Project_Start</f>
-        <v>46064</v>
-      </c>
-      <c r="F25" s="96">
-        <f>E25+9</f>
-        <v>46073</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="4">
-        <f t="shared" si="30"/>
-        <v>10</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>21</v>
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="39"/>
@@ -5121,8 +5215,8 @@
       <c r="R25" s="39"/>
       <c r="S25" s="39"/>
       <c r="T25" s="39"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
+      <c r="U25" s="39"/>
+      <c r="V25" s="39"/>
       <c r="W25" s="39"/>
       <c r="X25" s="39"/>
       <c r="Y25" s="39"/>
@@ -5194,26 +5288,27 @@
       <c r="CM25" s="39"/>
       <c r="CN25" s="39"/>
     </row>
-    <row r="26" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A26" s="12"/>
       <c r="B26" s="47" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="48"/>
       <c r="D26" s="49">
-        <v>1</v>
-      </c>
-      <c r="E26" s="96">
-        <v>46083</v>
-      </c>
-      <c r="F26" s="96">
-        <f>E26+10</f>
-        <v>46093</v>
+        <v>0.8</v>
+      </c>
+      <c r="E26" s="95">
+        <f>Project_Start</f>
+        <v>46064</v>
+      </c>
+      <c r="F26" s="95">
+        <f>E26+9</f>
+        <v>46073</v>
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="4">
-        <f t="shared" si="30"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>10</v>
       </c>
       <c r="I26" s="39"/>
       <c r="J26" s="39"/>
@@ -5227,8 +5322,8 @@
       <c r="R26" s="39"/>
       <c r="S26" s="39"/>
       <c r="T26" s="39"/>
-      <c r="U26" s="39"/>
-      <c r="V26" s="39"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
       <c r="W26" s="39"/>
       <c r="X26" s="39"/>
       <c r="Y26" s="39"/>
@@ -5300,27 +5395,26 @@
       <c r="CM26" s="39"/>
       <c r="CN26" s="39"/>
     </row>
-    <row r="27" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A27" s="12"/>
       <c r="B27" s="47" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C27" s="48"/>
       <c r="D27" s="49">
         <v>1</v>
       </c>
-      <c r="E27" s="96">
-        <f>F26+1</f>
-        <v>46094</v>
-      </c>
-      <c r="F27" s="96">
-        <f>E27+7</f>
-        <v>46101</v>
+      <c r="E27" s="95">
+        <v>46083</v>
+      </c>
+      <c r="F27" s="95">
+        <f>E27+10</f>
+        <v>46093</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="4">
-        <f t="shared" si="30"/>
-        <v>8</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>11</v>
       </c>
       <c r="I27" s="39"/>
       <c r="J27" s="39"/>
@@ -5338,7 +5432,7 @@
       <c r="V27" s="39"/>
       <c r="W27" s="39"/>
       <c r="X27" s="39"/>
-      <c r="Y27" s="43"/>
+      <c r="Y27" s="39"/>
       <c r="Z27" s="39"/>
       <c r="AA27" s="39"/>
       <c r="AB27" s="39"/>
@@ -5407,26 +5501,26 @@
       <c r="CM27" s="39"/>
       <c r="CN27" s="39"/>
     </row>
-    <row r="28" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A28" s="12"/>
       <c r="B28" s="47" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C28" s="48"/>
       <c r="D28" s="49">
-        <v>0</v>
-      </c>
-      <c r="E28" s="96">
-        <f>E27</f>
+        <v>1</v>
+      </c>
+      <c r="E28" s="95">
+        <f>F27+1</f>
         <v>46094</v>
       </c>
-      <c r="F28" s="96">
+      <c r="F28" s="95">
         <f>E28+7</f>
         <v>46101</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I28" s="39"/>
@@ -5445,7 +5539,7 @@
       <c r="V28" s="39"/>
       <c r="W28" s="39"/>
       <c r="X28" s="39"/>
-      <c r="Y28" s="39"/>
+      <c r="Y28" s="43"/>
       <c r="Z28" s="39"/>
       <c r="AA28" s="39"/>
       <c r="AB28" s="39"/>
@@ -5514,25 +5608,28 @@
       <c r="CM28" s="39"/>
       <c r="CN28" s="39"/>
     </row>
-    <row r="29" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A29" s="12"/>
       <c r="B29" s="47" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="C29" s="48"/>
       <c r="D29" s="49">
         <v>1</v>
       </c>
-      <c r="E29" s="96">
-        <f>F27+1</f>
-        <v>46102</v>
-      </c>
-      <c r="F29" s="96">
+      <c r="E29" s="95">
+        <f>E28</f>
+        <v>46094</v>
+      </c>
+      <c r="F29" s="95">
         <f>E29+7</f>
-        <v>46109</v>
+        <v>46101</v>
       </c>
       <c r="G29" s="14"/>
-      <c r="H29" s="4"/>
+      <c r="H29" s="4">
+        <f t="shared" ca="1" si="30"/>
+        <v>8</v>
+      </c>
       <c r="I29" s="39"/>
       <c r="J29" s="39"/>
       <c r="K29" s="39"/>
@@ -5618,28 +5715,25 @@
       <c r="CM29" s="39"/>
       <c r="CN29" s="39"/>
     </row>
-    <row r="30" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A30" s="12"/>
       <c r="B30" s="47" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C30" s="48"/>
       <c r="D30" s="49">
         <v>1</v>
       </c>
-      <c r="E30" s="96">
+      <c r="E30" s="95">
         <f>F28+1</f>
         <v>46102</v>
       </c>
-      <c r="F30" s="96">
+      <c r="F30" s="95">
         <f>E30+7</f>
         <v>46109</v>
       </c>
       <c r="G30" s="14"/>
-      <c r="H30" s="4">
-        <f t="shared" si="30"/>
-        <v>8</v>
-      </c>
+      <c r="H30" s="4"/>
       <c r="I30" s="39"/>
       <c r="J30" s="39"/>
       <c r="K30" s="39"/>
@@ -5725,27 +5819,27 @@
       <c r="CM30" s="39"/>
       <c r="CN30" s="39"/>
     </row>
-    <row r="31" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A31" s="12"/>
       <c r="B31" s="47" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C31" s="48"/>
       <c r="D31" s="49">
-        <v>0.15</v>
-      </c>
-      <c r="E31" s="96">
-        <f>F30+1</f>
-        <v>46110</v>
-      </c>
-      <c r="F31" s="96">
-        <f>E31+3</f>
-        <v>46113</v>
+        <v>1</v>
+      </c>
+      <c r="E31" s="95">
+        <f>F29+1</f>
+        <v>46102</v>
+      </c>
+      <c r="F31" s="95">
+        <f>E31+7</f>
+        <v>46109</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="4">
-        <f t="shared" si="30"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>8</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="39"/>
@@ -5832,27 +5926,27 @@
       <c r="CM31" s="39"/>
       <c r="CN31" s="39"/>
     </row>
-    <row r="32" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A32" s="12"/>
       <c r="B32" s="47" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C32" s="48"/>
       <c r="D32" s="49">
-        <v>0</v>
-      </c>
-      <c r="E32" s="96">
+        <v>0.15</v>
+      </c>
+      <c r="E32" s="95">
         <f>F31+1</f>
-        <v>46114</v>
-      </c>
-      <c r="F32" s="96">
-        <f>E32+8</f>
-        <v>46122</v>
+        <v>46110</v>
+      </c>
+      <c r="F32" s="95">
+        <f>E32+3</f>
+        <v>46113</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="4">
-        <f t="shared" si="30"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>4</v>
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="39"/>
@@ -5939,27 +6033,27 @@
       <c r="CM32" s="39"/>
       <c r="CN32" s="39"/>
     </row>
-    <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A33" s="12"/>
       <c r="B33" s="47" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C33" s="48"/>
       <c r="D33" s="49">
         <v>0</v>
       </c>
-      <c r="E33" s="96">
-        <f>F31+1</f>
+      <c r="E33" s="95">
+        <f>F32+1</f>
         <v>46114</v>
       </c>
-      <c r="F33" s="96">
-        <f>E33+7</f>
-        <v>46121</v>
+      <c r="F33" s="95">
+        <f>E33+8</f>
+        <v>46122</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="4">
-        <f t="shared" si="30"/>
-        <v>8</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>9</v>
       </c>
       <c r="I33" s="39"/>
       <c r="J33" s="39"/>
@@ -6046,26 +6140,26 @@
       <c r="CM33" s="39"/>
       <c r="CN33" s="39"/>
     </row>
-    <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A34" s="12"/>
       <c r="B34" s="47" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C34" s="48"/>
       <c r="D34" s="49">
         <v>0</v>
       </c>
-      <c r="E34" s="96">
+      <c r="E34" s="95">
         <f>F32+1</f>
-        <v>46123</v>
-      </c>
-      <c r="F34" s="96">
+        <v>46114</v>
+      </c>
+      <c r="F34" s="95">
         <f>E34+7</f>
-        <v>46130</v>
+        <v>46121</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I34" s="39"/>
@@ -6153,233 +6247,233 @@
       <c r="CM34" s="39"/>
       <c r="CN34" s="39"/>
     </row>
-    <row r="35" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="12"/>
-      <c r="B35" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="51"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="98"/>
+      <c r="B35" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="48"/>
+      <c r="D35" s="49">
+        <v>0</v>
+      </c>
+      <c r="E35" s="95">
+        <f>F33+1</f>
+        <v>46123</v>
+      </c>
+      <c r="F35" s="95">
+        <f>E35+7</f>
+        <v>46130</v>
+      </c>
       <c r="G35" s="14"/>
-      <c r="H35" s="4" t="str">
-        <f t="shared" si="30"/>
+      <c r="H35" s="4">
+        <f t="shared" ca="1" si="30"/>
+        <v>8</v>
+      </c>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="39"/>
+      <c r="S35" s="39"/>
+      <c r="T35" s="39"/>
+      <c r="U35" s="39"/>
+      <c r="V35" s="39"/>
+      <c r="W35" s="39"/>
+      <c r="X35" s="39"/>
+      <c r="Y35" s="39"/>
+      <c r="Z35" s="39"/>
+      <c r="AA35" s="39"/>
+      <c r="AB35" s="39"/>
+      <c r="AC35" s="39"/>
+      <c r="AD35" s="39"/>
+      <c r="AE35" s="39"/>
+      <c r="AF35" s="39"/>
+      <c r="AG35" s="39"/>
+      <c r="AH35" s="39"/>
+      <c r="AI35" s="39"/>
+      <c r="AJ35" s="39"/>
+      <c r="AK35" s="39"/>
+      <c r="AL35" s="39"/>
+      <c r="AM35" s="39"/>
+      <c r="AN35" s="39"/>
+      <c r="AO35" s="39"/>
+      <c r="AP35" s="39"/>
+      <c r="AQ35" s="39"/>
+      <c r="AR35" s="39"/>
+      <c r="AS35" s="39"/>
+      <c r="AT35" s="39"/>
+      <c r="AU35" s="39"/>
+      <c r="AV35" s="39"/>
+      <c r="AW35" s="39"/>
+      <c r="AX35" s="39"/>
+      <c r="AY35" s="39"/>
+      <c r="AZ35" s="39"/>
+      <c r="BA35" s="39"/>
+      <c r="BB35" s="39"/>
+      <c r="BC35" s="39"/>
+      <c r="BD35" s="39"/>
+      <c r="BE35" s="39"/>
+      <c r="BF35" s="39"/>
+      <c r="BG35" s="39"/>
+      <c r="BH35" s="39"/>
+      <c r="BI35" s="39"/>
+      <c r="BJ35" s="39"/>
+      <c r="BK35" s="39"/>
+      <c r="BL35" s="39"/>
+      <c r="BM35" s="39"/>
+      <c r="BN35" s="39"/>
+      <c r="BO35" s="39"/>
+      <c r="BP35" s="39"/>
+      <c r="BQ35" s="39"/>
+      <c r="BR35" s="39"/>
+      <c r="BS35" s="39"/>
+      <c r="BT35" s="39"/>
+      <c r="BU35" s="39"/>
+      <c r="BV35" s="39"/>
+      <c r="BW35" s="39"/>
+      <c r="BX35" s="39"/>
+      <c r="BY35" s="39"/>
+      <c r="BZ35" s="39"/>
+      <c r="CA35" s="39"/>
+      <c r="CB35" s="39"/>
+      <c r="CC35" s="39"/>
+      <c r="CD35" s="39"/>
+      <c r="CE35" s="39"/>
+      <c r="CF35" s="39"/>
+      <c r="CG35" s="39"/>
+      <c r="CH35" s="39"/>
+      <c r="CI35" s="39"/>
+      <c r="CJ35" s="39"/>
+      <c r="CK35" s="39"/>
+      <c r="CL35" s="39"/>
+      <c r="CM35" s="39"/>
+      <c r="CN35" s="39"/>
+    </row>
+    <row r="36" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A36" s="12"/>
+      <c r="B36" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="51"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="97"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="4" t="str">
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="53"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="53"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="53"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="53"/>
-      <c r="V35" s="53"/>
-      <c r="W35" s="53"/>
-      <c r="X35" s="53"/>
-      <c r="Y35" s="53"/>
-      <c r="Z35" s="53"/>
-      <c r="AA35" s="53"/>
-      <c r="AB35" s="53"/>
-      <c r="AC35" s="53"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="53"/>
-      <c r="AF35" s="53"/>
-      <c r="AG35" s="53"/>
-      <c r="AH35" s="53"/>
-      <c r="AI35" s="53"/>
-      <c r="AJ35" s="53"/>
-      <c r="AK35" s="53"/>
-      <c r="AL35" s="53"/>
-      <c r="AM35" s="53"/>
-      <c r="AN35" s="53"/>
-      <c r="AO35" s="53"/>
-      <c r="AP35" s="53"/>
-      <c r="AQ35" s="53"/>
-      <c r="AR35" s="53"/>
-      <c r="AS35" s="53"/>
-      <c r="AT35" s="53"/>
-      <c r="AU35" s="53"/>
-      <c r="AV35" s="53"/>
-      <c r="AW35" s="53"/>
-      <c r="AX35" s="53"/>
-      <c r="AY35" s="53"/>
-      <c r="AZ35" s="53"/>
-      <c r="BA35" s="53"/>
-      <c r="BB35" s="53"/>
-      <c r="BC35" s="53"/>
-      <c r="BD35" s="53"/>
-      <c r="BE35" s="53"/>
-      <c r="BF35" s="53"/>
-      <c r="BG35" s="53"/>
-      <c r="BH35" s="53"/>
-      <c r="BI35" s="53"/>
-      <c r="BJ35" s="53"/>
-      <c r="BK35" s="53"/>
-      <c r="BL35" s="53"/>
-      <c r="BM35" s="53"/>
-      <c r="BN35" s="53"/>
-      <c r="BO35" s="53"/>
-      <c r="BP35" s="53"/>
-      <c r="BQ35" s="53"/>
-      <c r="BR35" s="53"/>
-      <c r="BS35" s="53"/>
-      <c r="BT35" s="53"/>
-      <c r="BU35" s="53"/>
-      <c r="BV35" s="53"/>
-      <c r="BW35" s="53"/>
-      <c r="BX35" s="53"/>
-      <c r="BY35" s="53"/>
-      <c r="BZ35" s="53"/>
-      <c r="CA35" s="53"/>
-      <c r="CB35" s="53"/>
-      <c r="CC35" s="53"/>
-      <c r="CD35" s="53"/>
-      <c r="CE35" s="53"/>
-      <c r="CF35" s="53"/>
-      <c r="CG35" s="53"/>
-      <c r="CH35" s="53"/>
-      <c r="CI35" s="53"/>
-      <c r="CJ35" s="53"/>
-      <c r="CK35" s="53"/>
-      <c r="CL35" s="53"/>
-      <c r="CM35" s="53"/>
-      <c r="CN35" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="53"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="53"/>
+      <c r="U36" s="53"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="53"/>
+      <c r="AC36" s="53"/>
+      <c r="AD36" s="53"/>
+      <c r="AE36" s="53"/>
+      <c r="AF36" s="53"/>
+      <c r="AG36" s="53"/>
+      <c r="AH36" s="53"/>
+      <c r="AI36" s="53"/>
+      <c r="AJ36" s="53"/>
+      <c r="AK36" s="53"/>
+      <c r="AL36" s="53"/>
+      <c r="AM36" s="53"/>
+      <c r="AN36" s="53"/>
+      <c r="AO36" s="53"/>
+      <c r="AP36" s="53"/>
+      <c r="AQ36" s="53"/>
+      <c r="AR36" s="53"/>
+      <c r="AS36" s="53"/>
+      <c r="AT36" s="53"/>
+      <c r="AU36" s="53"/>
+      <c r="AV36" s="53"/>
+      <c r="AW36" s="53"/>
+      <c r="AX36" s="53"/>
+      <c r="AY36" s="53"/>
+      <c r="AZ36" s="53"/>
+      <c r="BA36" s="53"/>
+      <c r="BB36" s="53"/>
+      <c r="BC36" s="53"/>
+      <c r="BD36" s="53"/>
+      <c r="BE36" s="53"/>
+      <c r="BF36" s="53"/>
+      <c r="BG36" s="53"/>
+      <c r="BH36" s="53"/>
+      <c r="BI36" s="53"/>
+      <c r="BJ36" s="53"/>
+      <c r="BK36" s="53"/>
+      <c r="BL36" s="53"/>
+      <c r="BM36" s="53"/>
+      <c r="BN36" s="53"/>
+      <c r="BO36" s="53"/>
+      <c r="BP36" s="53"/>
+      <c r="BQ36" s="53"/>
+      <c r="BR36" s="53"/>
+      <c r="BS36" s="53"/>
+      <c r="BT36" s="53"/>
+      <c r="BU36" s="53"/>
+      <c r="BV36" s="53"/>
+      <c r="BW36" s="53"/>
+      <c r="BX36" s="53"/>
+      <c r="BY36" s="53"/>
+      <c r="BZ36" s="53"/>
+      <c r="CA36" s="53"/>
+      <c r="CB36" s="53"/>
+      <c r="CC36" s="53"/>
+      <c r="CD36" s="53"/>
+      <c r="CE36" s="53"/>
+      <c r="CF36" s="53"/>
+      <c r="CG36" s="53"/>
+      <c r="CH36" s="53"/>
+      <c r="CI36" s="53"/>
+      <c r="CJ36" s="53"/>
+      <c r="CK36" s="53"/>
+      <c r="CL36" s="53"/>
+      <c r="CM36" s="53"/>
+      <c r="CN36" s="53"/>
     </row>
-    <row r="36" spans="1:92" s="35" customFormat="1" ht="68" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12"/>
-      <c r="B36" s="109" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="56">
-        <v>0.2</v>
-      </c>
-      <c r="E36" s="99">
-        <f>Project_Start</f>
-        <v>46064</v>
-      </c>
-      <c r="F36" s="99">
-        <f>E36+14</f>
-        <v>46078</v>
-      </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="4">
-        <f t="shared" si="30"/>
-        <v>15</v>
-      </c>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="39"/>
-      <c r="S36" s="39"/>
-      <c r="T36" s="39"/>
-      <c r="U36" s="39"/>
-      <c r="V36" s="39"/>
-      <c r="W36" s="39"/>
-      <c r="X36" s="39"/>
-      <c r="Y36" s="39"/>
-      <c r="Z36" s="39"/>
-      <c r="AA36" s="39"/>
-      <c r="AB36" s="39"/>
-      <c r="AC36" s="39"/>
-      <c r="AD36" s="39"/>
-      <c r="AE36" s="39"/>
-      <c r="AF36" s="39"/>
-      <c r="AG36" s="39"/>
-      <c r="AH36" s="39"/>
-      <c r="AI36" s="39"/>
-      <c r="AJ36" s="39"/>
-      <c r="AK36" s="39"/>
-      <c r="AL36" s="39"/>
-      <c r="AM36" s="39"/>
-      <c r="AN36" s="39"/>
-      <c r="AO36" s="39"/>
-      <c r="AP36" s="39"/>
-      <c r="AQ36" s="39"/>
-      <c r="AR36" s="39"/>
-      <c r="AS36" s="39"/>
-      <c r="AT36" s="39"/>
-      <c r="AU36" s="39"/>
-      <c r="AV36" s="39"/>
-      <c r="AW36" s="39"/>
-      <c r="AX36" s="39"/>
-      <c r="AY36" s="39"/>
-      <c r="AZ36" s="39"/>
-      <c r="BA36" s="39"/>
-      <c r="BB36" s="39"/>
-      <c r="BC36" s="39"/>
-      <c r="BD36" s="39"/>
-      <c r="BE36" s="39"/>
-      <c r="BF36" s="39"/>
-      <c r="BG36" s="39"/>
-      <c r="BH36" s="39"/>
-      <c r="BI36" s="39"/>
-      <c r="BJ36" s="39"/>
-      <c r="BK36" s="39"/>
-      <c r="BL36" s="39"/>
-      <c r="BM36" s="39"/>
-      <c r="BN36" s="39"/>
-      <c r="BO36" s="39"/>
-      <c r="BP36" s="39"/>
-      <c r="BQ36" s="39"/>
-      <c r="BR36" s="39"/>
-      <c r="BS36" s="39"/>
-      <c r="BT36" s="39"/>
-      <c r="BU36" s="39"/>
-      <c r="BV36" s="39"/>
-      <c r="BW36" s="39"/>
-      <c r="BX36" s="39"/>
-      <c r="BY36" s="39"/>
-      <c r="BZ36" s="39"/>
-      <c r="CA36" s="39"/>
-      <c r="CB36" s="39"/>
-      <c r="CC36" s="39"/>
-      <c r="CD36" s="39"/>
-      <c r="CE36" s="39"/>
-      <c r="CF36" s="39"/>
-      <c r="CG36" s="39"/>
-      <c r="CH36" s="39"/>
-      <c r="CI36" s="39"/>
-      <c r="CJ36" s="39"/>
-      <c r="CK36" s="39"/>
-      <c r="CL36" s="39"/>
-      <c r="CM36" s="39"/>
-      <c r="CN36" s="39"/>
-    </row>
-    <row r="37" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:92" s="35" customFormat="1" ht="68.099999999999994" customHeight="1" thickBot="1">
       <c r="A37" s="12"/>
-      <c r="B37" s="54" t="s">
-        <v>42</v>
+      <c r="B37" s="108" t="s">
+        <v>36</v>
       </c>
       <c r="C37" s="55"/>
       <c r="D37" s="56">
         <v>0.2</v>
       </c>
-      <c r="E37" s="99">
-        <f>F36+1</f>
-        <v>46079</v>
-      </c>
-      <c r="F37" s="99">
-        <f>F34</f>
-        <v>46130</v>
+      <c r="E37" s="98">
+        <f>Project_Start</f>
+        <v>46064</v>
+      </c>
+      <c r="F37" s="98">
+        <f>E37+14</f>
+        <v>46078</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="4">
-        <f t="shared" si="30"/>
-        <v>52</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>15</v>
       </c>
       <c r="I37" s="39"/>
       <c r="J37" s="39"/>
@@ -6466,235 +6560,235 @@
       <c r="CM37" s="39"/>
       <c r="CN37" s="39"/>
     </row>
-    <row r="38" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A38" s="12"/>
-      <c r="B38" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="98"/>
+      <c r="B38" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56">
+        <v>0.2</v>
+      </c>
+      <c r="E38" s="98">
+        <f>F37+1</f>
+        <v>46079</v>
+      </c>
+      <c r="F38" s="98">
+        <f>F35</f>
+        <v>46130</v>
+      </c>
       <c r="G38" s="14"/>
-      <c r="H38" s="4" t="str">
-        <f t="shared" si="30"/>
+      <c r="H38" s="4">
+        <f t="shared" ca="1" si="30"/>
+        <v>52</v>
+      </c>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
+      <c r="R38" s="39"/>
+      <c r="S38" s="39"/>
+      <c r="T38" s="39"/>
+      <c r="U38" s="39"/>
+      <c r="V38" s="39"/>
+      <c r="W38" s="39"/>
+      <c r="X38" s="39"/>
+      <c r="Y38" s="39"/>
+      <c r="Z38" s="39"/>
+      <c r="AA38" s="39"/>
+      <c r="AB38" s="39"/>
+      <c r="AC38" s="39"/>
+      <c r="AD38" s="39"/>
+      <c r="AE38" s="39"/>
+      <c r="AF38" s="39"/>
+      <c r="AG38" s="39"/>
+      <c r="AH38" s="39"/>
+      <c r="AI38" s="39"/>
+      <c r="AJ38" s="39"/>
+      <c r="AK38" s="39"/>
+      <c r="AL38" s="39"/>
+      <c r="AM38" s="39"/>
+      <c r="AN38" s="39"/>
+      <c r="AO38" s="39"/>
+      <c r="AP38" s="39"/>
+      <c r="AQ38" s="39"/>
+      <c r="AR38" s="39"/>
+      <c r="AS38" s="39"/>
+      <c r="AT38" s="39"/>
+      <c r="AU38" s="39"/>
+      <c r="AV38" s="39"/>
+      <c r="AW38" s="39"/>
+      <c r="AX38" s="39"/>
+      <c r="AY38" s="39"/>
+      <c r="AZ38" s="39"/>
+      <c r="BA38" s="39"/>
+      <c r="BB38" s="39"/>
+      <c r="BC38" s="39"/>
+      <c r="BD38" s="39"/>
+      <c r="BE38" s="39"/>
+      <c r="BF38" s="39"/>
+      <c r="BG38" s="39"/>
+      <c r="BH38" s="39"/>
+      <c r="BI38" s="39"/>
+      <c r="BJ38" s="39"/>
+      <c r="BK38" s="39"/>
+      <c r="BL38" s="39"/>
+      <c r="BM38" s="39"/>
+      <c r="BN38" s="39"/>
+      <c r="BO38" s="39"/>
+      <c r="BP38" s="39"/>
+      <c r="BQ38" s="39"/>
+      <c r="BR38" s="39"/>
+      <c r="BS38" s="39"/>
+      <c r="BT38" s="39"/>
+      <c r="BU38" s="39"/>
+      <c r="BV38" s="39"/>
+      <c r="BW38" s="39"/>
+      <c r="BX38" s="39"/>
+      <c r="BY38" s="39"/>
+      <c r="BZ38" s="39"/>
+      <c r="CA38" s="39"/>
+      <c r="CB38" s="39"/>
+      <c r="CC38" s="39"/>
+      <c r="CD38" s="39"/>
+      <c r="CE38" s="39"/>
+      <c r="CF38" s="39"/>
+      <c r="CG38" s="39"/>
+      <c r="CH38" s="39"/>
+      <c r="CI38" s="39"/>
+      <c r="CJ38" s="39"/>
+      <c r="CK38" s="39"/>
+      <c r="CL38" s="39"/>
+      <c r="CM38" s="39"/>
+      <c r="CN38" s="39"/>
+    </row>
+    <row r="39" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A39" s="12"/>
+      <c r="B39" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="51"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="96"/>
+      <c r="F39" s="97"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="4" t="str">
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53"/>
-      <c r="O38" s="53"/>
-      <c r="P38" s="53"/>
-      <c r="Q38" s="53"/>
-      <c r="R38" s="53"/>
-      <c r="S38" s="53"/>
-      <c r="T38" s="53"/>
-      <c r="U38" s="53"/>
-      <c r="V38" s="53"/>
-      <c r="W38" s="53"/>
-      <c r="X38" s="53"/>
-      <c r="Y38" s="53"/>
-      <c r="Z38" s="53"/>
-      <c r="AA38" s="53"/>
-      <c r="AB38" s="53"/>
-      <c r="AC38" s="53"/>
-      <c r="AD38" s="53"/>
-      <c r="AE38" s="53"/>
-      <c r="AF38" s="53"/>
-      <c r="AG38" s="53"/>
-      <c r="AH38" s="53"/>
-      <c r="AI38" s="53"/>
-      <c r="AJ38" s="53"/>
-      <c r="AK38" s="53"/>
-      <c r="AL38" s="53"/>
-      <c r="AM38" s="53"/>
-      <c r="AN38" s="53"/>
-      <c r="AO38" s="53"/>
-      <c r="AP38" s="53"/>
-      <c r="AQ38" s="53"/>
-      <c r="AR38" s="53"/>
-      <c r="AS38" s="53"/>
-      <c r="AT38" s="53"/>
-      <c r="AU38" s="53"/>
-      <c r="AV38" s="53"/>
-      <c r="AW38" s="53"/>
-      <c r="AX38" s="53"/>
-      <c r="AY38" s="53"/>
-      <c r="AZ38" s="53"/>
-      <c r="BA38" s="53"/>
-      <c r="BB38" s="53"/>
-      <c r="BC38" s="53"/>
-      <c r="BD38" s="53"/>
-      <c r="BE38" s="53"/>
-      <c r="BF38" s="53"/>
-      <c r="BG38" s="53"/>
-      <c r="BH38" s="53"/>
-      <c r="BI38" s="53"/>
-      <c r="BJ38" s="53"/>
-      <c r="BK38" s="53"/>
-      <c r="BL38" s="53"/>
-      <c r="BM38" s="53"/>
-      <c r="BN38" s="53"/>
-      <c r="BO38" s="53"/>
-      <c r="BP38" s="53"/>
-      <c r="BQ38" s="53"/>
-      <c r="BR38" s="53"/>
-      <c r="BS38" s="53"/>
-      <c r="BT38" s="53"/>
-      <c r="BU38" s="53"/>
-      <c r="BV38" s="53"/>
-      <c r="BW38" s="53"/>
-      <c r="BX38" s="53"/>
-      <c r="BY38" s="53"/>
-      <c r="BZ38" s="53"/>
-      <c r="CA38" s="53"/>
-      <c r="CB38" s="53"/>
-      <c r="CC38" s="53"/>
-      <c r="CD38" s="53"/>
-      <c r="CE38" s="53"/>
-      <c r="CF38" s="53"/>
-      <c r="CG38" s="53"/>
-      <c r="CH38" s="53"/>
-      <c r="CI38" s="53"/>
-      <c r="CJ38" s="53"/>
-      <c r="CK38" s="53"/>
-      <c r="CL38" s="53"/>
-      <c r="CM38" s="53"/>
-      <c r="CN38" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="53"/>
+      <c r="N39" s="53"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="53"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="53"/>
+      <c r="S39" s="53"/>
+      <c r="T39" s="53"/>
+      <c r="U39" s="53"/>
+      <c r="V39" s="53"/>
+      <c r="W39" s="53"/>
+      <c r="X39" s="53"/>
+      <c r="Y39" s="53"/>
+      <c r="Z39" s="53"/>
+      <c r="AA39" s="53"/>
+      <c r="AB39" s="53"/>
+      <c r="AC39" s="53"/>
+      <c r="AD39" s="53"/>
+      <c r="AE39" s="53"/>
+      <c r="AF39" s="53"/>
+      <c r="AG39" s="53"/>
+      <c r="AH39" s="53"/>
+      <c r="AI39" s="53"/>
+      <c r="AJ39" s="53"/>
+      <c r="AK39" s="53"/>
+      <c r="AL39" s="53"/>
+      <c r="AM39" s="53"/>
+      <c r="AN39" s="53"/>
+      <c r="AO39" s="53"/>
+      <c r="AP39" s="53"/>
+      <c r="AQ39" s="53"/>
+      <c r="AR39" s="53"/>
+      <c r="AS39" s="53"/>
+      <c r="AT39" s="53"/>
+      <c r="AU39" s="53"/>
+      <c r="AV39" s="53"/>
+      <c r="AW39" s="53"/>
+      <c r="AX39" s="53"/>
+      <c r="AY39" s="53"/>
+      <c r="AZ39" s="53"/>
+      <c r="BA39" s="53"/>
+      <c r="BB39" s="53"/>
+      <c r="BC39" s="53"/>
+      <c r="BD39" s="53"/>
+      <c r="BE39" s="53"/>
+      <c r="BF39" s="53"/>
+      <c r="BG39" s="53"/>
+      <c r="BH39" s="53"/>
+      <c r="BI39" s="53"/>
+      <c r="BJ39" s="53"/>
+      <c r="BK39" s="53"/>
+      <c r="BL39" s="53"/>
+      <c r="BM39" s="53"/>
+      <c r="BN39" s="53"/>
+      <c r="BO39" s="53"/>
+      <c r="BP39" s="53"/>
+      <c r="BQ39" s="53"/>
+      <c r="BR39" s="53"/>
+      <c r="BS39" s="53"/>
+      <c r="BT39" s="53"/>
+      <c r="BU39" s="53"/>
+      <c r="BV39" s="53"/>
+      <c r="BW39" s="53"/>
+      <c r="BX39" s="53"/>
+      <c r="BY39" s="53"/>
+      <c r="BZ39" s="53"/>
+      <c r="CA39" s="53"/>
+      <c r="CB39" s="53"/>
+      <c r="CC39" s="53"/>
+      <c r="CD39" s="53"/>
+      <c r="CE39" s="53"/>
+      <c r="CF39" s="53"/>
+      <c r="CG39" s="53"/>
+      <c r="CH39" s="53"/>
+      <c r="CI39" s="53"/>
+      <c r="CJ39" s="53"/>
+      <c r="CK39" s="53"/>
+      <c r="CL39" s="53"/>
+      <c r="CM39" s="53"/>
+      <c r="CN39" s="53"/>
     </row>
-    <row r="39" spans="1:92" s="35" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
-      <c r="B39" s="109" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="55"/>
-      <c r="D39" s="56">
+    <row r="40" spans="1:92" s="35" customFormat="1" ht="42.95" thickBot="1">
+      <c r="A40" s="12"/>
+      <c r="B40" s="108" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="56">
         <v>0.9</v>
       </c>
-      <c r="E39" s="99">
+      <c r="E40" s="98">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F39" s="99">
-        <f>E39+21</f>
+      <c r="F40" s="98">
+        <f>E40+21</f>
         <v>46085</v>
       </c>
-      <c r="G39" s="111" t="s">
-        <v>64</v>
-      </c>
-      <c r="H39" s="4">
-        <f t="shared" si="30"/>
+      <c r="G40" s="110" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" ca="1" si="30"/>
         <v>22</v>
-      </c>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="39"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="39"/>
-      <c r="S39" s="39"/>
-      <c r="T39" s="39"/>
-      <c r="U39" s="39"/>
-      <c r="V39" s="39"/>
-      <c r="W39" s="39"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="39"/>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="39"/>
-      <c r="AB39" s="39"/>
-      <c r="AC39" s="39"/>
-      <c r="AD39" s="39"/>
-      <c r="AE39" s="39"/>
-      <c r="AF39" s="39"/>
-      <c r="AG39" s="39"/>
-      <c r="AH39" s="39"/>
-      <c r="AI39" s="39"/>
-      <c r="AJ39" s="39"/>
-      <c r="AK39" s="39"/>
-      <c r="AL39" s="39"/>
-      <c r="AM39" s="39"/>
-      <c r="AN39" s="39"/>
-      <c r="AO39" s="39"/>
-      <c r="AP39" s="39"/>
-      <c r="AQ39" s="39"/>
-      <c r="AR39" s="39"/>
-      <c r="AS39" s="39"/>
-      <c r="AT39" s="39"/>
-      <c r="AU39" s="39"/>
-      <c r="AV39" s="39"/>
-      <c r="AW39" s="39"/>
-      <c r="AX39" s="39"/>
-      <c r="AY39" s="39"/>
-      <c r="AZ39" s="39"/>
-      <c r="BA39" s="39"/>
-      <c r="BB39" s="39"/>
-      <c r="BC39" s="39"/>
-      <c r="BD39" s="39"/>
-      <c r="BE39" s="39"/>
-      <c r="BF39" s="39"/>
-      <c r="BG39" s="39"/>
-      <c r="BH39" s="39"/>
-      <c r="BI39" s="39"/>
-      <c r="BJ39" s="39"/>
-      <c r="BK39" s="39"/>
-      <c r="BL39" s="39"/>
-      <c r="BM39" s="39"/>
-      <c r="BN39" s="39"/>
-      <c r="BO39" s="39"/>
-      <c r="BP39" s="39"/>
-      <c r="BQ39" s="39"/>
-      <c r="BR39" s="39"/>
-      <c r="BS39" s="39"/>
-      <c r="BT39" s="39"/>
-      <c r="BU39" s="39"/>
-      <c r="BV39" s="39"/>
-      <c r="BW39" s="39"/>
-      <c r="BX39" s="39"/>
-      <c r="BY39" s="39"/>
-      <c r="BZ39" s="39"/>
-      <c r="CA39" s="39"/>
-      <c r="CB39" s="39"/>
-      <c r="CC39" s="39"/>
-      <c r="CD39" s="39"/>
-      <c r="CE39" s="39"/>
-      <c r="CF39" s="39"/>
-      <c r="CG39" s="39"/>
-      <c r="CH39" s="39"/>
-      <c r="CI39" s="39"/>
-      <c r="CJ39" s="39"/>
-      <c r="CK39" s="39"/>
-      <c r="CL39" s="39"/>
-      <c r="CM39" s="39"/>
-      <c r="CN39" s="39"/>
-    </row>
-    <row r="40" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12"/>
-      <c r="B40" s="109" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="56">
-        <v>0.3</v>
-      </c>
-      <c r="E40" s="99">
-        <f>F39</f>
-        <v>46085</v>
-      </c>
-      <c r="F40" s="99">
-        <f>F34</f>
-        <v>46130</v>
-      </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="4">
-        <f t="shared" si="30"/>
-        <v>46</v>
       </c>
       <c r="I40" s="39"/>
       <c r="J40" s="39"/>
@@ -6781,25 +6875,28 @@
       <c r="CM40" s="39"/>
       <c r="CN40" s="39"/>
     </row>
-    <row r="41" spans="1:92" s="35" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1">
       <c r="A41" s="12"/>
-      <c r="B41" s="54" t="s">
-        <v>65</v>
+      <c r="B41" s="108" t="s">
+        <v>41</v>
       </c>
       <c r="C41" s="55"/>
       <c r="D41" s="56">
-        <v>1</v>
-      </c>
-      <c r="E41" s="99">
-        <f>F39</f>
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="98">
+        <f>F40</f>
         <v>46085</v>
       </c>
-      <c r="F41" s="99">
-        <f>F34</f>
+      <c r="F41" s="98">
+        <f>F35</f>
         <v>46130</v>
       </c>
       <c r="G41" s="14"/>
-      <c r="H41" s="4"/>
+      <c r="H41" s="4">
+        <f t="shared" ca="1" si="30"/>
+        <v>46</v>
+      </c>
       <c r="I41" s="39"/>
       <c r="J41" s="39"/>
       <c r="K41" s="39"/>
@@ -6885,22 +6982,25 @@
       <c r="CM41" s="39"/>
       <c r="CN41" s="39"/>
     </row>
-    <row r="42" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:92" s="35" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
       <c r="A42" s="12"/>
       <c r="B42" s="54" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C42" s="55"/>
       <c r="D42" s="56">
-        <v>0</v>
-      </c>
-      <c r="E42" s="99"/>
-      <c r="F42" s="99"/>
+        <v>1</v>
+      </c>
+      <c r="E42" s="98">
+        <f>F40</f>
+        <v>46085</v>
+      </c>
+      <c r="F42" s="98">
+        <f>F35</f>
+        <v>46130</v>
+      </c>
       <c r="G42" s="14"/>
-      <c r="H42" s="4" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
+      <c r="H42" s="4"/>
       <c r="I42" s="39"/>
       <c r="J42" s="39"/>
       <c r="K42" s="39"/>
@@ -6986,232 +7086,227 @@
       <c r="CM42" s="39"/>
       <c r="CN42" s="39"/>
     </row>
-    <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A43" s="12"/>
-      <c r="B43" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="58"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="100"/>
-      <c r="F43" s="101"/>
+      <c r="B43" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="55"/>
+      <c r="D43" s="56">
+        <v>0</v>
+      </c>
+      <c r="E43" s="98"/>
+      <c r="F43" s="98"/>
       <c r="G43" s="14"/>
       <c r="H43" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
-      <c r="I43" s="60"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="60"/>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="60"/>
-      <c r="O43" s="60"/>
-      <c r="P43" s="60"/>
-      <c r="Q43" s="60"/>
-      <c r="R43" s="60"/>
-      <c r="S43" s="60"/>
-      <c r="T43" s="60"/>
-      <c r="U43" s="60"/>
-      <c r="V43" s="60"/>
-      <c r="W43" s="60"/>
-      <c r="X43" s="60"/>
-      <c r="Y43" s="60"/>
-      <c r="Z43" s="60"/>
-      <c r="AA43" s="60"/>
-      <c r="AB43" s="60"/>
-      <c r="AC43" s="60"/>
-      <c r="AD43" s="60"/>
-      <c r="AE43" s="60"/>
-      <c r="AF43" s="60"/>
-      <c r="AG43" s="60"/>
-      <c r="AH43" s="60"/>
-      <c r="AI43" s="60"/>
-      <c r="AJ43" s="60"/>
-      <c r="AK43" s="60"/>
-      <c r="AL43" s="60"/>
-      <c r="AM43" s="60"/>
-      <c r="AN43" s="60"/>
-      <c r="AO43" s="60"/>
-      <c r="AP43" s="60"/>
-      <c r="AQ43" s="60"/>
-      <c r="AR43" s="60"/>
-      <c r="AS43" s="60"/>
-      <c r="AT43" s="60"/>
-      <c r="AU43" s="60"/>
-      <c r="AV43" s="60"/>
-      <c r="AW43" s="60"/>
-      <c r="AX43" s="60"/>
-      <c r="AY43" s="60"/>
-      <c r="AZ43" s="60"/>
-      <c r="BA43" s="60"/>
-      <c r="BB43" s="60"/>
-      <c r="BC43" s="60"/>
-      <c r="BD43" s="60"/>
-      <c r="BE43" s="60"/>
-      <c r="BF43" s="60"/>
-      <c r="BG43" s="60"/>
-      <c r="BH43" s="60"/>
-      <c r="BI43" s="60"/>
-      <c r="BJ43" s="60"/>
-      <c r="BK43" s="60"/>
-      <c r="BL43" s="60"/>
-      <c r="BM43" s="60"/>
-      <c r="BN43" s="60"/>
-      <c r="BO43" s="60"/>
-      <c r="BP43" s="60"/>
-      <c r="BQ43" s="60"/>
-      <c r="BR43" s="60"/>
-      <c r="BS43" s="60"/>
-      <c r="BT43" s="60"/>
-      <c r="BU43" s="60"/>
-      <c r="BV43" s="60"/>
-      <c r="BW43" s="60"/>
-      <c r="BX43" s="60"/>
-      <c r="BY43" s="60"/>
-      <c r="BZ43" s="60"/>
-      <c r="CA43" s="60"/>
-      <c r="CB43" s="60"/>
-      <c r="CC43" s="60"/>
-      <c r="CD43" s="60"/>
-      <c r="CE43" s="60"/>
-      <c r="CF43" s="60"/>
-      <c r="CG43" s="60"/>
-      <c r="CH43" s="60"/>
-      <c r="CI43" s="60"/>
-      <c r="CJ43" s="60"/>
-      <c r="CK43" s="60"/>
-      <c r="CL43" s="60"/>
-      <c r="CM43" s="60"/>
-      <c r="CN43" s="60"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
+      <c r="M43" s="39"/>
+      <c r="N43" s="39"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="39"/>
+      <c r="Q43" s="39"/>
+      <c r="R43" s="39"/>
+      <c r="S43" s="39"/>
+      <c r="T43" s="39"/>
+      <c r="U43" s="39"/>
+      <c r="V43" s="39"/>
+      <c r="W43" s="39"/>
+      <c r="X43" s="39"/>
+      <c r="Y43" s="39"/>
+      <c r="Z43" s="39"/>
+      <c r="AA43" s="39"/>
+      <c r="AB43" s="39"/>
+      <c r="AC43" s="39"/>
+      <c r="AD43" s="39"/>
+      <c r="AE43" s="39"/>
+      <c r="AF43" s="39"/>
+      <c r="AG43" s="39"/>
+      <c r="AH43" s="39"/>
+      <c r="AI43" s="39"/>
+      <c r="AJ43" s="39"/>
+      <c r="AK43" s="39"/>
+      <c r="AL43" s="39"/>
+      <c r="AM43" s="39"/>
+      <c r="AN43" s="39"/>
+      <c r="AO43" s="39"/>
+      <c r="AP43" s="39"/>
+      <c r="AQ43" s="39"/>
+      <c r="AR43" s="39"/>
+      <c r="AS43" s="39"/>
+      <c r="AT43" s="39"/>
+      <c r="AU43" s="39"/>
+      <c r="AV43" s="39"/>
+      <c r="AW43" s="39"/>
+      <c r="AX43" s="39"/>
+      <c r="AY43" s="39"/>
+      <c r="AZ43" s="39"/>
+      <c r="BA43" s="39"/>
+      <c r="BB43" s="39"/>
+      <c r="BC43" s="39"/>
+      <c r="BD43" s="39"/>
+      <c r="BE43" s="39"/>
+      <c r="BF43" s="39"/>
+      <c r="BG43" s="39"/>
+      <c r="BH43" s="39"/>
+      <c r="BI43" s="39"/>
+      <c r="BJ43" s="39"/>
+      <c r="BK43" s="39"/>
+      <c r="BL43" s="39"/>
+      <c r="BM43" s="39"/>
+      <c r="BN43" s="39"/>
+      <c r="BO43" s="39"/>
+      <c r="BP43" s="39"/>
+      <c r="BQ43" s="39"/>
+      <c r="BR43" s="39"/>
+      <c r="BS43" s="39"/>
+      <c r="BT43" s="39"/>
+      <c r="BU43" s="39"/>
+      <c r="BV43" s="39"/>
+      <c r="BW43" s="39"/>
+      <c r="BX43" s="39"/>
+      <c r="BY43" s="39"/>
+      <c r="BZ43" s="39"/>
+      <c r="CA43" s="39"/>
+      <c r="CB43" s="39"/>
+      <c r="CC43" s="39"/>
+      <c r="CD43" s="39"/>
+      <c r="CE43" s="39"/>
+      <c r="CF43" s="39"/>
+      <c r="CG43" s="39"/>
+      <c r="CH43" s="39"/>
+      <c r="CI43" s="39"/>
+      <c r="CJ43" s="39"/>
+      <c r="CK43" s="39"/>
+      <c r="CL43" s="39"/>
+      <c r="CM43" s="39"/>
+      <c r="CN43" s="39"/>
     </row>
-    <row r="44" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A44" s="12"/>
-      <c r="B44" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="63">
-        <v>1</v>
-      </c>
-      <c r="E44" s="102">
-        <f>E36</f>
-        <v>46064</v>
-      </c>
-      <c r="F44" s="102">
-        <f>E48-3</f>
-        <v>46157</v>
-      </c>
+      <c r="B44" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="58"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="100"/>
       <c r="G44" s="14"/>
-      <c r="H44" s="4">
-        <f t="shared" si="30"/>
-        <v>94</v>
-      </c>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="39"/>
-      <c r="Q44" s="39"/>
-      <c r="R44" s="39"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="39"/>
-      <c r="U44" s="39"/>
-      <c r="V44" s="39"/>
-      <c r="W44" s="39"/>
-      <c r="X44" s="39"/>
-      <c r="Y44" s="39"/>
-      <c r="Z44" s="39"/>
-      <c r="AA44" s="39"/>
-      <c r="AB44" s="39"/>
-      <c r="AC44" s="39"/>
-      <c r="AD44" s="39"/>
-      <c r="AE44" s="39"/>
-      <c r="AF44" s="39"/>
-      <c r="AG44" s="39"/>
-      <c r="AH44" s="39"/>
-      <c r="AI44" s="39"/>
-      <c r="AJ44" s="39"/>
-      <c r="AK44" s="39"/>
-      <c r="AL44" s="39"/>
-      <c r="AM44" s="39"/>
-      <c r="AN44" s="39"/>
-      <c r="AO44" s="39"/>
-      <c r="AP44" s="39"/>
-      <c r="AQ44" s="39"/>
-      <c r="AR44" s="39"/>
-      <c r="AS44" s="39"/>
-      <c r="AT44" s="39"/>
-      <c r="AU44" s="39"/>
-      <c r="AV44" s="39"/>
-      <c r="AW44" s="39"/>
-      <c r="AX44" s="39"/>
-      <c r="AY44" s="39"/>
-      <c r="AZ44" s="39"/>
-      <c r="BA44" s="39"/>
-      <c r="BB44" s="39"/>
-      <c r="BC44" s="39"/>
-      <c r="BD44" s="39"/>
-      <c r="BE44" s="39"/>
-      <c r="BF44" s="39"/>
-      <c r="BG44" s="39"/>
-      <c r="BH44" s="39"/>
-      <c r="BI44" s="39"/>
-      <c r="BJ44" s="39"/>
-      <c r="BK44" s="39"/>
-      <c r="BL44" s="39"/>
-      <c r="BM44" s="39"/>
-      <c r="BN44" s="39"/>
-      <c r="BO44" s="39"/>
-      <c r="BP44" s="39"/>
-      <c r="BQ44" s="39"/>
-      <c r="BR44" s="39"/>
-      <c r="BS44" s="39"/>
-      <c r="BT44" s="39"/>
-      <c r="BU44" s="39"/>
-      <c r="BV44" s="39"/>
-      <c r="BW44" s="39"/>
-      <c r="BX44" s="39"/>
-      <c r="BY44" s="39"/>
-      <c r="BZ44" s="39"/>
-      <c r="CA44" s="39"/>
-      <c r="CB44" s="39"/>
-      <c r="CC44" s="39"/>
-      <c r="CD44" s="39"/>
-      <c r="CE44" s="39"/>
-      <c r="CF44" s="39"/>
-      <c r="CG44" s="39"/>
-      <c r="CH44" s="39"/>
-      <c r="CI44" s="39"/>
-      <c r="CJ44" s="39"/>
-      <c r="CK44" s="39"/>
-      <c r="CL44" s="39"/>
-      <c r="CM44" s="39"/>
-      <c r="CN44" s="39"/>
+      <c r="H44" s="4" t="str">
+        <f t="shared" ca="1" si="30"/>
+        <v/>
+      </c>
+      <c r="I44" s="60"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="60"/>
+      <c r="L44" s="60"/>
+      <c r="M44" s="60"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="60"/>
+      <c r="P44" s="60"/>
+      <c r="Q44" s="60"/>
+      <c r="R44" s="60"/>
+      <c r="S44" s="60"/>
+      <c r="T44" s="60"/>
+      <c r="U44" s="60"/>
+      <c r="V44" s="60"/>
+      <c r="W44" s="60"/>
+      <c r="X44" s="60"/>
+      <c r="Y44" s="60"/>
+      <c r="Z44" s="60"/>
+      <c r="AA44" s="60"/>
+      <c r="AB44" s="60"/>
+      <c r="AC44" s="60"/>
+      <c r="AD44" s="60"/>
+      <c r="AE44" s="60"/>
+      <c r="AF44" s="60"/>
+      <c r="AG44" s="60"/>
+      <c r="AH44" s="60"/>
+      <c r="AI44" s="60"/>
+      <c r="AJ44" s="60"/>
+      <c r="AK44" s="60"/>
+      <c r="AL44" s="60"/>
+      <c r="AM44" s="60"/>
+      <c r="AN44" s="60"/>
+      <c r="AO44" s="60"/>
+      <c r="AP44" s="60"/>
+      <c r="AQ44" s="60"/>
+      <c r="AR44" s="60"/>
+      <c r="AS44" s="60"/>
+      <c r="AT44" s="60"/>
+      <c r="AU44" s="60"/>
+      <c r="AV44" s="60"/>
+      <c r="AW44" s="60"/>
+      <c r="AX44" s="60"/>
+      <c r="AY44" s="60"/>
+      <c r="AZ44" s="60"/>
+      <c r="BA44" s="60"/>
+      <c r="BB44" s="60"/>
+      <c r="BC44" s="60"/>
+      <c r="BD44" s="60"/>
+      <c r="BE44" s="60"/>
+      <c r="BF44" s="60"/>
+      <c r="BG44" s="60"/>
+      <c r="BH44" s="60"/>
+      <c r="BI44" s="60"/>
+      <c r="BJ44" s="60"/>
+      <c r="BK44" s="60"/>
+      <c r="BL44" s="60"/>
+      <c r="BM44" s="60"/>
+      <c r="BN44" s="60"/>
+      <c r="BO44" s="60"/>
+      <c r="BP44" s="60"/>
+      <c r="BQ44" s="60"/>
+      <c r="BR44" s="60"/>
+      <c r="BS44" s="60"/>
+      <c r="BT44" s="60"/>
+      <c r="BU44" s="60"/>
+      <c r="BV44" s="60"/>
+      <c r="BW44" s="60"/>
+      <c r="BX44" s="60"/>
+      <c r="BY44" s="60"/>
+      <c r="BZ44" s="60"/>
+      <c r="CA44" s="60"/>
+      <c r="CB44" s="60"/>
+      <c r="CC44" s="60"/>
+      <c r="CD44" s="60"/>
+      <c r="CE44" s="60"/>
+      <c r="CF44" s="60"/>
+      <c r="CG44" s="60"/>
+      <c r="CH44" s="60"/>
+      <c r="CI44" s="60"/>
+      <c r="CJ44" s="60"/>
+      <c r="CK44" s="60"/>
+      <c r="CL44" s="60"/>
+      <c r="CM44" s="60"/>
+      <c r="CN44" s="60"/>
     </row>
-    <row r="45" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A45" s="12"/>
       <c r="B45" s="61" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C45" s="62"/>
       <c r="D45" s="63">
-        <v>0.9</v>
-      </c>
-      <c r="E45" s="102">
-        <v>46146</v>
-      </c>
-      <c r="F45" s="102">
-        <f>E45+7</f>
-        <v>46153</v>
+        <v>1</v>
+      </c>
+      <c r="E45" s="101">
+        <f>E37</f>
+        <v>46064</v>
+      </c>
+      <c r="F45" s="101">
+        <f>E49-3</f>
+        <v>46157</v>
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="4">
-        <f t="shared" si="30"/>
-        <v>8</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>94</v>
       </c>
       <c r="I45" s="39"/>
       <c r="J45" s="39"/>
@@ -7298,25 +7393,25 @@
       <c r="CM45" s="39"/>
       <c r="CN45" s="39"/>
     </row>
-    <row r="46" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A46" s="12"/>
       <c r="B46" s="61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="63">
-        <v>0</v>
-      </c>
-      <c r="E46" s="102">
+        <v>0.9</v>
+      </c>
+      <c r="E46" s="101">
         <v>46146</v>
       </c>
-      <c r="F46" s="102">
+      <c r="F46" s="101">
         <f>E46+7</f>
         <v>46153</v>
       </c>
       <c r="G46" s="14"/>
       <c r="H46" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I46" s="39"/>
@@ -7404,26 +7499,25 @@
       <c r="CM46" s="39"/>
       <c r="CN46" s="39"/>
     </row>
-    <row r="47" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A47" s="12"/>
       <c r="B47" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" s="62"/>
       <c r="D47" s="63">
         <v>0</v>
       </c>
-      <c r="E47" s="102">
-        <f>F46</f>
+      <c r="E47" s="101">
+        <v>46146</v>
+      </c>
+      <c r="F47" s="101">
+        <f>E47+7</f>
         <v>46153</v>
-      </c>
-      <c r="F47" s="102">
-        <f>E47+7</f>
-        <v>46160</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I47" s="39"/>
@@ -7511,26 +7605,26 @@
       <c r="CM47" s="39"/>
       <c r="CN47" s="39"/>
     </row>
-    <row r="48" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A48" s="12"/>
       <c r="B48" s="61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="62"/>
       <c r="D48" s="63">
         <v>0</v>
       </c>
-      <c r="E48" s="102">
+      <c r="E48" s="101">
         <f>F47</f>
+        <v>46153</v>
+      </c>
+      <c r="F48" s="101">
+        <f>E48+7</f>
         <v>46160</v>
-      </c>
-      <c r="F48" s="102">
-        <f>E48+7</f>
-        <v>46167</v>
       </c>
       <c r="G48" s="14"/>
       <c r="H48" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I48" s="39"/>
@@ -7618,27 +7712,27 @@
       <c r="CM48" s="39"/>
       <c r="CN48" s="39"/>
     </row>
-    <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A49" s="12"/>
       <c r="B49" s="61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="62"/>
       <c r="D49" s="63">
         <v>0</v>
       </c>
-      <c r="E49" s="102">
+      <c r="E49" s="101">
         <f>F48</f>
+        <v>46160</v>
+      </c>
+      <c r="F49" s="101">
+        <f>E49+7</f>
         <v>46167</v>
-      </c>
-      <c r="F49" s="102">
-        <f>E49+14</f>
-        <v>46181</v>
       </c>
       <c r="G49" s="14"/>
       <c r="H49" s="4">
-        <f t="shared" si="30"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>8</v>
       </c>
       <c r="I49" s="39"/>
       <c r="J49" s="39"/>
@@ -7725,213 +7819,320 @@
       <c r="CM49" s="39"/>
       <c r="CN49" s="39"/>
     </row>
-    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A50" s="12"/>
-      <c r="B50" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="65"/>
-      <c r="D50" s="66"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="103"/>
+      <c r="B50" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" s="62"/>
+      <c r="D50" s="63">
+        <v>0</v>
+      </c>
+      <c r="E50" s="101">
+        <f>F49</f>
+        <v>46167</v>
+      </c>
+      <c r="F50" s="101">
+        <f>E50+14</f>
+        <v>46181</v>
+      </c>
       <c r="G50" s="14"/>
-      <c r="H50" s="4" t="str">
-        <f t="shared" si="30"/>
+      <c r="H50" s="4">
+        <f t="shared" ca="1" si="30"/>
+        <v>15</v>
+      </c>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="39"/>
+      <c r="L50" s="39"/>
+      <c r="M50" s="39"/>
+      <c r="N50" s="39"/>
+      <c r="O50" s="39"/>
+      <c r="P50" s="39"/>
+      <c r="Q50" s="39"/>
+      <c r="R50" s="39"/>
+      <c r="S50" s="39"/>
+      <c r="T50" s="39"/>
+      <c r="U50" s="39"/>
+      <c r="V50" s="39"/>
+      <c r="W50" s="39"/>
+      <c r="X50" s="39"/>
+      <c r="Y50" s="39"/>
+      <c r="Z50" s="39"/>
+      <c r="AA50" s="39"/>
+      <c r="AB50" s="39"/>
+      <c r="AC50" s="39"/>
+      <c r="AD50" s="39"/>
+      <c r="AE50" s="39"/>
+      <c r="AF50" s="39"/>
+      <c r="AG50" s="39"/>
+      <c r="AH50" s="39"/>
+      <c r="AI50" s="39"/>
+      <c r="AJ50" s="39"/>
+      <c r="AK50" s="39"/>
+      <c r="AL50" s="39"/>
+      <c r="AM50" s="39"/>
+      <c r="AN50" s="39"/>
+      <c r="AO50" s="39"/>
+      <c r="AP50" s="39"/>
+      <c r="AQ50" s="39"/>
+      <c r="AR50" s="39"/>
+      <c r="AS50" s="39"/>
+      <c r="AT50" s="39"/>
+      <c r="AU50" s="39"/>
+      <c r="AV50" s="39"/>
+      <c r="AW50" s="39"/>
+      <c r="AX50" s="39"/>
+      <c r="AY50" s="39"/>
+      <c r="AZ50" s="39"/>
+      <c r="BA50" s="39"/>
+      <c r="BB50" s="39"/>
+      <c r="BC50" s="39"/>
+      <c r="BD50" s="39"/>
+      <c r="BE50" s="39"/>
+      <c r="BF50" s="39"/>
+      <c r="BG50" s="39"/>
+      <c r="BH50" s="39"/>
+      <c r="BI50" s="39"/>
+      <c r="BJ50" s="39"/>
+      <c r="BK50" s="39"/>
+      <c r="BL50" s="39"/>
+      <c r="BM50" s="39"/>
+      <c r="BN50" s="39"/>
+      <c r="BO50" s="39"/>
+      <c r="BP50" s="39"/>
+      <c r="BQ50" s="39"/>
+      <c r="BR50" s="39"/>
+      <c r="BS50" s="39"/>
+      <c r="BT50" s="39"/>
+      <c r="BU50" s="39"/>
+      <c r="BV50" s="39"/>
+      <c r="BW50" s="39"/>
+      <c r="BX50" s="39"/>
+      <c r="BY50" s="39"/>
+      <c r="BZ50" s="39"/>
+      <c r="CA50" s="39"/>
+      <c r="CB50" s="39"/>
+      <c r="CC50" s="39"/>
+      <c r="CD50" s="39"/>
+      <c r="CE50" s="39"/>
+      <c r="CF50" s="39"/>
+      <c r="CG50" s="39"/>
+      <c r="CH50" s="39"/>
+      <c r="CI50" s="39"/>
+      <c r="CJ50" s="39"/>
+      <c r="CK50" s="39"/>
+      <c r="CL50" s="39"/>
+      <c r="CM50" s="39"/>
+      <c r="CN50" s="39"/>
+    </row>
+    <row r="51" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A51" s="12"/>
+      <c r="B51" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="65"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="102"/>
+      <c r="F51" s="102"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="4" t="str">
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
-      <c r="S50" s="34"/>
-      <c r="T50" s="34"/>
-      <c r="U50" s="34"/>
-      <c r="V50" s="34"/>
-      <c r="W50" s="34"/>
-      <c r="X50" s="34"/>
-      <c r="Y50" s="34"/>
-      <c r="Z50" s="34"/>
-      <c r="AA50" s="34"/>
-      <c r="AB50" s="34"/>
-      <c r="AC50" s="34"/>
-      <c r="AD50" s="34"/>
-      <c r="AE50" s="34"/>
-      <c r="AF50" s="34"/>
-      <c r="AG50" s="34"/>
-      <c r="AH50" s="34"/>
-      <c r="AI50" s="34"/>
-      <c r="AJ50" s="34"/>
-      <c r="AK50" s="34"/>
-      <c r="AL50" s="34"/>
-      <c r="AM50" s="34"/>
-      <c r="AN50" s="34"/>
-      <c r="AO50" s="34"/>
-      <c r="AP50" s="34"/>
-      <c r="AQ50" s="34"/>
-      <c r="AR50" s="34"/>
-      <c r="AS50" s="34"/>
-      <c r="AT50" s="34"/>
-      <c r="AU50" s="34"/>
-      <c r="AV50" s="34"/>
-      <c r="AW50" s="34"/>
-      <c r="AX50" s="34"/>
-      <c r="AY50" s="34"/>
-      <c r="AZ50" s="34"/>
-      <c r="BA50" s="34"/>
-      <c r="BB50" s="34"/>
-      <c r="BC50" s="34"/>
-      <c r="BD50" s="34"/>
-      <c r="BE50" s="34"/>
-      <c r="BF50" s="34"/>
-      <c r="BG50" s="34"/>
-      <c r="BH50" s="34"/>
-      <c r="BI50" s="34"/>
-      <c r="BJ50" s="34"/>
-      <c r="BK50" s="34"/>
-      <c r="BL50" s="34"/>
-      <c r="BM50" s="34"/>
-      <c r="BN50" s="34"/>
-      <c r="BO50" s="34"/>
-      <c r="BP50" s="34"/>
-      <c r="BQ50" s="34"/>
-      <c r="BR50" s="34"/>
-      <c r="BS50" s="34"/>
-      <c r="BT50" s="34"/>
-      <c r="BU50" s="34"/>
-      <c r="BV50" s="34"/>
-      <c r="BW50" s="34"/>
-      <c r="BX50" s="34"/>
-      <c r="BY50" s="34"/>
-      <c r="BZ50" s="34"/>
-      <c r="CA50" s="34"/>
-      <c r="CB50" s="34"/>
-      <c r="CC50" s="34"/>
-      <c r="CD50" s="34"/>
-      <c r="CE50" s="34"/>
-      <c r="CF50" s="34"/>
-      <c r="CG50" s="34"/>
-      <c r="CH50" s="34"/>
-      <c r="CI50" s="34"/>
-      <c r="CJ50" s="34"/>
-      <c r="CK50" s="34"/>
-      <c r="CL50" s="34"/>
-      <c r="CM50" s="34"/>
-      <c r="CN50" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="34"/>
+      <c r="N51" s="34"/>
+      <c r="O51" s="34"/>
+      <c r="P51" s="34"/>
+      <c r="Q51" s="34"/>
+      <c r="R51" s="34"/>
+      <c r="S51" s="34"/>
+      <c r="T51" s="34"/>
+      <c r="U51" s="34"/>
+      <c r="V51" s="34"/>
+      <c r="W51" s="34"/>
+      <c r="X51" s="34"/>
+      <c r="Y51" s="34"/>
+      <c r="Z51" s="34"/>
+      <c r="AA51" s="34"/>
+      <c r="AB51" s="34"/>
+      <c r="AC51" s="34"/>
+      <c r="AD51" s="34"/>
+      <c r="AE51" s="34"/>
+      <c r="AF51" s="34"/>
+      <c r="AG51" s="34"/>
+      <c r="AH51" s="34"/>
+      <c r="AI51" s="34"/>
+      <c r="AJ51" s="34"/>
+      <c r="AK51" s="34"/>
+      <c r="AL51" s="34"/>
+      <c r="AM51" s="34"/>
+      <c r="AN51" s="34"/>
+      <c r="AO51" s="34"/>
+      <c r="AP51" s="34"/>
+      <c r="AQ51" s="34"/>
+      <c r="AR51" s="34"/>
+      <c r="AS51" s="34"/>
+      <c r="AT51" s="34"/>
+      <c r="AU51" s="34"/>
+      <c r="AV51" s="34"/>
+      <c r="AW51" s="34"/>
+      <c r="AX51" s="34"/>
+      <c r="AY51" s="34"/>
+      <c r="AZ51" s="34"/>
+      <c r="BA51" s="34"/>
+      <c r="BB51" s="34"/>
+      <c r="BC51" s="34"/>
+      <c r="BD51" s="34"/>
+      <c r="BE51" s="34"/>
+      <c r="BF51" s="34"/>
+      <c r="BG51" s="34"/>
+      <c r="BH51" s="34"/>
+      <c r="BI51" s="34"/>
+      <c r="BJ51" s="34"/>
+      <c r="BK51" s="34"/>
+      <c r="BL51" s="34"/>
+      <c r="BM51" s="34"/>
+      <c r="BN51" s="34"/>
+      <c r="BO51" s="34"/>
+      <c r="BP51" s="34"/>
+      <c r="BQ51" s="34"/>
+      <c r="BR51" s="34"/>
+      <c r="BS51" s="34"/>
+      <c r="BT51" s="34"/>
+      <c r="BU51" s="34"/>
+      <c r="BV51" s="34"/>
+      <c r="BW51" s="34"/>
+      <c r="BX51" s="34"/>
+      <c r="BY51" s="34"/>
+      <c r="BZ51" s="34"/>
+      <c r="CA51" s="34"/>
+      <c r="CB51" s="34"/>
+      <c r="CC51" s="34"/>
+      <c r="CD51" s="34"/>
+      <c r="CE51" s="34"/>
+      <c r="CF51" s="34"/>
+      <c r="CG51" s="34"/>
+      <c r="CH51" s="34"/>
+      <c r="CI51" s="34"/>
+      <c r="CJ51" s="34"/>
+      <c r="CK51" s="34"/>
+      <c r="CL51" s="34"/>
+      <c r="CM51" s="34"/>
+      <c r="CN51" s="34"/>
     </row>
-    <row r="51" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="81"/>
-      <c r="B51" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="104"/>
-      <c r="F51" s="105"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="5" t="str">
-        <f t="shared" si="30"/>
+    <row r="52" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A52" s="112"/>
+      <c r="B52" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="68"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="103"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="5" t="str">
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
-      <c r="I51" s="70"/>
-      <c r="J51" s="70"/>
-      <c r="K51" s="70"/>
-      <c r="L51" s="70"/>
-      <c r="M51" s="70"/>
-      <c r="N51" s="70"/>
-      <c r="O51" s="70"/>
-      <c r="P51" s="70"/>
-      <c r="Q51" s="70"/>
-      <c r="R51" s="70"/>
-      <c r="S51" s="70"/>
-      <c r="T51" s="70"/>
-      <c r="U51" s="70"/>
-      <c r="V51" s="70"/>
-      <c r="W51" s="70"/>
-      <c r="X51" s="70"/>
-      <c r="Y51" s="70"/>
-      <c r="Z51" s="70"/>
-      <c r="AA51" s="70"/>
-      <c r="AB51" s="70"/>
-      <c r="AC51" s="70"/>
-      <c r="AD51" s="70"/>
-      <c r="AE51" s="70"/>
-      <c r="AF51" s="70"/>
-      <c r="AG51" s="70"/>
-      <c r="AH51" s="70"/>
-      <c r="AI51" s="70"/>
-      <c r="AJ51" s="70"/>
-      <c r="AK51" s="70"/>
-      <c r="AL51" s="70"/>
-      <c r="AM51" s="70"/>
-      <c r="AN51" s="70"/>
-      <c r="AO51" s="70"/>
-      <c r="AP51" s="70"/>
-      <c r="AQ51" s="70"/>
-      <c r="AR51" s="70"/>
-      <c r="AS51" s="70"/>
-      <c r="AT51" s="70"/>
-      <c r="AU51" s="70"/>
-      <c r="AV51" s="70"/>
-      <c r="AW51" s="70"/>
-      <c r="AX51" s="70"/>
-      <c r="AY51" s="70"/>
-      <c r="AZ51" s="70"/>
-      <c r="BA51" s="70"/>
-      <c r="BB51" s="70"/>
-      <c r="BC51" s="70"/>
-      <c r="BD51" s="70"/>
-      <c r="BE51" s="70"/>
-      <c r="BF51" s="70"/>
-      <c r="BG51" s="70"/>
-      <c r="BH51" s="70"/>
-      <c r="BI51" s="70"/>
-      <c r="BJ51" s="70"/>
-      <c r="BK51" s="70"/>
-      <c r="BL51" s="70"/>
-      <c r="BM51" s="70"/>
-      <c r="BN51" s="70"/>
-      <c r="BO51" s="70"/>
-      <c r="BP51" s="70"/>
-      <c r="BQ51" s="70"/>
-      <c r="BR51" s="70"/>
-      <c r="BS51" s="70"/>
-      <c r="BT51" s="70"/>
-      <c r="BU51" s="70"/>
-      <c r="BV51" s="70"/>
-      <c r="BW51" s="70"/>
-      <c r="BX51" s="70"/>
-      <c r="BY51" s="70"/>
-      <c r="BZ51" s="70"/>
-      <c r="CA51" s="70"/>
-      <c r="CB51" s="70"/>
-      <c r="CC51" s="70"/>
-      <c r="CD51" s="70"/>
-      <c r="CE51" s="70"/>
-      <c r="CF51" s="70"/>
-      <c r="CG51" s="70"/>
-      <c r="CH51" s="70"/>
-      <c r="CI51" s="70"/>
-      <c r="CJ51" s="70"/>
-      <c r="CK51" s="70"/>
-      <c r="CL51" s="70"/>
-      <c r="CM51" s="70"/>
-      <c r="CN51" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="70"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="70"/>
+      <c r="M52" s="70"/>
+      <c r="N52" s="70"/>
+      <c r="O52" s="70"/>
+      <c r="P52" s="70"/>
+      <c r="Q52" s="70"/>
+      <c r="R52" s="70"/>
+      <c r="S52" s="70"/>
+      <c r="T52" s="70"/>
+      <c r="U52" s="70"/>
+      <c r="V52" s="70"/>
+      <c r="W52" s="70"/>
+      <c r="X52" s="70"/>
+      <c r="Y52" s="70"/>
+      <c r="Z52" s="70"/>
+      <c r="AA52" s="70"/>
+      <c r="AB52" s="70"/>
+      <c r="AC52" s="70"/>
+      <c r="AD52" s="70"/>
+      <c r="AE52" s="70"/>
+      <c r="AF52" s="70"/>
+      <c r="AG52" s="70"/>
+      <c r="AH52" s="70"/>
+      <c r="AI52" s="70"/>
+      <c r="AJ52" s="70"/>
+      <c r="AK52" s="70"/>
+      <c r="AL52" s="70"/>
+      <c r="AM52" s="70"/>
+      <c r="AN52" s="70"/>
+      <c r="AO52" s="70"/>
+      <c r="AP52" s="70"/>
+      <c r="AQ52" s="70"/>
+      <c r="AR52" s="70"/>
+      <c r="AS52" s="70"/>
+      <c r="AT52" s="70"/>
+      <c r="AU52" s="70"/>
+      <c r="AV52" s="70"/>
+      <c r="AW52" s="70"/>
+      <c r="AX52" s="70"/>
+      <c r="AY52" s="70"/>
+      <c r="AZ52" s="70"/>
+      <c r="BA52" s="70"/>
+      <c r="BB52" s="70"/>
+      <c r="BC52" s="70"/>
+      <c r="BD52" s="70"/>
+      <c r="BE52" s="70"/>
+      <c r="BF52" s="70"/>
+      <c r="BG52" s="70"/>
+      <c r="BH52" s="70"/>
+      <c r="BI52" s="70"/>
+      <c r="BJ52" s="70"/>
+      <c r="BK52" s="70"/>
+      <c r="BL52" s="70"/>
+      <c r="BM52" s="70"/>
+      <c r="BN52" s="70"/>
+      <c r="BO52" s="70"/>
+      <c r="BP52" s="70"/>
+      <c r="BQ52" s="70"/>
+      <c r="BR52" s="70"/>
+      <c r="BS52" s="70"/>
+      <c r="BT52" s="70"/>
+      <c r="BU52" s="70"/>
+      <c r="BV52" s="70"/>
+      <c r="BW52" s="70"/>
+      <c r="BX52" s="70"/>
+      <c r="BY52" s="70"/>
+      <c r="BZ52" s="70"/>
+      <c r="CA52" s="70"/>
+      <c r="CB52" s="70"/>
+      <c r="CC52" s="70"/>
+      <c r="CD52" s="70"/>
+      <c r="CE52" s="70"/>
+      <c r="CF52" s="70"/>
+      <c r="CG52" s="70"/>
+      <c r="CH52" s="70"/>
+      <c r="CI52" s="70"/>
+      <c r="CJ52" s="70"/>
+      <c r="CK52" s="70"/>
+      <c r="CL52" s="70"/>
+      <c r="CM52" s="70"/>
+      <c r="CN52" s="70"/>
     </row>
-    <row r="52" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G52" s="2"/>
+    <row r="53" spans="1:92" ht="30" customHeight="1">
+      <c r="G53" s="2"/>
     </row>
-    <row r="53" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C53" s="13"/>
-      <c r="F53" s="108"/>
+    <row r="54" spans="1:92" ht="30" customHeight="1">
+      <c r="C54" s="13"/>
+      <c r="F54" s="107"/>
     </row>
-    <row r="54" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C54" s="3"/>
+    <row r="55" spans="1:92" ht="30" customHeight="1">
+      <c r="C55" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -7958,7 +8159,7 @@
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:D51">
+  <conditionalFormatting sqref="D7:D52">
     <cfRule type="dataBar" priority="102">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -7972,62 +8173,62 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:BK31 I32:BM34">
+  <conditionalFormatting sqref="I25:BK32 I33:BM35">
     <cfRule type="expression" dxfId="44" priority="84" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I34:BK45 I4:BK8 I9:BZ10 BL14 I14:BK16 I19:BK21 I23:BK31 BL34:BM34 BL37 BL41:BZ41 BL44:CA44 BL45:BM45 I46:BM46 I48:BK49 I32:BM33">
+  <conditionalFormatting sqref="I35:BK46 I4:BK8 I9:BZ10 BL15 I15:BK17 I20:BK22 I24:BK32 I33:BM34 BL35:BM35 BL38 BL42:BZ42 BL45:CA45 BL46:BM46 I47:BM47 I49:BK50">
     <cfRule type="expression" dxfId="43" priority="80">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I36:BK37 BL37 I40:BK42 BL41:BZ41">
+  <conditionalFormatting sqref="I37:BK38 BL38 I41:BK43 BL42:BZ42">
     <cfRule type="expression" dxfId="42" priority="82" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:BK39">
+  <conditionalFormatting sqref="I40:BK40">
     <cfRule type="expression" dxfId="41" priority="22" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:BZ10 I14:BL14 I16:BL16 I20:CC21">
+  <conditionalFormatting sqref="I9:BZ10 I15:BL15 I17:BL17 I21:CC22">
     <cfRule type="expression" dxfId="40" priority="86" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:CN14 I16:CN18 I20:CN22">
+  <conditionalFormatting sqref="I9:CN15 I17:CN19 I21:CN23">
     <cfRule type="expression" dxfId="39" priority="28">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:CN34">
+  <conditionalFormatting sqref="I25:CN35">
     <cfRule type="expression" dxfId="38" priority="26">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I36:CN37">
+  <conditionalFormatting sqref="I37:CN38">
     <cfRule type="expression" dxfId="37" priority="24">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:CN42">
+  <conditionalFormatting sqref="I40:CN43">
     <cfRule type="expression" dxfId="36" priority="15">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL24:BL31 BS24:BS31 BZ24:BZ32 CG24:CG34 CN24:CN34 BS33:BS34">
+  <conditionalFormatting sqref="BL25:BL32 BS25:BS32 BZ25:BZ33 CG25:CG35 CN25:CN35 BS34:BS35">
     <cfRule type="expression" dxfId="35" priority="121" stopIfTrue="1">
       <formula>AND(task_end&gt;=BL$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL36 BS36 BZ36 CG36:CG37 CN36:CN37 BL39 BS39 BZ39 CG39:CG42 CN39:CN42 BL42 BS42 BZ42">
+  <conditionalFormatting sqref="BL37 BS37 BZ37 CG37:CG38 CN37:CN38 BL40 BS40 BZ40 CG40:CG43 CN40:CN43 BL43 BS43 BZ43">
     <cfRule type="expression" dxfId="34" priority="123" stopIfTrue="1">
       <formula>AND(task_end&gt;=BL$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BL44:CA44 I44:BK45 BL45:BM45 I46:BM46 I48:BK49">
+  <conditionalFormatting sqref="BL45:CA45 I45:BK46 BL46:BM46 I47:BM47 I49:BK50">
     <cfRule type="expression" dxfId="33" priority="115">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
@@ -8035,27 +8236,27 @@
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM24:BR31 BN32:BS34">
+  <conditionalFormatting sqref="BM25:BR32 BN33:BS35">
     <cfRule type="expression" dxfId="31" priority="45" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM36:BR37 BM42:BR42">
+  <conditionalFormatting sqref="BM37:BR38 BM43:BR43">
     <cfRule type="expression" dxfId="30" priority="43" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM39:BR39">
+  <conditionalFormatting sqref="BM40:BR40">
     <cfRule type="expression" dxfId="29" priority="20" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM14:BT14">
+  <conditionalFormatting sqref="BM15:BT15">
     <cfRule type="expression" dxfId="28" priority="47" stopIfTrue="1">
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN45:BT46 I47:BT47">
+  <conditionalFormatting sqref="BN46:BT47 I48:BT48">
     <cfRule type="expression" dxfId="27" priority="48">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
@@ -8063,42 +8264,42 @@
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BS14:BS15 BL4:BL8 BS4:BS8 BZ4:BZ8 BL15 BZ15 BL19 BS19 BZ19 BL23:BL31 BS23:BS31 BZ23:BZ32 BL35:BL36 BZ35:BZ36 BL38:BL39 BS38:BS39 BZ38:BZ39 BL42:BL43 BS42:BS43 BZ42:BZ43 CG45:CG48 BL48 BS33:BS36 CG4:CG43 CN4:CN49">
+  <conditionalFormatting sqref="BS15:BS16 BS34:BS37 BL4:BL8 BS4:BS8 BZ4:BZ8 CG4:CG44 CN4:CN50 BL16 BZ16 BL20 BS20 BZ20 BL24:BL32 BS24:BS32 BZ24:BZ33 BL36:BL37 BZ36:BZ37 BL39:BL40 BS39:BS40 BZ39:BZ40 BL43:BL44 BS43:BS44 BZ43:BZ44 CG46:CG49 BL49">
     <cfRule type="expression" dxfId="25" priority="117">
       <formula>AND(TODAY()&gt;=BL$5, TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BS14:BT14 BM35:BR39 BM4:BR8 BM14:BR15 BM19:BR19 BM23:BR31 BM42:BR43 BN45:BT46 I47:BT47 BN32:BS34">
+  <conditionalFormatting sqref="BS15:BT15 BM36:BR40 BM4:BR8 BM15:BR16 BM20:BR20 BM24:BR32 BN33:BS35 BM43:BR44 BN46:BT47 I48:BT48">
     <cfRule type="expression" dxfId="24" priority="41">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT24:BY34">
+  <conditionalFormatting sqref="BT25:BY35">
     <cfRule type="expression" dxfId="23" priority="36" stopIfTrue="1">
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT36:BY36 BT42:BY42">
+  <conditionalFormatting sqref="BT37:BY37 BT43:BY43">
     <cfRule type="expression" dxfId="22" priority="34" stopIfTrue="1">
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT38:BY39 BT4:BY8 BZ14 BT14:BY15 BT19:BY19 BT42:BY43 BU45:CA45 BT23:BY36">
+  <conditionalFormatting sqref="BT39:BY40 BT4:BY8 BZ15 BT15:BY16 BT20:BY20 BT24:BY37 BT43:BY44 BU46:CA46">
     <cfRule type="expression" dxfId="21" priority="32">
       <formula>AND(TODAY()&gt;=BT$5, TODAY()&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT39:BY39">
+  <conditionalFormatting sqref="BT40:BY40">
     <cfRule type="expression" dxfId="20" priority="18" stopIfTrue="1">
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BT14:BZ14">
+  <conditionalFormatting sqref="BT15:BZ15">
     <cfRule type="expression" dxfId="19" priority="38" stopIfTrue="1">
       <formula>AND(task_end&gt;=BT$5,task_start&lt;BU$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU45:CA45">
+  <conditionalFormatting sqref="BU46:CA46">
     <cfRule type="expression" dxfId="18" priority="39">
       <formula>AND(task_start&lt;=BU$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BU$5)</formula>
     </cfRule>
@@ -8106,32 +8307,32 @@
       <formula>AND(task_end&gt;=BU$5,task_start&lt;BV$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA9:CF10 I11:CF13 CA14:CF14 BM16:CF16 I17:CF18 CD20:CF21 I22:CF22">
+  <conditionalFormatting sqref="CA9:CF10 I11:CF14 CA15:CF15 BM17:CF17 I18:CF19 CD21:CF22 I23:CF23">
     <cfRule type="expression" dxfId="16" priority="29" stopIfTrue="1">
       <formula>AND(task_end&gt;=I$5,task_start&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA24:CF32 BZ33:CF34">
+  <conditionalFormatting sqref="CA25:CF33 BZ34:CF35">
     <cfRule type="expression" dxfId="15" priority="27" stopIfTrue="1">
       <formula>AND(task_end&gt;=BZ$5,task_start&lt;CA$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA36:CF36 BS37:CF37 BL40:CF40 CA41:CF42">
+  <conditionalFormatting sqref="CA37:CF37 BS38:CF38 BL41:CF41 CA42:CF43">
     <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
       <formula>AND(task_end&gt;=BL$5,task_start&lt;BM$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA38:CF39 CA4:CF10 I11:CF13 CA14:CF15 BL16:CF16 I17:CF18 CA19:CF19 BL20:CF21 I22:CF22 CA23:CF32 CA35:CF36 BS37:CF37 BL40:CF40 CA41:CF43 CB44:CF45 BU46:CF47 BM48:CF48 BZ33:CF34">
+  <conditionalFormatting sqref="CA39:CF40 CA4:CF10 I11:CF14 CA15:CF16 BL17:CF17 I18:CF19 CA20:CF20 BL21:CF22 I23:CF23 CA24:CF33 BZ34:CF35 CA36:CF37 BS38:CF38 BL41:CF41 CA42:CF44 CB45:CF46 BU47:CF48 BM49:CF49">
     <cfRule type="expression" dxfId="13" priority="23">
       <formula>AND(TODAY()&gt;=I$5, TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CA39:CF39">
+  <conditionalFormatting sqref="CA40:CF40">
     <cfRule type="expression" dxfId="12" priority="16" stopIfTrue="1">
       <formula>AND(task_end&gt;=CA$5,task_start&lt;CB$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB44:CF45 BU46:CF47 BM48:CF48">
+  <conditionalFormatting sqref="CB45:CF46 BU47:CF48 BM49:CF49">
     <cfRule type="expression" dxfId="11" priority="30">
       <formula>AND(task_start&lt;=BM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BM$5)</formula>
     </cfRule>
@@ -8139,12 +8340,12 @@
       <formula>AND(task_end&gt;=BM$5,task_start&lt;BN$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CG9:CG14 CN9:CN14 BS14 CG16:CG18 CN16:CN18 CG20:CG22 CN20:CN22">
+  <conditionalFormatting sqref="CG9:CG15 CN9:CN15 BS15 CG17:CG19 CN17:CN19 CG21:CG23 CN21:CN23">
     <cfRule type="expression" dxfId="9" priority="119" stopIfTrue="1">
       <formula>AND(task_end&gt;=BS$5,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CG44:CM44 CH45:CM48 BL49:CM49">
+  <conditionalFormatting sqref="CG45:CM45 CH46:CM49 BL50:CM50">
     <cfRule type="expression" dxfId="8" priority="6">
       <formula>AND(task_start&lt;=BL$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BL$5)</formula>
     </cfRule>
@@ -8152,32 +8353,32 @@
       <formula>AND(task_end&gt;=BL$5,task_start&lt;BM$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CG44:CM44 CH45:CM48 BL49:CM49 CH4:CM43">
+  <conditionalFormatting sqref="CH4:CM44 CG45:CM45 CH46:CM49 BL50:CM50">
     <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(TODAY()&gt;=BL$5, TODAY()&lt;BM$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH9:CM14 CH16:CM18 CH20:CM22">
+  <conditionalFormatting sqref="CH9:CM15 CH17:CM19 CH21:CM23">
     <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH24:CM34">
+  <conditionalFormatting sqref="CH25:CM35">
     <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH36:CM37 CH40:CM42">
+  <conditionalFormatting sqref="CH37:CM38 CH41:CM43">
     <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CH39:CM39">
+  <conditionalFormatting sqref="CH40:CM40">
     <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
       <formula>AND(task_end&gt;=CH$5,task_start&lt;CI$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CN44:CN49 CG45:CG48 BL48">
+  <conditionalFormatting sqref="CN45:CN50 CG46:CG49 BL49">
     <cfRule type="expression" dxfId="1" priority="124">
       <formula>AND(task_start&lt;=BL$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BL$5)</formula>
     </cfRule>
@@ -8194,13 +8395,13 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the name of the Project Lead in cell C3. Enter the Project Start date in cell Q1. Project Start: label is in cell I1." sqref="A3" xr:uid="{EEA7C783-457F-401F-98B9-9035587B9210}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="The Display week in cell Q2 is the starting week to display in the project schedule in cell I4. The project start date is Week 1. To change the display week, enter a new week number in cell Q2._x000a__x000a_Start date for each week is auto calculated starting in I4." sqref="A4" xr:uid="{43382715-6BC7-4B19-A31B-4B13A11ED166}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cells I5 through BL5 contain the day number for the week represented in the cell block above each date and are auto calculated._x000a__x000a_Today's date is outlined from today's date in row 5 through the entire date column to the end of the project schedule." sqref="A5:A6" xr:uid="{7A3789A6-A3FB-43B6-A4F7-8C0AC564F67E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B8 contains the Phase 1 sample title. Enter a new title in cell B8._x000a_To delete the phase and work only from tasks, simply delete this row." sqref="A19 A8 A15" xr:uid="{CEC78982-AFA8-419E-B0A2-676B709E5100}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="B9 contains the task name.  C9 is the assignee.  D9 is a progress bar that shades based on the number entered into the cell.  _x000a__x000a_E9 contains the start date and F9 contains the end date._x000a__x000a_The Gantt chart will fill in starting in cell I9 based on task dates." sqref="A20:A21 A9 A16" xr:uid="{D870A2F6-6B07-4F5A-A81D-4BCCFADF8796}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Rows 10 through 13 repeat the pattern from row 9. _x000a__x000a_Repeat the instructions from cell A9 for all task rows in this worksheet. _x000a__x000a_Continue entering tasks in cells A10 through A13 or go to cell A14 to learn more." sqref="A22 A10 A17" xr:uid="{872449A7-C3CC-45B6-BA90-B1AAD66BA0E5}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B14 contains the Phase 2 sample title. Enter a new title in cell B14._x000a_To delete the phase and work only from tasks, simply delete this row. To remove the phase, simply delete the row. Add tasks to previous phase by entering a new row above this one._x000a_" sqref="A23" xr:uid="{4F48FC41-E335-47F1-87AA-3333A52AD81C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 3's sample block starts in cell B20." sqref="A35 A38" xr:uid="{956902D1-D3B5-416D-BB69-9362D193BC0A}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 4's sample block starts in cell B26." sqref="A43" xr:uid="{DE54E5DE-526D-4D71-8D03-E99B4AB2FEE5}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. _x000a_Insert new rows ABOVE this one to continue building out your Project Schedule." sqref="A51" xr:uid="{79B9237E-4DD3-4E0F-8ED6-E0B695A99D96}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B8 contains the Phase 1 sample title. Enter a new title in cell B8._x000a_To delete the phase and work only from tasks, simply delete this row." sqref="A20 A8 A16" xr:uid="{CEC78982-AFA8-419E-B0A2-676B709E5100}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="B9 contains the task name.  C9 is the assignee.  D9 is a progress bar that shades based on the number entered into the cell.  _x000a__x000a_E9 contains the start date and F9 contains the end date._x000a__x000a_The Gantt chart will fill in starting in cell I9 based on task dates." sqref="A21:A22 A9 A17" xr:uid="{D870A2F6-6B07-4F5A-A81D-4BCCFADF8796}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Rows 10 through 13 repeat the pattern from row 9. _x000a__x000a_Repeat the instructions from cell A9 for all task rows in this worksheet. _x000a__x000a_Continue entering tasks in cells A10 through A13 or go to cell A14 to learn more." sqref="A23 A10 A18" xr:uid="{872449A7-C3CC-45B6-BA90-B1AAD66BA0E5}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cell B14 contains the Phase 2 sample title. Enter a new title in cell B14._x000a_To delete the phase and work only from tasks, simply delete this row. To remove the phase, simply delete the row. Add tasks to previous phase by entering a new row above this one._x000a_" sqref="A24" xr:uid="{4F48FC41-E335-47F1-87AA-3333A52AD81C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 3's sample block starts in cell B20." sqref="A36 A39" xr:uid="{956902D1-D3B5-416D-BB69-9362D193BC0A}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Phase 4's sample block starts in cell B26." sqref="A44" xr:uid="{DE54E5DE-526D-4D71-8D03-E99B4AB2FEE5}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Project Schedule. DO NOT enter anything in this row. _x000a_Insert new rows ABOVE this one to continue building out your Project Schedule." sqref="A52" xr:uid="{79B9237E-4DD3-4E0F-8ED6-E0B695A99D96}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -8257,7 +8458,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D51</xm:sqref>
+          <xm:sqref>D7:D52</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -8268,110 +8469,110 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.95"/>
   <cols>
     <col min="1" max="1" width="87" style="6" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="1:2" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1"/>
+    <row r="2" spans="1:2" s="8" customFormat="1" ht="15.95">
       <c r="A2" s="74" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B2" s="7"/>
     </row>
-    <row r="3" spans="1:2" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" s="10" customFormat="1" ht="27" customHeight="1">
       <c r="A3" s="75"/>
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A4" s="76" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="74.25" customHeight="1">
       <c r="A5" s="77" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="26.25" customHeight="1">
       <c r="A6" s="76" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="6" customFormat="1" ht="205.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" s="6" customFormat="1" ht="205.35" customHeight="1">
       <c r="A7" s="78" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A8" s="76" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="60">
       <c r="A9" s="77" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="6" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" s="6" customFormat="1" ht="28.35" customHeight="1">
       <c r="A10" s="79" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A11" s="76" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="30">
       <c r="A12" s="77" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="6" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" s="6" customFormat="1" ht="28.35" customHeight="1">
       <c r="A13" s="79" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A14" s="76" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="75" customHeight="1">
       <c r="A15" s="77" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:2" ht="75">
       <c r="A16" s="77" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="80"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="80"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="80"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="80"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="80"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="80"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="80"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="80"/>
     </row>
   </sheetData>
@@ -8387,6 +8588,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8395,7 +8616,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8707,65 +8928,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -25,7 +25,7 @@
     <definedName name="task_start" localSheetId="0">'Project schedule'!$E1</definedName>
     <definedName name="today" localSheetId="0">TODAY()</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,9 +48,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
-    <t>Tier Plus</t>
-  </si>
-  <si>
     <t>Project start:</t>
   </si>
   <si>
@@ -60,7 +57,7 @@
     <t>Display week:</t>
   </si>
   <si>
-    <t>scroll to see more dates</t>
+    <t>SIMPLE GANTT CHART by Vertex42.com</t>
   </si>
   <si>
     <t>https://www.vertex42.com/ExcelTemplates/simple-gantt-chart.html</t>
@@ -84,130 +81,7 @@
     <t xml:space="preserve">Do not delete this row. This row is hidden to preserve a formula that is used to highlight the current day within the project schedule. </t>
   </si>
   <si>
-    <t>Data Collection - Efficacy and Cost params</t>
-  </si>
-  <si>
-    <t>Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing </t>
-  </si>
-  <si>
-    <t>Monitoring and retention</t>
-  </si>
-  <si>
-    <t>AHD and prophylaxis</t>
-  </si>
-  <si>
-    <t>ANC and PNC</t>
-  </si>
-  <si>
-    <t>Costing</t>
-  </si>
-  <si>
-    <t>Test app integration</t>
-  </si>
-  <si>
-    <t>Data Collection - Additional assumption and rates (e.g mortality rates per group)</t>
-  </si>
-  <si>
-    <t>Create parameter list with dummy values</t>
-  </si>
-  <si>
-    <t>Collect data</t>
-  </si>
-  <si>
-    <t>Integrate into app</t>
-  </si>
-  <si>
-    <t>Data Collection - Baseline intervention values (where available)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collect any available data </t>
-  </si>
-  <si>
-    <t>Define assumptions for baseline interventions in the abscence of data</t>
-  </si>
-  <si>
-    <t>Integrate both into app</t>
-  </si>
-  <si>
-    <t>Core Logic Testing - test code and documentation - usually results in app fixes as well</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Mortality</t>
-  </si>
-  <si>
-    <t>General viral suppression and infections</t>
-  </si>
-  <si>
-    <t>Populations and 95's (potentially incoporated in during above sections)</t>
-  </si>
-  <si>
-    <t>Relative scenario and baseline counts</t>
-  </si>
-  <si>
-    <t>Re-test with all new data</t>
-  </si>
-  <si>
-    <t>Validation - Logic (some incoporated during core logic testing)</t>
-  </si>
-  <si>
-    <t>Define validation cases, logic and assumptions (including eligble populations, minimum or maximum groups, overlapping interventions, impact on 90's etc)</t>
-  </si>
-  <si>
-    <t>Implement and Test</t>
-  </si>
-  <si>
-    <t>Input Validation - App - Implement and test</t>
-  </si>
-  <si>
-    <t>Define validation cases, logic and assumption (e.g prep_len + prep_oral cannot exceed eligible pop)</t>
-  </si>
-  <si>
-    <t>Need a check for if I'm missing things</t>
-  </si>
-  <si>
-    <t>Implement: Input limits (where relevant)</t>
-  </si>
-  <si>
-    <t>Implement: Limits on combinations (prep+mmd)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement: </t>
-  </si>
-  <si>
-    <t>Integrated Testing and User feedback</t>
-  </si>
-  <si>
-    <t>Figure out app publishing</t>
-  </si>
-  <si>
-    <t>Test reasonable scenarios</t>
-  </si>
-  <si>
-    <t>Test unreasonable scenarios</t>
-  </si>
-  <si>
-    <t>Fix problems</t>
-  </si>
-  <si>
-    <t>Gather user feedback</t>
-  </si>
-  <si>
-    <t>Integrate feedback</t>
-  </si>
-  <si>
-    <t>END PLANNING: JUNE 15th Max</t>
-  </si>
-  <si>
     <t>Insert new rows ABOVE this one</t>
-  </si>
-  <si>
-    <t>SIMPLE GANTT CHART by Vertex42.com</t>
   </si>
   <si>
     <t>About This Template</t>
@@ -253,6 +127,132 @@
   <si>
     <t>Businesses will find invoices, time sheets, inventory trackers, financial statements, and project planning templates. Teachers and students will find resources such as class schedules, grade books, and attendance sheets. Organize your family life with meal planners, checklists, and exercise logs. Each template is thoroughly researched, refined, and improved over time through feedback from thousands of users.</t>
   </si>
+  <si>
+    <t>Tier Plus</t>
+  </si>
+  <si>
+    <t>Data Collection - Efficacy and Cost params</t>
+  </si>
+  <si>
+    <t>Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing </t>
+  </si>
+  <si>
+    <t>Monitoring and retention</t>
+  </si>
+  <si>
+    <t>AHD and prophylaxis</t>
+  </si>
+  <si>
+    <t>ANC and PNC</t>
+  </si>
+  <si>
+    <t>Data Collection - Additional assumption and rates (e.g mortality rates per group)</t>
+  </si>
+  <si>
+    <t>Collect data</t>
+  </si>
+  <si>
+    <t>Integrate into app</t>
+  </si>
+  <si>
+    <t>Create parameter list with dummy values</t>
+  </si>
+  <si>
+    <t>Data Collection - Baseline intervention values (where available)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collect any available data </t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>General viral suppression and infections</t>
+  </si>
+  <si>
+    <t>Costing</t>
+  </si>
+  <si>
+    <t>Test app integration</t>
+  </si>
+  <si>
+    <t>Implement and Test</t>
+  </si>
+  <si>
+    <t>Define validation cases, logic and assumptions (including eligble populations, minimum or maximum groups, overlapping interventions, impact on 90's etc)</t>
+  </si>
+  <si>
+    <t>Input Validation - App - Implement and test</t>
+  </si>
+  <si>
+    <t>Define validation cases, logic and assumption (e.g prep_len + prep_oral cannot exceed eligible pop)</t>
+  </si>
+  <si>
+    <t>Integrated Testing and User feedback</t>
+  </si>
+  <si>
+    <t>Test unreasonable scenarios</t>
+  </si>
+  <si>
+    <t>Fix problems</t>
+  </si>
+  <si>
+    <t>Gather user feedback</t>
+  </si>
+  <si>
+    <t>Integrate feedback</t>
+  </si>
+  <si>
+    <t>Test reasonable scenarios</t>
+  </si>
+  <si>
+    <t>Integrate both into app</t>
+  </si>
+  <si>
+    <t>Core Logic Testing - test code and documentation - usually results in app fixes as well</t>
+  </si>
+  <si>
+    <t>Populations and 95's (potentially incoporated in during above sections)</t>
+  </si>
+  <si>
+    <t>Implement: Input limits (where relevant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement: </t>
+  </si>
+  <si>
+    <t>END PLANNING: JUNE 15th Max</t>
+  </si>
+  <si>
+    <t>Figure out app publishing</t>
+  </si>
+  <si>
+    <t>Validation - Logic (some incoporated during core logic testing)</t>
+  </si>
+  <si>
+    <t>Re-test with all new data</t>
+  </si>
+  <si>
+    <t>Mortality</t>
+  </si>
+  <si>
+    <t>scroll to see more dates</t>
+  </si>
+  <si>
+    <t>Define assumptions for baseline interventions in the abscence of data</t>
+  </si>
+  <si>
+    <t>Need a check for if I'm missing things</t>
+  </si>
+  <si>
+    <t>Implement: Limits on combinations (prep+mmd)</t>
+  </si>
+  <si>
+    <t>Relative scenario and baseline counts</t>
+  </si>
 </sst>
 </file>
 
@@ -267,7 +267,7 @@
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="169" formatCode="[$-409]d\-mmm;@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -849,7 +849,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1069,6 +1069,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1151,16 +1154,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1170,32 +1191,10 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -1206,7 +1205,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Name" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
     <cellStyle name="Project Start" xfId="9" xr:uid="{8EB8A09A-C31C-40A3-B2C1-9449520178B8}"/>
     <cellStyle name="Task" xfId="12" xr:uid="{6391D789-272B-4DD2-9BF3-2CDCF610FA41}"/>
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
@@ -2379,331 +2378,238 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CN55"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="37.375" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="105" customWidth="1"/>
-    <col min="6" max="6" width="6.625" style="106" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.875" customWidth="1"/>
-    <col min="8" max="8" width="0.625" customWidth="1"/>
-    <col min="9" max="92" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="106" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="107" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="0.6640625" customWidth="1"/>
+    <col min="9" max="92" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" ht="90" customHeight="1">
-      <c r="A1" s="112"/>
+    <row r="1" spans="1:92" ht="90" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="A1" s="81"/>
       <c r="B1" s="73" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="16"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="83"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="123" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
+      <c r="I1" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="122">
+      <c r="Q1" s="116">
         <v>46064</v>
       </c>
-      <c r="R1" s="126"/>
-      <c r="S1" s="126"/>
-      <c r="T1" s="126"/>
-      <c r="U1" s="126"/>
-      <c r="V1" s="126"/>
-      <c r="W1" s="126"/>
-      <c r="X1" s="126"/>
-      <c r="Y1" s="126"/>
-      <c r="Z1" s="126"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
     </row>
-    <row r="2" spans="1:92" ht="30" customHeight="1">
+    <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="71"/>
       <c r="C2" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="85"/>
+      <c r="I2" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="84"/>
-      <c r="I2" s="123" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="125"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="121">
+      <c r="Q2" s="114">
         <v>5</v>
       </c>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="127"/>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="115"/>
+      <c r="U2" s="115"/>
+      <c r="V2" s="115"/>
+      <c r="W2" s="115"/>
+      <c r="X2" s="115"/>
+      <c r="Y2" s="115"/>
+      <c r="Z2" s="115"/>
       <c r="AP2" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12"/>
       <c r="B3" s="19"/>
-      <c r="C3" s="111"/>
       <c r="D3" s="21"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="111"/>
-      <c r="AB3" s="111"/>
-      <c r="AC3" s="111"/>
-      <c r="AD3" s="111"/>
-      <c r="AE3" s="111"/>
-      <c r="AF3" s="111"/>
-      <c r="AG3" s="111"/>
-      <c r="AH3" s="111"/>
-      <c r="AI3" s="111"/>
-      <c r="AJ3" s="111"/>
-      <c r="AK3" s="111"/>
-      <c r="AL3" s="111"/>
-      <c r="AM3" s="111"/>
-      <c r="AN3" s="111"/>
-      <c r="AO3" s="111"/>
-      <c r="AP3" s="111"/>
-      <c r="AQ3" s="111"/>
-      <c r="AR3" s="111"/>
-      <c r="AS3" s="111"/>
-      <c r="AT3" s="111"/>
-      <c r="AU3" s="111"/>
-      <c r="AV3" s="111"/>
-      <c r="AW3" s="111"/>
-      <c r="AX3" s="111"/>
-      <c r="AY3" s="111"/>
-      <c r="AZ3" s="111"/>
-      <c r="BA3" s="111"/>
-      <c r="BB3" s="111"/>
-      <c r="BC3" s="111"/>
-      <c r="BD3" s="111"/>
-      <c r="BE3" s="111"/>
-      <c r="BF3" s="111"/>
-      <c r="BG3" s="111"/>
-      <c r="BH3" s="111"/>
-      <c r="BI3" s="111"/>
-      <c r="BJ3" s="111"/>
-      <c r="BK3" s="111"/>
-      <c r="BL3" s="111"/>
-      <c r="BM3" s="111"/>
-      <c r="BN3" s="111"/>
-      <c r="BO3" s="111"/>
-      <c r="BP3" s="111"/>
-      <c r="BQ3" s="111"/>
-      <c r="BR3" s="111"/>
-      <c r="BS3" s="111"/>
-      <c r="BT3" s="111"/>
-      <c r="BU3" s="111"/>
-      <c r="BV3" s="111"/>
-      <c r="BW3" s="111"/>
-      <c r="BX3" s="111"/>
-      <c r="BY3" s="111"/>
-      <c r="BZ3" s="111"/>
-      <c r="CA3" s="111"/>
-      <c r="CB3" s="111"/>
-      <c r="CC3" s="111"/>
-      <c r="CD3" s="111"/>
-      <c r="CE3" s="111"/>
-      <c r="CF3" s="111"/>
-      <c r="CG3" s="111"/>
-      <c r="CH3" s="111"/>
-      <c r="CI3" s="111"/>
-      <c r="CJ3" s="111"/>
-      <c r="CK3" s="111"/>
-      <c r="CL3" s="111"/>
-      <c r="CM3" s="111"/>
-      <c r="CN3" s="111"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="87"/>
     </row>
-    <row r="4" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="112"/>
-      <c r="B4" s="109" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="124">
+    <row r="4" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="81"/>
+      <c r="B4" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="88"/>
+      <c r="F4" s="87"/>
+      <c r="I4" s="120">
         <f>I5</f>
         <v>46090</v>
       </c>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="119">
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112">
         <f>P5</f>
         <v>46097</v>
       </c>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119">
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112">
         <f>W5</f>
         <v>46104</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="119"/>
-      <c r="Z4" s="119"/>
-      <c r="AA4" s="119"/>
-      <c r="AB4" s="119"/>
-      <c r="AC4" s="119"/>
-      <c r="AD4" s="119">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112">
         <f>AD5</f>
         <v>46111</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112">
         <f>AK5</f>
         <v>46118</v>
       </c>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="119"/>
-      <c r="AQ4" s="119"/>
-      <c r="AR4" s="119">
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="112"/>
+      <c r="AQ4" s="112"/>
+      <c r="AR4" s="112">
         <f>AR5</f>
         <v>46125</v>
       </c>
-      <c r="AS4" s="119"/>
-      <c r="AT4" s="119"/>
-      <c r="AU4" s="119"/>
-      <c r="AV4" s="119"/>
-      <c r="AW4" s="119"/>
-      <c r="AX4" s="119"/>
-      <c r="AY4" s="119">
+      <c r="AS4" s="112"/>
+      <c r="AT4" s="112"/>
+      <c r="AU4" s="112"/>
+      <c r="AV4" s="112"/>
+      <c r="AW4" s="112"/>
+      <c r="AX4" s="112"/>
+      <c r="AY4" s="112">
         <f>AY5</f>
         <v>46132</v>
       </c>
-      <c r="AZ4" s="119"/>
-      <c r="BA4" s="119"/>
-      <c r="BB4" s="119"/>
-      <c r="BC4" s="119"/>
-      <c r="BD4" s="119"/>
-      <c r="BE4" s="119"/>
-      <c r="BF4" s="119">
+      <c r="AZ4" s="112"/>
+      <c r="BA4" s="112"/>
+      <c r="BB4" s="112"/>
+      <c r="BC4" s="112"/>
+      <c r="BD4" s="112"/>
+      <c r="BE4" s="112"/>
+      <c r="BF4" s="112">
         <f>BF5</f>
         <v>46139</v>
       </c>
-      <c r="BG4" s="119"/>
-      <c r="BH4" s="119"/>
-      <c r="BI4" s="119"/>
-      <c r="BJ4" s="119"/>
-      <c r="BK4" s="119"/>
-      <c r="BL4" s="120"/>
-      <c r="BM4" s="119">
+      <c r="BG4" s="112"/>
+      <c r="BH4" s="112"/>
+      <c r="BI4" s="112"/>
+      <c r="BJ4" s="112"/>
+      <c r="BK4" s="112"/>
+      <c r="BL4" s="113"/>
+      <c r="BM4" s="112">
         <f>BM5</f>
         <v>46146</v>
       </c>
-      <c r="BN4" s="119"/>
-      <c r="BO4" s="119"/>
-      <c r="BP4" s="119"/>
-      <c r="BQ4" s="119"/>
-      <c r="BR4" s="119"/>
-      <c r="BS4" s="120"/>
-      <c r="BT4" s="119">
+      <c r="BN4" s="112"/>
+      <c r="BO4" s="112"/>
+      <c r="BP4" s="112"/>
+      <c r="BQ4" s="112"/>
+      <c r="BR4" s="112"/>
+      <c r="BS4" s="113"/>
+      <c r="BT4" s="112">
         <f>BT5</f>
         <v>46153</v>
       </c>
-      <c r="BU4" s="119"/>
-      <c r="BV4" s="119"/>
-      <c r="BW4" s="119"/>
-      <c r="BX4" s="119"/>
-      <c r="BY4" s="119"/>
-      <c r="BZ4" s="120"/>
-      <c r="CA4" s="119">
+      <c r="BU4" s="112"/>
+      <c r="BV4" s="112"/>
+      <c r="BW4" s="112"/>
+      <c r="BX4" s="112"/>
+      <c r="BY4" s="112"/>
+      <c r="BZ4" s="113"/>
+      <c r="CA4" s="112">
         <f>CA5</f>
         <v>46160</v>
       </c>
-      <c r="CB4" s="119"/>
-      <c r="CC4" s="119"/>
-      <c r="CD4" s="119"/>
-      <c r="CE4" s="119"/>
-      <c r="CF4" s="119"/>
-      <c r="CG4" s="120"/>
-      <c r="CH4" s="119">
+      <c r="CB4" s="112"/>
+      <c r="CC4" s="112"/>
+      <c r="CD4" s="112"/>
+      <c r="CE4" s="112"/>
+      <c r="CF4" s="112"/>
+      <c r="CG4" s="113"/>
+      <c r="CH4" s="112">
         <f>CH5</f>
         <v>46167</v>
       </c>
-      <c r="CI4" s="119"/>
-      <c r="CJ4" s="119"/>
-      <c r="CK4" s="119"/>
-      <c r="CL4" s="119"/>
-      <c r="CM4" s="119"/>
-      <c r="CN4" s="120"/>
+      <c r="CI4" s="112"/>
+      <c r="CJ4" s="112"/>
+      <c r="CK4" s="112"/>
+      <c r="CL4" s="112"/>
+      <c r="CM4" s="112"/>
+      <c r="CN4" s="113"/>
     </row>
-    <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="114"/>
-      <c r="B5" s="115" t="s">
+    <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="123"/>
+      <c r="B5" s="124" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="D5" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="E5" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="113" t="s">
+      <c r="F5" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="113" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
       <c r="I5" s="22">
         <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
         <v>46090</v>
@@ -3041,15 +2947,13 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="114"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
+    <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="123"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
       <c r="I6" s="25" t="str">
         <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -3387,18 +3291,17 @@
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:92" s="20" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1">
+    <row r="7" spans="1:92" s="20" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="28"/>
       <c r="C7" s="29"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111" t="str">
-        <f ca="1">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="H7" s="20" t="str">
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I7" s="30"/>
@@ -3486,18 +3389,18 @@
       <c r="CM7" s="30"/>
       <c r="CN7" s="30"/>
     </row>
-    <row r="8" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A8" s="112"/>
+    <row r="8" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="81"/>
       <c r="B8" s="31" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C8" s="32"/>
       <c r="D8" s="33"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="91"/>
       <c r="G8" s="14"/>
       <c r="H8" s="4" t="str">
-        <f t="shared" ref="H8:H19" ca="1" si="29">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H8:H19" si="29">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I8" s="34"/>
@@ -3585,26 +3488,26 @@
       <c r="CM8" s="34"/>
       <c r="CN8" s="34"/>
     </row>
-    <row r="9" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A9" s="112"/>
+    <row r="9" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="81"/>
       <c r="B9" s="36" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="38">
         <v>0</v>
       </c>
-      <c r="E9" s="91">
+      <c r="E9" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F9" s="91">
+      <c r="F9" s="92">
         <f>E9+58</f>
         <v>46122</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I9" s="39"/>
@@ -3692,26 +3595,26 @@
       <c r="CM9" s="39"/>
       <c r="CN9" s="39"/>
     </row>
-    <row r="10" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A10" s="112"/>
+    <row r="10" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="81"/>
       <c r="B10" s="40" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="42">
         <v>0.8</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F10" s="91">
+      <c r="F10" s="92">
         <f>E10+58</f>
         <v>46122</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I10" s="39"/>
@@ -3799,26 +3702,26 @@
       <c r="CM10" s="39"/>
       <c r="CN10" s="39"/>
     </row>
-    <row r="11" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="11" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="40" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="42">
         <v>0</v>
       </c>
-      <c r="E11" s="91">
+      <c r="E11" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F11" s="91">
+      <c r="F11" s="92">
         <f>E11+58</f>
         <v>46122</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I11" s="39"/>
@@ -3906,26 +3809,26 @@
       <c r="CM11" s="39"/>
       <c r="CN11" s="39"/>
     </row>
-    <row r="12" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="12" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="40" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C12" s="41"/>
       <c r="D12" s="42">
         <v>0</v>
       </c>
-      <c r="E12" s="91">
+      <c r="E12" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F12" s="91">
+      <c r="F12" s="92">
         <f>E12+58</f>
         <v>46122</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I12" s="39"/>
@@ -4013,26 +3916,26 @@
       <c r="CM12" s="39"/>
       <c r="CN12" s="39"/>
     </row>
-    <row r="13" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="13" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="40" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="42">
         <v>0</v>
       </c>
-      <c r="E13" s="91">
+      <c r="E13" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F13" s="91">
+      <c r="F13" s="92">
         <f>E13+58</f>
         <v>46122</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I13" s="39"/>
@@ -4120,20 +4023,20 @@
       <c r="CM13" s="39"/>
       <c r="CN13" s="39"/>
     </row>
-    <row r="14" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="14" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="40" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C14" s="41"/>
       <c r="D14" s="42">
         <v>0.9</v>
       </c>
-      <c r="E14" s="91">
+      <c r="E14" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F14" s="91">
+      <c r="F14" s="92">
         <f>E14+58</f>
         <v>46122</v>
       </c>
@@ -4224,26 +4127,26 @@
       <c r="CM14" s="39"/>
       <c r="CN14" s="39"/>
     </row>
-    <row r="15" spans="1:92" s="35" customFormat="1" ht="53.1" customHeight="1" thickBot="1">
+    <row r="15" spans="1:92" s="35" customFormat="1" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="40" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="42">
         <v>0</v>
       </c>
-      <c r="E15" s="91">
+      <c r="E15" s="92">
         <f>F13+1</f>
         <v>46123</v>
       </c>
-      <c r="F15" s="91">
+      <c r="F15" s="92">
         <f>E15+14</f>
         <v>46137</v>
       </c>
-      <c r="G15" s="110"/>
+      <c r="G15" s="111"/>
       <c r="H15" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>15</v>
       </c>
       <c r="I15" s="39"/>
@@ -4331,18 +4234,18 @@
       <c r="CM15" s="39"/>
       <c r="CN15" s="39"/>
     </row>
-    <row r="16" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A16" s="112"/>
+    <row r="16" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="81"/>
       <c r="B16" s="31" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C16" s="32"/>
       <c r="D16" s="33"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="91"/>
       <c r="G16" s="14"/>
       <c r="H16" s="4" t="str">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="I16" s="34"/>
@@ -4430,26 +4333,26 @@
       <c r="CM16" s="34"/>
       <c r="CN16" s="34"/>
     </row>
-    <row r="17" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A17" s="112"/>
+    <row r="17" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="81"/>
       <c r="B17" s="36" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C17" s="37"/>
       <c r="D17" s="38">
         <v>1</v>
       </c>
-      <c r="E17" s="91">
+      <c r="E17" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F17" s="91">
+      <c r="F17" s="92">
         <f>E17+58</f>
         <v>46122</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I17" s="39"/>
@@ -4537,26 +4440,26 @@
       <c r="CM17" s="39"/>
       <c r="CN17" s="39"/>
     </row>
-    <row r="18" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A18" s="112"/>
+    <row r="18" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="81"/>
       <c r="B18" s="40" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="42">
         <v>0</v>
       </c>
-      <c r="E18" s="91">
+      <c r="E18" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F18" s="91">
+      <c r="F18" s="92">
         <f>E18+58</f>
         <v>46122</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I18" s="39"/>
@@ -4644,26 +4547,26 @@
       <c r="CM18" s="39"/>
       <c r="CN18" s="39"/>
     </row>
-    <row r="19" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="19" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="40" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="42">
         <v>0</v>
       </c>
-      <c r="E19" s="91">
+      <c r="E19" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F19" s="92">
+      <c r="F19" s="93">
         <f>F18</f>
         <v>46122</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="4">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="I19" s="39"/>
@@ -4751,18 +4654,18 @@
       <c r="CM19" s="39"/>
       <c r="CN19" s="39"/>
     </row>
-    <row r="20" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A20" s="112"/>
+    <row r="20" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="81"/>
       <c r="B20" s="31" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="33"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="91"/>
       <c r="G20" s="14"/>
       <c r="H20" s="4" t="str">
-        <f t="shared" ref="H20:H52" ca="1" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H20:H52" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I20" s="34"/>
@@ -4850,26 +4753,26 @@
       <c r="CM20" s="34"/>
       <c r="CN20" s="34"/>
     </row>
-    <row r="21" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A21" s="112"/>
+    <row r="21" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81"/>
       <c r="B21" s="36" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38">
         <v>0.33</v>
       </c>
-      <c r="E21" s="91">
+      <c r="E21" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F21" s="91">
+      <c r="F21" s="92">
         <f>E21+58</f>
         <v>46122</v>
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>59</v>
       </c>
       <c r="I21" s="39"/>
@@ -4957,18 +4860,18 @@
       <c r="CM21" s="39"/>
       <c r="CN21" s="39"/>
     </row>
-    <row r="22" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A22" s="112"/>
+    <row r="22" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="81"/>
       <c r="B22" s="36" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="38"/>
-      <c r="E22" s="91">
+      <c r="E22" s="92">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F22" s="91">
+      <c r="F22" s="92">
         <f>E22+58</f>
         <v>46122</v>
       </c>
@@ -5059,26 +4962,26 @@
       <c r="CM22" s="39"/>
       <c r="CN22" s="39"/>
     </row>
-    <row r="23" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A23" s="112"/>
+    <row r="23" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="81"/>
       <c r="B23" s="40" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C23" s="41"/>
       <c r="D23" s="42">
         <v>0.33</v>
       </c>
-      <c r="E23" s="91">
+      <c r="E23" s="92">
         <f>F22+1</f>
         <v>46123</v>
       </c>
-      <c r="F23" s="92">
+      <c r="F23" s="93">
         <f>E23+7</f>
         <v>46130</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I23" s="39"/>
@@ -5166,41 +5069,41 @@
       <c r="CM23" s="39"/>
       <c r="CN23" s="39"/>
     </row>
-    <row r="24" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A24" s="112"/>
+    <row r="24" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="81"/>
       <c r="B24" s="44" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C24" s="45"/>
       <c r="D24" s="46"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="95"/>
       <c r="G24" s="14"/>
       <c r="H24" s="4" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A25" s="112"/>
+    <row r="25" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="81"/>
       <c r="B25" s="47" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="49">
         <v>1</v>
       </c>
-      <c r="E25" s="95">
+      <c r="E25" s="96">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="96">
         <f>E25+20</f>
         <v>46084</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>21</v>
       </c>
       <c r="I25" s="39"/>
@@ -5288,26 +5191,26 @@
       <c r="CM25" s="39"/>
       <c r="CN25" s="39"/>
     </row>
-    <row r="26" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="26" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="47" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C26" s="48"/>
       <c r="D26" s="49">
         <v>0.8</v>
       </c>
-      <c r="E26" s="95">
+      <c r="E26" s="96">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F26" s="95">
+      <c r="F26" s="96">
         <f>E26+9</f>
         <v>46073</v>
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>10</v>
       </c>
       <c r="I26" s="39"/>
@@ -5395,25 +5298,25 @@
       <c r="CM26" s="39"/>
       <c r="CN26" s="39"/>
     </row>
-    <row r="27" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="27" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="47" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C27" s="48"/>
       <c r="D27" s="49">
         <v>1</v>
       </c>
-      <c r="E27" s="95">
+      <c r="E27" s="96">
         <v>46083</v>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="96">
         <f>E27+10</f>
         <v>46093</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>11</v>
       </c>
       <c r="I27" s="39"/>
@@ -5501,26 +5404,26 @@
       <c r="CM27" s="39"/>
       <c r="CN27" s="39"/>
     </row>
-    <row r="28" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="28" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>
       <c r="B28" s="47" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C28" s="48"/>
       <c r="D28" s="49">
         <v>1</v>
       </c>
-      <c r="E28" s="95">
+      <c r="E28" s="96">
         <f>F27+1</f>
         <v>46094</v>
       </c>
-      <c r="F28" s="95">
+      <c r="F28" s="96">
         <f>E28+7</f>
         <v>46101</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I28" s="39"/>
@@ -5608,26 +5511,26 @@
       <c r="CM28" s="39"/>
       <c r="CN28" s="39"/>
     </row>
-    <row r="29" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="29" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>
       <c r="B29" s="47" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C29" s="48"/>
       <c r="D29" s="49">
         <v>1</v>
       </c>
-      <c r="E29" s="95">
+      <c r="E29" s="96">
         <f>E28</f>
         <v>46094</v>
       </c>
-      <c r="F29" s="95">
+      <c r="F29" s="96">
         <f>E29+7</f>
         <v>46101</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I29" s="39"/>
@@ -5715,20 +5618,20 @@
       <c r="CM29" s="39"/>
       <c r="CN29" s="39"/>
     </row>
-    <row r="30" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="30" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="47" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C30" s="48"/>
       <c r="D30" s="49">
         <v>1</v>
       </c>
-      <c r="E30" s="95">
+      <c r="E30" s="96">
         <f>F28+1</f>
         <v>46102</v>
       </c>
-      <c r="F30" s="95">
+      <c r="F30" s="96">
         <f>E30+7</f>
         <v>46109</v>
       </c>
@@ -5819,26 +5722,26 @@
       <c r="CM30" s="39"/>
       <c r="CN30" s="39"/>
     </row>
-    <row r="31" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="31" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
       <c r="B31" s="47" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C31" s="48"/>
       <c r="D31" s="49">
         <v>1</v>
       </c>
-      <c r="E31" s="95">
+      <c r="E31" s="96">
         <f>F29+1</f>
         <v>46102</v>
       </c>
-      <c r="F31" s="95">
+      <c r="F31" s="96">
         <f>E31+7</f>
         <v>46109</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I31" s="39"/>
@@ -5926,26 +5829,26 @@
       <c r="CM31" s="39"/>
       <c r="CN31" s="39"/>
     </row>
-    <row r="32" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="32" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12"/>
       <c r="B32" s="47" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32" s="48"/>
       <c r="D32" s="49">
         <v>0.15</v>
       </c>
-      <c r="E32" s="95">
+      <c r="E32" s="96">
         <f>F31+1</f>
         <v>46110</v>
       </c>
-      <c r="F32" s="95">
+      <c r="F32" s="96">
         <f>E32+3</f>
         <v>46113</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>4</v>
       </c>
       <c r="I32" s="39"/>
@@ -6033,26 +5936,26 @@
       <c r="CM32" s="39"/>
       <c r="CN32" s="39"/>
     </row>
-    <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
       <c r="B33" s="47" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C33" s="48"/>
       <c r="D33" s="49">
         <v>0</v>
       </c>
-      <c r="E33" s="95">
+      <c r="E33" s="96">
         <f>F32+1</f>
         <v>46114</v>
       </c>
-      <c r="F33" s="95">
+      <c r="F33" s="96">
         <f>E33+8</f>
         <v>46122</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>9</v>
       </c>
       <c r="I33" s="39"/>
@@ -6140,26 +6043,26 @@
       <c r="CM33" s="39"/>
       <c r="CN33" s="39"/>
     </row>
-    <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12"/>
       <c r="B34" s="47" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C34" s="48"/>
       <c r="D34" s="49">
         <v>0</v>
       </c>
-      <c r="E34" s="95">
+      <c r="E34" s="96">
         <f>F32+1</f>
         <v>46114</v>
       </c>
-      <c r="F34" s="95">
+      <c r="F34" s="96">
         <f>E34+7</f>
         <v>46121</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I34" s="39"/>
@@ -6247,26 +6150,26 @@
       <c r="CM34" s="39"/>
       <c r="CN34" s="39"/>
     </row>
-    <row r="35" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="35" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
       <c r="B35" s="47" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C35" s="48"/>
       <c r="D35" s="49">
         <v>0</v>
       </c>
-      <c r="E35" s="95">
+      <c r="E35" s="96">
         <f>F33+1</f>
         <v>46123</v>
       </c>
-      <c r="F35" s="95">
+      <c r="F35" s="96">
         <f>E35+7</f>
         <v>46130</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I35" s="39"/>
@@ -6354,18 +6257,18 @@
       <c r="CM35" s="39"/>
       <c r="CN35" s="39"/>
     </row>
-    <row r="36" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="36" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12"/>
       <c r="B36" s="50" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="52"/>
-      <c r="E36" s="96"/>
-      <c r="F36" s="97"/>
+      <c r="E36" s="97"/>
+      <c r="F36" s="98"/>
       <c r="G36" s="14"/>
       <c r="H36" s="4" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="I36" s="53"/>
@@ -6453,26 +6356,26 @@
       <c r="CM36" s="53"/>
       <c r="CN36" s="53"/>
     </row>
-    <row r="37" spans="1:92" s="35" customFormat="1" ht="68.099999999999994" customHeight="1" thickBot="1">
+    <row r="37" spans="1:92" s="35" customFormat="1" ht="68" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12"/>
-      <c r="B37" s="108" t="s">
-        <v>36</v>
+      <c r="B37" s="109" t="s">
+        <v>43</v>
       </c>
       <c r="C37" s="55"/>
       <c r="D37" s="56">
         <v>0.2</v>
       </c>
-      <c r="E37" s="98">
+      <c r="E37" s="99">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F37" s="98">
+      <c r="F37" s="99">
         <f>E37+14</f>
         <v>46078</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="I37" s="39"/>
@@ -6560,26 +6463,26 @@
       <c r="CM37" s="39"/>
       <c r="CN37" s="39"/>
     </row>
-    <row r="38" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="38" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
       <c r="B38" s="54" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C38" s="55"/>
       <c r="D38" s="56">
         <v>0.2</v>
       </c>
-      <c r="E38" s="98">
+      <c r="E38" s="99">
         <f>F37+1</f>
         <v>46079</v>
       </c>
-      <c r="F38" s="98">
+      <c r="F38" s="99">
         <f>F35</f>
         <v>46130</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>52</v>
       </c>
       <c r="I38" s="39"/>
@@ -6667,18 +6570,18 @@
       <c r="CM38" s="39"/>
       <c r="CN38" s="39"/>
     </row>
-    <row r="39" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="39" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
       <c r="B39" s="50" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C39" s="51"/>
       <c r="D39" s="52"/>
-      <c r="E39" s="96"/>
-      <c r="F39" s="97"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="98"/>
       <c r="G39" s="14"/>
       <c r="H39" s="4" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="I39" s="53"/>
@@ -6766,28 +6669,28 @@
       <c r="CM39" s="53"/>
       <c r="CN39" s="53"/>
     </row>
-    <row r="40" spans="1:92" s="35" customFormat="1" ht="42.95" thickBot="1">
+    <row r="40" spans="1:92" s="35" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="108" t="s">
-        <v>39</v>
+      <c r="B40" s="109" t="s">
+        <v>45</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="56">
         <v>0.9</v>
       </c>
-      <c r="E40" s="98">
+      <c r="E40" s="99">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F40" s="98">
+      <c r="F40" s="99">
         <f>E40+21</f>
         <v>46085</v>
       </c>
-      <c r="G40" s="110" t="s">
-        <v>40</v>
+      <c r="G40" s="111" t="s">
+        <v>64</v>
       </c>
       <c r="H40" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>22</v>
       </c>
       <c r="I40" s="39"/>
@@ -6875,26 +6778,26 @@
       <c r="CM40" s="39"/>
       <c r="CN40" s="39"/>
     </row>
-    <row r="41" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1">
+    <row r="41" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12"/>
-      <c r="B41" s="108" t="s">
-        <v>41</v>
+      <c r="B41" s="109" t="s">
+        <v>55</v>
       </c>
       <c r="C41" s="55"/>
       <c r="D41" s="56">
         <v>0.3</v>
       </c>
-      <c r="E41" s="98">
+      <c r="E41" s="99">
         <f>F40</f>
         <v>46085</v>
       </c>
-      <c r="F41" s="98">
+      <c r="F41" s="99">
         <f>F35</f>
         <v>46130</v>
       </c>
       <c r="G41" s="14"/>
       <c r="H41" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>46</v>
       </c>
       <c r="I41" s="39"/>
@@ -6982,20 +6885,20 @@
       <c r="CM41" s="39"/>
       <c r="CN41" s="39"/>
     </row>
-    <row r="42" spans="1:92" s="35" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
+    <row r="42" spans="1:92" s="35" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12"/>
       <c r="B42" s="54" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C42" s="55"/>
       <c r="D42" s="56">
         <v>1</v>
       </c>
-      <c r="E42" s="98">
+      <c r="E42" s="99">
         <f>F40</f>
         <v>46085</v>
       </c>
-      <c r="F42" s="98">
+      <c r="F42" s="99">
         <f>F35</f>
         <v>46130</v>
       </c>
@@ -7086,20 +6989,20 @@
       <c r="CM42" s="39"/>
       <c r="CN42" s="39"/>
     </row>
-    <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>
       <c r="B43" s="54" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C43" s="55"/>
       <c r="D43" s="56">
         <v>0</v>
       </c>
-      <c r="E43" s="98"/>
-      <c r="F43" s="98"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
       <c r="G43" s="14"/>
       <c r="H43" s="4" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="I43" s="39"/>
@@ -7187,18 +7090,18 @@
       <c r="CM43" s="39"/>
       <c r="CN43" s="39"/>
     </row>
-    <row r="44" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="44" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="57" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C44" s="58"/>
       <c r="D44" s="59"/>
-      <c r="E44" s="99"/>
-      <c r="F44" s="100"/>
+      <c r="E44" s="100"/>
+      <c r="F44" s="101"/>
       <c r="G44" s="14"/>
       <c r="H44" s="4" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="I44" s="60"/>
@@ -7286,26 +7189,26 @@
       <c r="CM44" s="60"/>
       <c r="CN44" s="60"/>
     </row>
-    <row r="45" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="45" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
       <c r="B45" s="61" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C45" s="62"/>
       <c r="D45" s="63">
         <v>1</v>
       </c>
-      <c r="E45" s="101">
+      <c r="E45" s="102">
         <f>E37</f>
         <v>46064</v>
       </c>
-      <c r="F45" s="101">
+      <c r="F45" s="102">
         <f>E49-3</f>
         <v>46157</v>
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>94</v>
       </c>
       <c r="I45" s="39"/>
@@ -7393,25 +7296,25 @@
       <c r="CM45" s="39"/>
       <c r="CN45" s="39"/>
     </row>
-    <row r="46" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="46" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
       <c r="B46" s="61" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="63">
         <v>0.9</v>
       </c>
-      <c r="E46" s="101">
+      <c r="E46" s="102">
         <v>46146</v>
       </c>
-      <c r="F46" s="101">
+      <c r="F46" s="102">
         <f>E46+7</f>
         <v>46153</v>
       </c>
       <c r="G46" s="14"/>
       <c r="H46" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I46" s="39"/>
@@ -7499,7 +7402,7 @@
       <c r="CM46" s="39"/>
       <c r="CN46" s="39"/>
     </row>
-    <row r="47" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="47" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
       <c r="B47" s="61" t="s">
         <v>47</v>
@@ -7508,16 +7411,16 @@
       <c r="D47" s="63">
         <v>0</v>
       </c>
-      <c r="E47" s="101">
+      <c r="E47" s="102">
         <v>46146</v>
       </c>
-      <c r="F47" s="101">
+      <c r="F47" s="102">
         <f>E47+7</f>
         <v>46153</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I47" s="39"/>
@@ -7605,7 +7508,7 @@
       <c r="CM47" s="39"/>
       <c r="CN47" s="39"/>
     </row>
-    <row r="48" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="48" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
       <c r="B48" s="61" t="s">
         <v>48</v>
@@ -7614,17 +7517,17 @@
       <c r="D48" s="63">
         <v>0</v>
       </c>
-      <c r="E48" s="101">
+      <c r="E48" s="102">
         <f>F47</f>
         <v>46153</v>
       </c>
-      <c r="F48" s="101">
+      <c r="F48" s="102">
         <f>E48+7</f>
         <v>46160</v>
       </c>
       <c r="G48" s="14"/>
       <c r="H48" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I48" s="39"/>
@@ -7712,7 +7615,7 @@
       <c r="CM48" s="39"/>
       <c r="CN48" s="39"/>
     </row>
-    <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>
       <c r="B49" s="61" t="s">
         <v>49</v>
@@ -7721,17 +7624,17 @@
       <c r="D49" s="63">
         <v>0</v>
       </c>
-      <c r="E49" s="101">
+      <c r="E49" s="102">
         <f>F48</f>
         <v>46160</v>
       </c>
-      <c r="F49" s="101">
+      <c r="F49" s="102">
         <f>E49+7</f>
         <v>46167</v>
       </c>
       <c r="G49" s="14"/>
       <c r="H49" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="I49" s="39"/>
@@ -7819,7 +7722,7 @@
       <c r="CM49" s="39"/>
       <c r="CN49" s="39"/>
     </row>
-    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>
       <c r="B50" s="61" t="s">
         <v>50</v>
@@ -7828,17 +7731,17 @@
       <c r="D50" s="63">
         <v>0</v>
       </c>
-      <c r="E50" s="101">
+      <c r="E50" s="102">
         <f>F49</f>
         <v>46167</v>
       </c>
-      <c r="F50" s="101">
+      <c r="F50" s="102">
         <f>E50+14</f>
         <v>46181</v>
       </c>
       <c r="G50" s="14"/>
       <c r="H50" s="4">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="I50" s="39"/>
@@ -7926,18 +7829,18 @@
       <c r="CM50" s="39"/>
       <c r="CN50" s="39"/>
     </row>
-    <row r="51" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="51" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12"/>
       <c r="B51" s="64" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C51" s="65"/>
       <c r="D51" s="66"/>
-      <c r="E51" s="102"/>
-      <c r="F51" s="102"/>
+      <c r="E51" s="103"/>
+      <c r="F51" s="103"/>
       <c r="G51" s="14"/>
       <c r="H51" s="4" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="I51" s="34"/>
@@ -8025,18 +7928,18 @@
       <c r="CM51" s="34"/>
       <c r="CN51" s="34"/>
     </row>
-    <row r="52" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A52" s="112"/>
+    <row r="52" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="81"/>
       <c r="B52" s="67" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C52" s="68"/>
       <c r="D52" s="69"/>
-      <c r="E52" s="103"/>
-      <c r="F52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="105"/>
       <c r="G52" s="14"/>
       <c r="H52" s="5" t="str">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="I52" s="70"/>
@@ -8124,18 +8027,24 @@
       <c r="CM52" s="70"/>
       <c r="CN52" s="70"/>
     </row>
-    <row r="53" spans="1:92" ht="30" customHeight="1">
+    <row r="53" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:92" ht="30" customHeight="1">
+    <row r="54" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="13"/>
-      <c r="F54" s="107"/>
+      <c r="F54" s="108"/>
     </row>
-    <row r="55" spans="1:92" ht="30" customHeight="1">
+    <row r="55" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -8152,12 +8061,6 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D52">
     <cfRule type="dataBar" priority="102">
@@ -8469,110 +8372,110 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="87" style="6" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1"/>
-    <row r="2" spans="1:2" s="8" customFormat="1" ht="15.95">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="1:2" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="74" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="B2" s="7"/>
     </row>
-    <row r="3" spans="1:2" s="10" customFormat="1" ht="27" customHeight="1">
+    <row r="3" spans="1:2" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="75"/>
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:2" s="9" customFormat="1" ht="30.95">
+    <row r="4" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
       <c r="A4" s="76" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74.25" customHeight="1">
+    <row r="5" spans="1:2" ht="74.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="77" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1">
+    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="76" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="6" customFormat="1" ht="205.35" customHeight="1">
+    <row r="7" spans="1:2" s="6" customFormat="1" ht="205.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="78" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="9" customFormat="1" ht="30.95">
+    <row r="8" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
       <c r="A8" s="76" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="60">
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.15">
       <c r="A9" s="77" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="6" customFormat="1" ht="28.35" customHeight="1">
+    <row r="10" spans="1:2" s="6" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="79" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="9" customFormat="1" ht="30.95">
+    <row r="11" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
       <c r="A11" s="76" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30">
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.15">
       <c r="A12" s="77" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="6" customFormat="1" ht="28.35" customHeight="1">
+    <row r="13" spans="1:2" s="6" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="79" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="9" customFormat="1" ht="30.95">
+    <row r="14" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
       <c r="A14" s="76" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="75" customHeight="1">
+    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="77" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="75">
+    <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.15">
       <c r="A16" s="77" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="80"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="80"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="80"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="80"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="80"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="80"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="80"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="80"/>
     </row>
   </sheetData>
@@ -8588,35 +8491,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8928,16 +8802,74 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -25,7 +25,7 @@
     <definedName name="task_start" localSheetId="0">'Project schedule'!$E1</definedName>
     <definedName name="today" localSheetId="0">TODAY()</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -48,6 +48,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
+    <t>Tier Plus</t>
+  </si>
+  <si>
     <t>Project start:</t>
   </si>
   <si>
@@ -57,7 +60,7 @@
     <t>Display week:</t>
   </si>
   <si>
-    <t>SIMPLE GANTT CHART by Vertex42.com</t>
+    <t>scroll to see more dates</t>
   </si>
   <si>
     <t>https://www.vertex42.com/ExcelTemplates/simple-gantt-chart.html</t>
@@ -81,7 +84,130 @@
     <t xml:space="preserve">Do not delete this row. This row is hidden to preserve a formula that is used to highlight the current day within the project schedule. </t>
   </si>
   <si>
+    <t>Data Collection - Efficacy and Cost params</t>
+  </si>
+  <si>
+    <t>Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing </t>
+  </si>
+  <si>
+    <t>Monitoring and retention</t>
+  </si>
+  <si>
+    <t>AHD and prophylaxis</t>
+  </si>
+  <si>
+    <t>ANC and PNC</t>
+  </si>
+  <si>
+    <t>Costing</t>
+  </si>
+  <si>
+    <t>Test app integration</t>
+  </si>
+  <si>
+    <t>Data Collection - Additional assumption and rates (e.g mortality rates per group)</t>
+  </si>
+  <si>
+    <t>Create parameter list with dummy values</t>
+  </si>
+  <si>
+    <t>Collect data</t>
+  </si>
+  <si>
+    <t>Integrate into app</t>
+  </si>
+  <si>
+    <t>Data Collection - Baseline intervention values (where available)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collect any available data </t>
+  </si>
+  <si>
+    <t>Define assumptions for baseline interventions in the abscence of data</t>
+  </si>
+  <si>
+    <t>Integrate both into app</t>
+  </si>
+  <si>
+    <t>Core Logic Testing - test code and documentation - usually results in app fixes as well</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Mortality</t>
+  </si>
+  <si>
+    <t>General viral suppression and infections</t>
+  </si>
+  <si>
+    <t>Populations and 95's (potentially incoporated in during above sections)</t>
+  </si>
+  <si>
+    <t>Relative scenario and baseline counts</t>
+  </si>
+  <si>
+    <t>Re-test with all new data</t>
+  </si>
+  <si>
+    <t>Validation - Logic (some incoporated during core logic testing)</t>
+  </si>
+  <si>
+    <t>Define validation cases, logic and assumptions (including eligble populations, minimum or maximum groups, overlapping interventions, impact on 90's etc)</t>
+  </si>
+  <si>
+    <t>Implement and Test</t>
+  </si>
+  <si>
+    <t>Input Validation - App - Implement and test</t>
+  </si>
+  <si>
+    <t>Define validation cases, logic and assumption (e.g prep_len + prep_oral cannot exceed eligible pop)</t>
+  </si>
+  <si>
+    <t>Need a check for if I'm missing things</t>
+  </si>
+  <si>
+    <t>Implement: Input limits (where relevant)</t>
+  </si>
+  <si>
+    <t>Implement: Limits on combinations (prep+mmd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement: </t>
+  </si>
+  <si>
+    <t>Integrated Testing and User feedback</t>
+  </si>
+  <si>
+    <t>Figure out app publishing</t>
+  </si>
+  <si>
+    <t>Test reasonable scenarios</t>
+  </si>
+  <si>
+    <t>Test unreasonable scenarios</t>
+  </si>
+  <si>
+    <t>Fix problems</t>
+  </si>
+  <si>
+    <t>Gather user feedback</t>
+  </si>
+  <si>
+    <t>Integrate feedback</t>
+  </si>
+  <si>
+    <t>END PLANNING: JUNE 15th Max</t>
+  </si>
+  <si>
     <t>Insert new rows ABOVE this one</t>
+  </si>
+  <si>
+    <t>SIMPLE GANTT CHART by Vertex42.com</t>
   </si>
   <si>
     <t>About This Template</t>
@@ -127,132 +253,6 @@
   <si>
     <t>Businesses will find invoices, time sheets, inventory trackers, financial statements, and project planning templates. Teachers and students will find resources such as class schedules, grade books, and attendance sheets. Organize your family life with meal planners, checklists, and exercise logs. Each template is thoroughly researched, refined, and improved over time through feedback from thousands of users.</t>
   </si>
-  <si>
-    <t>Tier Plus</t>
-  </si>
-  <si>
-    <t>Data Collection - Efficacy and Cost params</t>
-  </si>
-  <si>
-    <t>Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing </t>
-  </si>
-  <si>
-    <t>Monitoring and retention</t>
-  </si>
-  <si>
-    <t>AHD and prophylaxis</t>
-  </si>
-  <si>
-    <t>ANC and PNC</t>
-  </si>
-  <si>
-    <t>Data Collection - Additional assumption and rates (e.g mortality rates per group)</t>
-  </si>
-  <si>
-    <t>Collect data</t>
-  </si>
-  <si>
-    <t>Integrate into app</t>
-  </si>
-  <si>
-    <t>Create parameter list with dummy values</t>
-  </si>
-  <si>
-    <t>Data Collection - Baseline intervention values (where available)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collect any available data </t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>General viral suppression and infections</t>
-  </si>
-  <si>
-    <t>Costing</t>
-  </si>
-  <si>
-    <t>Test app integration</t>
-  </si>
-  <si>
-    <t>Implement and Test</t>
-  </si>
-  <si>
-    <t>Define validation cases, logic and assumptions (including eligble populations, minimum or maximum groups, overlapping interventions, impact on 90's etc)</t>
-  </si>
-  <si>
-    <t>Input Validation - App - Implement and test</t>
-  </si>
-  <si>
-    <t>Define validation cases, logic and assumption (e.g prep_len + prep_oral cannot exceed eligible pop)</t>
-  </si>
-  <si>
-    <t>Integrated Testing and User feedback</t>
-  </si>
-  <si>
-    <t>Test unreasonable scenarios</t>
-  </si>
-  <si>
-    <t>Fix problems</t>
-  </si>
-  <si>
-    <t>Gather user feedback</t>
-  </si>
-  <si>
-    <t>Integrate feedback</t>
-  </si>
-  <si>
-    <t>Test reasonable scenarios</t>
-  </si>
-  <si>
-    <t>Integrate both into app</t>
-  </si>
-  <si>
-    <t>Core Logic Testing - test code and documentation - usually results in app fixes as well</t>
-  </si>
-  <si>
-    <t>Populations and 95's (potentially incoporated in during above sections)</t>
-  </si>
-  <si>
-    <t>Implement: Input limits (where relevant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implement: </t>
-  </si>
-  <si>
-    <t>END PLANNING: JUNE 15th Max</t>
-  </si>
-  <si>
-    <t>Figure out app publishing</t>
-  </si>
-  <si>
-    <t>Validation - Logic (some incoporated during core logic testing)</t>
-  </si>
-  <si>
-    <t>Re-test with all new data</t>
-  </si>
-  <si>
-    <t>Mortality</t>
-  </si>
-  <si>
-    <t>scroll to see more dates</t>
-  </si>
-  <si>
-    <t>Define assumptions for baseline interventions in the abscence of data</t>
-  </si>
-  <si>
-    <t>Need a check for if I'm missing things</t>
-  </si>
-  <si>
-    <t>Implement: Limits on combinations (prep+mmd)</t>
-  </si>
-  <si>
-    <t>Relative scenario and baseline counts</t>
-  </si>
 </sst>
 </file>
 
@@ -267,7 +267,7 @@
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="169" formatCode="[$-409]d\-mmm;@"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -849,7 +849,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1069,9 +1069,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1154,6 +1151,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1163,38 +1182,20 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -1205,7 +1206,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Name" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="Project Start" xfId="9" xr:uid="{8EB8A09A-C31C-40A3-B2C1-9449520178B8}"/>
     <cellStyle name="Task" xfId="12" xr:uid="{6391D789-272B-4DD2-9BF3-2CDCF610FA41}"/>
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
@@ -2378,238 +2379,331 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CN55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" style="106" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" style="107" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
-    <col min="8" max="8" width="0.6640625" customWidth="1"/>
-    <col min="9" max="92" width="2.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="37.375" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="105" customWidth="1"/>
+    <col min="6" max="6" width="6.625" style="106" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.875" customWidth="1"/>
+    <col min="8" max="8" width="0.625" customWidth="1"/>
+    <col min="9" max="92" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:92" ht="90" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A1" s="81"/>
+    <row r="1" spans="1:92" ht="90" customHeight="1">
+      <c r="A1" s="112"/>
       <c r="B1" s="73" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="16"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="83"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="82"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
+      <c r="I1" s="123" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="116">
+      <c r="Q1" s="122">
         <v>46064</v>
       </c>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
+      <c r="R1" s="126"/>
+      <c r="S1" s="126"/>
+      <c r="T1" s="126"/>
+      <c r="U1" s="126"/>
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
     </row>
-    <row r="2" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:92" ht="30" customHeight="1">
       <c r="B2" s="71"/>
       <c r="C2" s="72" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="17"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="85"/>
-      <c r="I2" s="118" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="84"/>
+      <c r="I2" s="123" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="114">
+      <c r="Q2" s="121">
         <v>5</v>
       </c>
-      <c r="R2" s="115"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="115"/>
-      <c r="U2" s="115"/>
-      <c r="V2" s="115"/>
-      <c r="W2" s="115"/>
-      <c r="X2" s="115"/>
-      <c r="Y2" s="115"/>
-      <c r="Z2" s="115"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
       <c r="AP2" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="12"/>
       <c r="B3" s="19"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="21"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="87"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="111"/>
+      <c r="Y3" s="111"/>
+      <c r="Z3" s="111"/>
+      <c r="AA3" s="111"/>
+      <c r="AB3" s="111"/>
+      <c r="AC3" s="111"/>
+      <c r="AD3" s="111"/>
+      <c r="AE3" s="111"/>
+      <c r="AF3" s="111"/>
+      <c r="AG3" s="111"/>
+      <c r="AH3" s="111"/>
+      <c r="AI3" s="111"/>
+      <c r="AJ3" s="111"/>
+      <c r="AK3" s="111"/>
+      <c r="AL3" s="111"/>
+      <c r="AM3" s="111"/>
+      <c r="AN3" s="111"/>
+      <c r="AO3" s="111"/>
+      <c r="AP3" s="111"/>
+      <c r="AQ3" s="111"/>
+      <c r="AR3" s="111"/>
+      <c r="AS3" s="111"/>
+      <c r="AT3" s="111"/>
+      <c r="AU3" s="111"/>
+      <c r="AV3" s="111"/>
+      <c r="AW3" s="111"/>
+      <c r="AX3" s="111"/>
+      <c r="AY3" s="111"/>
+      <c r="AZ3" s="111"/>
+      <c r="BA3" s="111"/>
+      <c r="BB3" s="111"/>
+      <c r="BC3" s="111"/>
+      <c r="BD3" s="111"/>
+      <c r="BE3" s="111"/>
+      <c r="BF3" s="111"/>
+      <c r="BG3" s="111"/>
+      <c r="BH3" s="111"/>
+      <c r="BI3" s="111"/>
+      <c r="BJ3" s="111"/>
+      <c r="BK3" s="111"/>
+      <c r="BL3" s="111"/>
+      <c r="BM3" s="111"/>
+      <c r="BN3" s="111"/>
+      <c r="BO3" s="111"/>
+      <c r="BP3" s="111"/>
+      <c r="BQ3" s="111"/>
+      <c r="BR3" s="111"/>
+      <c r="BS3" s="111"/>
+      <c r="BT3" s="111"/>
+      <c r="BU3" s="111"/>
+      <c r="BV3" s="111"/>
+      <c r="BW3" s="111"/>
+      <c r="BX3" s="111"/>
+      <c r="BY3" s="111"/>
+      <c r="BZ3" s="111"/>
+      <c r="CA3" s="111"/>
+      <c r="CB3" s="111"/>
+      <c r="CC3" s="111"/>
+      <c r="CD3" s="111"/>
+      <c r="CE3" s="111"/>
+      <c r="CF3" s="111"/>
+      <c r="CG3" s="111"/>
+      <c r="CH3" s="111"/>
+      <c r="CI3" s="111"/>
+      <c r="CJ3" s="111"/>
+      <c r="CK3" s="111"/>
+      <c r="CL3" s="111"/>
+      <c r="CM3" s="111"/>
+      <c r="CN3" s="111"/>
     </row>
-    <row r="4" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="81"/>
-      <c r="B4" s="110" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="87"/>
-      <c r="I4" s="120">
+    <row r="4" spans="1:92" s="20" customFormat="1" ht="30" customHeight="1">
+      <c r="A4" s="112"/>
+      <c r="B4" s="109" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="124">
         <f>I5</f>
         <v>46090</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112">
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="119">
         <f>P5</f>
         <v>46097</v>
       </c>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112">
+      <c r="Q4" s="119"/>
+      <c r="R4" s="119"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="119"/>
+      <c r="W4" s="119">
         <f>W5</f>
         <v>46104</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="119"/>
+      <c r="Z4" s="119"/>
+      <c r="AA4" s="119"/>
+      <c r="AB4" s="119"/>
+      <c r="AC4" s="119"/>
+      <c r="AD4" s="119">
         <f>AD5</f>
         <v>46111</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119">
         <f>AK5</f>
         <v>46118</v>
       </c>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="112"/>
-      <c r="AQ4" s="112"/>
-      <c r="AR4" s="112">
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="119"/>
+      <c r="AQ4" s="119"/>
+      <c r="AR4" s="119">
         <f>AR5</f>
         <v>46125</v>
       </c>
-      <c r="AS4" s="112"/>
-      <c r="AT4" s="112"/>
-      <c r="AU4" s="112"/>
-      <c r="AV4" s="112"/>
-      <c r="AW4" s="112"/>
-      <c r="AX4" s="112"/>
-      <c r="AY4" s="112">
+      <c r="AS4" s="119"/>
+      <c r="AT4" s="119"/>
+      <c r="AU4" s="119"/>
+      <c r="AV4" s="119"/>
+      <c r="AW4" s="119"/>
+      <c r="AX4" s="119"/>
+      <c r="AY4" s="119">
         <f>AY5</f>
         <v>46132</v>
       </c>
-      <c r="AZ4" s="112"/>
-      <c r="BA4" s="112"/>
-      <c r="BB4" s="112"/>
-      <c r="BC4" s="112"/>
-      <c r="BD4" s="112"/>
-      <c r="BE4" s="112"/>
-      <c r="BF4" s="112">
+      <c r="AZ4" s="119"/>
+      <c r="BA4" s="119"/>
+      <c r="BB4" s="119"/>
+      <c r="BC4" s="119"/>
+      <c r="BD4" s="119"/>
+      <c r="BE4" s="119"/>
+      <c r="BF4" s="119">
         <f>BF5</f>
         <v>46139</v>
       </c>
-      <c r="BG4" s="112"/>
-      <c r="BH4" s="112"/>
-      <c r="BI4" s="112"/>
-      <c r="BJ4" s="112"/>
-      <c r="BK4" s="112"/>
-      <c r="BL4" s="113"/>
-      <c r="BM4" s="112">
+      <c r="BG4" s="119"/>
+      <c r="BH4" s="119"/>
+      <c r="BI4" s="119"/>
+      <c r="BJ4" s="119"/>
+      <c r="BK4" s="119"/>
+      <c r="BL4" s="120"/>
+      <c r="BM4" s="119">
         <f>BM5</f>
         <v>46146</v>
       </c>
-      <c r="BN4" s="112"/>
-      <c r="BO4" s="112"/>
-      <c r="BP4" s="112"/>
-      <c r="BQ4" s="112"/>
-      <c r="BR4" s="112"/>
-      <c r="BS4" s="113"/>
-      <c r="BT4" s="112">
+      <c r="BN4" s="119"/>
+      <c r="BO4" s="119"/>
+      <c r="BP4" s="119"/>
+      <c r="BQ4" s="119"/>
+      <c r="BR4" s="119"/>
+      <c r="BS4" s="120"/>
+      <c r="BT4" s="119">
         <f>BT5</f>
         <v>46153</v>
       </c>
-      <c r="BU4" s="112"/>
-      <c r="BV4" s="112"/>
-      <c r="BW4" s="112"/>
-      <c r="BX4" s="112"/>
-      <c r="BY4" s="112"/>
-      <c r="BZ4" s="113"/>
-      <c r="CA4" s="112">
+      <c r="BU4" s="119"/>
+      <c r="BV4" s="119"/>
+      <c r="BW4" s="119"/>
+      <c r="BX4" s="119"/>
+      <c r="BY4" s="119"/>
+      <c r="BZ4" s="120"/>
+      <c r="CA4" s="119">
         <f>CA5</f>
         <v>46160</v>
       </c>
-      <c r="CB4" s="112"/>
-      <c r="CC4" s="112"/>
-      <c r="CD4" s="112"/>
-      <c r="CE4" s="112"/>
-      <c r="CF4" s="112"/>
-      <c r="CG4" s="113"/>
-      <c r="CH4" s="112">
+      <c r="CB4" s="119"/>
+      <c r="CC4" s="119"/>
+      <c r="CD4" s="119"/>
+      <c r="CE4" s="119"/>
+      <c r="CF4" s="119"/>
+      <c r="CG4" s="120"/>
+      <c r="CH4" s="119">
         <f>CH5</f>
         <v>46167</v>
       </c>
-      <c r="CI4" s="112"/>
-      <c r="CJ4" s="112"/>
-      <c r="CK4" s="112"/>
-      <c r="CL4" s="112"/>
-      <c r="CM4" s="112"/>
-      <c r="CN4" s="113"/>
+      <c r="CI4" s="119"/>
+      <c r="CJ4" s="119"/>
+      <c r="CK4" s="119"/>
+      <c r="CL4" s="119"/>
+      <c r="CM4" s="119"/>
+      <c r="CN4" s="120"/>
     </row>
-    <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="123"/>
-      <c r="B5" s="124" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="126" t="s">
+    <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="114"/>
+      <c r="B5" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="128" t="s">
+      <c r="C5" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="121" t="s">
+      <c r="D5" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="121" t="s">
+      <c r="E5" s="113" t="s">
         <v>9</v>
       </c>
+      <c r="F5" s="113" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
       <c r="I5" s="22">
         <f>Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
         <v>46090</v>
@@ -2947,13 +3041,15 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="123"/>
-      <c r="B6" s="125"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
+    <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A6" s="114"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
       <c r="I6" s="25" t="str">
         <f t="shared" ref="I6:AN6" si="23">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -3291,17 +3387,18 @@
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:92" s="20" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:92" s="20" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1">
       <c r="A7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="28"/>
       <c r="C7" s="29"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="H7" s="20" t="str">
-        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111" t="str">
+        <f ca="1">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I7" s="30"/>
@@ -3389,18 +3486,18 @@
       <c r="CM7" s="30"/>
       <c r="CN7" s="30"/>
     </row>
-    <row r="8" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="81"/>
+    <row r="8" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A8" s="112"/>
       <c r="B8" s="31" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C8" s="32"/>
       <c r="D8" s="33"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="91"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="90"/>
       <c r="G8" s="14"/>
       <c r="H8" s="4" t="str">
-        <f t="shared" ref="H8:H19" si="29">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H8:H19" ca="1" si="29">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I8" s="34"/>
@@ -3488,26 +3585,26 @@
       <c r="CM8" s="34"/>
       <c r="CN8" s="34"/>
     </row>
-    <row r="9" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="81"/>
+    <row r="9" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A9" s="112"/>
       <c r="B9" s="36" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="38">
         <v>0</v>
       </c>
-      <c r="E9" s="92">
+      <c r="E9" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F9" s="92">
+      <c r="F9" s="91">
         <f>E9+58</f>
         <v>46122</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I9" s="39"/>
@@ -3595,26 +3692,26 @@
       <c r="CM9" s="39"/>
       <c r="CN9" s="39"/>
     </row>
-    <row r="10" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="81"/>
+    <row r="10" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A10" s="112"/>
       <c r="B10" s="40" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="42">
         <v>0.8</v>
       </c>
-      <c r="E10" s="92">
+      <c r="E10" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F10" s="92">
+      <c r="F10" s="91">
         <f>E10+58</f>
         <v>46122</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I10" s="39"/>
@@ -3702,26 +3799,26 @@
       <c r="CM10" s="39"/>
       <c r="CN10" s="39"/>
     </row>
-    <row r="11" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A11" s="12"/>
       <c r="B11" s="40" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="42">
         <v>0</v>
       </c>
-      <c r="E11" s="92">
+      <c r="E11" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F11" s="92">
+      <c r="F11" s="91">
         <f>E11+58</f>
         <v>46122</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I11" s="39"/>
@@ -3809,26 +3906,26 @@
       <c r="CM11" s="39"/>
       <c r="CN11" s="39"/>
     </row>
-    <row r="12" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A12" s="12"/>
       <c r="B12" s="40" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C12" s="41"/>
       <c r="D12" s="42">
         <v>0</v>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="91">
         <f>E12+58</f>
         <v>46122</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I12" s="39"/>
@@ -3916,26 +4013,26 @@
       <c r="CM12" s="39"/>
       <c r="CN12" s="39"/>
     </row>
-    <row r="13" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A13" s="12"/>
       <c r="B13" s="40" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="42">
         <v>0</v>
       </c>
-      <c r="E13" s="92">
+      <c r="E13" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F13" s="92">
+      <c r="F13" s="91">
         <f>E13+58</f>
         <v>46122</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I13" s="39"/>
@@ -4023,20 +4120,20 @@
       <c r="CM13" s="39"/>
       <c r="CN13" s="39"/>
     </row>
-    <row r="14" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A14" s="12"/>
       <c r="B14" s="40" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C14" s="41"/>
       <c r="D14" s="42">
         <v>0.9</v>
       </c>
-      <c r="E14" s="92">
+      <c r="E14" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="91">
         <f>E14+58</f>
         <v>46122</v>
       </c>
@@ -4127,26 +4224,26 @@
       <c r="CM14" s="39"/>
       <c r="CN14" s="39"/>
     </row>
-    <row r="15" spans="1:92" s="35" customFormat="1" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:92" s="35" customFormat="1" ht="53.1" customHeight="1" thickBot="1">
       <c r="A15" s="12"/>
       <c r="B15" s="40" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="42">
         <v>0</v>
       </c>
-      <c r="E15" s="92">
+      <c r="E15" s="91">
         <f>F13+1</f>
         <v>46123</v>
       </c>
-      <c r="F15" s="92">
+      <c r="F15" s="91">
         <f>E15+14</f>
         <v>46137</v>
       </c>
-      <c r="G15" s="111"/>
+      <c r="G15" s="110"/>
       <c r="H15" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>15</v>
       </c>
       <c r="I15" s="39"/>
@@ -4234,18 +4331,18 @@
       <c r="CM15" s="39"/>
       <c r="CN15" s="39"/>
     </row>
-    <row r="16" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="81"/>
+    <row r="16" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A16" s="112"/>
       <c r="B16" s="31" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C16" s="32"/>
       <c r="D16" s="33"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="91"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="90"/>
       <c r="G16" s="14"/>
       <c r="H16" s="4" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v/>
       </c>
       <c r="I16" s="34"/>
@@ -4333,26 +4430,26 @@
       <c r="CM16" s="34"/>
       <c r="CN16" s="34"/>
     </row>
-    <row r="17" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="81"/>
+    <row r="17" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A17" s="112"/>
       <c r="B17" s="36" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C17" s="37"/>
       <c r="D17" s="38">
         <v>1</v>
       </c>
-      <c r="E17" s="92">
+      <c r="E17" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F17" s="92">
+      <c r="F17" s="91">
         <f>E17+58</f>
         <v>46122</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I17" s="39"/>
@@ -4440,26 +4537,26 @@
       <c r="CM17" s="39"/>
       <c r="CN17" s="39"/>
     </row>
-    <row r="18" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="81"/>
+    <row r="18" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A18" s="112"/>
       <c r="B18" s="40" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="42">
         <v>0</v>
       </c>
-      <c r="E18" s="92">
+      <c r="E18" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F18" s="92">
+      <c r="F18" s="91">
         <f>E18+58</f>
         <v>46122</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I18" s="39"/>
@@ -4547,26 +4644,26 @@
       <c r="CM18" s="39"/>
       <c r="CN18" s="39"/>
     </row>
-    <row r="19" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A19" s="12"/>
       <c r="B19" s="40" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="42">
         <v>0</v>
       </c>
-      <c r="E19" s="92">
+      <c r="E19" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F19" s="93">
+      <c r="F19" s="92">
         <f>F18</f>
         <v>46122</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" ca="1" si="29"/>
         <v>59</v>
       </c>
       <c r="I19" s="39"/>
@@ -4654,18 +4751,18 @@
       <c r="CM19" s="39"/>
       <c r="CN19" s="39"/>
     </row>
-    <row r="20" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="81"/>
+    <row r="20" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A20" s="112"/>
       <c r="B20" s="31" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="33"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="91"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="90"/>
       <c r="G20" s="14"/>
       <c r="H20" s="4" t="str">
-        <f t="shared" ref="H20:H52" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H20:H52" ca="1" si="30">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I20" s="34"/>
@@ -4753,26 +4850,26 @@
       <c r="CM20" s="34"/>
       <c r="CN20" s="34"/>
     </row>
-    <row r="21" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="81"/>
+    <row r="21" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A21" s="112"/>
       <c r="B21" s="36" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38">
         <v>0.33</v>
       </c>
-      <c r="E21" s="92">
+      <c r="E21" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F21" s="92">
+      <c r="F21" s="91">
         <f>E21+58</f>
         <v>46122</v>
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>59</v>
       </c>
       <c r="I21" s="39"/>
@@ -4860,18 +4957,18 @@
       <c r="CM21" s="39"/>
       <c r="CN21" s="39"/>
     </row>
-    <row r="22" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="81"/>
+    <row r="22" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A22" s="112"/>
       <c r="B22" s="36" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="38"/>
-      <c r="E22" s="92">
+      <c r="E22" s="91">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F22" s="92">
+      <c r="F22" s="91">
         <f>E22+58</f>
         <v>46122</v>
       </c>
@@ -4962,26 +5059,26 @@
       <c r="CM22" s="39"/>
       <c r="CN22" s="39"/>
     </row>
-    <row r="23" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="81"/>
+    <row r="23" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A23" s="112"/>
       <c r="B23" s="40" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C23" s="41"/>
       <c r="D23" s="42">
         <v>0.33</v>
       </c>
-      <c r="E23" s="92">
+      <c r="E23" s="91">
         <f>F22+1</f>
         <v>46123</v>
       </c>
-      <c r="F23" s="93">
+      <c r="F23" s="92">
         <f>E23+7</f>
         <v>46130</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I23" s="39"/>
@@ -5069,41 +5166,41 @@
       <c r="CM23" s="39"/>
       <c r="CN23" s="39"/>
     </row>
-    <row r="24" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="81"/>
+    <row r="24" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A24" s="112"/>
       <c r="B24" s="44" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C24" s="45"/>
       <c r="D24" s="46"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="95"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94"/>
       <c r="G24" s="14"/>
       <c r="H24" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="81"/>
+    <row r="25" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A25" s="112"/>
       <c r="B25" s="47" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="49">
         <v>1</v>
       </c>
-      <c r="E25" s="96">
+      <c r="E25" s="95">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F25" s="96">
+      <c r="F25" s="95">
         <f>E25+20</f>
         <v>46084</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>21</v>
       </c>
       <c r="I25" s="39"/>
@@ -5191,26 +5288,26 @@
       <c r="CM25" s="39"/>
       <c r="CN25" s="39"/>
     </row>
-    <row r="26" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A26" s="12"/>
       <c r="B26" s="47" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C26" s="48"/>
       <c r="D26" s="49">
         <v>0.8</v>
       </c>
-      <c r="E26" s="96">
+      <c r="E26" s="95">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F26" s="96">
+      <c r="F26" s="95">
         <f>E26+9</f>
         <v>46073</v>
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>10</v>
       </c>
       <c r="I26" s="39"/>
@@ -5298,25 +5395,25 @@
       <c r="CM26" s="39"/>
       <c r="CN26" s="39"/>
     </row>
-    <row r="27" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A27" s="12"/>
       <c r="B27" s="47" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C27" s="48"/>
       <c r="D27" s="49">
         <v>1</v>
       </c>
-      <c r="E27" s="96">
+      <c r="E27" s="95">
         <v>46083</v>
       </c>
-      <c r="F27" s="96">
+      <c r="F27" s="95">
         <f>E27+10</f>
         <v>46093</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>11</v>
       </c>
       <c r="I27" s="39"/>
@@ -5404,26 +5501,26 @@
       <c r="CM27" s="39"/>
       <c r="CN27" s="39"/>
     </row>
-    <row r="28" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A28" s="12"/>
       <c r="B28" s="47" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C28" s="48"/>
       <c r="D28" s="49">
         <v>1</v>
       </c>
-      <c r="E28" s="96">
+      <c r="E28" s="95">
         <f>F27+1</f>
         <v>46094</v>
       </c>
-      <c r="F28" s="96">
+      <c r="F28" s="95">
         <f>E28+7</f>
         <v>46101</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I28" s="39"/>
@@ -5511,26 +5608,26 @@
       <c r="CM28" s="39"/>
       <c r="CN28" s="39"/>
     </row>
-    <row r="29" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A29" s="12"/>
       <c r="B29" s="47" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C29" s="48"/>
       <c r="D29" s="49">
         <v>1</v>
       </c>
-      <c r="E29" s="96">
+      <c r="E29" s="95">
         <f>E28</f>
         <v>46094</v>
       </c>
-      <c r="F29" s="96">
+      <c r="F29" s="95">
         <f>E29+7</f>
         <v>46101</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I29" s="39"/>
@@ -5618,20 +5715,20 @@
       <c r="CM29" s="39"/>
       <c r="CN29" s="39"/>
     </row>
-    <row r="30" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A30" s="12"/>
       <c r="B30" s="47" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="C30" s="48"/>
       <c r="D30" s="49">
         <v>1</v>
       </c>
-      <c r="E30" s="96">
+      <c r="E30" s="95">
         <f>F28+1</f>
         <v>46102</v>
       </c>
-      <c r="F30" s="96">
+      <c r="F30" s="95">
         <f>E30+7</f>
         <v>46109</v>
       </c>
@@ -5722,26 +5819,26 @@
       <c r="CM30" s="39"/>
       <c r="CN30" s="39"/>
     </row>
-    <row r="31" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A31" s="12"/>
       <c r="B31" s="47" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C31" s="48"/>
       <c r="D31" s="49">
         <v>1</v>
       </c>
-      <c r="E31" s="96">
+      <c r="E31" s="95">
         <f>F29+1</f>
         <v>46102</v>
       </c>
-      <c r="F31" s="96">
+      <c r="F31" s="95">
         <f>E31+7</f>
         <v>46109</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I31" s="39"/>
@@ -5829,26 +5926,26 @@
       <c r="CM31" s="39"/>
       <c r="CN31" s="39"/>
     </row>
-    <row r="32" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A32" s="12"/>
       <c r="B32" s="47" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C32" s="48"/>
       <c r="D32" s="49">
         <v>0.15</v>
       </c>
-      <c r="E32" s="96">
+      <c r="E32" s="95">
         <f>F31+1</f>
         <v>46110</v>
       </c>
-      <c r="F32" s="96">
+      <c r="F32" s="95">
         <f>E32+3</f>
         <v>46113</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>4</v>
       </c>
       <c r="I32" s="39"/>
@@ -5936,26 +6033,26 @@
       <c r="CM32" s="39"/>
       <c r="CN32" s="39"/>
     </row>
-    <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A33" s="12"/>
       <c r="B33" s="47" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C33" s="48"/>
       <c r="D33" s="49">
         <v>0</v>
       </c>
-      <c r="E33" s="96">
+      <c r="E33" s="95">
         <f>F32+1</f>
         <v>46114</v>
       </c>
-      <c r="F33" s="96">
+      <c r="F33" s="95">
         <f>E33+8</f>
         <v>46122</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>9</v>
       </c>
       <c r="I33" s="39"/>
@@ -6043,26 +6140,26 @@
       <c r="CM33" s="39"/>
       <c r="CN33" s="39"/>
     </row>
-    <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A34" s="12"/>
       <c r="B34" s="47" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C34" s="48"/>
       <c r="D34" s="49">
         <v>0</v>
       </c>
-      <c r="E34" s="96">
+      <c r="E34" s="95">
         <f>F32+1</f>
         <v>46114</v>
       </c>
-      <c r="F34" s="96">
+      <c r="F34" s="95">
         <f>E34+7</f>
         <v>46121</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I34" s="39"/>
@@ -6150,26 +6247,26 @@
       <c r="CM34" s="39"/>
       <c r="CN34" s="39"/>
     </row>
-    <row r="35" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="12"/>
       <c r="B35" s="47" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C35" s="48"/>
       <c r="D35" s="49">
         <v>0</v>
       </c>
-      <c r="E35" s="96">
+      <c r="E35" s="95">
         <f>F33+1</f>
         <v>46123</v>
       </c>
-      <c r="F35" s="96">
+      <c r="F35" s="95">
         <f>E35+7</f>
         <v>46130</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I35" s="39"/>
@@ -6257,18 +6354,18 @@
       <c r="CM35" s="39"/>
       <c r="CN35" s="39"/>
     </row>
-    <row r="36" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A36" s="12"/>
       <c r="B36" s="50" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="52"/>
-      <c r="E36" s="97"/>
-      <c r="F36" s="98"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="97"/>
       <c r="G36" s="14"/>
       <c r="H36" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="I36" s="53"/>
@@ -6356,26 +6453,26 @@
       <c r="CM36" s="53"/>
       <c r="CN36" s="53"/>
     </row>
-    <row r="37" spans="1:92" s="35" customFormat="1" ht="68" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:92" s="35" customFormat="1" ht="68.099999999999994" customHeight="1" thickBot="1">
       <c r="A37" s="12"/>
-      <c r="B37" s="109" t="s">
-        <v>43</v>
+      <c r="B37" s="108" t="s">
+        <v>36</v>
       </c>
       <c r="C37" s="55"/>
       <c r="D37" s="56">
         <v>0.2</v>
       </c>
-      <c r="E37" s="99">
+      <c r="E37" s="98">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F37" s="99">
+      <c r="F37" s="98">
         <f>E37+14</f>
         <v>46078</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>15</v>
       </c>
       <c r="I37" s="39"/>
@@ -6463,26 +6560,26 @@
       <c r="CM37" s="39"/>
       <c r="CN37" s="39"/>
     </row>
-    <row r="38" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A38" s="12"/>
       <c r="B38" s="54" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C38" s="55"/>
       <c r="D38" s="56">
         <v>0.2</v>
       </c>
-      <c r="E38" s="99">
+      <c r="E38" s="98">
         <f>F37+1</f>
         <v>46079</v>
       </c>
-      <c r="F38" s="99">
+      <c r="F38" s="98">
         <f>F35</f>
         <v>46130</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>52</v>
       </c>
       <c r="I38" s="39"/>
@@ -6570,18 +6667,18 @@
       <c r="CM38" s="39"/>
       <c r="CN38" s="39"/>
     </row>
-    <row r="39" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A39" s="12"/>
       <c r="B39" s="50" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C39" s="51"/>
       <c r="D39" s="52"/>
-      <c r="E39" s="97"/>
-      <c r="F39" s="98"/>
+      <c r="E39" s="96"/>
+      <c r="F39" s="97"/>
       <c r="G39" s="14"/>
       <c r="H39" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="I39" s="53"/>
@@ -6669,28 +6766,28 @@
       <c r="CM39" s="53"/>
       <c r="CN39" s="53"/>
     </row>
-    <row r="40" spans="1:92" s="35" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:92" s="35" customFormat="1" ht="42.95" thickBot="1">
       <c r="A40" s="12"/>
-      <c r="B40" s="109" t="s">
-        <v>45</v>
+      <c r="B40" s="108" t="s">
+        <v>39</v>
       </c>
       <c r="C40" s="55"/>
       <c r="D40" s="56">
         <v>0.9</v>
       </c>
-      <c r="E40" s="99">
+      <c r="E40" s="98">
         <f>Project_Start</f>
         <v>46064</v>
       </c>
-      <c r="F40" s="99">
+      <c r="F40" s="98">
         <f>E40+21</f>
         <v>46085</v>
       </c>
-      <c r="G40" s="111" t="s">
-        <v>64</v>
+      <c r="G40" s="110" t="s">
+        <v>40</v>
       </c>
       <c r="H40" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>22</v>
       </c>
       <c r="I40" s="39"/>
@@ -6778,26 +6875,26 @@
       <c r="CM40" s="39"/>
       <c r="CN40" s="39"/>
     </row>
-    <row r="41" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:92" s="35" customFormat="1" ht="24" customHeight="1" thickBot="1">
       <c r="A41" s="12"/>
-      <c r="B41" s="109" t="s">
-        <v>55</v>
+      <c r="B41" s="108" t="s">
+        <v>41</v>
       </c>
       <c r="C41" s="55"/>
       <c r="D41" s="56">
         <v>0.3</v>
       </c>
-      <c r="E41" s="99">
+      <c r="E41" s="98">
         <f>F40</f>
         <v>46085</v>
       </c>
-      <c r="F41" s="99">
+      <c r="F41" s="98">
         <f>F35</f>
         <v>46130</v>
       </c>
       <c r="G41" s="14"/>
       <c r="H41" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>46</v>
       </c>
       <c r="I41" s="39"/>
@@ -6885,20 +6982,20 @@
       <c r="CM41" s="39"/>
       <c r="CN41" s="39"/>
     </row>
-    <row r="42" spans="1:92" s="35" customFormat="1" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:92" s="35" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
       <c r="A42" s="12"/>
       <c r="B42" s="54" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C42" s="55"/>
       <c r="D42" s="56">
         <v>1</v>
       </c>
-      <c r="E42" s="99">
+      <c r="E42" s="98">
         <f>F40</f>
         <v>46085</v>
       </c>
-      <c r="F42" s="99">
+      <c r="F42" s="98">
         <f>F35</f>
         <v>46130</v>
       </c>
@@ -6989,20 +7086,20 @@
       <c r="CM42" s="39"/>
       <c r="CN42" s="39"/>
     </row>
-    <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A43" s="12"/>
       <c r="B43" s="54" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C43" s="55"/>
       <c r="D43" s="56">
         <v>0</v>
       </c>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
+      <c r="E43" s="98"/>
+      <c r="F43" s="98"/>
       <c r="G43" s="14"/>
       <c r="H43" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="I43" s="39"/>
@@ -7090,18 +7187,18 @@
       <c r="CM43" s="39"/>
       <c r="CN43" s="39"/>
     </row>
-    <row r="44" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A44" s="12"/>
       <c r="B44" s="57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C44" s="58"/>
       <c r="D44" s="59"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="101"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="100"/>
       <c r="G44" s="14"/>
       <c r="H44" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="I44" s="60"/>
@@ -7189,26 +7286,26 @@
       <c r="CM44" s="60"/>
       <c r="CN44" s="60"/>
     </row>
-    <row r="45" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A45" s="12"/>
       <c r="B45" s="61" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C45" s="62"/>
       <c r="D45" s="63">
         <v>1</v>
       </c>
-      <c r="E45" s="102">
+      <c r="E45" s="101">
         <f>E37</f>
         <v>46064</v>
       </c>
-      <c r="F45" s="102">
+      <c r="F45" s="101">
         <f>E49-3</f>
         <v>46157</v>
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>94</v>
       </c>
       <c r="I45" s="39"/>
@@ -7296,25 +7393,25 @@
       <c r="CM45" s="39"/>
       <c r="CN45" s="39"/>
     </row>
-    <row r="46" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A46" s="12"/>
       <c r="B46" s="61" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="63">
         <v>0.9</v>
       </c>
-      <c r="E46" s="102">
+      <c r="E46" s="101">
         <v>46146</v>
       </c>
-      <c r="F46" s="102">
+      <c r="F46" s="101">
         <f>E46+7</f>
         <v>46153</v>
       </c>
       <c r="G46" s="14"/>
       <c r="H46" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I46" s="39"/>
@@ -7402,7 +7499,7 @@
       <c r="CM46" s="39"/>
       <c r="CN46" s="39"/>
     </row>
-    <row r="47" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A47" s="12"/>
       <c r="B47" s="61" t="s">
         <v>47</v>
@@ -7411,16 +7508,16 @@
       <c r="D47" s="63">
         <v>0</v>
       </c>
-      <c r="E47" s="102">
+      <c r="E47" s="101">
         <v>46146</v>
       </c>
-      <c r="F47" s="102">
+      <c r="F47" s="101">
         <f>E47+7</f>
         <v>46153</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I47" s="39"/>
@@ -7508,7 +7605,7 @@
       <c r="CM47" s="39"/>
       <c r="CN47" s="39"/>
     </row>
-    <row r="48" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A48" s="12"/>
       <c r="B48" s="61" t="s">
         <v>48</v>
@@ -7517,17 +7614,17 @@
       <c r="D48" s="63">
         <v>0</v>
       </c>
-      <c r="E48" s="102">
+      <c r="E48" s="101">
         <f>F47</f>
         <v>46153</v>
       </c>
-      <c r="F48" s="102">
+      <c r="F48" s="101">
         <f>E48+7</f>
         <v>46160</v>
       </c>
       <c r="G48" s="14"/>
       <c r="H48" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I48" s="39"/>
@@ -7615,7 +7712,7 @@
       <c r="CM48" s="39"/>
       <c r="CN48" s="39"/>
     </row>
-    <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A49" s="12"/>
       <c r="B49" s="61" t="s">
         <v>49</v>
@@ -7624,17 +7721,17 @@
       <c r="D49" s="63">
         <v>0</v>
       </c>
-      <c r="E49" s="102">
+      <c r="E49" s="101">
         <f>F48</f>
         <v>46160</v>
       </c>
-      <c r="F49" s="102">
+      <c r="F49" s="101">
         <f>E49+7</f>
         <v>46167</v>
       </c>
       <c r="G49" s="14"/>
       <c r="H49" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>8</v>
       </c>
       <c r="I49" s="39"/>
@@ -7722,7 +7819,7 @@
       <c r="CM49" s="39"/>
       <c r="CN49" s="39"/>
     </row>
-    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A50" s="12"/>
       <c r="B50" s="61" t="s">
         <v>50</v>
@@ -7731,17 +7828,17 @@
       <c r="D50" s="63">
         <v>0</v>
       </c>
-      <c r="E50" s="102">
+      <c r="E50" s="101">
         <f>F49</f>
         <v>46167</v>
       </c>
-      <c r="F50" s="102">
+      <c r="F50" s="101">
         <f>E50+14</f>
         <v>46181</v>
       </c>
       <c r="G50" s="14"/>
       <c r="H50" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v>15</v>
       </c>
       <c r="I50" s="39"/>
@@ -7829,18 +7926,18 @@
       <c r="CM50" s="39"/>
       <c r="CN50" s="39"/>
     </row>
-    <row r="51" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A51" s="12"/>
       <c r="B51" s="64" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C51" s="65"/>
       <c r="D51" s="66"/>
-      <c r="E51" s="103"/>
-      <c r="F51" s="103"/>
+      <c r="E51" s="102"/>
+      <c r="F51" s="102"/>
       <c r="G51" s="14"/>
       <c r="H51" s="4" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="I51" s="34"/>
@@ -7928,18 +8025,18 @@
       <c r="CM51" s="34"/>
       <c r="CN51" s="34"/>
     </row>
-    <row r="52" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="81"/>
+    <row r="52" spans="1:92" s="35" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A52" s="112"/>
       <c r="B52" s="67" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C52" s="68"/>
       <c r="D52" s="69"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="105"/>
+      <c r="E52" s="103"/>
+      <c r="F52" s="104"/>
       <c r="G52" s="14"/>
       <c r="H52" s="5" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ca="1" si="30"/>
         <v/>
       </c>
       <c r="I52" s="70"/>
@@ -8027,24 +8124,18 @@
       <c r="CM52" s="70"/>
       <c r="CN52" s="70"/>
     </row>
-    <row r="53" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:92" ht="30" customHeight="1">
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:92" ht="30" customHeight="1">
       <c r="C54" s="13"/>
-      <c r="F54" s="108"/>
+      <c r="F54" s="107"/>
     </row>
-    <row r="55" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:92" ht="30" customHeight="1">
       <c r="C55" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -8061,6 +8152,12 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D52">
     <cfRule type="dataBar" priority="102">
@@ -8372,110 +8469,110 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.95"/>
   <cols>
     <col min="1" max="1" width="87" style="6" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="1:2" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1"/>
+    <row r="2" spans="1:2" s="8" customFormat="1" ht="15.95">
       <c r="A2" s="74" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B2" s="7"/>
     </row>
-    <row r="3" spans="1:2" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" s="10" customFormat="1" ht="27" customHeight="1">
       <c r="A3" s="75"/>
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A4" s="76" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="74.25" customHeight="1">
       <c r="A5" s="77" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="26.25" customHeight="1">
       <c r="A6" s="76" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="6" customFormat="1" ht="205.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" s="6" customFormat="1" ht="205.35" customHeight="1">
       <c r="A7" s="78" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A8" s="76" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="60">
       <c r="A9" s="77" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="6" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" s="6" customFormat="1" ht="28.35" customHeight="1">
       <c r="A10" s="79" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A11" s="76" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="30">
       <c r="A12" s="77" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="6" customFormat="1" ht="28.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" s="6" customFormat="1" ht="28.35" customHeight="1">
       <c r="A13" s="79" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" s="9" customFormat="1" ht="30.95">
       <c r="A14" s="76" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="75" customHeight="1">
       <c r="A15" s="77" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:2" ht="75">
       <c r="A16" s="77" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="80"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="80"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="80"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="80"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="80"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="80"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="80"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="80"/>
     </row>
   </sheetData>
@@ -8491,6 +8588,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8802,74 +8928,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/resources/TierPlus Planning.xlsx
+++ b/resources/TierPlus Planning.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -1155,9 +1155,31 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="169" fontId="20" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1170,32 +1192,10 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -2402,28 +2402,28 @@
       <c r="E1" s="81"/>
       <c r="F1" s="82"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="123" t="s">
+      <c r="I1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
       <c r="P1" s="18"/>
-      <c r="Q1" s="122">
+      <c r="Q1" s="117">
         <v>46064</v>
       </c>
-      <c r="R1" s="126"/>
-      <c r="S1" s="126"/>
-      <c r="T1" s="126"/>
-      <c r="U1" s="126"/>
-      <c r="V1" s="126"/>
-      <c r="W1" s="126"/>
-      <c r="X1" s="126"/>
-      <c r="Y1" s="126"/>
-      <c r="Z1" s="126"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="118"/>
+      <c r="Y1" s="118"/>
+      <c r="Z1" s="118"/>
     </row>
     <row r="2" spans="1:92" ht="30" customHeight="1">
       <c r="B2" s="71"/>
@@ -2433,28 +2433,28 @@
       <c r="D2" s="17"/>
       <c r="E2" s="83"/>
       <c r="F2" s="84"/>
-      <c r="I2" s="123" t="s">
+      <c r="I2" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="125"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
       <c r="P2" s="18"/>
-      <c r="Q2" s="121">
+      <c r="Q2" s="115">
         <v>5</v>
       </c>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="127"/>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
       <c r="AP2" t="s">
         <v>4</v>
       </c>
@@ -2564,142 +2564,142 @@
       <c r="F4" s="86"/>
       <c r="G4" s="111"/>
       <c r="H4" s="111"/>
-      <c r="I4" s="124">
+      <c r="I4" s="121">
         <f>I5</f>
         <v>46090</v>
       </c>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="119">
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
+      <c r="P4" s="113">
         <f>P5</f>
         <v>46097</v>
       </c>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119">
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113"/>
+      <c r="V4" s="113"/>
+      <c r="W4" s="113">
         <f>W5</f>
         <v>46104</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="119"/>
-      <c r="Z4" s="119"/>
-      <c r="AA4" s="119"/>
-      <c r="AB4" s="119"/>
-      <c r="AC4" s="119"/>
-      <c r="AD4" s="119">
+      <c r="X4" s="113"/>
+      <c r="Y4" s="113"/>
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="113">
         <f>AD5</f>
         <v>46111</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119">
+      <c r="AE4" s="113"/>
+      <c r="AF4" s="113"/>
+      <c r="AG4" s="113"/>
+      <c r="AH4" s="113"/>
+      <c r="AI4" s="113"/>
+      <c r="AJ4" s="113"/>
+      <c r="AK4" s="113">
         <f>AK5</f>
         <v>46118</v>
       </c>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="119"/>
-      <c r="AQ4" s="119"/>
-      <c r="AR4" s="119">
+      <c r="AL4" s="113"/>
+      <c r="AM4" s="113"/>
+      <c r="AN4" s="113"/>
+      <c r="AO4" s="113"/>
+      <c r="AP4" s="113"/>
+      <c r="AQ4" s="113"/>
+      <c r="AR4" s="113">
         <f>AR5</f>
         <v>46125</v>
       </c>
-      <c r="AS4" s="119"/>
-      <c r="AT4" s="119"/>
-      <c r="AU4" s="119"/>
-      <c r="AV4" s="119"/>
-      <c r="AW4" s="119"/>
-      <c r="AX4" s="119"/>
-      <c r="AY4" s="119">
+      <c r="AS4" s="113"/>
+      <c r="AT4" s="113"/>
+      <c r="AU4" s="113"/>
+      <c r="AV4" s="113"/>
+      <c r="AW4" s="113"/>
+      <c r="AX4" s="113"/>
+      <c r="AY4" s="113">
         <f>AY5</f>
         <v>46132</v>
       </c>
-      <c r="AZ4" s="119"/>
-      <c r="BA4" s="119"/>
-      <c r="BB4" s="119"/>
-      <c r="BC4" s="119"/>
-      <c r="BD4" s="119"/>
-      <c r="BE4" s="119"/>
-      <c r="BF4" s="119">
+      <c r="AZ4" s="113"/>
+      <c r="BA4" s="113"/>
+      <c r="BB4" s="113"/>
+      <c r="BC4" s="113"/>
+      <c r="BD4" s="113"/>
+      <c r="BE4" s="113"/>
+      <c r="BF4" s="113">
         <f>BF5</f>
         <v>46139</v>
       </c>
-      <c r="BG4" s="119"/>
-      <c r="BH4" s="119"/>
-      <c r="BI4" s="119"/>
-      <c r="BJ4" s="119"/>
-      <c r="BK4" s="119"/>
-      <c r="BL4" s="120"/>
-      <c r="BM4" s="119">
+      <c r="BG4" s="113"/>
+      <c r="BH4" s="113"/>
+      <c r="BI4" s="113"/>
+      <c r="BJ4" s="113"/>
+      <c r="BK4" s="113"/>
+      <c r="BL4" s="114"/>
+      <c r="BM4" s="113">
         <f>BM5</f>
         <v>46146</v>
       </c>
-      <c r="BN4" s="119"/>
-      <c r="BO4" s="119"/>
-      <c r="BP4" s="119"/>
-      <c r="BQ4" s="119"/>
-      <c r="BR4" s="119"/>
-      <c r="BS4" s="120"/>
-      <c r="BT4" s="119">
+      <c r="BN4" s="113"/>
+      <c r="BO4" s="113"/>
+      <c r="BP4" s="113"/>
+      <c r="BQ4" s="113"/>
+      <c r="BR4" s="113"/>
+      <c r="BS4" s="114"/>
+      <c r="BT4" s="113">
         <f>BT5</f>
         <v>46153</v>
       </c>
-      <c r="BU4" s="119"/>
-      <c r="BV4" s="119"/>
-      <c r="BW4" s="119"/>
-      <c r="BX4" s="119"/>
-      <c r="BY4" s="119"/>
-      <c r="BZ4" s="120"/>
-      <c r="CA4" s="119">
+      <c r="BU4" s="113"/>
+      <c r="BV4" s="113"/>
+      <c r="BW4" s="113"/>
+      <c r="BX4" s="113"/>
+      <c r="BY4" s="113"/>
+      <c r="BZ4" s="114"/>
+      <c r="CA4" s="113">
         <f>CA5</f>
         <v>46160</v>
       </c>
-      <c r="CB4" s="119"/>
-      <c r="CC4" s="119"/>
-      <c r="CD4" s="119"/>
-      <c r="CE4" s="119"/>
-      <c r="CF4" s="119"/>
-      <c r="CG4" s="120"/>
-      <c r="CH4" s="119">
+      <c r="CB4" s="113"/>
+      <c r="CC4" s="113"/>
+      <c r="CD4" s="113"/>
+      <c r="CE4" s="113"/>
+      <c r="CF4" s="113"/>
+      <c r="CG4" s="114"/>
+      <c r="CH4" s="113">
         <f>CH5</f>
         <v>46167</v>
       </c>
-      <c r="CI4" s="119"/>
-      <c r="CJ4" s="119"/>
-      <c r="CK4" s="119"/>
-      <c r="CL4" s="119"/>
-      <c r="CM4" s="119"/>
-      <c r="CN4" s="120"/>
+      <c r="CI4" s="113"/>
+      <c r="CJ4" s="113"/>
+      <c r="CK4" s="113"/>
+      <c r="CL4" s="113"/>
+      <c r="CM4" s="113"/>
+      <c r="CN4" s="114"/>
     </row>
     <row r="5" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="114"/>
-      <c r="B5" s="115" t="s">
+      <c r="A5" s="124"/>
+      <c r="B5" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="113" t="s">
+      <c r="E5" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="113" t="s">
+      <c r="F5" s="122" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="111"/>
@@ -3042,12 +3042,12 @@
       </c>
     </row>
     <row r="6" spans="1:92" s="20" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="114"/>
-      <c r="B6" s="116"/>
+      <c r="A6" s="124"/>
+      <c r="B6" s="126"/>
       <c r="C6" s="128"/>
       <c r="D6" s="128"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123"/>
       <c r="G6" s="111"/>
       <c r="H6" s="111"/>
       <c r="I6" s="25" t="str">
@@ -8136,6 +8136,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="CH4:CN4"/>
     <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
@@ -8152,12 +8158,6 @@
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D52">
     <cfRule type="dataBar" priority="102">
@@ -8588,35 +8588,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8928,8 +8899,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8937,7 +8937,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
